--- a/precios.xlsx
+++ b/precios.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Portal-Operativo-INTEGRA\RAMA PRUEBA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2607,7 +2607,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="171">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -2758,9 +2758,6 @@
     <t>SELLADOR</t>
   </si>
   <si>
-    <t>SALON PARA ISTITUCIONES</t>
-  </si>
-  <si>
     <t>VALOR UNICO x Día</t>
   </si>
   <si>
@@ -3147,6 +3144,15 @@
   </si>
   <si>
     <t>PIERNA ENTERA</t>
+  </si>
+  <si>
+    <t>In 90 (osecac)</t>
+  </si>
+  <si>
+    <t>SALON PARA INSTITUCIONES</t>
+  </si>
+  <si>
+    <t>In 90 (OSECAC)</t>
   </si>
 </sst>
 </file>
@@ -4185,7 +4191,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="8" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.140625" hidden="1" customWidth="1"/>
@@ -4207,36 +4213,36 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C2" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="E2" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="F2" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="68" t="s">
         <v>137</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="H2" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="68" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11">
@@ -4262,7 +4268,7 @@
     </row>
     <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11">
@@ -4283,7 +4289,7 @@
     </row>
     <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11">
@@ -4299,12 +4305,12 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11">
@@ -4327,42 +4333,42 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C7" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D7" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E7" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F7" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="H7" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I7" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J7" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K7" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K7" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="70"/>
       <c r="C8" s="70"/>
@@ -4381,7 +4387,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="11">
         <v>10000</v>
@@ -4403,7 +4409,7 @@
     </row>
     <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B10" s="11">
         <v>30000</v>
@@ -4424,7 +4430,7 @@
     </row>
     <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11">
         <v>25000</v>
@@ -4445,7 +4451,7 @@
     </row>
     <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4464,7 +4470,7 @@
     </row>
     <row r="13" spans="1:11" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4486,34 +4492,34 @@
         <v>16</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C14" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="E14" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="66" t="s">
+      <c r="F14" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="F14" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="H14" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="68" t="s">
-        <v>138</v>
-      </c>
       <c r="J14" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="K14" s="75" t="s">
         <v>144</v>
-      </c>
-      <c r="K14" s="75" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -4588,7 +4594,7 @@
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="69" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4608,33 +4614,33 @@
         <v>23</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E18" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F18" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="54" t="s">
+      <c r="H18" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I18" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="11">
         <v>20000</v>
@@ -4659,39 +4665,39 @@
         <v>19</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C20" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E20" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F20" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="H20" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I20" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J20" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K20" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B21" s="11">
         <v>35000</v>
@@ -4727,39 +4733,39 @@
         <v>30</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E22" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F22" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="54" t="s">
+      <c r="H22" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H22" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I22" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J22" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K22" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K22" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" s="11">
         <v>30000</v>
@@ -4792,42 +4798,42 @@
     </row>
     <row r="24" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C24" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E24" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F24" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="54" t="s">
+      <c r="H24" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I24" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J24" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K24" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="11">
         <v>20000</v>
@@ -4864,42 +4870,42 @@
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C26" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E26" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F26" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="54" t="s">
+      <c r="H26" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H26" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I26" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J26" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K26" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K26" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="11">
         <v>228334</v>
@@ -4936,42 +4942,42 @@
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C28" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E28" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F28" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="54" t="s">
+      <c r="H28" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I28" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J28" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K28" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K28" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="11">
         <v>72000</v>
@@ -5011,39 +5017,39 @@
         <v>1</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C30" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E30" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F30" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G30" s="54" t="s">
+      <c r="H30" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H30" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I30" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J30" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K30" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K30" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="11">
         <v>33000</v>
@@ -5083,39 +5089,39 @@
         <v>42</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C32" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E32" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F32" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="54" t="s">
+      <c r="H32" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I32" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J32" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K32" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K32" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B33" s="11">
         <v>24600</v>
@@ -5155,39 +5161,39 @@
         <v>22</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C34" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D34" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E34" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F34" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G34" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G34" s="54" t="s">
+      <c r="H34" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H34" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I34" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J34" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K34" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K34" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B35" s="11">
         <v>24600</v>
@@ -5227,39 +5233,39 @@
         <v>20</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C36" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D36" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E36" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F36" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="54" t="s">
+      <c r="H36" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H36" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I36" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J36" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K36" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K36" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B37" s="11">
         <v>24600</v>
@@ -5299,39 +5305,39 @@
         <v>21</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C38" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E38" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="54" t="s">
+      <c r="H38" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H38" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I38" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J38" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K38" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K38" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B39" s="11">
         <v>24600</v>
@@ -5368,42 +5374,42 @@
     </row>
     <row r="40" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C40" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E40" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F40" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="54" t="s">
+      <c r="H40" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H40" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I40" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J40" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K40" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K40" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" s="11">
         <v>72000</v>
@@ -5443,39 +5449,39 @@
         <v>2</v>
       </c>
       <c r="B42" s="53" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C42" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D42" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E42" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F42" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="54" t="s">
+      <c r="H42" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H42" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I42" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J42" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K42" s="68" t="s">
         <v>144</v>
-      </c>
-      <c r="K42" s="68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43" s="11">
         <v>12000</v>
@@ -5512,7 +5518,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" s="11">
         <v>12000</v>
@@ -5549,7 +5555,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B45" s="11">
         <v>12000</v>
@@ -5586,7 +5592,7 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="11">
         <v>12000</v>
@@ -5626,33 +5632,33 @@
         <v>3</v>
       </c>
       <c r="B47" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C47" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D47" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E47" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F47" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G47" s="54" t="s">
+      <c r="H47" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H47" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I47" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B48" s="79">
         <v>20000</v>
@@ -5684,7 +5690,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B49" s="79">
         <v>15000</v>
@@ -5716,7 +5722,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B50" s="79">
         <v>15000</v>
@@ -5747,7 +5753,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B51" s="79">
         <v>20000</v>
@@ -5778,7 +5784,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B52" s="79">
         <v>20000</v>
@@ -5809,7 +5815,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B53" s="79">
         <v>20000</v>
@@ -5840,7 +5846,7 @@
     </row>
     <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B54" s="79">
         <v>20000</v>
@@ -5874,33 +5880,33 @@
         <v>31</v>
       </c>
       <c r="B55" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C55" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D55" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D55" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E55" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F55" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G55" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G55" s="54" t="s">
+      <c r="H55" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H55" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I55" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B56" s="79">
         <v>15000</v>
@@ -5929,36 +5935,36 @@
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B57" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C57" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D57" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E57" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F57" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G57" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G57" s="54" t="s">
+      <c r="H57" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I57" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B58" s="11">
         <v>12000</v>
@@ -5989,31 +5995,31 @@
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C59" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E59" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F59" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G59" s="54" t="s">
+      <c r="H59" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I59" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -6189,33 +6195,33 @@
         <v>10</v>
       </c>
       <c r="B66" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C66" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D66" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E66" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F66" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G66" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G66" s="54" t="s">
+      <c r="H66" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H66" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I66" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B67" s="83">
         <v>111000</v>
@@ -6246,7 +6252,7 @@
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B68" s="92">
         <v>51000</v>
@@ -6277,36 +6283,36 @@
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="D69" s="65" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="F69" s="54" t="s">
+      <c r="G69" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G69" s="54" t="s">
+      <c r="H69" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H69" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I69" s="75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B70" s="83">
         <v>241000</v>
@@ -6337,7 +6343,7 @@
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B71" s="92">
         <v>68000</v>
@@ -6368,36 +6374,36 @@
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C72" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D72" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D72" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E72" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F72" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G72" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G72" s="54" t="s">
+      <c r="H72" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H72" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I72" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B73" s="83">
         <v>551000</v>
@@ -6428,7 +6434,7 @@
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="76" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B74" s="92">
         <v>132000</v>
@@ -6459,36 +6465,36 @@
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C75" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D75" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D75" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E75" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F75" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G75" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G75" s="54" t="s">
+      <c r="H75" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H75" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I75" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B76" s="83">
         <v>962000</v>
@@ -6519,7 +6525,7 @@
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B77" s="92">
         <v>203000</v>
@@ -6553,28 +6559,28 @@
         <v>11</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C78" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D78" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E78" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F78" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G78" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G78" s="54" t="s">
+      <c r="H78" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H78" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I78" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -6641,7 +6647,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B81" s="81">
         <v>41000</v>
@@ -6703,36 +6709,36 @@
     </row>
     <row r="83" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="21" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="B83" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C83" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D83" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D83" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E83" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F83" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G83" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G83" s="54" t="s">
+      <c r="H83" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H83" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I83" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B84" s="87">
         <v>64600</v>
@@ -6751,30 +6757,30 @@
       </c>
       <c r="B85" s="78"/>
       <c r="C85" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D85" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D85" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E85" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F85" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G85" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G85" s="54" t="s">
+      <c r="H85" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H85" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I85" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B86" s="83">
         <v>97000</v>
@@ -6805,7 +6811,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B87" s="83">
         <v>282000</v>
@@ -6836,7 +6842,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B88" s="83">
         <v>256000</v>
@@ -6867,7 +6873,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B89" s="83">
         <v>508000</v>
@@ -6898,7 +6904,7 @@
     </row>
     <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B90" s="83">
         <v>8200</v>
@@ -6932,28 +6938,28 @@
         <v>36</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C91" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D91" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E91" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F91" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G91" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G91" s="54" t="s">
+      <c r="H91" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H91" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I91" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -7042,28 +7048,28 @@
         <v>40</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C95" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D95" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D95" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E95" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F95" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G95" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G95" s="54" t="s">
+      <c r="H95" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H95" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I95" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -7164,33 +7170,33 @@
         <v>29</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C99" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D99" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D99" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E99" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F99" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="G99" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="G99" s="54" t="s">
+      <c r="H99" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H99" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I99" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B100" s="83">
         <v>55600</v>
@@ -7221,7 +7227,7 @@
     </row>
     <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B101" s="83">
         <v>13900</v>
@@ -7252,7 +7258,7 @@
     </row>
     <row r="102" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -7265,36 +7271,36 @@
     </row>
     <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C103" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D103" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D103" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E103" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F103" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G103" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G103" s="56" t="s">
+      <c r="H103" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H103" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I103" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B104" s="11">
         <v>88886</v>
@@ -7325,7 +7331,7 @@
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B105" s="11">
         <v>103703</v>
@@ -7356,7 +7362,7 @@
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B106" s="11">
         <v>174729</v>
@@ -7387,7 +7393,7 @@
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B107" s="11">
         <v>22223</v>
@@ -7418,7 +7424,7 @@
     </row>
     <row r="108" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B108" s="11">
         <v>111110</v>
@@ -7449,36 +7455,36 @@
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C109" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D109" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D109" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E109" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F109" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G109" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G109" s="56" t="s">
+      <c r="H109" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H109" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I109" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B110" s="11">
         <v>312686</v>
@@ -7509,7 +7515,7 @@
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B111" s="11">
         <v>349723</v>
@@ -7540,7 +7546,7 @@
     </row>
     <row r="112" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B112" s="11">
         <v>446016</v>
@@ -7571,36 +7577,36 @@
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C113" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D113" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D113" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E113" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F113" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G113" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G113" s="56" t="s">
+      <c r="H113" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H113" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I113" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B114" s="11">
         <v>128763</v>
@@ -7631,7 +7637,7 @@
     </row>
     <row r="115" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B115" s="11">
         <v>199762</v>
@@ -7662,36 +7668,36 @@
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C116" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D116" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D116" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E116" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F116" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G116" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G116" s="56" t="s">
+      <c r="H116" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H116" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I116" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B117" s="11">
         <v>477701</v>
@@ -7722,7 +7728,7 @@
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B118" s="11">
         <v>236516</v>
@@ -7753,7 +7759,7 @@
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B119" s="11">
         <v>274873</v>
@@ -7784,7 +7790,7 @@
     </row>
     <row r="120" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B120" s="11">
         <v>313203</v>
@@ -7815,36 +7821,36 @@
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C121" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D121" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D121" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E121" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F121" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G121" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G121" s="56" t="s">
+      <c r="H121" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H121" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I121" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B122" s="11">
         <v>139695</v>
@@ -7875,7 +7881,7 @@
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B123" s="11">
         <v>153373</v>
@@ -7906,7 +7912,7 @@
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B124" s="11">
         <v>184044</v>
@@ -7937,7 +7943,7 @@
     </row>
     <row r="125" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B125" s="11">
         <v>49078</v>
@@ -7968,36 +7974,36 @@
     </row>
     <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C126" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D126" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D126" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E126" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F126" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G126" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G126" s="56" t="s">
+      <c r="H126" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H126" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I126" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B127" s="11">
         <v>661862</v>
@@ -8028,7 +8034,7 @@
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B128" s="11">
         <v>692556</v>
@@ -8059,7 +8065,7 @@
     </row>
     <row r="129" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B129" s="11">
         <v>90078</v>
@@ -8090,36 +8096,36 @@
     </row>
     <row r="130" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="61" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C130" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D130" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="D130" s="65" t="s">
-        <v>136</v>
-      </c>
       <c r="E130" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F130" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G130" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="G130" s="56" t="s">
+      <c r="H130" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="H130" s="68" t="s">
-        <v>104</v>
-      </c>
       <c r="I130" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B131" s="86">
         <f>+G131/0.6</f>
@@ -8147,7 +8153,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B132" s="86">
         <f t="shared" ref="B132:B150" si="12">+G132/0.6</f>
@@ -8175,7 +8181,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B133" s="86">
         <f t="shared" si="12"/>
@@ -8203,7 +8209,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B134" s="86">
         <f t="shared" si="12"/>
@@ -8231,7 +8237,7 @@
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B135" s="86">
         <f t="shared" si="12"/>
@@ -8259,7 +8265,7 @@
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B136" s="86">
         <f t="shared" si="12"/>
@@ -8287,7 +8293,7 @@
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B137" s="86">
         <f t="shared" si="12"/>
@@ -8315,7 +8321,7 @@
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B138" s="86">
         <f t="shared" si="12"/>
@@ -8343,7 +8349,7 @@
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B139" s="86">
         <f t="shared" si="12"/>
@@ -8371,7 +8377,7 @@
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B140" s="86">
         <f t="shared" si="12"/>
@@ -8399,7 +8405,7 @@
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B141" s="86">
         <f t="shared" si="12"/>
@@ -8427,7 +8433,7 @@
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B142" s="86">
         <f t="shared" si="12"/>
@@ -8455,7 +8461,7 @@
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B143" s="86">
         <f t="shared" si="12"/>
@@ -8483,7 +8489,7 @@
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B144" s="86">
         <f t="shared" si="12"/>
@@ -8511,7 +8517,7 @@
     </row>
     <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B145" s="86">
         <f t="shared" si="12"/>
@@ -8539,7 +8545,7 @@
     </row>
     <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B146" s="86">
         <f t="shared" si="12"/>
@@ -8567,7 +8573,7 @@
     </row>
     <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B147" s="86">
         <f t="shared" si="12"/>
@@ -8595,7 +8601,7 @@
     </row>
     <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B148" s="86">
         <f t="shared" si="12"/>
@@ -8623,7 +8629,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B149" s="86">
         <f t="shared" si="12"/>
@@ -8651,7 +8657,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B150" s="86">
         <f t="shared" si="12"/>
@@ -8679,7 +8685,7 @@
     </row>
     <row r="151" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B151" s="11">
         <v>70000</v>
@@ -8726,28 +8732,28 @@
         <v>4</v>
       </c>
       <c r="B153" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C153" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="D153" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="D153" s="93" t="s">
-        <v>136</v>
-      </c>
       <c r="E153" s="93" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F153" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="G153" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="G153" s="93" t="s">
+      <c r="H153" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="H153" s="93" t="s">
-        <v>104</v>
-      </c>
       <c r="I153" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="154" spans="1:9" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -8782,7 +8788,7 @@
     </row>
     <row r="156" spans="1:9" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B156" s="93"/>
       <c r="C156" s="93"/>
@@ -8797,7 +8803,7 @@
     </row>
     <row r="157" spans="1:9" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B157" s="93"/>
       <c r="C157" s="93"/>
@@ -8812,7 +8818,7 @@
     </row>
     <row r="158" spans="1:9" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B158" s="93"/>
       <c r="C158" s="93"/>
@@ -8830,28 +8836,28 @@
         <v>15</v>
       </c>
       <c r="B159" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C159" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="D159" s="94" t="s">
         <v>135</v>
       </c>
-      <c r="D159" s="94" t="s">
-        <v>136</v>
-      </c>
       <c r="E159" s="95" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F159" s="100" t="s">
+        <v>101</v>
+      </c>
+      <c r="G159" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G159" s="100" t="s">
+      <c r="H159" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="H159" s="101" t="s">
-        <v>104</v>
-      </c>
       <c r="I159" s="101" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8871,7 +8877,7 @@
     </row>
     <row r="161" spans="1:9" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B161" s="79"/>
       <c r="C161" s="79"/>
@@ -8887,28 +8893,28 @@
         <v>8</v>
       </c>
       <c r="B162" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C162" s="96" t="s">
+        <v>134</v>
+      </c>
+      <c r="D162" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="D162" s="96" t="s">
-        <v>136</v>
-      </c>
       <c r="E162" s="97" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F162" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="G162" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="G162" s="93" t="s">
+      <c r="H162" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="H162" s="98" t="s">
-        <v>104</v>
-      </c>
       <c r="I162" s="98" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8928,36 +8934,36 @@
     </row>
     <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="62" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B164" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C164" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="D164" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="D164" s="93" t="s">
-        <v>136</v>
-      </c>
       <c r="E164" s="93" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F164" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="G164" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="G164" s="93" t="s">
+      <c r="H164" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="H164" s="93" t="s">
-        <v>104</v>
-      </c>
       <c r="I164" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B165" s="93"/>
       <c r="C165" s="93"/>
@@ -8974,7 +8980,7 @@
     </row>
     <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B166" s="93"/>
       <c r="C166" s="93"/>
@@ -8991,7 +8997,7 @@
     </row>
     <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B167" s="93"/>
       <c r="C167" s="93"/>
@@ -9008,7 +9014,7 @@
     </row>
     <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B168" s="93"/>
       <c r="C168" s="93"/>
@@ -9023,7 +9029,7 @@
     </row>
     <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B169" s="93"/>
       <c r="C169" s="93"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -13,7 +13,6 @@
   </bookViews>
   <sheets>
     <sheet name="JUNIO 2026" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'JUNIO 2026'!$A$47:$I$54</definedName>
@@ -2578,7 +2577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A164" authorId="0" shapeId="0">
+    <comment ref="A235" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2607,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="230">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -2647,12 +2646,6 @@
     <t>PANORAMICA</t>
   </si>
   <si>
-    <t>RX VARIAS</t>
-  </si>
-  <si>
-    <t>MAMOGRAFIA</t>
-  </si>
-  <si>
     <t>PETRAGLIA</t>
   </si>
   <si>
@@ -2672,9 +2665,6 @@
   </si>
   <si>
     <t>HONORARIOS RUBEN</t>
-  </si>
-  <si>
-    <t>FAMYL</t>
   </si>
   <si>
     <t>BONOS DE CONSULTA KINESIOLOGIA</t>
@@ -3038,9 +3028,6 @@
     <t>VALOR 6 DIAS</t>
   </si>
   <si>
-    <t>Ecografias</t>
-  </si>
-  <si>
     <t>COME BEAN</t>
   </si>
   <si>
@@ -3059,9 +3046,6 @@
     <t>$20 anual</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuota FLIAR </t>
-  </si>
-  <si>
     <t xml:space="preserve">Cuota FLIAR POR INTEGRANTES </t>
   </si>
   <si>
@@ -3153,17 +3137,210 @@
   </si>
   <si>
     <t>In 90 (OSECAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuota TITULAR </t>
+  </si>
+  <si>
+    <t>RX SUBSIGUIENTE</t>
+  </si>
+  <si>
+    <t>RX PRIMERA EXPOSICION</t>
+  </si>
+  <si>
+    <t>MAMO BILATERAL + PROYECCION AXILAR</t>
+  </si>
+  <si>
+    <t>ESPINOGRAMA FRENTE</t>
+  </si>
+  <si>
+    <t>DENSITOMETRIA 2 REGIONES</t>
+  </si>
+  <si>
+    <t>ECODDOPPLER COLOR TODAS LAS REGIONES</t>
+  </si>
+  <si>
+    <t>SCAN FETAL</t>
+  </si>
+  <si>
+    <t>MAMOGRAFIA CONVENCIONAL</t>
+  </si>
+  <si>
+    <t>RX CONVENCIONAL (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIAS (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>Ecografias Dra. Capponi</t>
+  </si>
+  <si>
+    <t>VESICAL (VEJIGA) C/MEDICION DE RESIDUO POSTMICCIONAL</t>
+  </si>
+  <si>
+    <t>CMD (FAMYL)</t>
+  </si>
+  <si>
+    <t>RX CRANEO, CARA, SENOS PARANASALES</t>
+  </si>
+  <si>
+    <t>RX RAQUIS - COLUMNA</t>
+  </si>
+  <si>
+    <t>RX HOMBRO, HUMERO, PELVIS, CADERA</t>
+  </si>
+  <si>
+    <t>RX CODO, ANTEBRAZO, MUÑECA, TOBILLO, PIE</t>
+  </si>
+  <si>
+    <t>RX TORAX</t>
+  </si>
+  <si>
+    <t>RX SIMPLE DE ABDOMEN</t>
+  </si>
+  <si>
+    <t>RX SIMPLE DE ARBOL URINARIO</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TOCOGINECOLOGICA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA MAMARIA UNI O BILATERAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA CEREBRAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TIORIDEA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TESTICULAR</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE AORTA ABDOMINAL DINAM. Y ESTAT.</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA PANCREATICA O SUPRARRENAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA PARA LA AMNIOCENTESIS</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA HEPATOBILIAR</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE PANCREAS</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA MUSCULO ESQUELETICO</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE CADERAS</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE PLEURA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TRANSVAGINAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA CERVICAL - CERVICOMETRIA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE VEJIGA Y PROSTATA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE VESICULAS SEMINALES</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE PENE</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE PARTES BLANDAS</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TIROIDEA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA ABDOMINAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA RENAL UNI O BILATERAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA HEPATO-BILIO-PANCREATICA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA VESICAL O VESICOPROSTATICA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA GINECOLOGICA</t>
+  </si>
+  <si>
+    <t>TAC OTROS ORGANOS Y REGIONES</t>
+  </si>
+  <si>
+    <t>TAC DE OIDOS</t>
+  </si>
+  <si>
+    <t>TAC DE SENOS PARANASALES</t>
+  </si>
+  <si>
+    <t>TAC DE MACIZO FACIAL</t>
+  </si>
+  <si>
+    <t>TAC DE MIEMBROS SUPERIORES UNILATERAL</t>
+  </si>
+  <si>
+    <t>TAC DE COLUMNA CERVICAL</t>
+  </si>
+  <si>
+    <t>TAC DE COLUMNA DORSAL</t>
+  </si>
+  <si>
+    <t>TAC DE COLUMNA LUMBO SACRA</t>
+  </si>
+  <si>
+    <t>TAC CEREBRAL</t>
+  </si>
+  <si>
+    <t>TAC TIROIDEA</t>
+  </si>
+  <si>
+    <t>TAC MAMARIA</t>
+  </si>
+  <si>
+    <t>TAC GINECOLOGICA</t>
+  </si>
+  <si>
+    <t>TAC HEPATOBILIAR</t>
+  </si>
+  <si>
+    <t>TAC TORACICA</t>
+  </si>
+  <si>
+    <t>TAC COLUMNA</t>
+  </si>
+  <si>
+    <t>TAC DE ARBOL URINARIO</t>
+  </si>
+  <si>
+    <t>TAC DE MIEMBROS INFERIORES UNILATERAL</t>
+  </si>
+  <si>
+    <t>TAC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3281,8 +3458,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3376,6 +3559,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3719,7 +3908,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3739,7 +3928,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3821,12 +4009,9 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3851,56 +4036,66 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda 2" xfId="1"/>
@@ -4187,197 +4382,203 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:L240"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="8" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="73" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.85546875" style="73" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="73" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5703125" style="73" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5703125" style="73" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="103">
+      <c r="B1" s="72">
         <v>46174</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="65" t="s">
+      <c r="A2" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="78" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79">
+        <v>5550</v>
+      </c>
+      <c r="D3" s="79">
+        <v>5550</v>
+      </c>
+      <c r="E3" s="79">
+        <v>5550</v>
+      </c>
+      <c r="F3" s="80">
+        <v>5550</v>
+      </c>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79">
+        <v>4550</v>
+      </c>
+      <c r="I3" s="79">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79">
+        <v>8500</v>
+      </c>
+      <c r="D4" s="79">
+        <v>8500</v>
+      </c>
+      <c r="E4" s="79">
+        <v>8500</v>
+      </c>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79">
+        <f>+I3*2</f>
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79">
+        <v>20000</v>
+      </c>
+      <c r="D5" s="79">
+        <v>20000</v>
+      </c>
+      <c r="E5" s="79">
+        <v>30000</v>
+      </c>
+      <c r="F5" s="79">
+        <v>15000</v>
+      </c>
+      <c r="G5" s="79">
+        <v>30000</v>
+      </c>
+      <c r="H5" s="79"/>
+      <c r="I5" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="65" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="79">
+        <v>14000</v>
+      </c>
+      <c r="D6" s="79">
+        <v>14000</v>
+      </c>
+      <c r="E6" s="79">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="82">
+        <f>+F5/2</f>
+        <v>7500</v>
+      </c>
+      <c r="G6" s="82">
+        <f>+G5/2</f>
+        <v>15000</v>
+      </c>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="68" t="s">
+      <c r="F7" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="61" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="68" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11">
-        <v>5500</v>
-      </c>
-      <c r="D3" s="11">
-        <v>5500</v>
-      </c>
-      <c r="E3" s="11">
-        <v>0</v>
-      </c>
-      <c r="F3" s="83">
-        <f>+E3+1150</f>
-        <v>1150</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11">
-        <v>4350</v>
-      </c>
-      <c r="I3" s="11">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11">
-        <v>8500</v>
-      </c>
-      <c r="D4" s="11">
-        <v>8500</v>
-      </c>
-      <c r="E4" s="11">
-        <v>8500</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11">
-        <v>8500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11">
-        <v>20000</v>
-      </c>
-      <c r="D5" s="11">
-        <v>20000</v>
-      </c>
-      <c r="E5" s="11">
-        <v>30000</v>
-      </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="67" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11">
-        <v>14000</v>
-      </c>
-      <c r="D6" s="11">
-        <v>14000</v>
-      </c>
-      <c r="E6" s="11">
-        <v>20000</v>
-      </c>
-      <c r="F6" s="81">
-        <v>15000</v>
-      </c>
-      <c r="G6" s="81">
-        <v>30000</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J7" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K7" s="68" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
       <c r="J8" s="11">
         <v>4800</v>
       </c>
@@ -4385,169 +4586,169 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="11">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="79">
         <v>10000</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11">
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79">
         <v>4200</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="81">
+      <c r="F9" s="79"/>
+      <c r="G9" s="82">
         <f>+B9*0.6</f>
         <v>6000</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="79">
         <v>30000</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11">
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79">
         <v>10000</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="81">
+      <c r="F10" s="79"/>
+      <c r="G10" s="82">
         <v>15000</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="79">
         <v>25000</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11">
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79">
         <v>8000</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="81">
+      <c r="F11" s="79"/>
+      <c r="G11" s="82">
         <v>12000</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79">
         <v>17000</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="79">
+      <c r="F12" s="79"/>
+      <c r="G12" s="84">
         <v>18000</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
-    <row r="13" spans="1:11" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79">
         <v>18400</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="79">
+      <c r="F13" s="79"/>
+      <c r="G13" s="84">
         <v>20000</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C14" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J14" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="K14" s="75" t="s">
-        <v>144</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="76" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="64" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="11">
+      <c r="A15" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="79">
         <v>88500</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11">
+      <c r="C15" s="79"/>
+      <c r="D15" s="79">
         <v>44800</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="79">
         <v>44800</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="82">
         <f>+B15*0.7</f>
         <v>61949.999999999993</v>
       </c>
-      <c r="G15" s="81">
+      <c r="G15" s="82">
         <f>+B15*0.6</f>
         <v>53100</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="79">
         <v>14750</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="79">
         <v>0</v>
       </c>
       <c r="J15" s="11">
@@ -4558,31 +4759,31 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="11">
+      <c r="A16" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="79">
         <v>177000</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11">
+      <c r="C16" s="79"/>
+      <c r="D16" s="79">
         <v>88500</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="79">
         <v>88500</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="82">
         <f>+B16*0.7</f>
         <v>123899.99999999999</v>
       </c>
-      <c r="G16" s="81">
+      <c r="G16" s="82">
         <f>+B16*0.6</f>
         <v>106200</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="79">
         <v>29500</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="79">
         <v>0</v>
       </c>
       <c r="J16" s="11">
@@ -4593,132 +4794,132 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="69" t="s">
-        <v>142</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11">
+      <c r="A17" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79">
         <v>16000</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C18" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="68" t="s">
-        <v>137</v>
+        <v>20</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="11">
+      <c r="A19" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="79">
         <v>20000</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11">
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79">
         <v>8000</v>
       </c>
-      <c r="F19" s="82">
+      <c r="F19" s="85">
         <v>0</v>
       </c>
-      <c r="G19" s="81">
+      <c r="G19" s="82">
         <f>+B19*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D20" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H20" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K20" s="68" t="s">
-        <v>144</v>
+      <c r="A20" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J20" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K20" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="11">
+      <c r="A21" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="79">
         <v>35000</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11">
+      <c r="C21" s="79"/>
+      <c r="D21" s="79">
         <v>20000</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="79">
         <v>20000</v>
       </c>
-      <c r="F21" s="82">
+      <c r="F21" s="85">
         <v>0</v>
       </c>
-      <c r="G21" s="81">
+      <c r="G21" s="82">
         <v>20000</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="79">
         <v>7000</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="79">
         <v>0</v>
       </c>
       <c r="J21" s="11">
@@ -4730,63 +4931,63 @@
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H22" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K22" s="68" t="s">
-        <v>144</v>
+        <v>27</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I22" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K22" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="11">
+      <c r="A23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="79">
         <v>30000</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11">
+      <c r="C23" s="79"/>
+      <c r="D23" s="79">
         <v>8200</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="79">
         <v>10400</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="85">
         <v>18000</v>
       </c>
-      <c r="G23" s="81">
+      <c r="G23" s="82">
         <v>15000</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="79">
         <v>4200</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="79">
         <v>0</v>
       </c>
       <c r="J23" s="11">
@@ -4798,67 +4999,67 @@
     </row>
     <row r="24" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H24" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J24" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K24" s="68" t="s">
-        <v>144</v>
+        <v>106</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K24" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="11">
+      <c r="A25" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="79">
         <v>20000</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="79">
         <v>12600</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="79">
         <v>8200</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="79">
         <v>12600</v>
       </c>
-      <c r="F25" s="82">
+      <c r="F25" s="85">
         <f>+B25*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G25" s="81">
+      <c r="G25" s="82">
         <f>+B25*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="79">
         <v>5400</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="79">
         <v>0</v>
       </c>
       <c r="J25" s="11">
@@ -4870,67 +5071,67 @@
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D26" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E26" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F26" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I26" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J26" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K26" s="68" t="s">
-        <v>144</v>
+      <c r="H26" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="11">
+      <c r="A27" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="79">
         <v>228334</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="79">
         <v>149000</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="79">
         <v>137000</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="79">
         <v>149000</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="85">
         <f>+B27*0.7</f>
         <v>159833.79999999999</v>
       </c>
-      <c r="G27" s="81">
+      <c r="G27" s="82">
         <f>+B27*0.6</f>
         <v>137000.4</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="79">
         <v>74000</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="79">
         <v>74000</v>
       </c>
       <c r="J27" s="11">
@@ -4942,67 +5143,67 @@
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F28" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H28" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I28" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J28" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K28" s="68" t="s">
-        <v>144</v>
+        <v>43</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K28" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="11">
+      <c r="A29" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="79">
         <v>72000</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="79">
         <v>36700</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="79">
         <v>31000</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="79">
         <v>36700</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="85">
         <f>+B29*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G29" s="81">
+      <c r="G29" s="82">
         <f>+B29*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="79">
         <v>16800</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="79">
         <v>16800</v>
       </c>
       <c r="J29" s="11">
@@ -5016,65 +5217,65 @@
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C30" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G30" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H30" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I30" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J30" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K30" s="68" t="s">
-        <v>144</v>
+      <c r="B30" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I30" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K30" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="11">
+      <c r="A31" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="79">
         <v>33000</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="79">
         <v>16600</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="79">
         <v>16600</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="79">
         <v>16600</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="85">
         <f>+B31*0.7</f>
         <v>23100</v>
       </c>
-      <c r="G31" s="81">
+      <c r="G31" s="82">
         <f>+B31*0.6</f>
         <v>19800</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="79">
         <v>10800</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="79">
         <v>10800</v>
       </c>
       <c r="J31" s="11">
@@ -5086,67 +5287,67 @@
     </row>
     <row r="32" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C32" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F32" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H32" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I32" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J32" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K32" s="68" t="s">
-        <v>144</v>
+        <v>39</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K32" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="11">
+      <c r="A33" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="79">
         <v>24600</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="79">
         <v>12500</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="79">
         <v>12500</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="79">
         <v>12500</v>
       </c>
-      <c r="F33" s="82">
+      <c r="F33" s="85">
         <f>+B33*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G33" s="81">
+      <c r="G33" s="82">
         <f>+B33*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="79">
         <v>6300</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="79">
         <v>6300</v>
       </c>
       <c r="J33" s="11">
@@ -5158,67 +5359,67 @@
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C34" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F34" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G34" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H34" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I34" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J34" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K34" s="68" t="s">
-        <v>144</v>
+        <v>19</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H34" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K34" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="11">
+      <c r="A35" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="79">
         <v>24600</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="79">
         <v>12500</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="79">
         <v>12500</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="79">
         <v>12500</v>
       </c>
-      <c r="F35" s="82">
+      <c r="F35" s="85">
         <f>+B35*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G35" s="81">
+      <c r="G35" s="82">
         <f>+B35*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="79">
         <v>6300</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="79">
         <v>6300</v>
       </c>
       <c r="J35" s="11">
@@ -5230,67 +5431,67 @@
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G36" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H36" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I36" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J36" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K36" s="68" t="s">
-        <v>144</v>
+        <v>17</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I36" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K36" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="11">
+      <c r="A37" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="79">
         <v>24600</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="79">
         <v>12500</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="79">
         <v>12500</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="79">
         <v>12500</v>
       </c>
-      <c r="F37" s="82">
+      <c r="F37" s="85">
         <f>+B37*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G37" s="81">
+      <c r="G37" s="82">
         <f>+B37*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="79">
         <v>6300</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="79">
         <v>6300</v>
       </c>
       <c r="J37" s="11">
@@ -5302,67 +5503,67 @@
     </row>
     <row r="38" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D38" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F38" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G38" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H38" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I38" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J38" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K38" s="68" t="s">
-        <v>144</v>
+        <v>18</v>
+      </c>
+      <c r="B38" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F38" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J38" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K38" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B39" s="11">
+      <c r="A39" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="79">
         <v>24600</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="79">
         <v>12500</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="79">
         <v>12500</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="79">
         <v>12500</v>
       </c>
-      <c r="F39" s="82">
+      <c r="F39" s="85">
         <f>+B39*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G39" s="81">
+      <c r="G39" s="82">
         <f>+B39*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="79">
         <v>6300</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="79">
         <v>6300</v>
       </c>
       <c r="J39" s="11">
@@ -5373,68 +5574,68 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E40" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F40" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H40" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I40" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J40" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K40" s="68" t="s">
-        <v>144</v>
+      <c r="A40" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C40" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H40" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I40" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K40" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" s="11">
+      <c r="A41" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="79">
         <v>72000</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="79">
         <v>36700</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="79">
         <v>31000</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="79">
         <v>36700</v>
       </c>
-      <c r="F41" s="82">
+      <c r="F41" s="85">
         <f>+B41*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G41" s="81">
+      <c r="G41" s="82">
         <f>+B41*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="79">
         <v>16800</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="79">
         <v>16800</v>
       </c>
       <c r="J41" s="11">
@@ -5448,65 +5649,65 @@
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="C42" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D42" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G42" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H42" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I42" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="J42" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="K42" s="68" t="s">
-        <v>144</v>
+      <c r="B42" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="C42" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H42" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I42" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K42" s="61" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" s="11">
+      <c r="A43" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="79">
         <v>12000</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="79">
         <v>4200</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="79">
         <v>0</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="79">
         <v>4200</v>
       </c>
-      <c r="F43" s="82">
+      <c r="F43" s="85">
         <f>+B43*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G43" s="82">
+      <c r="G43" s="85">
         <f>+B43*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="79">
         <v>0</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="79">
         <v>0</v>
       </c>
       <c r="J43" s="11">
@@ -5517,33 +5718,33 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" s="11">
+      <c r="A44" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="79">
         <v>12000</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="79">
         <v>4200</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="79">
         <v>0</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="79">
         <v>4200</v>
       </c>
-      <c r="F44" s="82">
+      <c r="F44" s="85">
         <f t="shared" ref="F44:F46" si="0">+B44*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G44" s="82">
+      <c r="G44" s="85">
         <f t="shared" ref="G44:G46" si="1">+B44*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="79">
         <v>0</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="79">
         <v>0</v>
       </c>
       <c r="J44" s="11">
@@ -5554,33 +5755,33 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" s="11">
+      <c r="A45" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="79">
         <v>12000</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="79">
         <v>4200</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="79">
         <v>0</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="79">
         <v>4200</v>
       </c>
-      <c r="F45" s="82">
+      <c r="F45" s="85">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G45" s="82">
+      <c r="G45" s="85">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="79">
         <v>0</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="79">
         <v>0</v>
       </c>
       <c r="J45" s="11">
@@ -5591,3131 +5792,3131 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B46" s="11">
+      <c r="A46" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="79">
         <v>12000</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="79">
         <v>4200</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="79">
         <v>0</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="79">
         <v>4200</v>
       </c>
-      <c r="F46" s="82">
+      <c r="F46" s="85">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G46" s="82">
+      <c r="G46" s="85">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="79">
         <v>0</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="79">
         <v>0</v>
       </c>
       <c r="J46" s="11">
         <v>5300</v>
       </c>
-      <c r="K46" s="85">
+      <c r="K46" s="69">
         <v>5300</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D47" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F47" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G47" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H47" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I47" s="68" t="s">
-        <v>137</v>
+      <c r="B47" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F47" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H47" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I47" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="B48" s="79">
+      <c r="A48" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="84">
         <v>20000</v>
       </c>
-      <c r="C48" s="79">
+      <c r="C48" s="84">
         <v>9500</v>
       </c>
-      <c r="D48" s="79">
+      <c r="D48" s="84">
         <v>9500</v>
       </c>
-      <c r="E48" s="79">
+      <c r="E48" s="84">
         <v>9500</v>
       </c>
-      <c r="F48" s="82">
+      <c r="F48" s="85">
         <f>+B48*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G48" s="82">
+      <c r="G48" s="85">
         <f>+B48*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="79">
         <v>4100</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="79">
         <v>4100</v>
       </c>
-      <c r="J48" s="84"/>
+      <c r="J48" s="68"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="B49" s="79">
+      <c r="A49" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="84">
         <v>15000</v>
       </c>
-      <c r="C49" s="79">
+      <c r="C49" s="84">
         <v>5900</v>
       </c>
-      <c r="D49" s="79">
+      <c r="D49" s="84">
         <v>5900</v>
       </c>
-      <c r="E49" s="79">
+      <c r="E49" s="84">
         <v>5900</v>
       </c>
-      <c r="F49" s="82">
+      <c r="F49" s="85">
         <f t="shared" ref="F49:F54" si="2">+B49*0.7</f>
         <v>10500</v>
       </c>
-      <c r="G49" s="82">
+      <c r="G49" s="85">
         <f t="shared" ref="G49:G54" si="3">+B49*0.6</f>
         <v>9000</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="79">
         <v>4900</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="79">
         <v>4900</v>
       </c>
-      <c r="J49" s="84"/>
+      <c r="J49" s="68"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" s="79">
+      <c r="A50" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="84">
         <v>15000</v>
       </c>
-      <c r="C50" s="79">
+      <c r="C50" s="84">
         <v>5800</v>
       </c>
-      <c r="D50" s="79">
+      <c r="D50" s="84">
         <v>5800</v>
       </c>
-      <c r="E50" s="79">
+      <c r="E50" s="84">
         <v>5800</v>
       </c>
-      <c r="F50" s="82">
+      <c r="F50" s="85">
         <f t="shared" si="2"/>
         <v>10500</v>
       </c>
-      <c r="G50" s="82">
+      <c r="G50" s="85">
         <f t="shared" si="3"/>
         <v>9000</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="79">
         <v>3400</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="79">
         <v>3400</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="79">
+      <c r="A51" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="84">
         <v>20000</v>
       </c>
-      <c r="C51" s="79">
+      <c r="C51" s="84">
         <v>5800</v>
       </c>
-      <c r="D51" s="79">
+      <c r="D51" s="84">
         <v>5800</v>
       </c>
-      <c r="E51" s="79">
+      <c r="E51" s="84">
         <v>5800</v>
       </c>
-      <c r="F51" s="82">
+      <c r="F51" s="85">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G51" s="82">
+      <c r="G51" s="85">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="79">
         <v>3400</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="79">
         <v>3400</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B52" s="79">
+      <c r="A52" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="84">
         <v>20000</v>
       </c>
-      <c r="C52" s="79">
+      <c r="C52" s="84">
         <v>9500</v>
       </c>
-      <c r="D52" s="79">
+      <c r="D52" s="84">
         <v>9500</v>
       </c>
-      <c r="E52" s="79">
+      <c r="E52" s="84">
         <v>9500</v>
       </c>
-      <c r="F52" s="82">
+      <c r="F52" s="85">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G52" s="82">
+      <c r="G52" s="85">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="79">
         <v>3400</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="79">
         <v>3400</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="B53" s="79">
+      <c r="A53" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="84">
         <v>20000</v>
       </c>
-      <c r="C53" s="79">
+      <c r="C53" s="84">
         <v>9500</v>
       </c>
-      <c r="D53" s="79">
+      <c r="D53" s="84">
         <v>9500</v>
       </c>
-      <c r="E53" s="79">
+      <c r="E53" s="84">
         <v>9500</v>
       </c>
-      <c r="F53" s="82">
+      <c r="F53" s="85">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G53" s="82">
+      <c r="G53" s="85">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="79">
         <v>3400</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="79">
         <v>3400</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="79">
+      <c r="A54" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="84">
         <v>20000</v>
       </c>
-      <c r="C54" s="79">
+      <c r="C54" s="84">
         <v>13800</v>
       </c>
-      <c r="D54" s="79">
+      <c r="D54" s="84">
         <v>13800</v>
       </c>
-      <c r="E54" s="79">
+      <c r="E54" s="84">
         <v>13800</v>
       </c>
-      <c r="F54" s="82">
+      <c r="F54" s="85">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G54" s="82">
+      <c r="G54" s="85">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="79">
         <v>5700</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="79">
         <v>5700</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C55" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D55" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G55" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H55" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I55" s="68" t="s">
-        <v>137</v>
+        <v>28</v>
+      </c>
+      <c r="B55" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D55" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F55" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G55" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H55" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I55" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B56" s="79">
+        <v>120</v>
+      </c>
+      <c r="B56" s="84">
         <v>15000</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="79">
         <v>7800</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="79">
         <v>7800</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="79">
         <v>7800</v>
       </c>
-      <c r="F56" s="83">
+      <c r="F56" s="80">
         <v>9000</v>
       </c>
-      <c r="G56" s="83">
+      <c r="G56" s="80">
         <v>7500</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="79">
         <v>2700</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="79">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C57" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E57" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F57" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G57" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H57" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I57" s="68" t="s">
-        <v>137</v>
+        <v>121</v>
+      </c>
+      <c r="B57" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H57" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I57" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="11">
+      <c r="A58" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="79">
         <v>12000</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="79">
         <v>6400</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="79">
         <v>6400</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="79">
         <v>6400</v>
       </c>
-      <c r="F58" s="83">
+      <c r="F58" s="80">
         <f>+B58*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G58" s="83">
+      <c r="G58" s="80">
         <f>+B58*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H58" s="11">
+      <c r="H58" s="79">
         <v>3900</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="79">
         <v>2700</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C59" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F59" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G59" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H59" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I59" s="68" t="s">
-        <v>137</v>
+        <v>123</v>
+      </c>
+      <c r="B59" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D59" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E59" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F59" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G59" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I59" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="11">
+      <c r="A60" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="79">
         <v>20000</v>
       </c>
-      <c r="C60" s="80">
+      <c r="C60" s="86">
         <v>10200</v>
       </c>
-      <c r="D60" s="80">
+      <c r="D60" s="86">
         <v>10200</v>
       </c>
-      <c r="E60" s="80">
+      <c r="E60" s="86">
         <v>10200</v>
       </c>
-      <c r="F60" s="83">
+      <c r="F60" s="80">
         <f>+B60*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G60" s="83">
+      <c r="G60" s="80">
         <f>+B60*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H60" s="11">
+      <c r="H60" s="79">
         <v>5500</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I60" s="79">
         <v>5500</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B61" s="11">
+      <c r="A61" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="79">
         <v>30000</v>
       </c>
-      <c r="C61" s="80">
+      <c r="C61" s="86">
         <v>15900</v>
       </c>
-      <c r="D61" s="80">
+      <c r="D61" s="86">
         <v>15900</v>
       </c>
-      <c r="E61" s="80">
+      <c r="E61" s="86">
         <v>15900</v>
       </c>
-      <c r="F61" s="83">
+      <c r="F61" s="80">
         <f t="shared" ref="F61:F64" si="4">+B61*0.7</f>
         <v>21000</v>
       </c>
-      <c r="G61" s="83">
+      <c r="G61" s="80">
         <f t="shared" ref="G61:G64" si="5">+B61*0.6</f>
         <v>18000</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="79">
         <v>8400</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="79">
         <v>8400</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B62" s="11">
+      <c r="A62" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" s="79">
         <v>20000</v>
       </c>
-      <c r="C62" s="80">
+      <c r="C62" s="86">
         <v>10000</v>
       </c>
-      <c r="D62" s="80">
+      <c r="D62" s="86">
         <v>10000</v>
       </c>
-      <c r="E62" s="80">
+      <c r="E62" s="86">
         <v>10000</v>
       </c>
-      <c r="F62" s="83">
+      <c r="F62" s="80">
         <f t="shared" si="4"/>
         <v>14000</v>
       </c>
-      <c r="G62" s="83">
+      <c r="G62" s="80">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H62" s="79">
         <v>5000</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="79">
         <v>5000</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B63" s="79">
+      <c r="A63" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" s="84">
         <v>30000</v>
       </c>
-      <c r="C63" s="80">
+      <c r="C63" s="86">
         <v>10000</v>
       </c>
-      <c r="D63" s="80">
+      <c r="D63" s="86">
         <v>10000</v>
       </c>
-      <c r="E63" s="80">
+      <c r="E63" s="86">
         <v>10000</v>
       </c>
-      <c r="F63" s="83">
+      <c r="F63" s="80">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G63" s="83">
+      <c r="G63" s="80">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="79">
         <v>5200</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="79">
         <v>5200</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B64" s="79">
+      <c r="A64" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" s="84">
         <v>30000</v>
       </c>
-      <c r="C64" s="80">
+      <c r="C64" s="86">
         <v>12300</v>
       </c>
-      <c r="D64" s="80">
+      <c r="D64" s="86">
         <v>12300</v>
       </c>
-      <c r="E64" s="80">
+      <c r="E64" s="86">
         <v>12300</v>
       </c>
-      <c r="F64" s="83">
+      <c r="F64" s="80">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G64" s="83">
+      <c r="G64" s="80">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H64" s="79">
         <v>7900</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="79">
         <v>7900</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
+      <c r="A65" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="87"/>
+      <c r="C65" s="87"/>
+      <c r="D65" s="87"/>
+      <c r="E65" s="87"/>
+      <c r="F65" s="87"/>
+      <c r="G65" s="87"/>
+      <c r="H65" s="87"/>
+      <c r="I65" s="87"/>
     </row>
     <row r="66" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="B66" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C66" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D66" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F66" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G66" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H66" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I66" s="68" t="s">
-        <v>137</v>
+      <c r="A66" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E66" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F66" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G66" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H66" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I66" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B67" s="83">
+        <v>124</v>
+      </c>
+      <c r="B67" s="80">
         <v>111000</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="79">
         <v>83700</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="79">
         <v>83700</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="79">
         <v>83700</v>
       </c>
-      <c r="F67" s="83">
+      <c r="F67" s="80">
         <f>+B67*0.7</f>
         <v>77700</v>
       </c>
-      <c r="G67" s="83">
+      <c r="G67" s="80">
         <f>+B67*0.6</f>
         <v>66600</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="79">
         <v>46700</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="79">
         <v>46700</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="71" t="s">
-        <v>165</v>
-      </c>
-      <c r="B68" s="92">
+      <c r="A68" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" s="88">
         <v>51000</v>
       </c>
-      <c r="C68" s="72">
+      <c r="C68" s="89">
         <v>51000</v>
       </c>
-      <c r="D68" s="72">
+      <c r="D68" s="89">
         <v>51000</v>
       </c>
-      <c r="E68" s="73">
+      <c r="E68" s="90">
         <v>51000</v>
       </c>
-      <c r="F68" s="83">
+      <c r="F68" s="80">
         <f>+B68*0.7</f>
         <v>35700</v>
       </c>
-      <c r="G68" s="83">
+      <c r="G68" s="80">
         <f>+B68*0.6</f>
         <v>30600</v>
       </c>
-      <c r="H68" s="74">
+      <c r="H68" s="91">
         <v>21300</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I68" s="79">
         <v>21300</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="40" t="s">
+      <c r="A69" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F69" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G69" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H69" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C69" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D69" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E69" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G69" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H69" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I69" s="75" t="s">
-        <v>137</v>
+      <c r="I69" s="92" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B70" s="83">
+        <v>125</v>
+      </c>
+      <c r="B70" s="80">
         <v>241000</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="79">
         <v>165000</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="79">
         <v>165000</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="79">
         <v>165000</v>
       </c>
-      <c r="F70" s="83">
+      <c r="F70" s="80">
         <f>+B70*0.7</f>
         <v>168700</v>
       </c>
-      <c r="G70" s="83">
+      <c r="G70" s="80">
         <f>+B70*0.6</f>
         <v>144600</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H70" s="79">
         <v>76000</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="79">
         <v>76000</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="71" t="s">
-        <v>166</v>
-      </c>
-      <c r="B71" s="92">
+      <c r="A71" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="88">
         <v>68000</v>
       </c>
-      <c r="C71" s="72">
+      <c r="C71" s="89">
         <v>68000</v>
       </c>
-      <c r="D71" s="72">
+      <c r="D71" s="89">
         <v>68000</v>
       </c>
-      <c r="E71" s="73">
+      <c r="E71" s="90">
         <v>68000</v>
       </c>
-      <c r="F71" s="83">
+      <c r="F71" s="80">
         <f>+B71*0.7</f>
         <v>47600</v>
       </c>
-      <c r="G71" s="83">
+      <c r="G71" s="80">
         <f t="shared" ref="G71:G98" si="6">+B71*0.6</f>
         <v>40800</v>
       </c>
-      <c r="H71" s="74">
+      <c r="H71" s="91">
         <v>48000</v>
       </c>
-      <c r="I71" s="74">
+      <c r="I71" s="91">
         <v>48000</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C72" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D72" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E72" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F72" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G72" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H72" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I72" s="68" t="s">
-        <v>137</v>
+        <v>72</v>
+      </c>
+      <c r="B72" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F72" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H72" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I72" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B73" s="83">
+        <v>125</v>
+      </c>
+      <c r="B73" s="80">
         <v>551000</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="79">
         <v>418000</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="79">
         <v>418000</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="79">
         <v>418000</v>
       </c>
-      <c r="F73" s="83">
+      <c r="F73" s="80">
         <f t="shared" ref="F73:F98" si="7">+B73*0.7</f>
         <v>385700</v>
       </c>
-      <c r="G73" s="83">
+      <c r="G73" s="80">
         <f t="shared" si="6"/>
         <v>330600</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H73" s="79">
         <v>209000</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I73" s="79">
         <v>209000</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="76" t="s">
-        <v>165</v>
-      </c>
-      <c r="B74" s="92">
+      <c r="A74" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" s="88">
         <v>132000</v>
       </c>
-      <c r="C74" s="72">
+      <c r="C74" s="89">
         <v>132000</v>
       </c>
-      <c r="D74" s="72">
+      <c r="D74" s="89">
         <v>132000</v>
       </c>
-      <c r="E74" s="73">
+      <c r="E74" s="90">
         <v>132000</v>
       </c>
-      <c r="F74" s="83">
+      <c r="F74" s="80">
         <f t="shared" si="7"/>
         <v>92400</v>
       </c>
-      <c r="G74" s="83">
+      <c r="G74" s="80">
         <f t="shared" si="6"/>
         <v>79200</v>
       </c>
-      <c r="H74" s="74">
+      <c r="H74" s="91">
         <v>75000</v>
       </c>
-      <c r="I74" s="74">
+      <c r="I74" s="91">
         <v>75000</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="B75" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C75" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D75" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E75" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F75" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G75" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H75" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I75" s="68" t="s">
-        <v>137</v>
+      <c r="A75" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D75" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E75" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F75" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G75" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H75" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I75" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="B76" s="83">
+      <c r="A76" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" s="80">
         <v>962000</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="79">
         <v>706000</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="79">
         <v>706000</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="79">
         <v>706000</v>
       </c>
-      <c r="F76" s="83">
+      <c r="F76" s="80">
         <f t="shared" si="7"/>
         <v>673400</v>
       </c>
-      <c r="G76" s="83">
+      <c r="G76" s="80">
         <f t="shared" si="6"/>
         <v>577200</v>
       </c>
-      <c r="H76" s="11">
+      <c r="H76" s="79">
         <v>464000</v>
       </c>
-      <c r="I76" s="11">
+      <c r="I76" s="79">
         <v>464000</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B77" s="92">
+        <v>161</v>
+      </c>
+      <c r="B77" s="88">
         <v>203000</v>
       </c>
-      <c r="C77" s="72">
+      <c r="C77" s="89">
         <v>203000</v>
       </c>
-      <c r="D77" s="72">
+      <c r="D77" s="89">
         <v>203000</v>
       </c>
-      <c r="E77" s="73">
+      <c r="E77" s="90">
         <v>203000</v>
       </c>
-      <c r="F77" s="83">
+      <c r="F77" s="80">
         <f t="shared" si="7"/>
         <v>142100</v>
       </c>
-      <c r="G77" s="83">
+      <c r="G77" s="80">
         <f t="shared" si="6"/>
         <v>121800</v>
       </c>
-      <c r="H77" s="74">
+      <c r="H77" s="91">
         <v>139000</v>
       </c>
-      <c r="I77" s="74">
+      <c r="I77" s="91">
         <v>139000</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C78" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D78" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F78" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G78" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H78" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I78" s="68" t="s">
-        <v>137</v>
+      <c r="A78" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D78" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E78" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G78" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H78" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I78" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B79" s="81">
+      <c r="A79" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" s="82">
         <v>176000</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="79">
         <v>176000</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="79">
         <v>176000</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="79">
         <v>176000</v>
       </c>
-      <c r="F79" s="83">
+      <c r="F79" s="80">
         <f t="shared" si="7"/>
         <v>123199.99999999999</v>
       </c>
-      <c r="G79" s="83">
+      <c r="G79" s="80">
         <f t="shared" si="6"/>
         <v>105600</v>
       </c>
-      <c r="H79" s="11">
+      <c r="H79" s="79">
         <v>176000</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I79" s="79">
         <v>176000</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80" s="81">
+      <c r="A80" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="82">
         <v>233000</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="79">
         <v>233000</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="79">
         <v>233000</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="79">
         <v>233000</v>
       </c>
-      <c r="F80" s="83">
+      <c r="F80" s="80">
         <f t="shared" si="7"/>
         <v>163100</v>
       </c>
-      <c r="G80" s="83">
+      <c r="G80" s="80">
         <f t="shared" si="6"/>
         <v>139800</v>
       </c>
-      <c r="H80" s="11">
+      <c r="H80" s="79">
         <v>233000</v>
       </c>
-      <c r="I80" s="11">
+      <c r="I80" s="79">
         <v>233000</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B81" s="81">
+        <v>159</v>
+      </c>
+      <c r="B81" s="82">
         <v>41000</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="79">
         <v>41000</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="79">
         <v>41000</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="79">
         <v>41000</v>
       </c>
-      <c r="F81" s="83">
+      <c r="F81" s="80">
         <f t="shared" si="7"/>
         <v>28699.999999999996</v>
       </c>
-      <c r="G81" s="83">
+      <c r="G81" s="80">
         <f t="shared" si="6"/>
         <v>24600</v>
       </c>
-      <c r="H81" s="11">
+      <c r="H81" s="79">
         <v>41000</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I81" s="79">
         <v>41000</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="81">
+      <c r="A82" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="82">
         <v>7700</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="79">
         <v>7700</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="79">
         <v>7700</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="79">
         <v>7700</v>
       </c>
-      <c r="F82" s="83">
+      <c r="F82" s="80">
         <f t="shared" si="7"/>
         <v>5390</v>
       </c>
-      <c r="G82" s="83">
+      <c r="G82" s="80">
         <f t="shared" si="6"/>
         <v>4620</v>
       </c>
-      <c r="H82" s="11">
+      <c r="H82" s="79">
         <v>7700</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="79">
         <v>7700</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="B83" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C83" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D83" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F83" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G83" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H83" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I83" s="68" t="s">
-        <v>137</v>
+      <c r="A83" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C83" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E83" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F83" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G83" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H83" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I83" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B84" s="87">
+      <c r="A84" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="93">
         <v>64600</v>
       </c>
-      <c r="C84" s="87"/>
-      <c r="D84" s="87"/>
-      <c r="E84" s="87"/>
-      <c r="F84" s="88"/>
-      <c r="G84" s="88"/>
-      <c r="H84" s="87"/>
-      <c r="I84" s="87"/>
+      <c r="C84" s="93"/>
+      <c r="D84" s="93"/>
+      <c r="E84" s="93"/>
+      <c r="F84" s="94"/>
+      <c r="G84" s="94"/>
+      <c r="H84" s="93"/>
+      <c r="I84" s="93"/>
     </row>
     <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="B85" s="78"/>
-      <c r="C85" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D85" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E85" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F85" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G85" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H85" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I85" s="68" t="s">
-        <v>137</v>
+      <c r="A85" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" s="95"/>
+      <c r="C85" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D85" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E85" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F85" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G85" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H85" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I85" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="B86" s="83">
+      <c r="A86" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="80">
         <v>97000</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="79">
         <v>57000</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="79">
         <v>57000</v>
       </c>
-      <c r="E86" s="11">
+      <c r="E86" s="79">
         <v>57000</v>
       </c>
-      <c r="F86" s="83">
+      <c r="F86" s="80">
         <f t="shared" si="7"/>
         <v>67900</v>
       </c>
-      <c r="G86" s="83">
+      <c r="G86" s="80">
         <f>+B86*0.6</f>
         <v>58200</v>
       </c>
-      <c r="H86" s="11">
+      <c r="H86" s="79">
         <v>23500</v>
       </c>
-      <c r="I86" s="11">
+      <c r="I86" s="79">
         <v>23500</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="B87" s="83">
+      <c r="A87" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87" s="80">
         <v>282000</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="79">
         <v>168000</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="79">
         <v>168000</v>
       </c>
-      <c r="E87" s="11">
+      <c r="E87" s="79">
         <v>168000</v>
       </c>
-      <c r="F87" s="83">
+      <c r="F87" s="80">
         <f t="shared" si="7"/>
         <v>197400</v>
       </c>
-      <c r="G87" s="83">
+      <c r="G87" s="80">
         <f>+B87*0.6</f>
         <v>169200</v>
       </c>
-      <c r="H87" s="11">
+      <c r="H87" s="79">
         <v>72000</v>
       </c>
-      <c r="I87" s="11">
+      <c r="I87" s="79">
         <v>72000</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="B88" s="83">
+      <c r="A88" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="B88" s="80">
         <v>256000</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="79">
         <v>140000</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="79">
         <v>140000</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="79">
         <v>140000</v>
       </c>
-      <c r="F88" s="83">
+      <c r="F88" s="80">
         <f t="shared" si="7"/>
         <v>179200</v>
       </c>
-      <c r="G88" s="83">
+      <c r="G88" s="80">
         <f t="shared" si="6"/>
         <v>153600</v>
       </c>
-      <c r="H88" s="11">
+      <c r="H88" s="79">
         <v>62000</v>
       </c>
-      <c r="I88" s="11">
+      <c r="I88" s="79">
         <v>62000</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="B89" s="83">
+      <c r="A89" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="80">
         <v>508000</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="79">
         <v>287000</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="79">
         <v>287000</v>
       </c>
-      <c r="E89" s="11">
+      <c r="E89" s="79">
         <v>287000</v>
       </c>
-      <c r="F89" s="83">
+      <c r="F89" s="80">
         <f t="shared" si="7"/>
         <v>355600</v>
       </c>
-      <c r="G89" s="83">
+      <c r="G89" s="80">
         <f t="shared" si="6"/>
         <v>304800</v>
       </c>
-      <c r="H89" s="11">
+      <c r="H89" s="79">
         <v>124000</v>
       </c>
-      <c r="I89" s="11">
+      <c r="I89" s="79">
         <v>1240000</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="47" t="s">
-        <v>163</v>
-      </c>
-      <c r="B90" s="83">
+      <c r="A90" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" s="80">
         <v>8200</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="79">
         <v>6200</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="79">
         <v>6200</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="79">
         <v>6200</v>
       </c>
-      <c r="F90" s="83">
+      <c r="F90" s="80">
         <f t="shared" si="7"/>
         <v>5740</v>
       </c>
-      <c r="G90" s="83">
+      <c r="G90" s="80">
         <f t="shared" si="6"/>
         <v>4920</v>
       </c>
-      <c r="H90" s="11">
+      <c r="H90" s="79">
         <v>2500</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I90" s="79">
         <v>2500</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B91" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C91" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D91" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E91" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F91" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G91" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H91" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I91" s="68" t="s">
-        <v>137</v>
+      <c r="A91" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C91" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E91" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F91" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H91" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I91" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="83">
+      <c r="A92" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B92" s="87"/>
+      <c r="C92" s="87"/>
+      <c r="D92" s="87"/>
+      <c r="E92" s="87"/>
+      <c r="F92" s="80">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G92" s="83">
+      <c r="G92" s="80">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
+      <c r="H92" s="87"/>
+      <c r="I92" s="87"/>
     </row>
     <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B93" s="83">
+      <c r="A93" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" s="80">
         <v>104000</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="79">
         <v>94000</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="79">
         <v>94000</v>
       </c>
-      <c r="E93" s="11">
+      <c r="E93" s="79">
         <v>94000</v>
       </c>
-      <c r="F93" s="83">
+      <c r="F93" s="80">
         <f t="shared" si="7"/>
         <v>72800</v>
       </c>
-      <c r="G93" s="83">
+      <c r="G93" s="80">
         <f t="shared" si="6"/>
         <v>62400</v>
       </c>
-      <c r="H93" s="11">
+      <c r="H93" s="79">
         <v>41600</v>
       </c>
-      <c r="I93" s="11">
+      <c r="I93" s="79">
         <v>41600</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B94" s="83">
+      <c r="A94" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" s="80">
         <v>144750</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="79">
         <v>106000</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="79">
         <v>106000</v>
       </c>
-      <c r="E94" s="11">
+      <c r="E94" s="79">
         <v>106000</v>
       </c>
-      <c r="F94" s="83">
+      <c r="F94" s="80">
         <f t="shared" si="7"/>
         <v>101325</v>
       </c>
-      <c r="G94" s="83">
+      <c r="G94" s="80">
         <f t="shared" si="6"/>
         <v>86850</v>
       </c>
-      <c r="H94" s="11">
+      <c r="H94" s="79">
         <v>57900</v>
       </c>
-      <c r="I94" s="11">
+      <c r="I94" s="79">
         <v>57900</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="C95" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D95" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E95" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F95" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G95" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H95" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I95" s="68" t="s">
-        <v>137</v>
+      <c r="A95" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="C95" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D95" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F95" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G95" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H95" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I95" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B96" s="89">
+      <c r="A96" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B96" s="80">
         <f>+E96/0.7</f>
         <v>13428.571428571429</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="79">
         <v>9400</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="79">
         <v>9400</v>
       </c>
-      <c r="E96" s="11">
+      <c r="E96" s="79">
         <v>9400</v>
       </c>
-      <c r="F96" s="89">
+      <c r="F96" s="80">
         <f t="shared" si="7"/>
         <v>9400</v>
       </c>
-      <c r="G96" s="89">
+      <c r="G96" s="80">
         <f t="shared" si="6"/>
         <v>8057.1428571428569</v>
       </c>
-      <c r="H96" s="90">
+      <c r="H96" s="94">
         <f>+B96*0.4</f>
         <v>5371.4285714285725</v>
       </c>
-      <c r="I96" s="11"/>
+      <c r="I96" s="79"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="B97" s="89">
+      <c r="A97" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B97" s="80">
         <f t="shared" ref="B97:B98" si="8">+E97/0.7</f>
         <v>19714.285714285714</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="79">
         <v>13800</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="79">
         <v>13800</v>
       </c>
-      <c r="E97" s="11">
+      <c r="E97" s="79">
         <v>13800</v>
       </c>
-      <c r="F97" s="83">
+      <c r="F97" s="80">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G97" s="89">
+      <c r="G97" s="80">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H97" s="90">
+      <c r="H97" s="94">
         <f t="shared" ref="H97:H98" si="9">+B97*0.4</f>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I97" s="11"/>
+      <c r="I97" s="79"/>
     </row>
     <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B98" s="89">
+      <c r="A98" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B98" s="80">
         <f t="shared" si="8"/>
         <v>19714.285714285714</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="79">
         <v>13800</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="79">
         <v>13800</v>
       </c>
-      <c r="E98" s="11">
+      <c r="E98" s="79">
         <v>13800</v>
       </c>
-      <c r="F98" s="83">
+      <c r="F98" s="80">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G98" s="89">
+      <c r="G98" s="80">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H98" s="90">
+      <c r="H98" s="94">
         <f t="shared" si="9"/>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I98" s="11"/>
+      <c r="I98" s="79"/>
     </row>
     <row r="99" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B99" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C99" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D99" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E99" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F99" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G99" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H99" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I99" s="68" t="s">
-        <v>137</v>
+      <c r="A99" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B99" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C99" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D99" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E99" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F99" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G99" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H99" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I99" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B100" s="83">
+      <c r="A100" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B100" s="80">
         <v>55600</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="79">
         <v>38700</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="79">
         <v>38700</v>
       </c>
-      <c r="E100" s="11">
+      <c r="E100" s="79">
         <v>38700</v>
       </c>
-      <c r="F100" s="83">
+      <c r="F100" s="80">
         <f>+B100*0.7</f>
         <v>38920</v>
       </c>
-      <c r="G100" s="83">
+      <c r="G100" s="80">
         <f>+B100*0.6</f>
         <v>33360</v>
       </c>
-      <c r="H100" s="11">
+      <c r="H100" s="79">
         <v>26800</v>
       </c>
-      <c r="I100" s="11">
+      <c r="I100" s="79">
         <v>26800</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B101" s="83">
+      <c r="A101" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="B101" s="80">
         <v>13900</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="79">
         <v>13900</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="79">
         <v>13900</v>
       </c>
-      <c r="E101" s="11">
+      <c r="E101" s="79">
         <v>13900</v>
       </c>
-      <c r="F101" s="83">
+      <c r="F101" s="80">
         <f>+B101*0.7</f>
         <v>9730</v>
       </c>
-      <c r="G101" s="83">
+      <c r="G101" s="80">
         <f>+B101*0.6</f>
         <v>8340</v>
       </c>
-      <c r="H101" s="91">
+      <c r="H101" s="96">
         <v>13900</v>
       </c>
-      <c r="I101" s="11">
+      <c r="I101" s="79">
         <v>13600</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="55" t="s">
+      <c r="A102" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B102" s="97"/>
+      <c r="C102" s="97"/>
+      <c r="D102" s="97"/>
+      <c r="E102" s="97"/>
+      <c r="F102" s="97"/>
+      <c r="G102" s="97"/>
+      <c r="H102" s="97"/>
+      <c r="I102" s="97"/>
+    </row>
+    <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B103" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C103" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D103" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E103" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F103" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G103" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H103" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I103" s="78" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="12"/>
-      <c r="G102" s="12"/>
-      <c r="H102" s="12"/>
-      <c r="I102" s="12"/>
-    </row>
-    <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="60" t="s">
-        <v>80</v>
-      </c>
-      <c r="B103" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C103" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D103" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E103" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F103" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G103" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H103" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I103" s="68" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B104" s="11">
+      <c r="B104" s="79">
         <v>88886</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="79">
         <v>44443</v>
       </c>
-      <c r="D104" s="11">
+      <c r="D104" s="79">
         <v>44443</v>
       </c>
-      <c r="E104" s="11">
+      <c r="E104" s="79">
         <v>44443</v>
       </c>
-      <c r="F104" s="83">
+      <c r="F104" s="80">
         <f>+B104*0.7</f>
         <v>62220.2</v>
       </c>
-      <c r="G104" s="83">
+      <c r="G104" s="80">
         <f>+B104*0.6</f>
         <v>53331.6</v>
       </c>
-      <c r="H104" s="11">
+      <c r="H104" s="79">
         <v>24647</v>
       </c>
-      <c r="I104" s="11">
+      <c r="I104" s="79">
         <v>24647</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B105" s="11">
+      <c r="A105" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B105" s="79">
         <v>103703</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="79">
         <v>51852</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="79">
         <v>51852</v>
       </c>
-      <c r="E105" s="11">
+      <c r="E105" s="79">
         <v>51852</v>
       </c>
-      <c r="F105" s="83">
+      <c r="F105" s="80">
         <f t="shared" ref="F105:F129" si="10">+B105*0.7</f>
         <v>72592.099999999991</v>
       </c>
-      <c r="G105" s="83">
+      <c r="G105" s="80">
         <f t="shared" ref="G105:G129" si="11">+B105*0.6</f>
         <v>62221.799999999996</v>
       </c>
-      <c r="H105" s="11">
+      <c r="H105" s="79">
         <v>28755</v>
       </c>
-      <c r="I105" s="11">
+      <c r="I105" s="79">
         <v>28755</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B106" s="11">
+      <c r="A106" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B106" s="79">
         <v>174729</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="79">
         <v>87365</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D106" s="79">
         <v>87365</v>
       </c>
-      <c r="E106" s="11">
+      <c r="E106" s="79">
         <v>87365</v>
       </c>
-      <c r="F106" s="83">
+      <c r="F106" s="80">
         <f t="shared" si="10"/>
         <v>122310.29999999999</v>
       </c>
-      <c r="G106" s="83">
+      <c r="G106" s="80">
         <f t="shared" si="11"/>
         <v>104837.4</v>
       </c>
-      <c r="H106" s="11">
+      <c r="H106" s="79">
         <v>48449</v>
       </c>
-      <c r="I106" s="11">
+      <c r="I106" s="79">
         <v>48449</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B107" s="11">
+      <c r="A107" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B107" s="79">
         <v>22223</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="79">
         <v>11112</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="79">
         <v>11112</v>
       </c>
-      <c r="E107" s="11">
+      <c r="E107" s="79">
         <v>11112</v>
       </c>
-      <c r="F107" s="83">
+      <c r="F107" s="80">
         <f t="shared" si="10"/>
         <v>15556.099999999999</v>
       </c>
-      <c r="G107" s="83">
+      <c r="G107" s="80">
         <f t="shared" si="11"/>
         <v>13333.8</v>
       </c>
-      <c r="H107" s="11">
+      <c r="H107" s="79">
         <v>6162</v>
       </c>
-      <c r="I107" s="11">
+      <c r="I107" s="79">
         <v>6162</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B108" s="11">
+      <c r="A108" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B108" s="79">
         <v>111110</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="79">
         <v>55555</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="79">
         <v>55555</v>
       </c>
-      <c r="E108" s="11">
+      <c r="E108" s="79">
         <v>55555</v>
       </c>
-      <c r="F108" s="83">
+      <c r="F108" s="80">
         <f t="shared" si="10"/>
         <v>77777</v>
       </c>
-      <c r="G108" s="83">
+      <c r="G108" s="80">
         <f t="shared" si="11"/>
         <v>66666</v>
       </c>
-      <c r="H108" s="11">
+      <c r="H108" s="79">
         <v>30809</v>
       </c>
-      <c r="I108" s="11">
+      <c r="I108" s="79">
         <v>30809</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="B109" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D109" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E109" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F109" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G109" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H109" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I109" s="68" t="s">
-        <v>137</v>
+      <c r="A109" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="B109" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C109" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D109" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E109" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F109" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G109" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H109" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I109" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B110" s="11">
+      <c r="A110" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B110" s="79">
         <v>312686</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="79">
         <v>156343</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="79">
         <v>156343</v>
       </c>
-      <c r="E110" s="11">
+      <c r="E110" s="79">
         <v>156343</v>
       </c>
-      <c r="F110" s="83">
+      <c r="F110" s="80">
         <f t="shared" si="10"/>
         <v>218880.19999999998</v>
       </c>
-      <c r="G110" s="83">
+      <c r="G110" s="80">
         <f t="shared" si="11"/>
         <v>187611.6</v>
       </c>
-      <c r="H110" s="11">
+      <c r="H110" s="79">
         <v>85421</v>
       </c>
-      <c r="I110" s="11">
+      <c r="I110" s="79">
         <v>85421</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B111" s="11">
+      <c r="A111" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B111" s="79">
         <v>349723</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="79">
         <v>174861</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="79">
         <v>174861</v>
       </c>
-      <c r="E111" s="11">
+      <c r="E111" s="79">
         <v>174861</v>
       </c>
-      <c r="F111" s="83">
+      <c r="F111" s="80">
         <f t="shared" si="10"/>
         <v>244806.09999999998</v>
       </c>
-      <c r="G111" s="83">
+      <c r="G111" s="80">
         <f t="shared" si="11"/>
         <v>209833.8</v>
       </c>
-      <c r="H111" s="11">
+      <c r="H111" s="79">
         <v>95539</v>
       </c>
-      <c r="I111" s="11">
+      <c r="I111" s="79">
         <v>95539</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B112" s="11">
+      <c r="A112" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B112" s="79">
         <v>446016</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="79">
         <v>223008</v>
       </c>
-      <c r="D112" s="11">
+      <c r="D112" s="79">
         <v>223008</v>
       </c>
-      <c r="E112" s="11">
+      <c r="E112" s="79">
         <v>223008</v>
       </c>
-      <c r="F112" s="83">
+      <c r="F112" s="80">
         <f t="shared" si="10"/>
         <v>312211.19999999995</v>
       </c>
-      <c r="G112" s="83">
+      <c r="G112" s="80">
         <f t="shared" si="11"/>
         <v>267609.59999999998</v>
       </c>
-      <c r="H112" s="11">
+      <c r="H112" s="79">
         <v>121845</v>
       </c>
-      <c r="I112" s="11">
+      <c r="I112" s="79">
         <v>121845</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="B113" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C113" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D113" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E113" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F113" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G113" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H113" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I113" s="68" t="s">
-        <v>137</v>
+      <c r="A113" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C113" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D113" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E113" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F113" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G113" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H113" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I113" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B114" s="11">
+      <c r="A114" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B114" s="79">
         <v>128763</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="79">
         <v>64381</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="79">
         <v>64381</v>
       </c>
-      <c r="E114" s="11">
+      <c r="E114" s="79">
         <v>64381</v>
       </c>
-      <c r="F114" s="83">
+      <c r="F114" s="80">
         <f t="shared" si="10"/>
         <v>90134.099999999991</v>
       </c>
-      <c r="G114" s="83">
+      <c r="G114" s="80">
         <f t="shared" si="11"/>
         <v>77257.8</v>
       </c>
-      <c r="H114" s="11">
+      <c r="H114" s="79">
         <v>35704</v>
       </c>
-      <c r="I114" s="11">
+      <c r="I114" s="79">
         <v>35704</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B115" s="11">
+      <c r="A115" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B115" s="79">
         <v>199762</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="79">
         <v>99881</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="79">
         <v>99881</v>
       </c>
-      <c r="E115" s="11">
+      <c r="E115" s="79">
         <v>99881</v>
       </c>
-      <c r="F115" s="83">
+      <c r="F115" s="80">
         <f t="shared" si="10"/>
         <v>139833.4</v>
       </c>
-      <c r="G115" s="83">
+      <c r="G115" s="80">
         <f t="shared" si="11"/>
         <v>119857.2</v>
       </c>
-      <c r="H115" s="11">
+      <c r="H115" s="79">
         <v>55391</v>
       </c>
-      <c r="I115" s="11">
+      <c r="I115" s="79">
         <v>55391</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="B116" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C116" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D116" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E116" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F116" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G116" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H116" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I116" s="68" t="s">
-        <v>137</v>
+      <c r="A116" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B116" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C116" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D116" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E116" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G116" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H116" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I116" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B117" s="11">
+      <c r="A117" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" s="79">
         <v>477701</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="79">
         <v>238851</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="79">
         <v>238851</v>
       </c>
-      <c r="E117" s="11">
+      <c r="E117" s="79">
         <v>238851</v>
       </c>
-      <c r="F117" s="83">
+      <c r="F117" s="80">
         <f t="shared" si="10"/>
         <v>334390.69999999995</v>
       </c>
-      <c r="G117" s="83">
+      <c r="G117" s="80">
         <f t="shared" si="11"/>
         <v>286620.59999999998</v>
       </c>
-      <c r="H117" s="11">
+      <c r="H117" s="79">
         <v>132458</v>
       </c>
-      <c r="I117" s="11">
+      <c r="I117" s="79">
         <v>132458</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="B118" s="11">
+      <c r="A118" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" s="79">
         <v>236516</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="79">
         <v>118258</v>
       </c>
-      <c r="D118" s="11">
+      <c r="D118" s="79">
         <v>118258</v>
       </c>
-      <c r="E118" s="11">
+      <c r="E118" s="79">
         <v>118258</v>
       </c>
-      <c r="F118" s="83">
+      <c r="F118" s="80">
         <f t="shared" si="10"/>
         <v>165561.19999999998</v>
       </c>
-      <c r="G118" s="83">
+      <c r="G118" s="80">
         <f t="shared" si="11"/>
         <v>141909.6</v>
       </c>
-      <c r="H118" s="11">
+      <c r="H118" s="79">
         <v>65582</v>
       </c>
-      <c r="I118" s="11">
+      <c r="I118" s="79">
         <v>65582</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B119" s="11">
+      <c r="A119" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B119" s="79">
         <v>274873</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="79">
         <v>137436</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="79">
         <v>137436</v>
       </c>
-      <c r="E119" s="11">
+      <c r="E119" s="79">
         <v>137436</v>
       </c>
-      <c r="F119" s="83">
+      <c r="F119" s="80">
         <f t="shared" si="10"/>
         <v>192411.09999999998</v>
       </c>
-      <c r="G119" s="83">
+      <c r="G119" s="80">
         <f t="shared" si="11"/>
         <v>164923.79999999999</v>
       </c>
-      <c r="H119" s="11">
+      <c r="H119" s="79">
         <v>76217</v>
       </c>
-      <c r="I119" s="11">
+      <c r="I119" s="79">
         <v>76217</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B120" s="11">
+      <c r="A120" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B120" s="79">
         <v>313203</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="79">
         <v>156601</v>
       </c>
-      <c r="D120" s="11">
+      <c r="D120" s="79">
         <v>156601</v>
       </c>
-      <c r="E120" s="11">
+      <c r="E120" s="79">
         <v>156601</v>
       </c>
-      <c r="F120" s="83">
+      <c r="F120" s="80">
         <f t="shared" si="10"/>
         <v>219242.09999999998</v>
       </c>
-      <c r="G120" s="83">
+      <c r="G120" s="80">
         <f t="shared" si="11"/>
         <v>187921.8</v>
       </c>
-      <c r="H120" s="11">
+      <c r="H120" s="79">
         <v>86846</v>
       </c>
-      <c r="I120" s="11">
+      <c r="I120" s="79">
         <v>86846</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="58" t="s">
-        <v>90</v>
-      </c>
-      <c r="B121" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C121" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D121" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E121" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F121" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G121" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H121" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I121" s="68" t="s">
-        <v>137</v>
+      <c r="A121" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C121" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D121" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E121" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F121" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G121" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H121" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I121" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B122" s="11">
+      <c r="A122" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B122" s="79">
         <v>139695</v>
       </c>
-      <c r="C122" s="11">
+      <c r="C122" s="79">
         <v>69848</v>
       </c>
-      <c r="D122" s="11">
+      <c r="D122" s="79">
         <v>69848</v>
       </c>
-      <c r="E122" s="11">
+      <c r="E122" s="79">
         <v>69848</v>
       </c>
-      <c r="F122" s="83">
+      <c r="F122" s="80">
         <f t="shared" si="10"/>
         <v>97786.5</v>
       </c>
-      <c r="G122" s="83">
+      <c r="G122" s="80">
         <f t="shared" si="11"/>
         <v>83817</v>
       </c>
-      <c r="H122" s="11">
+      <c r="H122" s="79">
         <v>38735</v>
       </c>
-      <c r="I122" s="11">
+      <c r="I122" s="79">
         <v>38735</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B123" s="11">
+      <c r="A123" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B123" s="79">
         <v>153373</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="79">
         <v>76687</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="79">
         <v>76687</v>
       </c>
-      <c r="E123" s="11">
+      <c r="E123" s="79">
         <v>76687</v>
       </c>
-      <c r="F123" s="83">
+      <c r="F123" s="80">
         <f t="shared" si="10"/>
         <v>107361.09999999999</v>
       </c>
-      <c r="G123" s="83">
+      <c r="G123" s="80">
         <f t="shared" si="11"/>
         <v>92023.8</v>
       </c>
-      <c r="H123" s="11">
+      <c r="H123" s="79">
         <v>42528</v>
       </c>
-      <c r="I123" s="11">
+      <c r="I123" s="79">
         <v>42528</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B124" s="11">
+      <c r="A124" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B124" s="79">
         <v>184044</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="79">
         <v>92022</v>
       </c>
-      <c r="D124" s="11">
+      <c r="D124" s="79">
         <v>92022</v>
       </c>
-      <c r="E124" s="11">
+      <c r="E124" s="79">
         <v>92022</v>
       </c>
-      <c r="F124" s="83">
+      <c r="F124" s="80">
         <f t="shared" si="10"/>
         <v>128830.79999999999</v>
       </c>
-      <c r="G124" s="83">
+      <c r="G124" s="80">
         <f t="shared" si="11"/>
         <v>110426.4</v>
       </c>
-      <c r="H124" s="11">
+      <c r="H124" s="79">
         <v>51032</v>
       </c>
-      <c r="I124" s="11">
+      <c r="I124" s="79">
         <v>51032</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B125" s="11">
+      <c r="A125" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B125" s="79">
         <v>49078</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="79">
         <v>24539</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="79">
         <v>24539</v>
       </c>
-      <c r="E125" s="11">
+      <c r="E125" s="79">
         <v>24539</v>
       </c>
-      <c r="F125" s="83">
+      <c r="F125" s="80">
         <f t="shared" si="10"/>
         <v>34354.6</v>
       </c>
-      <c r="G125" s="83">
+      <c r="G125" s="80">
         <f t="shared" si="11"/>
         <v>29446.799999999999</v>
       </c>
-      <c r="H125" s="11">
+      <c r="H125" s="79">
         <v>13608</v>
       </c>
-      <c r="I125" s="11">
+      <c r="I125" s="79">
         <v>13608</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="58" t="s">
+      <c r="A126" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="B126" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C126" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D126" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E126" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F126" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="B126" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C126" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D126" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E126" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F126" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G126" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H126" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I126" s="68" t="s">
-        <v>137</v>
+      <c r="G126" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H126" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I126" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B127" s="11">
+      <c r="A127" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B127" s="79">
         <v>661862</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="79">
         <v>330931</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="79">
         <v>330931</v>
       </c>
-      <c r="E127" s="11">
+      <c r="E127" s="79">
         <v>330931</v>
       </c>
-      <c r="F127" s="83">
+      <c r="F127" s="80">
         <f t="shared" si="10"/>
         <v>463303.39999999997</v>
       </c>
-      <c r="G127" s="83">
+      <c r="G127" s="80">
         <f t="shared" si="11"/>
         <v>397117.2</v>
       </c>
-      <c r="H127" s="11">
+      <c r="H127" s="79">
         <v>183523</v>
       </c>
-      <c r="I127" s="11">
+      <c r="I127" s="79">
         <v>183523</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B128" s="11">
+      <c r="A128" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B128" s="79">
         <v>692556</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="79">
         <v>346278</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D128" s="79">
         <v>346278</v>
       </c>
-      <c r="E128" s="11">
+      <c r="E128" s="79">
         <v>346278</v>
       </c>
-      <c r="F128" s="83">
+      <c r="F128" s="80">
         <f t="shared" si="10"/>
         <v>484789.19999999995</v>
       </c>
-      <c r="G128" s="83">
+      <c r="G128" s="80">
         <f t="shared" si="11"/>
         <v>415533.6</v>
       </c>
-      <c r="H128" s="11">
+      <c r="H128" s="79">
         <v>192034</v>
       </c>
-      <c r="I128" s="11">
+      <c r="I128" s="79">
         <v>192034</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="B129" s="11">
+      <c r="A129" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B129" s="79">
         <v>90078</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="79">
         <v>45039</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="79">
         <v>45039</v>
       </c>
-      <c r="E129" s="11">
+      <c r="E129" s="79">
         <v>45039</v>
       </c>
-      <c r="F129" s="83">
+      <c r="F129" s="80">
         <f t="shared" si="10"/>
         <v>63054.6</v>
       </c>
-      <c r="G129" s="83">
+      <c r="G129" s="80">
         <f t="shared" si="11"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="H129" s="11">
+      <c r="H129" s="79">
         <v>24977</v>
       </c>
-      <c r="I129" s="11">
+      <c r="I129" s="79">
         <v>24977</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A130" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B130" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C130" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D130" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E130" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="F130" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G130" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H130" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="I130" s="68" t="s">
-        <v>137</v>
+      <c r="A130" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="B130" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C130" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D130" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E130" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="F130" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G130" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H130" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="I130" s="78" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B131" s="86">
+        <v>48</v>
+      </c>
+      <c r="B131" s="79">
         <f>+G131/0.6</f>
         <v>157351.66666666669</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="79">
         <v>94411</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="79">
         <v>94411</v>
       </c>
-      <c r="E131" s="11">
+      <c r="E131" s="79">
         <v>94411</v>
       </c>
-      <c r="F131" s="86">
+      <c r="F131" s="79">
         <f>+B131*0.7</f>
         <v>110146.16666666667</v>
       </c>
-      <c r="G131" s="81">
+      <c r="G131" s="82">
         <f>+E131</f>
         <v>94411</v>
       </c>
-      <c r="H131" s="11"/>
-      <c r="I131" s="11"/>
+      <c r="H131" s="79"/>
+      <c r="I131" s="79"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B132" s="86">
+        <v>49</v>
+      </c>
+      <c r="B132" s="79">
         <f t="shared" ref="B132:B150" si="12">+G132/0.6</f>
         <v>78706.666666666672</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="79">
         <v>47224</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D132" s="79">
         <v>47224</v>
       </c>
-      <c r="E132" s="11">
+      <c r="E132" s="79">
         <v>47224</v>
       </c>
-      <c r="F132" s="86">
+      <c r="F132" s="79">
         <f t="shared" ref="F132:F151" si="13">+B132*0.7</f>
         <v>55094.666666666664</v>
       </c>
-      <c r="G132" s="81">
+      <c r="G132" s="82">
         <f t="shared" ref="G132:G150" si="14">+E132</f>
         <v>47224</v>
       </c>
-      <c r="H132" s="11"/>
-      <c r="I132" s="11"/>
+      <c r="H132" s="79"/>
+      <c r="I132" s="79"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B133" s="86">
+        <v>50</v>
+      </c>
+      <c r="B133" s="79">
         <f t="shared" si="12"/>
         <v>150468.33333333334</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="79">
         <v>90281</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="79">
         <v>90281</v>
       </c>
-      <c r="E133" s="11">
+      <c r="E133" s="79">
         <v>90281</v>
       </c>
-      <c r="F133" s="86">
+      <c r="F133" s="79">
         <f t="shared" si="13"/>
         <v>105327.83333333333</v>
       </c>
-      <c r="G133" s="81">
+      <c r="G133" s="82">
         <f t="shared" si="14"/>
         <v>90281</v>
       </c>
-      <c r="H133" s="11"/>
-      <c r="I133" s="11"/>
+      <c r="H133" s="79"/>
+      <c r="I133" s="79"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B134" s="86">
+        <v>51</v>
+      </c>
+      <c r="B134" s="79">
         <f t="shared" si="12"/>
         <v>141788.33333333334</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="79">
         <v>85073</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D134" s="79">
         <v>85073</v>
       </c>
-      <c r="E134" s="11">
+      <c r="E134" s="79">
         <v>85073</v>
       </c>
-      <c r="F134" s="86">
+      <c r="F134" s="79">
         <f t="shared" si="13"/>
         <v>99251.833333333328</v>
       </c>
-      <c r="G134" s="81">
+      <c r="G134" s="82">
         <f t="shared" si="14"/>
         <v>85073</v>
       </c>
-      <c r="H134" s="11"/>
-      <c r="I134" s="11"/>
+      <c r="H134" s="79"/>
+      <c r="I134" s="79"/>
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B135" s="86">
+        <v>52</v>
+      </c>
+      <c r="B135" s="79">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="79">
         <v>16783</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="79">
         <v>16783</v>
       </c>
-      <c r="E135" s="11">
+      <c r="E135" s="79">
         <v>16783</v>
       </c>
-      <c r="F135" s="86">
+      <c r="F135" s="79">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G135" s="81">
+      <c r="G135" s="82">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H135" s="11"/>
-      <c r="I135" s="11"/>
+      <c r="H135" s="79"/>
+      <c r="I135" s="79"/>
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B136" s="86">
+        <v>67</v>
+      </c>
+      <c r="B136" s="79">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="79">
         <v>16783</v>
       </c>
-      <c r="D136" s="11">
+      <c r="D136" s="79">
         <v>16783</v>
       </c>
-      <c r="E136" s="11">
+      <c r="E136" s="79">
         <v>16783</v>
       </c>
-      <c r="F136" s="86">
+      <c r="F136" s="79">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G136" s="81">
+      <c r="G136" s="82">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H136" s="11"/>
-      <c r="I136" s="11"/>
+      <c r="H136" s="79"/>
+      <c r="I136" s="79"/>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B137" s="86">
+        <v>65</v>
+      </c>
+      <c r="B137" s="79">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="79">
         <v>16783</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="79">
         <v>16783</v>
       </c>
-      <c r="E137" s="11">
+      <c r="E137" s="79">
         <v>16783</v>
       </c>
-      <c r="F137" s="86">
+      <c r="F137" s="79">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G137" s="81">
+      <c r="G137" s="82">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H137" s="11"/>
-      <c r="I137" s="11"/>
+      <c r="H137" s="79"/>
+      <c r="I137" s="79"/>
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B138" s="86">
+        <v>53</v>
+      </c>
+      <c r="B138" s="79">
         <f t="shared" si="12"/>
         <v>27198.333333333336</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="79">
         <v>16319</v>
       </c>
-      <c r="D138" s="11">
+      <c r="D138" s="79">
         <v>16319</v>
       </c>
-      <c r="E138" s="11">
+      <c r="E138" s="79">
         <v>16319</v>
       </c>
-      <c r="F138" s="86">
+      <c r="F138" s="79">
         <f t="shared" si="13"/>
         <v>19038.833333333332</v>
       </c>
-      <c r="G138" s="81">
+      <c r="G138" s="82">
         <f t="shared" si="14"/>
         <v>16319</v>
       </c>
-      <c r="H138" s="11"/>
-      <c r="I138" s="11"/>
+      <c r="H138" s="79"/>
+      <c r="I138" s="79"/>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B139" s="86">
+        <v>54</v>
+      </c>
+      <c r="B139" s="79">
         <f t="shared" si="12"/>
         <v>20146.666666666668</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="79">
         <v>12088</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="79">
         <v>12088</v>
       </c>
-      <c r="E139" s="11">
+      <c r="E139" s="79">
         <v>12088</v>
       </c>
-      <c r="F139" s="86">
+      <c r="F139" s="79">
         <f t="shared" si="13"/>
         <v>14102.666666666666</v>
       </c>
-      <c r="G139" s="81">
+      <c r="G139" s="82">
         <f t="shared" si="14"/>
         <v>12088</v>
       </c>
-      <c r="H139" s="11"/>
-      <c r="I139" s="11"/>
+      <c r="H139" s="79"/>
+      <c r="I139" s="79"/>
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B140" s="86">
+        <v>55</v>
+      </c>
+      <c r="B140" s="79">
         <f t="shared" si="12"/>
         <v>22550</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="79">
         <v>13530</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="79">
         <v>13530</v>
       </c>
-      <c r="E140" s="11">
+      <c r="E140" s="79">
         <v>13530</v>
       </c>
-      <c r="F140" s="86">
+      <c r="F140" s="79">
         <f t="shared" si="13"/>
         <v>15784.999999999998</v>
       </c>
-      <c r="G140" s="81">
+      <c r="G140" s="82">
         <f t="shared" si="14"/>
         <v>13530</v>
       </c>
-      <c r="H140" s="11"/>
-      <c r="I140" s="11"/>
+      <c r="H140" s="79"/>
+      <c r="I140" s="79"/>
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B141" s="86">
+        <v>69</v>
+      </c>
+      <c r="B141" s="79">
         <f t="shared" si="12"/>
         <v>22550</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="79">
         <v>13530</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="79">
         <v>13530</v>
       </c>
-      <c r="E141" s="11">
+      <c r="E141" s="79">
         <v>13530</v>
       </c>
-      <c r="F141" s="86">
+      <c r="F141" s="79">
         <f t="shared" si="13"/>
         <v>15784.999999999998</v>
       </c>
-      <c r="G141" s="81">
+      <c r="G141" s="82">
         <f t="shared" si="14"/>
         <v>13530</v>
       </c>
-      <c r="H141" s="11"/>
-      <c r="I141" s="11"/>
+      <c r="H141" s="79"/>
+      <c r="I141" s="79"/>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B142" s="86">
+        <v>56</v>
+      </c>
+      <c r="B142" s="79">
         <f t="shared" si="12"/>
         <v>33800</v>
       </c>
-      <c r="C142" s="11">
+      <c r="C142" s="79">
         <v>20280</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="79">
         <v>20280</v>
       </c>
-      <c r="E142" s="11">
+      <c r="E142" s="79">
         <v>20280</v>
       </c>
-      <c r="F142" s="86">
+      <c r="F142" s="79">
         <f t="shared" si="13"/>
         <v>23660</v>
       </c>
-      <c r="G142" s="81">
+      <c r="G142" s="82">
         <f t="shared" si="14"/>
         <v>20280</v>
       </c>
-      <c r="H142" s="11"/>
-      <c r="I142" s="11"/>
+      <c r="H142" s="79"/>
+      <c r="I142" s="79"/>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B143" s="86">
+        <v>57</v>
+      </c>
+      <c r="B143" s="79">
         <f t="shared" si="12"/>
         <v>28428.333333333336</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="79">
         <v>17057</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="79">
         <v>17057</v>
       </c>
-      <c r="E143" s="11">
+      <c r="E143" s="79">
         <v>17057</v>
       </c>
-      <c r="F143" s="86">
+      <c r="F143" s="79">
         <f t="shared" si="13"/>
         <v>19899.833333333332</v>
       </c>
-      <c r="G143" s="81">
+      <c r="G143" s="82">
         <f t="shared" si="14"/>
         <v>17057</v>
       </c>
-      <c r="H143" s="11"/>
-      <c r="I143" s="11"/>
+      <c r="H143" s="79"/>
+      <c r="I143" s="79"/>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B144" s="86">
+        <v>58</v>
+      </c>
+      <c r="B144" s="79">
         <f t="shared" si="12"/>
         <v>26893.333333333336</v>
       </c>
-      <c r="C144" s="11">
+      <c r="C144" s="79">
         <v>16136</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="79">
         <v>16136</v>
       </c>
-      <c r="E144" s="11">
+      <c r="E144" s="79">
         <v>16136</v>
       </c>
-      <c r="F144" s="86">
+      <c r="F144" s="79">
         <f t="shared" si="13"/>
         <v>18825.333333333332</v>
       </c>
-      <c r="G144" s="81">
+      <c r="G144" s="82">
         <f t="shared" si="14"/>
         <v>16136</v>
       </c>
-      <c r="H144" s="11"/>
-      <c r="I144" s="11"/>
-    </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H144" s="79"/>
+      <c r="I144" s="79"/>
+    </row>
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B145" s="86">
+        <v>59</v>
+      </c>
+      <c r="B145" s="79">
         <f t="shared" si="12"/>
         <v>26893.333333333336</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="79">
         <v>16136</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="79">
         <v>16136</v>
       </c>
-      <c r="E145" s="11">
+      <c r="E145" s="79">
         <v>16136</v>
       </c>
-      <c r="F145" s="86">
+      <c r="F145" s="79">
         <f t="shared" si="13"/>
         <v>18825.333333333332</v>
       </c>
-      <c r="G145" s="81">
+      <c r="G145" s="82">
         <f t="shared" si="14"/>
         <v>16136</v>
       </c>
-      <c r="H145" s="11"/>
-      <c r="I145" s="11"/>
-    </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H145" s="79"/>
+      <c r="I145" s="79"/>
+    </row>
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B146" s="86">
+        <v>60</v>
+      </c>
+      <c r="B146" s="79">
         <f t="shared" si="12"/>
         <v>27198.333333333336</v>
       </c>
-      <c r="C146" s="11">
+      <c r="C146" s="79">
         <v>16319</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="79">
         <v>16319</v>
       </c>
-      <c r="E146" s="11">
+      <c r="E146" s="79">
         <v>16319</v>
       </c>
-      <c r="F146" s="86">
+      <c r="F146" s="79">
         <f t="shared" si="13"/>
         <v>19038.833333333332</v>
       </c>
-      <c r="G146" s="81">
+      <c r="G146" s="82">
         <f t="shared" si="14"/>
         <v>16319</v>
       </c>
-      <c r="H146" s="11"/>
-      <c r="I146" s="11"/>
-    </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H146" s="79"/>
+      <c r="I146" s="79"/>
+    </row>
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B147" s="86">
+        <v>61</v>
+      </c>
+      <c r="B147" s="79">
         <f t="shared" si="12"/>
         <v>32386.666666666668</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="79">
         <v>19432</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="79">
         <v>19432</v>
       </c>
-      <c r="E147" s="11">
+      <c r="E147" s="79">
         <v>19432</v>
       </c>
-      <c r="F147" s="86">
+      <c r="F147" s="79">
         <f t="shared" si="13"/>
         <v>22670.666666666668</v>
       </c>
-      <c r="G147" s="81">
+      <c r="G147" s="82">
         <f t="shared" si="14"/>
         <v>19432</v>
       </c>
-      <c r="H147" s="11"/>
-      <c r="I147" s="11"/>
-    </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H147" s="79"/>
+      <c r="I147" s="79"/>
+    </row>
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B148" s="86">
+        <v>62</v>
+      </c>
+      <c r="B148" s="79">
         <f t="shared" si="12"/>
         <v>23586.666666666668</v>
       </c>
-      <c r="C148" s="11">
+      <c r="C148" s="79">
         <v>14152</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="79">
         <v>14152</v>
       </c>
-      <c r="E148" s="11">
+      <c r="E148" s="79">
         <v>14152</v>
       </c>
-      <c r="F148" s="86">
+      <c r="F148" s="79">
         <f t="shared" si="13"/>
         <v>16510.666666666668</v>
       </c>
-      <c r="G148" s="81">
+      <c r="G148" s="82">
         <f t="shared" si="14"/>
         <v>14152</v>
       </c>
-      <c r="H148" s="11"/>
-      <c r="I148" s="11"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H148" s="79"/>
+      <c r="I148" s="79"/>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B149" s="86">
+        <v>63</v>
+      </c>
+      <c r="B149" s="79">
         <f t="shared" si="12"/>
         <v>57160</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="79">
         <v>34296</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="79">
         <v>34296</v>
       </c>
-      <c r="E149" s="11">
+      <c r="E149" s="79">
         <v>34296</v>
       </c>
-      <c r="F149" s="86">
+      <c r="F149" s="79">
         <f t="shared" si="13"/>
         <v>40012</v>
       </c>
-      <c r="G149" s="81">
+      <c r="G149" s="82">
         <f t="shared" si="14"/>
         <v>34296</v>
       </c>
-      <c r="H149" s="11"/>
-      <c r="I149" s="11"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H149" s="79"/>
+      <c r="I149" s="79"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B150" s="86">
+        <v>64</v>
+      </c>
+      <c r="B150" s="79">
         <f t="shared" si="12"/>
         <v>61121.666666666672</v>
       </c>
-      <c r="C150" s="11">
+      <c r="C150" s="79">
         <v>36673</v>
       </c>
-      <c r="D150" s="11">
+      <c r="D150" s="79">
         <v>36673</v>
       </c>
-      <c r="E150" s="11">
+      <c r="E150" s="79">
         <v>36673</v>
       </c>
-      <c r="F150" s="86">
+      <c r="F150" s="79">
         <f t="shared" si="13"/>
         <v>42785.166666666664</v>
       </c>
-      <c r="G150" s="81">
+      <c r="G150" s="82">
         <f t="shared" si="14"/>
         <v>36673</v>
       </c>
-      <c r="H150" s="11"/>
-      <c r="I150" s="11"/>
-    </row>
-    <row r="151" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H150" s="79"/>
+      <c r="I150" s="79"/>
+    </row>
+    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B151" s="11">
+        <v>66</v>
+      </c>
+      <c r="B151" s="79">
         <v>70000</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="79">
         <v>40000</v>
       </c>
-      <c r="D151" s="11">
+      <c r="D151" s="79">
         <v>40000</v>
       </c>
-      <c r="E151" s="11">
+      <c r="E151" s="79">
         <v>40000</v>
       </c>
-      <c r="F151" s="86">
+      <c r="F151" s="79">
         <f t="shared" si="13"/>
         <v>49000</v>
       </c>
-      <c r="G151" s="81">
+      <c r="G151" s="82">
         <f>+B151*0.6</f>
         <v>42000</v>
       </c>
-      <c r="H151" s="11">
+      <c r="H151" s="79">
         <v>20000</v>
       </c>
-      <c r="I151" s="11">
+      <c r="I151" s="79">
         <v>20000</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="64" t="s">
+    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B152" s="99"/>
@@ -8727,320 +8928,1940 @@
       <c r="H152" s="99"/>
       <c r="I152" s="99"/>
     </row>
-    <row r="153" spans="1:9" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="62" t="s">
+    <row r="153" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A153" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B153" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C153" s="93" t="s">
-        <v>134</v>
-      </c>
-      <c r="D153" s="93" t="s">
-        <v>135</v>
-      </c>
-      <c r="E153" s="93" t="s">
+      <c r="B153" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C153" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="D153" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="E153" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="F153" s="100" t="s">
+        <v>98</v>
+      </c>
+      <c r="G153" s="100" t="s">
+        <v>99</v>
+      </c>
+      <c r="H153" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="I153" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="K153" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="L153" s="82">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A154" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B154" s="100"/>
+      <c r="C154" s="100"/>
+      <c r="D154" s="100"/>
+      <c r="E154" s="100"/>
+      <c r="F154" s="100"/>
+      <c r="G154" s="100">
+        <f>+$L$153</f>
+        <v>12000</v>
+      </c>
+      <c r="H154" s="100">
+        <f t="shared" ref="H154:I154" si="15">+$L$153</f>
+        <v>12000</v>
+      </c>
+      <c r="I154" s="100">
+        <f t="shared" si="15"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="B155" s="100"/>
+      <c r="C155" s="100"/>
+      <c r="D155" s="100"/>
+      <c r="E155" s="100"/>
+      <c r="F155" s="100"/>
+      <c r="G155" s="101">
+        <v>25000</v>
+      </c>
+      <c r="H155" s="100">
+        <f>+G155</f>
+        <v>25000</v>
+      </c>
+      <c r="I155" s="100">
+        <f>+G155</f>
+        <v>25000</v>
+      </c>
+      <c r="K155" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="F153" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="G153" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="H153" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="I153" s="93" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="36" t="s">
+      <c r="L155" s="82">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B156" s="100"/>
+      <c r="C156" s="100"/>
+      <c r="D156" s="100"/>
+      <c r="E156" s="100"/>
+      <c r="F156" s="100"/>
+      <c r="G156" s="100">
+        <f>+$L$155</f>
+        <v>22000</v>
+      </c>
+      <c r="H156" s="100">
+        <f t="shared" ref="H156:I167" si="16">+$L$155</f>
+        <v>22000</v>
+      </c>
+      <c r="I156" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A157" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B157" s="100"/>
+      <c r="C157" s="100"/>
+      <c r="D157" s="100"/>
+      <c r="E157" s="100"/>
+      <c r="F157" s="100"/>
+      <c r="G157" s="100">
+        <f t="shared" ref="G157:G167" si="17">+$L$155</f>
+        <v>22000</v>
+      </c>
+      <c r="H157" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I157" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A158" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="B158" s="100"/>
+      <c r="C158" s="100"/>
+      <c r="D158" s="100"/>
+      <c r="E158" s="100"/>
+      <c r="F158" s="100"/>
+      <c r="G158" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H158" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I158" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A159" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="B159" s="100"/>
+      <c r="C159" s="100"/>
+      <c r="D159" s="100"/>
+      <c r="E159" s="100"/>
+      <c r="F159" s="100"/>
+      <c r="G159" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H159" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I159" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B160" s="100"/>
+      <c r="C160" s="100"/>
+      <c r="D160" s="100"/>
+      <c r="E160" s="100"/>
+      <c r="F160" s="100"/>
+      <c r="G160" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H160" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I160" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="B161" s="100"/>
+      <c r="C161" s="100"/>
+      <c r="D161" s="100"/>
+      <c r="E161" s="100"/>
+      <c r="F161" s="100"/>
+      <c r="G161" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H161" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I161" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A162" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="B162" s="100"/>
+      <c r="C162" s="100"/>
+      <c r="D162" s="100"/>
+      <c r="E162" s="100"/>
+      <c r="F162" s="100"/>
+      <c r="G162" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H162" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I162" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B163" s="100"/>
+      <c r="C163" s="100"/>
+      <c r="D163" s="100"/>
+      <c r="E163" s="100"/>
+      <c r="F163" s="100"/>
+      <c r="G163" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H163" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I163" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A164" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B164" s="100"/>
+      <c r="C164" s="100"/>
+      <c r="D164" s="100"/>
+      <c r="E164" s="100"/>
+      <c r="F164" s="100"/>
+      <c r="G164" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H164" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I164" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A165" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B165" s="100"/>
+      <c r="C165" s="100"/>
+      <c r="D165" s="100"/>
+      <c r="E165" s="100"/>
+      <c r="F165" s="100"/>
+      <c r="G165" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H165" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I165" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A166" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B166" s="100"/>
+      <c r="C166" s="100"/>
+      <c r="D166" s="100"/>
+      <c r="E166" s="100"/>
+      <c r="F166" s="100"/>
+      <c r="G166" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H166" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I166" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B167" s="100"/>
+      <c r="C167" s="100"/>
+      <c r="D167" s="100"/>
+      <c r="E167" s="100"/>
+      <c r="F167" s="100"/>
+      <c r="G167" s="100">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="H167" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I167" s="100">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B168" s="100"/>
+      <c r="C168" s="100"/>
+      <c r="D168" s="100"/>
+      <c r="E168" s="100"/>
+      <c r="F168" s="100"/>
+      <c r="G168" s="101">
+        <v>32000</v>
+      </c>
+      <c r="H168" s="101">
+        <f t="shared" ref="H168:H169" si="18">+H167</f>
+        <v>22000</v>
+      </c>
+      <c r="I168" s="100"/>
+    </row>
+    <row r="169" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B169" s="100"/>
+      <c r="C169" s="100"/>
+      <c r="D169" s="100"/>
+      <c r="E169" s="100"/>
+      <c r="F169" s="100"/>
+      <c r="G169" s="101">
+        <v>32000</v>
+      </c>
+      <c r="H169" s="101">
+        <f t="shared" si="18"/>
+        <v>22000</v>
+      </c>
+      <c r="I169" s="100"/>
+    </row>
+    <row r="170" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="59" t="s">
+        <v>179</v>
+      </c>
+      <c r="B170" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C170" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D170" s="102" t="s">
+        <v>131</v>
+      </c>
+      <c r="E170" s="103" t="s">
+        <v>136</v>
+      </c>
+      <c r="F170" s="104" t="s">
+        <v>98</v>
+      </c>
+      <c r="G170" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="H170" s="105" t="s">
+        <v>100</v>
+      </c>
+      <c r="I170" s="105" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B171" s="84"/>
+      <c r="C171" s="84"/>
+      <c r="D171" s="84"/>
+      <c r="E171" s="84"/>
+      <c r="F171" s="84"/>
+      <c r="G171" s="82">
+        <v>24000</v>
+      </c>
+      <c r="H171" s="84">
+        <f>+G171</f>
+        <v>24000</v>
+      </c>
+      <c r="I171" s="84">
+        <f>+G171</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B172" s="84"/>
+      <c r="C172" s="84"/>
+      <c r="D172" s="84"/>
+      <c r="E172" s="84"/>
+      <c r="F172" s="84"/>
+      <c r="G172" s="84"/>
+      <c r="H172" s="84">
+        <f t="shared" ref="H172:I215" si="19">+G172</f>
+        <v>0</v>
+      </c>
+      <c r="I172" s="84">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" s="71" t="s">
+        <v>168</v>
+      </c>
+      <c r="B173" s="106"/>
+      <c r="C173" s="106"/>
+      <c r="D173" s="106"/>
+      <c r="E173" s="106"/>
+      <c r="F173" s="106"/>
+      <c r="G173" s="107">
+        <f>$L$173</f>
+        <v>16640</v>
+      </c>
+      <c r="H173" s="107">
+        <f t="shared" ref="H173:I173" si="20">$L$173</f>
+        <v>16640</v>
+      </c>
+      <c r="I173" s="107">
+        <f t="shared" si="20"/>
+        <v>16640</v>
+      </c>
+      <c r="K173" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="L173" s="82">
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" s="71" t="s">
+        <v>167</v>
+      </c>
+      <c r="B174" s="106"/>
+      <c r="C174" s="106"/>
+      <c r="D174" s="106"/>
+      <c r="E174" s="106"/>
+      <c r="F174" s="106"/>
+      <c r="G174" s="107">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H174" s="107">
+        <f t="shared" ref="H174:I174" si="21">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I174" s="107">
+        <f t="shared" si="21"/>
+        <v>9600</v>
+      </c>
+      <c r="K174" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="L174" s="82">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" s="108"/>
+      <c r="C175" s="108"/>
+      <c r="D175" s="108"/>
+      <c r="E175" s="108"/>
+      <c r="F175" s="108"/>
+      <c r="G175" s="108">
+        <f t="shared" ref="G175:I175" si="22">$L$173</f>
+        <v>16640</v>
+      </c>
+      <c r="H175" s="108">
+        <f t="shared" si="22"/>
+        <v>16640</v>
+      </c>
+      <c r="I175" s="108">
+        <f t="shared" si="22"/>
+        <v>16640</v>
+      </c>
+      <c r="L175" s="73"/>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B176" s="108"/>
+      <c r="C176" s="108"/>
+      <c r="D176" s="108"/>
+      <c r="E176" s="108"/>
+      <c r="F176" s="108"/>
+      <c r="G176" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H176" s="108">
+        <f t="shared" ref="H176:I176" si="23">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I176" s="108">
+        <f t="shared" si="23"/>
+        <v>9600</v>
+      </c>
+      <c r="K176" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="L176" s="82">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B177" s="108"/>
+      <c r="C177" s="108"/>
+      <c r="D177" s="108"/>
+      <c r="E177" s="108"/>
+      <c r="F177" s="108"/>
+      <c r="G177" s="108">
+        <f>$L$173</f>
+        <v>16640</v>
+      </c>
+      <c r="H177" s="108">
+        <f t="shared" ref="H177:I177" si="24">$L$173</f>
+        <v>16640</v>
+      </c>
+      <c r="I177" s="108">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B178" s="108"/>
+      <c r="C178" s="108"/>
+      <c r="D178" s="108"/>
+      <c r="E178" s="108"/>
+      <c r="F178" s="108"/>
+      <c r="G178" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H178" s="108">
+        <f t="shared" ref="H178:I178" si="25">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I178" s="108">
+        <f t="shared" si="25"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="108"/>
+      <c r="C179" s="108"/>
+      <c r="D179" s="108"/>
+      <c r="E179" s="108"/>
+      <c r="F179" s="108"/>
+      <c r="G179" s="108">
+        <f t="shared" ref="G179:I187" si="26">$L$173</f>
+        <v>16640</v>
+      </c>
+      <c r="H179" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="I179" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B180" s="108"/>
+      <c r="C180" s="108"/>
+      <c r="D180" s="108"/>
+      <c r="E180" s="108"/>
+      <c r="F180" s="108"/>
+      <c r="G180" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H180" s="108">
+        <f t="shared" ref="H180:I180" si="27">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I180" s="108">
+        <f t="shared" si="27"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B181" s="108"/>
+      <c r="C181" s="108"/>
+      <c r="D181" s="108"/>
+      <c r="E181" s="108"/>
+      <c r="F181" s="108"/>
+      <c r="G181" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="H181" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="I181" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B182" s="108"/>
+      <c r="C182" s="108"/>
+      <c r="D182" s="108"/>
+      <c r="E182" s="108"/>
+      <c r="F182" s="108"/>
+      <c r="G182" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H182" s="108">
+        <f t="shared" ref="H182:I182" si="28">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I182" s="108">
+        <f t="shared" si="28"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183" s="108"/>
+      <c r="C183" s="108"/>
+      <c r="D183" s="108"/>
+      <c r="E183" s="108"/>
+      <c r="F183" s="108"/>
+      <c r="G183" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="H183" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="I183" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B184" s="108"/>
+      <c r="C184" s="108"/>
+      <c r="D184" s="108"/>
+      <c r="E184" s="108"/>
+      <c r="F184" s="108"/>
+      <c r="G184" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H184" s="108">
+        <f t="shared" ref="H184:I184" si="29">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I184" s="108">
+        <f t="shared" si="29"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" s="108"/>
+      <c r="C185" s="108"/>
+      <c r="D185" s="108"/>
+      <c r="E185" s="108"/>
+      <c r="F185" s="108"/>
+      <c r="G185" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="H185" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="I185" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B186" s="108"/>
+      <c r="C186" s="108"/>
+      <c r="D186" s="108"/>
+      <c r="E186" s="108"/>
+      <c r="F186" s="108"/>
+      <c r="G186" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H186" s="108">
+        <f t="shared" ref="H186:I186" si="30">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I186" s="108">
+        <f t="shared" si="30"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B187" s="108"/>
+      <c r="C187" s="108"/>
+      <c r="D187" s="108"/>
+      <c r="E187" s="108"/>
+      <c r="F187" s="108"/>
+      <c r="G187" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="H187" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+      <c r="I187" s="108">
+        <f t="shared" si="26"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B188" s="108"/>
+      <c r="C188" s="108"/>
+      <c r="D188" s="108"/>
+      <c r="E188" s="108"/>
+      <c r="F188" s="108"/>
+      <c r="G188" s="108">
+        <f>$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="H188" s="108">
+        <f t="shared" ref="H188:I188" si="31">$L$174</f>
+        <v>9600</v>
+      </c>
+      <c r="I188" s="108">
+        <f t="shared" si="31"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B189" s="108"/>
+      <c r="C189" s="108"/>
+      <c r="D189" s="108"/>
+      <c r="E189" s="108"/>
+      <c r="F189" s="108"/>
+      <c r="G189" s="109">
+        <v>36000</v>
+      </c>
+      <c r="H189" s="108">
+        <f t="shared" si="19"/>
+        <v>36000</v>
+      </c>
+      <c r="I189" s="108">
+        <f>+G189</f>
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B190" s="108"/>
+      <c r="C190" s="108"/>
+      <c r="D190" s="108"/>
+      <c r="E190" s="108"/>
+      <c r="F190" s="108"/>
+      <c r="G190" s="108">
+        <f>$L$176</f>
+        <v>32000</v>
+      </c>
+      <c r="H190" s="108">
+        <f t="shared" ref="H190:I190" si="32">$L$176</f>
+        <v>32000</v>
+      </c>
+      <c r="I190" s="108">
+        <f t="shared" si="32"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B191" s="108"/>
+      <c r="C191" s="108"/>
+      <c r="D191" s="108"/>
+      <c r="E191" s="108"/>
+      <c r="F191" s="108"/>
+      <c r="G191" s="108">
+        <f t="shared" ref="G191:I208" si="33">$L$176</f>
+        <v>32000</v>
+      </c>
+      <c r="H191" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I191" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B192" s="108"/>
+      <c r="C192" s="108"/>
+      <c r="D192" s="108"/>
+      <c r="E192" s="108"/>
+      <c r="F192" s="108"/>
+      <c r="G192" s="108">
+        <f>$L$176</f>
+        <v>32000</v>
+      </c>
+      <c r="H192" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I192" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B193" s="108"/>
+      <c r="C193" s="108"/>
+      <c r="D193" s="108"/>
+      <c r="E193" s="108"/>
+      <c r="F193" s="108"/>
+      <c r="G193" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H193" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I193" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B194" s="108"/>
+      <c r="C194" s="108"/>
+      <c r="D194" s="108"/>
+      <c r="E194" s="108"/>
+      <c r="F194" s="108"/>
+      <c r="G194" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H194" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I194" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B195" s="108"/>
+      <c r="C195" s="108"/>
+      <c r="D195" s="108"/>
+      <c r="E195" s="108"/>
+      <c r="F195" s="108"/>
+      <c r="G195" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H195" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I195" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B196" s="108"/>
+      <c r="C196" s="108"/>
+      <c r="D196" s="108"/>
+      <c r="E196" s="108"/>
+      <c r="F196" s="108"/>
+      <c r="G196" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H196" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I196" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B197" s="108"/>
+      <c r="C197" s="108"/>
+      <c r="D197" s="108"/>
+      <c r="E197" s="108"/>
+      <c r="F197" s="108"/>
+      <c r="G197" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H197" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I197" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B198" s="108"/>
+      <c r="C198" s="108"/>
+      <c r="D198" s="108"/>
+      <c r="E198" s="108"/>
+      <c r="F198" s="108"/>
+      <c r="G198" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H198" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I198" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="B199" s="108"/>
+      <c r="C199" s="108"/>
+      <c r="D199" s="108"/>
+      <c r="E199" s="108"/>
+      <c r="F199" s="108"/>
+      <c r="G199" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H199" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I199" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B200" s="108"/>
+      <c r="C200" s="108"/>
+      <c r="D200" s="108"/>
+      <c r="E200" s="108"/>
+      <c r="F200" s="108"/>
+      <c r="G200" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H200" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I200" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B201" s="108"/>
+      <c r="C201" s="108"/>
+      <c r="D201" s="108"/>
+      <c r="E201" s="108"/>
+      <c r="F201" s="108"/>
+      <c r="G201" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H201" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I201" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="B202" s="108"/>
+      <c r="C202" s="108"/>
+      <c r="D202" s="108"/>
+      <c r="E202" s="108"/>
+      <c r="F202" s="108"/>
+      <c r="G202" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H202" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I202" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B203" s="108"/>
+      <c r="C203" s="108"/>
+      <c r="D203" s="108"/>
+      <c r="E203" s="108"/>
+      <c r="F203" s="108"/>
+      <c r="G203" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H203" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I203" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B204" s="108"/>
+      <c r="C204" s="108"/>
+      <c r="D204" s="108"/>
+      <c r="E204" s="108"/>
+      <c r="F204" s="108"/>
+      <c r="G204" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H204" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I204" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="B205" s="108"/>
+      <c r="C205" s="108"/>
+      <c r="D205" s="108"/>
+      <c r="E205" s="108"/>
+      <c r="F205" s="108"/>
+      <c r="G205" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H205" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I205" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="70" t="s">
+        <v>200</v>
+      </c>
+      <c r="B206" s="108"/>
+      <c r="C206" s="108"/>
+      <c r="D206" s="108"/>
+      <c r="E206" s="108"/>
+      <c r="F206" s="108"/>
+      <c r="G206" s="109">
+        <v>35000</v>
+      </c>
+      <c r="H206" s="108">
+        <f>+G206</f>
+        <v>35000</v>
+      </c>
+      <c r="I206" s="108">
+        <f>+G206</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B207" s="108"/>
+      <c r="C207" s="108"/>
+      <c r="D207" s="108"/>
+      <c r="E207" s="108"/>
+      <c r="F207" s="108"/>
+      <c r="G207" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H207" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I207" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="B208" s="108"/>
+      <c r="C208" s="108"/>
+      <c r="D208" s="108"/>
+      <c r="E208" s="108"/>
+      <c r="F208" s="108"/>
+      <c r="G208" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="H208" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+      <c r="I208" s="108">
+        <f t="shared" si="33"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="B209" s="108"/>
+      <c r="C209" s="108"/>
+      <c r="D209" s="108"/>
+      <c r="E209" s="108"/>
+      <c r="F209" s="108"/>
+      <c r="G209" s="108">
+        <f t="shared" ref="G209:I210" si="34">$L$176</f>
+        <v>32000</v>
+      </c>
+      <c r="H209" s="108">
+        <f t="shared" si="34"/>
+        <v>32000</v>
+      </c>
+      <c r="I209" s="108">
+        <f t="shared" si="34"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B210" s="108"/>
+      <c r="C210" s="108"/>
+      <c r="D210" s="108"/>
+      <c r="E210" s="108"/>
+      <c r="F210" s="108"/>
+      <c r="G210" s="108">
+        <f t="shared" si="34"/>
+        <v>32000</v>
+      </c>
+      <c r="H210" s="108">
+        <f t="shared" si="34"/>
+        <v>32000</v>
+      </c>
+      <c r="I210" s="108">
+        <f t="shared" si="34"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B211" s="108"/>
+      <c r="C211" s="108"/>
+      <c r="D211" s="108"/>
+      <c r="E211" s="108"/>
+      <c r="F211" s="108"/>
+      <c r="G211" s="108">
+        <v>78000</v>
+      </c>
+      <c r="H211" s="108">
+        <f t="shared" si="19"/>
+        <v>78000</v>
+      </c>
+      <c r="I211" s="108">
+        <f t="shared" si="19"/>
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B212" s="108"/>
+      <c r="C212" s="108"/>
+      <c r="D212" s="108"/>
+      <c r="E212" s="108"/>
+      <c r="F212" s="108"/>
+      <c r="G212" s="108">
+        <v>60000</v>
+      </c>
+      <c r="H212" s="108">
+        <f t="shared" si="19"/>
+        <v>60000</v>
+      </c>
+      <c r="I212" s="108">
+        <f t="shared" si="19"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="B213" s="108"/>
+      <c r="C213" s="108"/>
+      <c r="D213" s="108"/>
+      <c r="E213" s="108"/>
+      <c r="F213" s="108"/>
+      <c r="G213" s="109">
+        <v>100000</v>
+      </c>
+      <c r="H213" s="108">
+        <f t="shared" si="19"/>
+        <v>100000</v>
+      </c>
+      <c r="I213" s="108">
+        <f t="shared" si="19"/>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" s="70" t="s">
+        <v>173</v>
+      </c>
+      <c r="B214" s="108"/>
+      <c r="C214" s="108"/>
+      <c r="D214" s="108"/>
+      <c r="E214" s="108"/>
+      <c r="F214" s="108"/>
+      <c r="G214" s="109">
+        <v>75000</v>
+      </c>
+      <c r="H214" s="108">
+        <f t="shared" si="19"/>
+        <v>75000</v>
+      </c>
+      <c r="I214" s="108">
+        <f t="shared" si="19"/>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B215" s="108"/>
+      <c r="C215" s="108"/>
+      <c r="D215" s="108"/>
+      <c r="E215" s="108"/>
+      <c r="F215" s="108"/>
+      <c r="G215" s="108">
+        <f>+$L$215</f>
+        <v>106880</v>
+      </c>
+      <c r="H215" s="108">
+        <f t="shared" ref="H215:I230" si="35">+$L$215</f>
+        <v>106880</v>
+      </c>
+      <c r="I215" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="K215" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="L215" s="82">
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B216" s="108"/>
+      <c r="C216" s="108"/>
+      <c r="D216" s="108"/>
+      <c r="E216" s="108"/>
+      <c r="F216" s="108"/>
+      <c r="G216" s="108">
+        <f t="shared" ref="G216:I231" si="36">+$L$215</f>
+        <v>106880</v>
+      </c>
+      <c r="H216" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I216" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B217" s="108"/>
+      <c r="C217" s="108"/>
+      <c r="D217" s="108"/>
+      <c r="E217" s="108"/>
+      <c r="F217" s="108"/>
+      <c r="G217" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H217" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I217" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B218" s="108"/>
+      <c r="C218" s="108"/>
+      <c r="D218" s="108"/>
+      <c r="E218" s="108"/>
+      <c r="F218" s="108"/>
+      <c r="G218" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H218" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I218" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A219" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B219" s="108"/>
+      <c r="C219" s="108"/>
+      <c r="D219" s="108"/>
+      <c r="E219" s="108"/>
+      <c r="F219" s="108"/>
+      <c r="G219" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H219" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I219" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A220" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B220" s="108"/>
+      <c r="C220" s="108"/>
+      <c r="D220" s="108"/>
+      <c r="E220" s="108"/>
+      <c r="F220" s="108"/>
+      <c r="G220" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H220" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I220" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A221" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B221" s="108"/>
+      <c r="C221" s="108"/>
+      <c r="D221" s="108"/>
+      <c r="E221" s="108"/>
+      <c r="F221" s="108"/>
+      <c r="G221" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H221" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I221" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A222" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B222" s="108"/>
+      <c r="C222" s="108"/>
+      <c r="D222" s="108"/>
+      <c r="E222" s="108"/>
+      <c r="F222" s="108"/>
+      <c r="G222" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H222" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I222" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B223" s="108"/>
+      <c r="C223" s="108"/>
+      <c r="D223" s="108"/>
+      <c r="E223" s="108"/>
+      <c r="F223" s="108"/>
+      <c r="G223" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H223" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I223" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B224" s="108"/>
+      <c r="C224" s="108"/>
+      <c r="D224" s="108"/>
+      <c r="E224" s="108"/>
+      <c r="F224" s="108"/>
+      <c r="G224" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H224" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I224" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B225" s="108"/>
+      <c r="C225" s="108"/>
+      <c r="D225" s="108"/>
+      <c r="E225" s="108"/>
+      <c r="F225" s="108"/>
+      <c r="G225" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H225" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I225" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B226" s="108"/>
+      <c r="C226" s="108"/>
+      <c r="D226" s="108"/>
+      <c r="E226" s="108"/>
+      <c r="F226" s="108"/>
+      <c r="G226" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H226" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I226" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B227" s="108"/>
+      <c r="C227" s="108"/>
+      <c r="D227" s="108"/>
+      <c r="E227" s="108"/>
+      <c r="F227" s="108"/>
+      <c r="G227" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H227" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I227" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B228" s="108"/>
+      <c r="C228" s="108"/>
+      <c r="D228" s="108"/>
+      <c r="E228" s="108"/>
+      <c r="F228" s="108"/>
+      <c r="G228" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H228" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I228" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B229" s="108"/>
+      <c r="C229" s="108"/>
+      <c r="D229" s="108"/>
+      <c r="E229" s="108"/>
+      <c r="F229" s="108"/>
+      <c r="G229" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H229" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I229" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B230" s="108"/>
+      <c r="C230" s="108"/>
+      <c r="D230" s="108"/>
+      <c r="E230" s="108"/>
+      <c r="F230" s="108"/>
+      <c r="G230" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H230" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+      <c r="I230" s="108">
+        <f t="shared" si="35"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B231" s="108"/>
+      <c r="C231" s="108"/>
+      <c r="D231" s="108"/>
+      <c r="E231" s="108"/>
+      <c r="F231" s="108"/>
+      <c r="G231" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="H231" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+      <c r="I231" s="108">
+        <f t="shared" si="36"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="35"/>
+      <c r="B232" s="108"/>
+      <c r="C232" s="108"/>
+      <c r="D232" s="108"/>
+      <c r="E232" s="108"/>
+      <c r="F232" s="108"/>
+      <c r="G232" s="108"/>
+      <c r="H232" s="108"/>
+      <c r="I232" s="108"/>
+    </row>
+    <row r="233" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B154" s="93"/>
-      <c r="C154" s="93"/>
-      <c r="D154" s="93"/>
-      <c r="E154" s="93"/>
-      <c r="F154" s="93"/>
-      <c r="G154" s="102">
-        <v>12000</v>
-      </c>
-      <c r="H154" s="93"/>
-      <c r="I154" s="93"/>
-    </row>
-    <row r="155" spans="1:9" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B155" s="93"/>
-      <c r="C155" s="93"/>
-      <c r="D155" s="93"/>
-      <c r="E155" s="93"/>
-      <c r="F155" s="93"/>
-      <c r="G155" s="102">
-        <v>22000</v>
-      </c>
-      <c r="H155" s="93"/>
-      <c r="I155" s="93"/>
-    </row>
-    <row r="156" spans="1:9" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B156" s="93"/>
-      <c r="C156" s="93"/>
-      <c r="D156" s="93"/>
-      <c r="E156" s="93"/>
-      <c r="F156" s="93"/>
-      <c r="G156" s="102">
-        <v>25000</v>
-      </c>
-      <c r="H156" s="93"/>
-      <c r="I156" s="93"/>
-    </row>
-    <row r="157" spans="1:9" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="24" t="s">
+      <c r="B233" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C233" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="D233" s="110" t="s">
+        <v>131</v>
+      </c>
+      <c r="E233" s="111" t="s">
+        <v>136</v>
+      </c>
+      <c r="F233" s="100" t="s">
+        <v>98</v>
+      </c>
+      <c r="G233" s="100" t="s">
+        <v>99</v>
+      </c>
+      <c r="H233" s="112" t="s">
+        <v>100</v>
+      </c>
+      <c r="I233" s="112" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B234" s="84"/>
+      <c r="C234" s="84"/>
+      <c r="D234" s="84"/>
+      <c r="E234" s="84"/>
+      <c r="F234" s="84"/>
+      <c r="G234" s="82">
+        <v>40000</v>
+      </c>
+      <c r="H234" s="84"/>
+      <c r="I234" s="84"/>
+    </row>
+    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B235" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C235" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="D235" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="E235" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="F235" s="100" t="s">
+        <v>98</v>
+      </c>
+      <c r="G235" s="100" t="s">
+        <v>99</v>
+      </c>
+      <c r="H235" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="I235" s="100" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A236" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="B157" s="93"/>
-      <c r="C157" s="93"/>
-      <c r="D157" s="93"/>
-      <c r="E157" s="93"/>
-      <c r="F157" s="93"/>
-      <c r="G157" s="102">
-        <v>32000</v>
-      </c>
-      <c r="H157" s="93"/>
-      <c r="I157" s="93"/>
-    </row>
-    <row r="158" spans="1:9" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="B158" s="93"/>
-      <c r="C158" s="93"/>
-      <c r="D158" s="93"/>
-      <c r="E158" s="93"/>
-      <c r="F158" s="93"/>
-      <c r="G158" s="102">
-        <v>32000</v>
-      </c>
-      <c r="H158" s="93"/>
-      <c r="I158" s="93"/>
-    </row>
-    <row r="159" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C159" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="D159" s="94" t="s">
-        <v>135</v>
-      </c>
-      <c r="E159" s="95" t="s">
-        <v>141</v>
-      </c>
-      <c r="F159" s="100" t="s">
-        <v>101</v>
-      </c>
-      <c r="G159" s="100" t="s">
-        <v>102</v>
-      </c>
-      <c r="H159" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="I159" s="101" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B160" s="79"/>
-      <c r="C160" s="79"/>
-      <c r="D160" s="79"/>
-      <c r="E160" s="79"/>
-      <c r="F160" s="79"/>
-      <c r="G160" s="81">
-        <v>24000</v>
-      </c>
-      <c r="H160" s="79"/>
-      <c r="I160" s="79"/>
-    </row>
-    <row r="161" spans="1:9" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B161" s="79"/>
-      <c r="C161" s="79"/>
-      <c r="D161" s="79"/>
-      <c r="E161" s="79"/>
-      <c r="F161" s="79"/>
-      <c r="G161" s="79"/>
-      <c r="H161" s="79"/>
-      <c r="I161" s="79"/>
-    </row>
-    <row r="162" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="B162" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C162" s="96" t="s">
-        <v>134</v>
-      </c>
-      <c r="D162" s="96" t="s">
-        <v>135</v>
-      </c>
-      <c r="E162" s="97" t="s">
-        <v>141</v>
-      </c>
-      <c r="F162" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="G162" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="H162" s="98" t="s">
-        <v>103</v>
-      </c>
-      <c r="I162" s="98" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B163" s="79"/>
-      <c r="C163" s="79"/>
-      <c r="D163" s="79"/>
-      <c r="E163" s="79"/>
-      <c r="F163" s="79"/>
-      <c r="G163" s="81">
-        <v>40000</v>
-      </c>
-      <c r="H163" s="79"/>
-      <c r="I163" s="79"/>
-    </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="62" t="s">
+      <c r="B236" s="100"/>
+      <c r="C236" s="100"/>
+      <c r="D236" s="100"/>
+      <c r="E236" s="100"/>
+      <c r="F236" s="101">
+        <v>15000</v>
+      </c>
+      <c r="G236" s="101">
+        <v>15000</v>
+      </c>
+      <c r="H236" s="100"/>
+      <c r="I236" s="100"/>
+    </row>
+    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A237" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B237" s="100"/>
+      <c r="C237" s="100"/>
+      <c r="D237" s="100"/>
+      <c r="E237" s="100"/>
+      <c r="F237" s="101">
+        <v>18000</v>
+      </c>
+      <c r="G237" s="101">
+        <v>15000</v>
+      </c>
+      <c r="H237" s="100"/>
+      <c r="I237" s="100"/>
+    </row>
+    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A238" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B238" s="100"/>
+      <c r="C238" s="100"/>
+      <c r="D238" s="100"/>
+      <c r="E238" s="100"/>
+      <c r="F238" s="101">
+        <v>18000</v>
+      </c>
+      <c r="G238" s="101">
+        <v>15000</v>
+      </c>
+      <c r="H238" s="100"/>
+      <c r="I238" s="100"/>
+    </row>
+    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A239" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B239" s="100"/>
+      <c r="C239" s="100"/>
+      <c r="D239" s="100"/>
+      <c r="E239" s="100"/>
+      <c r="F239" s="100"/>
+      <c r="G239" s="101">
+        <v>20000</v>
+      </c>
+      <c r="H239" s="100"/>
+      <c r="I239" s="100"/>
+    </row>
+    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A240" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="B164" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C164" s="93" t="s">
-        <v>134</v>
-      </c>
-      <c r="D164" s="93" t="s">
-        <v>135</v>
-      </c>
-      <c r="E164" s="93" t="s">
-        <v>141</v>
-      </c>
-      <c r="F164" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="G164" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="H164" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="I164" s="93" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B165" s="93"/>
-      <c r="C165" s="93"/>
-      <c r="D165" s="93"/>
-      <c r="E165" s="93"/>
-      <c r="F165" s="102">
-        <v>15000</v>
-      </c>
-      <c r="G165" s="102">
-        <v>15000</v>
-      </c>
-      <c r="H165" s="93"/>
-      <c r="I165" s="93"/>
-    </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B166" s="93"/>
-      <c r="C166" s="93"/>
-      <c r="D166" s="93"/>
-      <c r="E166" s="93"/>
-      <c r="F166" s="102">
-        <v>18000</v>
-      </c>
-      <c r="G166" s="102">
-        <v>15000</v>
-      </c>
-      <c r="H166" s="93"/>
-      <c r="I166" s="93"/>
-    </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="B167" s="93"/>
-      <c r="C167" s="93"/>
-      <c r="D167" s="93"/>
-      <c r="E167" s="93"/>
-      <c r="F167" s="102">
-        <v>18000</v>
-      </c>
-      <c r="G167" s="102">
-        <v>15000</v>
-      </c>
-      <c r="H167" s="93"/>
-      <c r="I167" s="93"/>
-    </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B168" s="93"/>
-      <c r="C168" s="93"/>
-      <c r="D168" s="93"/>
-      <c r="E168" s="93"/>
-      <c r="F168" s="93"/>
-      <c r="G168" s="102">
+      <c r="B240" s="100"/>
+      <c r="C240" s="100"/>
+      <c r="D240" s="100"/>
+      <c r="E240" s="100"/>
+      <c r="F240" s="100"/>
+      <c r="G240" s="101">
         <v>20000</v>
       </c>
-      <c r="H168" s="93"/>
-      <c r="I168" s="93"/>
-    </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="B169" s="93"/>
-      <c r="C169" s="93"/>
-      <c r="D169" s="93"/>
-      <c r="E169" s="93"/>
-      <c r="F169" s="93"/>
-      <c r="G169" s="102">
-        <v>20000</v>
-      </c>
-      <c r="H169" s="93"/>
-      <c r="I169" s="93"/>
+      <c r="H240" s="100"/>
+      <c r="I240" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9048,15 +10869,9 @@
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G174" formula="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2577,7 +2577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A235" authorId="0" shapeId="0">
+    <comment ref="A234" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="224">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3031,15 +3031,6 @@
     <t>COME BEAN</t>
   </si>
   <si>
-    <t>Ad</t>
-  </si>
-  <si>
-    <t>Cos</t>
-  </si>
-  <si>
-    <t>MM</t>
-  </si>
-  <si>
     <t>Asistencial</t>
   </si>
   <si>
@@ -3049,18 +3040,9 @@
     <t xml:space="preserve">Cuota FLIAR POR INTEGRANTES </t>
   </si>
   <si>
-    <t>MM/Com</t>
-  </si>
-  <si>
     <t xml:space="preserve"> CADA SESION</t>
   </si>
   <si>
-    <t>No afilido Osecac</t>
-  </si>
-  <si>
-    <t>Mon/Op no cos</t>
-  </si>
-  <si>
     <t>In 90</t>
   </si>
   <si>
@@ -3082,9 +3064,6 @@
     <t>CONSULTA MEDICA C</t>
   </si>
   <si>
-    <t>NEURO TERAPIA</t>
-  </si>
-  <si>
     <t>ADMISION</t>
   </si>
   <si>
@@ -3094,9 +3073,6 @@
     <t>PISCOPEDAGOGIA</t>
   </si>
   <si>
-    <t>FONOADIOLOGIA</t>
-  </si>
-  <si>
     <t>TERAPIA OCUPACIONAL</t>
   </si>
   <si>
@@ -3329,6 +3305,12 @@
   </si>
   <si>
     <t>TAC</t>
+  </si>
+  <si>
+    <t>FONOAUDIOLOGIA</t>
+  </si>
+  <si>
+    <t>NEXO TERAPIA</t>
   </si>
 </sst>
 </file>
@@ -3340,7 +3322,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3464,6 +3446,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -3569,7 +3558,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -3901,6 +3890,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3908,7 +4076,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4002,9 +4170,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4027,15 +4192,6 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4051,51 +4207,211 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda 2" xfId="1"/>
@@ -4382,81 +4698,71 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L240"/>
+  <dimension ref="A1:L239"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="73" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.85546875" style="73" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="73" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.5703125" style="73" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5703125" style="73" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="72" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.85546875" style="72" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="72" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5703125" style="72" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5703125" style="72" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="72">
-        <v>46174</v>
-      </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="75" t="s">
+      <c r="B2" s="121"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D2" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79">
+      <c r="B3" s="69"/>
+      <c r="C3" s="69">
         <v>5550</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="69">
         <v>5550</v>
       </c>
-      <c r="E3" s="79">
+      <c r="E3" s="69">
         <v>5550</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="78">
         <v>5550</v>
       </c>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79">
+      <c r="G3" s="69"/>
+      <c r="H3" s="69">
         <v>4550</v>
       </c>
-      <c r="I3" s="79">
+      <c r="I3" s="69">
         <v>5550</v>
       </c>
     </row>
@@ -4464,121 +4770,111 @@
       <c r="A4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79">
+      <c r="B4" s="69"/>
+      <c r="C4" s="69">
         <v>8500</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="69">
         <v>8500</v>
       </c>
-      <c r="E4" s="79">
+      <c r="E4" s="69">
         <v>8500</v>
       </c>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79">
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69">
         <f>+I3*2</f>
         <v>11100</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79">
+        <v>158</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69">
         <v>20000</v>
       </c>
-      <c r="D5" s="79">
+      <c r="D5" s="69">
         <v>20000</v>
       </c>
-      <c r="E5" s="79">
+      <c r="E5" s="69">
         <v>30000</v>
       </c>
-      <c r="F5" s="79">
+      <c r="F5" s="69">
         <v>15000</v>
       </c>
-      <c r="G5" s="79">
+      <c r="G5" s="69">
         <v>30000</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="81" t="s">
-        <v>134</v>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79">
+        <v>132</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69">
         <v>14000</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="69">
         <v>14000</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="69">
         <v>20000</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="75">
         <f>+F5/2</f>
         <v>7500</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="75">
         <f>+G5/2</f>
         <v>15000</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="75" t="s">
+      <c r="B7" s="121"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K7" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J7" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K7" s="57"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
       <c r="J8" s="11">
         <v>4800</v>
       </c>
@@ -4590,42 +4886,42 @@
       <c r="A9" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="69">
         <v>10000</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79">
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69">
         <v>4200</v>
       </c>
-      <c r="F9" s="79"/>
-      <c r="G9" s="82">
+      <c r="F9" s="69"/>
+      <c r="G9" s="75">
         <f>+B9*0.6</f>
         <v>6000</v>
       </c>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="79">
+        <v>138</v>
+      </c>
+      <c r="B10" s="69">
         <v>30000</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79">
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69">
         <v>10000</v>
       </c>
-      <c r="F10" s="79"/>
-      <c r="G10" s="82">
+      <c r="F10" s="69"/>
+      <c r="G10" s="75">
         <v>15000</v>
       </c>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
     </row>
@@ -4633,58 +4929,58 @@
       <c r="A11" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="69">
         <v>25000</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79">
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69">
         <v>8000</v>
       </c>
-      <c r="F11" s="79"/>
-      <c r="G11" s="82">
+      <c r="F11" s="69"/>
+      <c r="G11" s="75">
         <v>12000</v>
       </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79">
+        <v>139</v>
+      </c>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69">
         <v>17000</v>
       </c>
-      <c r="F12" s="79"/>
-      <c r="G12" s="84">
+      <c r="F12" s="69"/>
+      <c r="G12" s="76">
         <v>18000</v>
       </c>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79">
+        <v>140</v>
+      </c>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69">
         <v>18400</v>
       </c>
-      <c r="F13" s="79"/>
-      <c r="G13" s="84">
+      <c r="F13" s="69"/>
+      <c r="G13" s="76">
         <v>20000</v>
       </c>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
@@ -4692,63 +4988,53 @@
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="75" t="s">
+      <c r="B14" s="121"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D14" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J14" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="K14" s="64" t="s">
-        <v>139</v>
-      </c>
+      <c r="J14" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="60"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="79">
+      <c r="B15" s="69">
         <v>88500</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79">
+      <c r="C15" s="69"/>
+      <c r="D15" s="69">
         <v>44800</v>
       </c>
-      <c r="E15" s="79">
+      <c r="E15" s="69">
         <v>44800</v>
       </c>
-      <c r="F15" s="82">
+      <c r="F15" s="75">
         <f>+B15*0.7</f>
         <v>61949.999999999993</v>
       </c>
-      <c r="G15" s="82">
+      <c r="G15" s="75">
         <f>+B15*0.6</f>
         <v>53100</v>
       </c>
-      <c r="H15" s="79">
+      <c r="H15" s="69">
         <v>14750</v>
       </c>
-      <c r="I15" s="79">
+      <c r="I15" s="69">
         <v>0</v>
       </c>
       <c r="J15" s="11">
@@ -4762,28 +5048,28 @@
       <c r="A16" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="69">
         <v>177000</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79">
+      <c r="C16" s="69"/>
+      <c r="D16" s="69">
         <v>88500</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E16" s="69">
         <v>88500</v>
       </c>
-      <c r="F16" s="82">
+      <c r="F16" s="75">
         <f>+B16*0.7</f>
         <v>123899.99999999999</v>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="75">
         <f>+B16*0.6</f>
         <v>106200</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H16" s="69">
         <v>29500</v>
       </c>
-      <c r="I16" s="79">
+      <c r="I16" s="69">
         <v>0</v>
       </c>
       <c r="J16" s="11">
@@ -4794,19 +5080,19 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79">
+      <c r="A17" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69">
         <v>16000</v>
       </c>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
@@ -4814,112 +5100,94 @@
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="75" t="s">
+      <c r="B18" s="121"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D18" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I18" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="69">
         <v>20000</v>
       </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79">
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69">
         <v>8000</v>
       </c>
-      <c r="F19" s="85">
+      <c r="F19" s="77">
         <v>0</v>
       </c>
-      <c r="G19" s="82">
+      <c r="G19" s="75">
         <f>+B19*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C20" s="75" t="s">
+      <c r="B20" s="121"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H20" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J20" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K20" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J20" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K20" s="57"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="69">
         <v>35000</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79">
+      <c r="C21" s="69"/>
+      <c r="D21" s="69">
         <v>20000</v>
       </c>
-      <c r="E21" s="79">
+      <c r="E21" s="69">
         <v>20000</v>
       </c>
-      <c r="F21" s="85">
+      <c r="F21" s="77">
         <v>0</v>
       </c>
-      <c r="G21" s="82">
+      <c r="G21" s="75">
         <v>20000</v>
       </c>
-      <c r="H21" s="79">
+      <c r="H21" s="69">
         <v>7000</v>
       </c>
-      <c r="I21" s="79">
+      <c r="I21" s="69">
         <v>0</v>
       </c>
       <c r="J21" s="11">
@@ -4933,61 +5201,51 @@
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="75" t="s">
+      <c r="B22" s="121"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I22" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D22" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G22" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I22" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J22" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K22" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J22" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K22" s="57"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="79">
+      <c r="B23" s="69">
         <v>30000</v>
       </c>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79">
+      <c r="C23" s="69"/>
+      <c r="D23" s="69">
         <v>8200</v>
       </c>
-      <c r="E23" s="79">
+      <c r="E23" s="69">
         <v>10400</v>
       </c>
-      <c r="F23" s="85">
+      <c r="F23" s="77">
         <v>18000</v>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="75">
         <v>15000</v>
       </c>
-      <c r="H23" s="79">
+      <c r="H23" s="69">
         <v>4200</v>
       </c>
-      <c r="I23" s="79">
+      <c r="I23" s="69">
         <v>0</v>
       </c>
       <c r="J23" s="11">
@@ -5001,65 +5259,55 @@
       <c r="A24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C24" s="75" t="s">
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I24" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K24" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J24" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K24" s="57"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="79">
+      <c r="B25" s="69">
         <v>20000</v>
       </c>
-      <c r="C25" s="79">
+      <c r="C25" s="69">
         <v>12600</v>
       </c>
-      <c r="D25" s="79">
+      <c r="D25" s="69">
         <v>8200</v>
       </c>
-      <c r="E25" s="79">
+      <c r="E25" s="69">
         <v>12600</v>
       </c>
-      <c r="F25" s="85">
+      <c r="F25" s="77">
         <f>+B25*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G25" s="82">
+      <c r="G25" s="75">
         <f>+B25*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H25" s="79">
+      <c r="H25" s="69">
         <v>5400</v>
       </c>
-      <c r="I25" s="79">
+      <c r="I25" s="69">
         <v>0</v>
       </c>
       <c r="J25" s="11">
@@ -5073,65 +5321,55 @@
       <c r="A26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" s="75" t="s">
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F26" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G26" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J26" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K26" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J26" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K26" s="57"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="79">
+      <c r="B27" s="69">
         <v>228334</v>
       </c>
-      <c r="C27" s="79">
+      <c r="C27" s="69">
         <v>149000</v>
       </c>
-      <c r="D27" s="79">
+      <c r="D27" s="69">
         <v>137000</v>
       </c>
-      <c r="E27" s="79">
+      <c r="E27" s="69">
         <v>149000</v>
       </c>
-      <c r="F27" s="85">
+      <c r="F27" s="77">
         <f>+B27*0.7</f>
         <v>159833.79999999999</v>
       </c>
-      <c r="G27" s="82">
+      <c r="G27" s="75">
         <f>+B27*0.6</f>
         <v>137000.4</v>
       </c>
-      <c r="H27" s="79">
+      <c r="H27" s="69">
         <v>74000</v>
       </c>
-      <c r="I27" s="79">
+      <c r="I27" s="69">
         <v>74000</v>
       </c>
       <c r="J27" s="11">
@@ -5145,65 +5383,55 @@
       <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C28" s="75" t="s">
+      <c r="B28" s="121"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F28" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G28" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I28" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J28" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K28" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J28" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K28" s="57"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="79">
+      <c r="B29" s="69">
         <v>72000</v>
       </c>
-      <c r="C29" s="79">
+      <c r="C29" s="69">
         <v>36700</v>
       </c>
-      <c r="D29" s="79">
+      <c r="D29" s="69">
         <v>31000</v>
       </c>
-      <c r="E29" s="79">
+      <c r="E29" s="69">
         <v>36700</v>
       </c>
-      <c r="F29" s="85">
+      <c r="F29" s="77">
         <f>+B29*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G29" s="82">
+      <c r="G29" s="75">
         <f>+B29*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H29" s="79">
+      <c r="H29" s="69">
         <v>16800</v>
       </c>
-      <c r="I29" s="79">
+      <c r="I29" s="69">
         <v>16800</v>
       </c>
       <c r="J29" s="11">
@@ -5217,65 +5445,55 @@
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C30" s="75" t="s">
+      <c r="B30" s="121"/>
+      <c r="C30" s="122"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I30" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F30" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G30" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H30" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I30" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J30" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K30" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J30" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K30" s="57"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="79">
+      <c r="B31" s="69">
         <v>33000</v>
       </c>
-      <c r="C31" s="79">
+      <c r="C31" s="69">
         <v>16600</v>
       </c>
-      <c r="D31" s="79">
+      <c r="D31" s="69">
         <v>16600</v>
       </c>
-      <c r="E31" s="79">
+      <c r="E31" s="69">
         <v>16600</v>
       </c>
-      <c r="F31" s="85">
+      <c r="F31" s="77">
         <f>+B31*0.7</f>
         <v>23100</v>
       </c>
-      <c r="G31" s="82">
+      <c r="G31" s="75">
         <f>+B31*0.6</f>
         <v>19800</v>
       </c>
-      <c r="H31" s="79">
+      <c r="H31" s="69">
         <v>10800</v>
       </c>
-      <c r="I31" s="79">
+      <c r="I31" s="69">
         <v>10800</v>
       </c>
       <c r="J31" s="11">
@@ -5289,65 +5507,55 @@
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C32" s="75" t="s">
+      <c r="B32" s="121"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F32" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H32" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J32" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K32" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J32" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K32" s="57"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="79">
+      <c r="B33" s="69">
         <v>24600</v>
       </c>
-      <c r="C33" s="79">
+      <c r="C33" s="69">
         <v>12500</v>
       </c>
-      <c r="D33" s="79">
+      <c r="D33" s="69">
         <v>12500</v>
       </c>
-      <c r="E33" s="79">
+      <c r="E33" s="69">
         <v>12500</v>
       </c>
-      <c r="F33" s="85">
+      <c r="F33" s="77">
         <f>+B33*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G33" s="82">
+      <c r="G33" s="75">
         <f>+B33*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H33" s="79">
+      <c r="H33" s="69">
         <v>6300</v>
       </c>
-      <c r="I33" s="79">
+      <c r="I33" s="69">
         <v>6300</v>
       </c>
       <c r="J33" s="11">
@@ -5361,65 +5569,55 @@
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C34" s="75" t="s">
+      <c r="B34" s="121"/>
+      <c r="C34" s="122"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H34" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D34" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E34" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F34" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G34" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J34" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K34" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J34" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K34" s="57"/>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="79">
+      <c r="B35" s="69">
         <v>24600</v>
       </c>
-      <c r="C35" s="79">
+      <c r="C35" s="69">
         <v>12500</v>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="69">
         <v>12500</v>
       </c>
-      <c r="E35" s="79">
+      <c r="E35" s="69">
         <v>12500</v>
       </c>
-      <c r="F35" s="85">
+      <c r="F35" s="77">
         <f>+B35*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G35" s="82">
+      <c r="G35" s="75">
         <f>+B35*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H35" s="79">
+      <c r="H35" s="69">
         <v>6300</v>
       </c>
-      <c r="I35" s="79">
+      <c r="I35" s="69">
         <v>6300</v>
       </c>
       <c r="J35" s="11">
@@ -5433,65 +5631,55 @@
       <c r="A36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" s="75" t="s">
+      <c r="B36" s="121"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I36" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G36" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H36" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I36" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J36" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K36" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J36" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K36" s="57"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="79">
+      <c r="B37" s="69">
         <v>24600</v>
       </c>
-      <c r="C37" s="79">
+      <c r="C37" s="69">
         <v>12500</v>
       </c>
-      <c r="D37" s="79">
+      <c r="D37" s="69">
         <v>12500</v>
       </c>
-      <c r="E37" s="79">
+      <c r="E37" s="69">
         <v>12500</v>
       </c>
-      <c r="F37" s="85">
+      <c r="F37" s="77">
         <f>+B37*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G37" s="82">
+      <c r="G37" s="75">
         <f>+B37*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H37" s="79">
+      <c r="H37" s="69">
         <v>6300</v>
       </c>
-      <c r="I37" s="79">
+      <c r="I37" s="69">
         <v>6300</v>
       </c>
       <c r="J37" s="11">
@@ -5505,65 +5693,55 @@
       <c r="A38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C38" s="75" t="s">
+      <c r="B38" s="121"/>
+      <c r="C38" s="122"/>
+      <c r="D38" s="122"/>
+      <c r="E38" s="123"/>
+      <c r="F38" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F38" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G38" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I38" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J38" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K38" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J38" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K38" s="57"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="79">
+      <c r="B39" s="69">
         <v>24600</v>
       </c>
-      <c r="C39" s="79">
+      <c r="C39" s="69">
         <v>12500</v>
       </c>
-      <c r="D39" s="79">
+      <c r="D39" s="69">
         <v>12500</v>
       </c>
-      <c r="E39" s="79">
+      <c r="E39" s="69">
         <v>12500</v>
       </c>
-      <c r="F39" s="85">
+      <c r="F39" s="77">
         <f>+B39*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G39" s="82">
+      <c r="G39" s="75">
         <f>+B39*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H39" s="79">
+      <c r="H39" s="69">
         <v>6300</v>
       </c>
-      <c r="I39" s="79">
+      <c r="I39" s="69">
         <v>6300</v>
       </c>
       <c r="J39" s="11">
@@ -5577,65 +5755,55 @@
       <c r="A40" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C40" s="75" t="s">
+      <c r="B40" s="121"/>
+      <c r="C40" s="122"/>
+      <c r="D40" s="122"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H40" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I40" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D40" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F40" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G40" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H40" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I40" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J40" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K40" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J40" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K40" s="57"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="79">
+      <c r="B41" s="69">
         <v>72000</v>
       </c>
-      <c r="C41" s="79">
+      <c r="C41" s="69">
         <v>36700</v>
       </c>
-      <c r="D41" s="79">
+      <c r="D41" s="69">
         <v>31000</v>
       </c>
-      <c r="E41" s="79">
+      <c r="E41" s="69">
         <v>36700</v>
       </c>
-      <c r="F41" s="85">
+      <c r="F41" s="77">
         <f>+B41*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G41" s="82">
+      <c r="G41" s="75">
         <f>+B41*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H41" s="79">
+      <c r="H41" s="69">
         <v>16800</v>
       </c>
-      <c r="I41" s="79">
+      <c r="I41" s="69">
         <v>16800</v>
       </c>
       <c r="J41" s="11">
@@ -5649,65 +5817,55 @@
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="74" t="s">
-        <v>163</v>
-      </c>
-      <c r="C42" s="75" t="s">
+      <c r="B42" s="121"/>
+      <c r="C42" s="122"/>
+      <c r="D42" s="122"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H42" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I42" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D42" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F42" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G42" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H42" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I42" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="J42" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="K42" s="61" t="s">
-        <v>139</v>
-      </c>
+      <c r="J42" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="K42" s="57"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="B43" s="79">
+      <c r="B43" s="69">
         <v>12000</v>
       </c>
-      <c r="C43" s="79">
+      <c r="C43" s="69">
         <v>4200</v>
       </c>
-      <c r="D43" s="79">
+      <c r="D43" s="69">
         <v>0</v>
       </c>
-      <c r="E43" s="79">
+      <c r="E43" s="69">
         <v>4200</v>
       </c>
-      <c r="F43" s="85">
+      <c r="F43" s="77">
         <f>+B43*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G43" s="85">
+      <c r="G43" s="77">
         <f>+B43*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H43" s="79">
+      <c r="H43" s="69">
         <v>0</v>
       </c>
-      <c r="I43" s="79">
+      <c r="I43" s="69">
         <v>0</v>
       </c>
       <c r="J43" s="11">
@@ -5721,30 +5879,30 @@
       <c r="A44" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B44" s="79">
+      <c r="B44" s="69">
         <v>12000</v>
       </c>
-      <c r="C44" s="79">
+      <c r="C44" s="69">
         <v>4200</v>
       </c>
-      <c r="D44" s="79">
+      <c r="D44" s="69">
         <v>0</v>
       </c>
-      <c r="E44" s="79">
+      <c r="E44" s="69">
         <v>4200</v>
       </c>
-      <c r="F44" s="85">
+      <c r="F44" s="77">
         <f t="shared" ref="F44:F46" si="0">+B44*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G44" s="85">
+      <c r="G44" s="77">
         <f t="shared" ref="G44:G46" si="1">+B44*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H44" s="79">
+      <c r="H44" s="69">
         <v>0</v>
       </c>
-      <c r="I44" s="79">
+      <c r="I44" s="69">
         <v>0</v>
       </c>
       <c r="J44" s="11">
@@ -5758,30 +5916,30 @@
       <c r="A45" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B45" s="79">
+      <c r="B45" s="69">
         <v>12000</v>
       </c>
-      <c r="C45" s="79">
+      <c r="C45" s="69">
         <v>4200</v>
       </c>
-      <c r="D45" s="79">
+      <c r="D45" s="69">
         <v>0</v>
       </c>
-      <c r="E45" s="79">
+      <c r="E45" s="69">
         <v>4200</v>
       </c>
-      <c r="F45" s="85">
+      <c r="F45" s="77">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G45" s="85">
+      <c r="G45" s="77">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H45" s="79">
+      <c r="H45" s="69">
         <v>0</v>
       </c>
-      <c r="I45" s="79">
+      <c r="I45" s="69">
         <v>0</v>
       </c>
       <c r="J45" s="11">
@@ -5795,36 +5953,36 @@
       <c r="A46" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="79">
+      <c r="B46" s="69">
         <v>12000</v>
       </c>
-      <c r="C46" s="79">
+      <c r="C46" s="69">
         <v>4200</v>
       </c>
-      <c r="D46" s="79">
+      <c r="D46" s="69">
         <v>0</v>
       </c>
-      <c r="E46" s="79">
+      <c r="E46" s="69">
         <v>4200</v>
       </c>
-      <c r="F46" s="85">
+      <c r="F46" s="77">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G46" s="85">
+      <c r="G46" s="77">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H46" s="79">
+      <c r="H46" s="69">
         <v>0</v>
       </c>
-      <c r="I46" s="79">
+      <c r="I46" s="69">
         <v>0</v>
       </c>
       <c r="J46" s="11">
         <v>5300</v>
       </c>
-      <c r="K46" s="69">
+      <c r="K46" s="65">
         <v>5300</v>
       </c>
     </row>
@@ -5832,123 +5990,115 @@
       <c r="A47" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" s="75" t="s">
+      <c r="B47" s="121"/>
+      <c r="C47" s="122"/>
+      <c r="D47" s="122"/>
+      <c r="E47" s="123"/>
+      <c r="F47" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H47" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I47" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D47" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F47" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G47" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H47" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I47" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="84">
+        <v>154</v>
+      </c>
+      <c r="B48" s="76">
         <v>20000</v>
       </c>
-      <c r="C48" s="84">
+      <c r="C48" s="76">
         <v>9500</v>
       </c>
-      <c r="D48" s="84">
+      <c r="D48" s="76">
         <v>9500</v>
       </c>
-      <c r="E48" s="84">
+      <c r="E48" s="76">
         <v>9500</v>
       </c>
-      <c r="F48" s="85">
+      <c r="F48" s="77">
         <f>+B48*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G48" s="85">
+      <c r="G48" s="77">
         <f>+B48*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H48" s="79">
+      <c r="H48" s="69">
         <v>4100</v>
       </c>
-      <c r="I48" s="79">
+      <c r="I48" s="69">
         <v>4100</v>
       </c>
-      <c r="J48" s="68"/>
+      <c r="J48" s="64"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="84">
+      <c r="B49" s="76">
         <v>15000</v>
       </c>
-      <c r="C49" s="84">
+      <c r="C49" s="76">
         <v>5900</v>
       </c>
-      <c r="D49" s="84">
+      <c r="D49" s="76">
         <v>5900</v>
       </c>
-      <c r="E49" s="84">
+      <c r="E49" s="76">
         <v>5900</v>
       </c>
-      <c r="F49" s="85">
+      <c r="F49" s="77">
         <f t="shared" ref="F49:F54" si="2">+B49*0.7</f>
         <v>10500</v>
       </c>
-      <c r="G49" s="85">
+      <c r="G49" s="77">
         <f t="shared" ref="G49:G54" si="3">+B49*0.6</f>
         <v>9000</v>
       </c>
-      <c r="H49" s="79">
+      <c r="H49" s="69">
         <v>4900</v>
       </c>
-      <c r="I49" s="79">
+      <c r="I49" s="69">
         <v>4900</v>
       </c>
-      <c r="J49" s="68"/>
+      <c r="J49" s="64"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="84">
+      <c r="B50" s="76">
         <v>15000</v>
       </c>
-      <c r="C50" s="84">
+      <c r="C50" s="76">
         <v>5800</v>
       </c>
-      <c r="D50" s="84">
+      <c r="D50" s="76">
         <v>5800</v>
       </c>
-      <c r="E50" s="84">
+      <c r="E50" s="76">
         <v>5800</v>
       </c>
-      <c r="F50" s="85">
+      <c r="F50" s="77">
         <f t="shared" si="2"/>
         <v>10500</v>
       </c>
-      <c r="G50" s="85">
+      <c r="G50" s="77">
         <f t="shared" si="3"/>
         <v>9000</v>
       </c>
-      <c r="H50" s="79">
+      <c r="H50" s="69">
         <v>3400</v>
       </c>
-      <c r="I50" s="79">
+      <c r="I50" s="69">
         <v>3400</v>
       </c>
     </row>
@@ -5956,30 +6106,30 @@
       <c r="A51" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="84">
+      <c r="B51" s="76">
         <v>20000</v>
       </c>
-      <c r="C51" s="84">
+      <c r="C51" s="76">
         <v>5800</v>
       </c>
-      <c r="D51" s="84">
+      <c r="D51" s="76">
         <v>5800</v>
       </c>
-      <c r="E51" s="84">
+      <c r="E51" s="76">
         <v>5800</v>
       </c>
-      <c r="F51" s="85">
+      <c r="F51" s="77">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G51" s="85">
+      <c r="G51" s="77">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H51" s="79">
+      <c r="H51" s="69">
         <v>3400</v>
       </c>
-      <c r="I51" s="79">
+      <c r="I51" s="69">
         <v>3400</v>
       </c>
     </row>
@@ -5987,30 +6137,30 @@
       <c r="A52" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="84">
+      <c r="B52" s="76">
         <v>20000</v>
       </c>
-      <c r="C52" s="84">
+      <c r="C52" s="76">
         <v>9500</v>
       </c>
-      <c r="D52" s="84">
+      <c r="D52" s="76">
         <v>9500</v>
       </c>
-      <c r="E52" s="84">
+      <c r="E52" s="76">
         <v>9500</v>
       </c>
-      <c r="F52" s="85">
+      <c r="F52" s="77">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G52" s="85">
+      <c r="G52" s="77">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H52" s="79">
+      <c r="H52" s="69">
         <v>3400</v>
       </c>
-      <c r="I52" s="79">
+      <c r="I52" s="69">
         <v>3400</v>
       </c>
     </row>
@@ -6018,30 +6168,30 @@
       <c r="A53" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="84">
+      <c r="B53" s="76">
         <v>20000</v>
       </c>
-      <c r="C53" s="84">
+      <c r="C53" s="76">
         <v>9500</v>
       </c>
-      <c r="D53" s="84">
+      <c r="D53" s="76">
         <v>9500</v>
       </c>
-      <c r="E53" s="84">
+      <c r="E53" s="76">
         <v>9500</v>
       </c>
-      <c r="F53" s="85">
+      <c r="F53" s="77">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G53" s="85">
+      <c r="G53" s="77">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H53" s="79">
+      <c r="H53" s="69">
         <v>3400</v>
       </c>
-      <c r="I53" s="79">
+      <c r="I53" s="69">
         <v>3400</v>
       </c>
     </row>
@@ -6049,30 +6199,30 @@
       <c r="A54" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="84">
+      <c r="B54" s="76">
         <v>20000</v>
       </c>
-      <c r="C54" s="84">
+      <c r="C54" s="76">
         <v>13800</v>
       </c>
-      <c r="D54" s="84">
+      <c r="D54" s="76">
         <v>13800</v>
       </c>
-      <c r="E54" s="84">
+      <c r="E54" s="76">
         <v>13800</v>
       </c>
-      <c r="F54" s="85">
+      <c r="F54" s="77">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G54" s="85">
+      <c r="G54" s="77">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H54" s="79">
+      <c r="H54" s="69">
         <v>5700</v>
       </c>
-      <c r="I54" s="79">
+      <c r="I54" s="69">
         <v>5700</v>
       </c>
     </row>
@@ -6080,57 +6230,49 @@
       <c r="A55" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C55" s="75" t="s">
+      <c r="B55" s="121"/>
+      <c r="C55" s="122"/>
+      <c r="D55" s="122"/>
+      <c r="E55" s="123"/>
+      <c r="F55" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G55" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H55" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I55" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D55" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E55" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F55" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G55" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H55" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I55" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="84">
+      <c r="B56" s="76">
         <v>15000</v>
       </c>
-      <c r="C56" s="79">
+      <c r="C56" s="69">
         <v>7800</v>
       </c>
-      <c r="D56" s="79">
+      <c r="D56" s="69">
         <v>7800</v>
       </c>
-      <c r="E56" s="79">
+      <c r="E56" s="69">
         <v>7800</v>
       </c>
-      <c r="F56" s="80">
+      <c r="F56" s="78">
         <v>9000</v>
       </c>
-      <c r="G56" s="80">
+      <c r="G56" s="78">
         <v>7500</v>
       </c>
-      <c r="H56" s="79">
+      <c r="H56" s="69">
         <v>2700</v>
       </c>
-      <c r="I56" s="79">
+      <c r="I56" s="69">
         <v>0</v>
       </c>
     </row>
@@ -6138,59 +6280,51 @@
       <c r="A57" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C57" s="75" t="s">
+      <c r="B57" s="121"/>
+      <c r="C57" s="122"/>
+      <c r="D57" s="122"/>
+      <c r="E57" s="123"/>
+      <c r="F57" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H57" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I57" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D57" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F57" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G57" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H57" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I57" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="79">
+      <c r="B58" s="69">
         <v>12000</v>
       </c>
-      <c r="C58" s="79">
+      <c r="C58" s="69">
         <v>6400</v>
       </c>
-      <c r="D58" s="79">
+      <c r="D58" s="69">
         <v>6400</v>
       </c>
-      <c r="E58" s="79">
+      <c r="E58" s="69">
         <v>6400</v>
       </c>
-      <c r="F58" s="80">
+      <c r="F58" s="78">
         <f>+B58*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G58" s="80">
+      <c r="G58" s="78">
         <f>+B58*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H58" s="79">
+      <c r="H58" s="69">
         <v>3900</v>
       </c>
-      <c r="I58" s="79">
+      <c r="I58" s="69">
         <v>2700</v>
       </c>
     </row>
@@ -6198,59 +6332,51 @@
       <c r="A59" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C59" s="75" t="s">
+      <c r="B59" s="121"/>
+      <c r="C59" s="122"/>
+      <c r="D59" s="122"/>
+      <c r="E59" s="123"/>
+      <c r="F59" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G59" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I59" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D59" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E59" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F59" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G59" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H59" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I59" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="79">
+      <c r="B60" s="69">
         <v>20000</v>
       </c>
-      <c r="C60" s="86">
+      <c r="C60" s="124">
         <v>10200</v>
       </c>
-      <c r="D60" s="86">
+      <c r="D60" s="124">
         <v>10200</v>
       </c>
-      <c r="E60" s="86">
+      <c r="E60" s="124">
         <v>10200</v>
       </c>
-      <c r="F60" s="80">
+      <c r="F60" s="78">
         <f>+B60*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G60" s="80">
+      <c r="G60" s="78">
         <f>+B60*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H60" s="79">
+      <c r="H60" s="69">
         <v>5500</v>
       </c>
-      <c r="I60" s="79">
+      <c r="I60" s="69">
         <v>5500</v>
       </c>
     </row>
@@ -6258,30 +6384,30 @@
       <c r="A61" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="79">
+      <c r="B61" s="69">
         <v>30000</v>
       </c>
-      <c r="C61" s="86">
+      <c r="C61" s="124">
         <v>15900</v>
       </c>
-      <c r="D61" s="86">
+      <c r="D61" s="124">
         <v>15900</v>
       </c>
-      <c r="E61" s="86">
+      <c r="E61" s="124">
         <v>15900</v>
       </c>
-      <c r="F61" s="80">
+      <c r="F61" s="78">
         <f t="shared" ref="F61:F64" si="4">+B61*0.7</f>
         <v>21000</v>
       </c>
-      <c r="G61" s="80">
+      <c r="G61" s="78">
         <f t="shared" ref="G61:G64" si="5">+B61*0.6</f>
         <v>18000</v>
       </c>
-      <c r="H61" s="79">
+      <c r="H61" s="69">
         <v>8400</v>
       </c>
-      <c r="I61" s="79">
+      <c r="I61" s="69">
         <v>8400</v>
       </c>
     </row>
@@ -6289,30 +6415,30 @@
       <c r="A62" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="79">
+      <c r="B62" s="69">
         <v>20000</v>
       </c>
-      <c r="C62" s="86">
+      <c r="C62" s="124">
         <v>10000</v>
       </c>
-      <c r="D62" s="86">
+      <c r="D62" s="124">
         <v>10000</v>
       </c>
-      <c r="E62" s="86">
+      <c r="E62" s="124">
         <v>10000</v>
       </c>
-      <c r="F62" s="80">
+      <c r="F62" s="78">
         <f t="shared" si="4"/>
         <v>14000</v>
       </c>
-      <c r="G62" s="80">
+      <c r="G62" s="78">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H62" s="79">
+      <c r="H62" s="69">
         <v>5000</v>
       </c>
-      <c r="I62" s="79">
+      <c r="I62" s="69">
         <v>5000</v>
       </c>
     </row>
@@ -6320,30 +6446,30 @@
       <c r="A63" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="84">
+      <c r="B63" s="76">
         <v>30000</v>
       </c>
-      <c r="C63" s="86">
+      <c r="C63" s="124">
         <v>10000</v>
       </c>
-      <c r="D63" s="86">
+      <c r="D63" s="124">
         <v>10000</v>
       </c>
-      <c r="E63" s="86">
+      <c r="E63" s="124">
         <v>10000</v>
       </c>
-      <c r="F63" s="80">
+      <c r="F63" s="78">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G63" s="80">
+      <c r="G63" s="78">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H63" s="79">
+      <c r="H63" s="69">
         <v>5200</v>
       </c>
-      <c r="I63" s="79">
+      <c r="I63" s="69">
         <v>5200</v>
       </c>
     </row>
@@ -6351,30 +6477,30 @@
       <c r="A64" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="84">
+      <c r="B64" s="76">
         <v>30000</v>
       </c>
-      <c r="C64" s="86">
+      <c r="C64" s="124">
         <v>12300</v>
       </c>
-      <c r="D64" s="86">
+      <c r="D64" s="124">
         <v>12300</v>
       </c>
-      <c r="E64" s="86">
+      <c r="E64" s="124">
         <v>12300</v>
       </c>
-      <c r="F64" s="80">
+      <c r="F64" s="78">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G64" s="80">
+      <c r="G64" s="78">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H64" s="79">
+      <c r="H64" s="69">
         <v>7900</v>
       </c>
-      <c r="I64" s="79">
+      <c r="I64" s="69">
         <v>7900</v>
       </c>
     </row>
@@ -6382,103 +6508,97 @@
       <c r="A65" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="87"/>
-      <c r="C65" s="87"/>
-      <c r="D65" s="87"/>
-      <c r="E65" s="87"/>
-      <c r="F65" s="87"/>
-      <c r="G65" s="87"/>
-      <c r="H65" s="87"/>
-      <c r="I65" s="87"/>
+      <c r="B65" s="79"/>
+      <c r="C65" s="79"/>
+      <c r="D65" s="79"/>
+      <c r="E65" s="79"/>
+      <c r="F65" s="79"/>
+      <c r="G65" s="79"/>
+      <c r="H65" s="79"/>
+      <c r="I65" s="79"/>
     </row>
     <row r="66" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C66" s="75" t="s">
+      <c r="B66" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="122"/>
+      <c r="D66" s="122"/>
+      <c r="E66" s="123"/>
+      <c r="F66" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G66" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H66" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I66" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D66" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E66" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G66" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H66" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I66" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B67" s="80">
+      <c r="B67" s="78">
         <v>111000</v>
       </c>
-      <c r="C67" s="79">
+      <c r="C67" s="69">
         <v>83700</v>
       </c>
-      <c r="D67" s="79">
+      <c r="D67" s="69">
         <v>83700</v>
       </c>
-      <c r="E67" s="79">
+      <c r="E67" s="69">
         <v>83700</v>
       </c>
-      <c r="F67" s="80">
+      <c r="F67" s="78">
         <f>+B67*0.7</f>
         <v>77700</v>
       </c>
-      <c r="G67" s="80">
+      <c r="G67" s="78">
         <f>+B67*0.6</f>
         <v>66600</v>
       </c>
-      <c r="H67" s="79">
+      <c r="H67" s="69">
         <v>46700</v>
       </c>
-      <c r="I67" s="79">
+      <c r="I67" s="69">
         <v>46700</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="B68" s="88">
+      <c r="A68" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="125">
         <v>51000</v>
       </c>
-      <c r="C68" s="89">
+      <c r="C68" s="126">
         <v>51000</v>
       </c>
-      <c r="D68" s="89">
+      <c r="D68" s="126">
         <v>51000</v>
       </c>
-      <c r="E68" s="90">
+      <c r="E68" s="127">
         <v>51000</v>
       </c>
-      <c r="F68" s="80">
+      <c r="F68" s="78">
         <f>+B68*0.7</f>
         <v>35700</v>
       </c>
-      <c r="G68" s="80">
+      <c r="G68" s="78">
         <f>+B68*0.6</f>
         <v>30600</v>
       </c>
-      <c r="H68" s="91">
+      <c r="H68" s="80">
         <v>21300</v>
       </c>
-      <c r="I68" s="79">
+      <c r="I68" s="69">
         <v>21300</v>
       </c>
     </row>
@@ -6486,90 +6606,84 @@
       <c r="A69" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B69" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C69" s="75" t="s">
+      <c r="B69" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="122"/>
+      <c r="D69" s="122"/>
+      <c r="E69" s="123"/>
+      <c r="F69" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G69" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H69" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I69" s="81" t="s">
         <v>130</v>
-      </c>
-      <c r="D69" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F69" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G69" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H69" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I69" s="92" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B70" s="80">
+      <c r="B70" s="78">
         <v>241000</v>
       </c>
-      <c r="C70" s="79">
+      <c r="C70" s="69">
         <v>165000</v>
       </c>
-      <c r="D70" s="79">
+      <c r="D70" s="69">
         <v>165000</v>
       </c>
-      <c r="E70" s="79">
+      <c r="E70" s="69">
         <v>165000</v>
       </c>
-      <c r="F70" s="80">
+      <c r="F70" s="78">
         <f>+B70*0.7</f>
         <v>168700</v>
       </c>
-      <c r="G70" s="80">
+      <c r="G70" s="78">
         <f>+B70*0.6</f>
         <v>144600</v>
       </c>
-      <c r="H70" s="79">
+      <c r="H70" s="69">
         <v>76000</v>
       </c>
-      <c r="I70" s="79">
+      <c r="I70" s="69">
         <v>76000</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="63" t="s">
-        <v>161</v>
-      </c>
-      <c r="B71" s="88">
+      <c r="A71" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="125">
         <v>68000</v>
       </c>
-      <c r="C71" s="89">
+      <c r="C71" s="126">
         <v>68000</v>
       </c>
-      <c r="D71" s="89">
+      <c r="D71" s="126">
         <v>68000</v>
       </c>
-      <c r="E71" s="90">
+      <c r="E71" s="127">
         <v>68000</v>
       </c>
-      <c r="F71" s="80">
+      <c r="F71" s="78">
         <f>+B71*0.7</f>
         <v>47600</v>
       </c>
-      <c r="G71" s="80">
+      <c r="G71" s="78">
         <f t="shared" ref="G71:G98" si="6">+B71*0.6</f>
         <v>40800</v>
       </c>
-      <c r="H71" s="91">
+      <c r="H71" s="80">
         <v>48000</v>
       </c>
-      <c r="I71" s="91">
+      <c r="I71" s="80">
         <v>48000</v>
       </c>
     </row>
@@ -6577,90 +6691,84 @@
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C72" s="75" t="s">
+      <c r="B72" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="122"/>
+      <c r="D72" s="122"/>
+      <c r="E72" s="123"/>
+      <c r="F72" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H72" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I72" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D72" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E72" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F72" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G72" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H72" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I72" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B73" s="80">
+      <c r="B73" s="78">
         <v>551000</v>
       </c>
-      <c r="C73" s="79">
+      <c r="C73" s="69">
         <v>418000</v>
       </c>
-      <c r="D73" s="79">
+      <c r="D73" s="69">
         <v>418000</v>
       </c>
-      <c r="E73" s="79">
+      <c r="E73" s="69">
         <v>418000</v>
       </c>
-      <c r="F73" s="80">
+      <c r="F73" s="78">
         <f t="shared" ref="F73:F98" si="7">+B73*0.7</f>
         <v>385700</v>
       </c>
-      <c r="G73" s="80">
+      <c r="G73" s="78">
         <f t="shared" si="6"/>
         <v>330600</v>
       </c>
-      <c r="H73" s="79">
+      <c r="H73" s="69">
         <v>209000</v>
       </c>
-      <c r="I73" s="79">
+      <c r="I73" s="69">
         <v>209000</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="B74" s="88">
+      <c r="A74" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="125">
         <v>132000</v>
       </c>
-      <c r="C74" s="89">
+      <c r="C74" s="126">
         <v>132000</v>
       </c>
-      <c r="D74" s="89">
+      <c r="D74" s="126">
         <v>132000</v>
       </c>
-      <c r="E74" s="90">
+      <c r="E74" s="127">
         <v>132000</v>
       </c>
-      <c r="F74" s="80">
+      <c r="F74" s="78">
         <f t="shared" si="7"/>
         <v>92400</v>
       </c>
-      <c r="G74" s="80">
+      <c r="G74" s="78">
         <f t="shared" si="6"/>
         <v>79200</v>
       </c>
-      <c r="H74" s="91">
+      <c r="H74" s="80">
         <v>75000</v>
       </c>
-      <c r="I74" s="91">
+      <c r="I74" s="80">
         <v>75000</v>
       </c>
     </row>
@@ -6668,90 +6776,84 @@
       <c r="A75" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C75" s="75" t="s">
+      <c r="B75" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C75" s="122"/>
+      <c r="D75" s="122"/>
+      <c r="E75" s="123"/>
+      <c r="F75" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G75" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H75" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I75" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D75" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E75" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F75" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G75" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H75" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I75" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="80">
+      <c r="B76" s="78">
         <v>962000</v>
       </c>
-      <c r="C76" s="79">
+      <c r="C76" s="69">
         <v>706000</v>
       </c>
-      <c r="D76" s="79">
+      <c r="D76" s="69">
         <v>706000</v>
       </c>
-      <c r="E76" s="79">
+      <c r="E76" s="69">
         <v>706000</v>
       </c>
-      <c r="F76" s="80">
+      <c r="F76" s="78">
         <f t="shared" si="7"/>
         <v>673400</v>
       </c>
-      <c r="G76" s="80">
+      <c r="G76" s="78">
         <f t="shared" si="6"/>
         <v>577200</v>
       </c>
-      <c r="H76" s="79">
+      <c r="H76" s="69">
         <v>464000</v>
       </c>
-      <c r="I76" s="79">
+      <c r="I76" s="69">
         <v>464000</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B77" s="88">
+        <v>153</v>
+      </c>
+      <c r="B77" s="125">
         <v>203000</v>
       </c>
-      <c r="C77" s="89">
+      <c r="C77" s="126">
         <v>203000</v>
       </c>
-      <c r="D77" s="89">
+      <c r="D77" s="126">
         <v>203000</v>
       </c>
-      <c r="E77" s="90">
+      <c r="E77" s="127">
         <v>203000</v>
       </c>
-      <c r="F77" s="80">
+      <c r="F77" s="78">
         <f t="shared" si="7"/>
         <v>142100</v>
       </c>
-      <c r="G77" s="80">
+      <c r="G77" s="78">
         <f t="shared" si="6"/>
         <v>121800</v>
       </c>
-      <c r="H77" s="91">
+      <c r="H77" s="80">
         <v>139000</v>
       </c>
-      <c r="I77" s="91">
+      <c r="I77" s="80">
         <v>139000</v>
       </c>
     </row>
@@ -6759,59 +6861,51 @@
       <c r="A78" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B78" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C78" s="75" t="s">
+      <c r="B78" s="121"/>
+      <c r="C78" s="122"/>
+      <c r="D78" s="122"/>
+      <c r="E78" s="123"/>
+      <c r="F78" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G78" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H78" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I78" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D78" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E78" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F78" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G78" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H78" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I78" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="82">
+      <c r="B79" s="75">
         <v>176000</v>
       </c>
-      <c r="C79" s="79">
+      <c r="C79" s="69">
         <v>176000</v>
       </c>
-      <c r="D79" s="79">
+      <c r="D79" s="69">
         <v>176000</v>
       </c>
-      <c r="E79" s="79">
+      <c r="E79" s="69">
         <v>176000</v>
       </c>
-      <c r="F79" s="80">
+      <c r="F79" s="78">
         <f t="shared" si="7"/>
         <v>123199.99999999999</v>
       </c>
-      <c r="G79" s="80">
+      <c r="G79" s="78">
         <f t="shared" si="6"/>
         <v>105600</v>
       </c>
-      <c r="H79" s="79">
+      <c r="H79" s="69">
         <v>176000</v>
       </c>
-      <c r="I79" s="79">
+      <c r="I79" s="69">
         <v>176000</v>
       </c>
     </row>
@@ -6819,61 +6913,61 @@
       <c r="A80" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="82">
+      <c r="B80" s="75">
         <v>233000</v>
       </c>
-      <c r="C80" s="79">
+      <c r="C80" s="69">
         <v>233000</v>
       </c>
-      <c r="D80" s="79">
+      <c r="D80" s="69">
         <v>233000</v>
       </c>
-      <c r="E80" s="79">
+      <c r="E80" s="69">
         <v>233000</v>
       </c>
-      <c r="F80" s="80">
+      <c r="F80" s="78">
         <f t="shared" si="7"/>
         <v>163100</v>
       </c>
-      <c r="G80" s="80">
+      <c r="G80" s="78">
         <f t="shared" si="6"/>
         <v>139800</v>
       </c>
-      <c r="H80" s="79">
+      <c r="H80" s="69">
         <v>233000</v>
       </c>
-      <c r="I80" s="79">
+      <c r="I80" s="69">
         <v>233000</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B81" s="82">
+        <v>151</v>
+      </c>
+      <c r="B81" s="75">
         <v>41000</v>
       </c>
-      <c r="C81" s="79">
+      <c r="C81" s="69">
         <v>41000</v>
       </c>
-      <c r="D81" s="79">
+      <c r="D81" s="69">
         <v>41000</v>
       </c>
-      <c r="E81" s="79">
+      <c r="E81" s="69">
         <v>41000</v>
       </c>
-      <c r="F81" s="80">
+      <c r="F81" s="78">
         <f t="shared" si="7"/>
         <v>28699.999999999996</v>
       </c>
-      <c r="G81" s="80">
+      <c r="G81" s="78">
         <f t="shared" si="6"/>
         <v>24600</v>
       </c>
-      <c r="H81" s="79">
+      <c r="H81" s="69">
         <v>41000</v>
       </c>
-      <c r="I81" s="79">
+      <c r="I81" s="69">
         <v>41000</v>
       </c>
     </row>
@@ -6881,132 +6975,120 @@
       <c r="A82" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B82" s="82">
+      <c r="B82" s="75">
         <v>7700</v>
       </c>
-      <c r="C82" s="79">
+      <c r="C82" s="69">
         <v>7700</v>
       </c>
-      <c r="D82" s="79">
+      <c r="D82" s="69">
         <v>7700</v>
       </c>
-      <c r="E82" s="79">
+      <c r="E82" s="69">
         <v>7700</v>
       </c>
-      <c r="F82" s="80">
+      <c r="F82" s="78">
         <f t="shared" si="7"/>
         <v>5390</v>
       </c>
-      <c r="G82" s="80">
+      <c r="G82" s="78">
         <f t="shared" si="6"/>
         <v>4620</v>
       </c>
-      <c r="H82" s="79">
+      <c r="H82" s="69">
         <v>7700</v>
       </c>
-      <c r="I82" s="79">
+      <c r="I82" s="69">
         <v>7700</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C83" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="B83" s="121"/>
+      <c r="C83" s="122"/>
+      <c r="D83" s="122"/>
+      <c r="E83" s="123"/>
+      <c r="F83" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G83" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H83" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I83" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D83" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E83" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F83" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G83" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H83" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I83" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="B84" s="93">
+      <c r="B84" s="83">
         <v>64600</v>
       </c>
-      <c r="C84" s="93"/>
-      <c r="D84" s="93"/>
-      <c r="E84" s="93"/>
-      <c r="F84" s="94"/>
-      <c r="G84" s="94"/>
-      <c r="H84" s="93"/>
-      <c r="I84" s="93"/>
+      <c r="C84" s="83"/>
+      <c r="D84" s="83"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="83"/>
+      <c r="I84" s="83"/>
     </row>
     <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="66" t="s">
+      <c r="A85" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="B85" s="95"/>
-      <c r="C85" s="75" t="s">
+      <c r="B85" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C85" s="122"/>
+      <c r="D85" s="122"/>
+      <c r="E85" s="123"/>
+      <c r="F85" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G85" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H85" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I85" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D85" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E85" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F85" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G85" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H85" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I85" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="B86" s="80">
+      <c r="B86" s="78">
         <v>97000</v>
       </c>
-      <c r="C86" s="79">
+      <c r="C86" s="69">
         <v>57000</v>
       </c>
-      <c r="D86" s="79">
+      <c r="D86" s="69">
         <v>57000</v>
       </c>
-      <c r="E86" s="79">
+      <c r="E86" s="69">
         <v>57000</v>
       </c>
-      <c r="F86" s="80">
+      <c r="F86" s="78">
         <f t="shared" si="7"/>
         <v>67900</v>
       </c>
-      <c r="G86" s="80">
+      <c r="G86" s="78">
         <f>+B86*0.6</f>
         <v>58200</v>
       </c>
-      <c r="H86" s="79">
+      <c r="H86" s="69">
         <v>23500</v>
       </c>
-      <c r="I86" s="79">
+      <c r="I86" s="69">
         <v>23500</v>
       </c>
     </row>
@@ -7014,61 +7096,61 @@
       <c r="A87" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B87" s="80">
+      <c r="B87" s="78">
         <v>282000</v>
       </c>
-      <c r="C87" s="79">
+      <c r="C87" s="69">
         <v>168000</v>
       </c>
-      <c r="D87" s="79">
+      <c r="D87" s="69">
         <v>168000</v>
       </c>
-      <c r="E87" s="79">
+      <c r="E87" s="69">
         <v>168000</v>
       </c>
-      <c r="F87" s="80">
+      <c r="F87" s="78">
         <f t="shared" si="7"/>
         <v>197400</v>
       </c>
-      <c r="G87" s="80">
+      <c r="G87" s="78">
         <f>+B87*0.6</f>
         <v>169200</v>
       </c>
-      <c r="H87" s="79">
+      <c r="H87" s="69">
         <v>72000</v>
       </c>
-      <c r="I87" s="79">
+      <c r="I87" s="69">
         <v>72000</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="B88" s="80">
+        <v>149</v>
+      </c>
+      <c r="B88" s="78">
         <v>256000</v>
       </c>
-      <c r="C88" s="79">
+      <c r="C88" s="69">
         <v>140000</v>
       </c>
-      <c r="D88" s="79">
+      <c r="D88" s="69">
         <v>140000</v>
       </c>
-      <c r="E88" s="79">
+      <c r="E88" s="69">
         <v>140000</v>
       </c>
-      <c r="F88" s="80">
+      <c r="F88" s="78">
         <f t="shared" si="7"/>
         <v>179200</v>
       </c>
-      <c r="G88" s="80">
+      <c r="G88" s="78">
         <f t="shared" si="6"/>
         <v>153600</v>
       </c>
-      <c r="H88" s="79">
+      <c r="H88" s="69">
         <v>62000</v>
       </c>
-      <c r="I88" s="79">
+      <c r="I88" s="69">
         <v>62000</v>
       </c>
     </row>
@@ -7076,140 +7158,134 @@
       <c r="A89" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="B89" s="80">
+      <c r="B89" s="78">
         <v>508000</v>
       </c>
-      <c r="C89" s="79">
+      <c r="C89" s="69">
         <v>287000</v>
       </c>
-      <c r="D89" s="79">
+      <c r="D89" s="69">
         <v>287000</v>
       </c>
-      <c r="E89" s="79">
+      <c r="E89" s="69">
         <v>287000</v>
       </c>
-      <c r="F89" s="80">
+      <c r="F89" s="78">
         <f t="shared" si="7"/>
         <v>355600</v>
       </c>
-      <c r="G89" s="80">
+      <c r="G89" s="78">
         <f t="shared" si="6"/>
         <v>304800</v>
       </c>
-      <c r="H89" s="79">
+      <c r="H89" s="69">
         <v>124000</v>
       </c>
-      <c r="I89" s="79">
+      <c r="I89" s="69">
         <v>1240000</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="B90" s="80">
+      <c r="A90" s="131" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" s="132">
         <v>8200</v>
       </c>
-      <c r="C90" s="79">
+      <c r="C90" s="117">
         <v>6200</v>
       </c>
-      <c r="D90" s="79">
+      <c r="D90" s="117">
         <v>6200</v>
       </c>
-      <c r="E90" s="79">
+      <c r="E90" s="117">
         <v>6200</v>
       </c>
-      <c r="F90" s="80">
+      <c r="F90" s="132">
         <f t="shared" si="7"/>
         <v>5740</v>
       </c>
-      <c r="G90" s="80">
+      <c r="G90" s="132">
         <f t="shared" si="6"/>
         <v>4920</v>
       </c>
-      <c r="H90" s="79">
+      <c r="H90" s="117">
         <v>2500</v>
       </c>
-      <c r="I90" s="79">
+      <c r="I90" s="117">
         <v>2500</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="47" t="s">
+    <row r="91" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C91" s="75" t="s">
+      <c r="B91" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C91" s="135"/>
+      <c r="D91" s="135"/>
+      <c r="E91" s="136"/>
+      <c r="F91" s="137" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="H91" s="138" t="s">
+        <v>100</v>
+      </c>
+      <c r="I91" s="138" t="s">
         <v>130</v>
       </c>
-      <c r="D91" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E91" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F91" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G91" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H91" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I91" s="78" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="48" t="s">
+      <c r="A92" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B92" s="87"/>
-      <c r="C92" s="87"/>
-      <c r="D92" s="87"/>
-      <c r="E92" s="87"/>
-      <c r="F92" s="80">
+      <c r="B92" s="133"/>
+      <c r="C92" s="133"/>
+      <c r="D92" s="133"/>
+      <c r="E92" s="133"/>
+      <c r="F92" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G92" s="80">
+      <c r="G92" s="134">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H92" s="87"/>
-      <c r="I92" s="87"/>
+      <c r="H92" s="133"/>
+      <c r="I92" s="133"/>
     </row>
     <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B93" s="80">
+      <c r="B93" s="78">
         <v>104000</v>
       </c>
-      <c r="C93" s="79">
+      <c r="C93" s="69">
         <v>94000</v>
       </c>
-      <c r="D93" s="79">
+      <c r="D93" s="69">
         <v>94000</v>
       </c>
-      <c r="E93" s="79">
+      <c r="E93" s="69">
         <v>94000</v>
       </c>
-      <c r="F93" s="80">
+      <c r="F93" s="78">
         <f t="shared" si="7"/>
         <v>72800</v>
       </c>
-      <c r="G93" s="80">
+      <c r="G93" s="78">
         <f t="shared" si="6"/>
         <v>62400</v>
       </c>
-      <c r="H93" s="79">
+      <c r="H93" s="69">
         <v>41600</v>
       </c>
-      <c r="I93" s="79">
+      <c r="I93" s="69">
         <v>41600</v>
       </c>
     </row>
@@ -7217,316 +7293,298 @@
       <c r="A94" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B94" s="80">
+      <c r="B94" s="78">
         <v>144750</v>
       </c>
-      <c r="C94" s="79">
+      <c r="C94" s="69">
         <v>106000</v>
       </c>
-      <c r="D94" s="79">
+      <c r="D94" s="69">
         <v>106000</v>
       </c>
-      <c r="E94" s="79">
+      <c r="E94" s="69">
         <v>106000</v>
       </c>
-      <c r="F94" s="80">
+      <c r="F94" s="78">
         <f t="shared" si="7"/>
         <v>101325</v>
       </c>
-      <c r="G94" s="80">
+      <c r="G94" s="78">
         <f t="shared" si="6"/>
         <v>86850</v>
       </c>
-      <c r="H94" s="79">
+      <c r="H94" s="69">
         <v>57900</v>
       </c>
-      <c r="I94" s="79">
+      <c r="I94" s="69">
         <v>57900</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="49" t="s">
+      <c r="A95" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B95" s="74" t="s">
-        <v>163</v>
-      </c>
-      <c r="C95" s="75" t="s">
+      <c r="B95" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C95" s="122"/>
+      <c r="D95" s="122"/>
+      <c r="E95" s="123"/>
+      <c r="F95" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G95" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H95" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I95" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D95" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E95" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F95" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G95" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H95" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I95" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B96" s="80">
+      <c r="B96" s="78">
         <f>+E96/0.7</f>
         <v>13428.571428571429</v>
       </c>
-      <c r="C96" s="79">
+      <c r="C96" s="69">
         <v>9400</v>
       </c>
-      <c r="D96" s="79">
+      <c r="D96" s="69">
         <v>9400</v>
       </c>
-      <c r="E96" s="79">
+      <c r="E96" s="69">
         <v>9400</v>
       </c>
-      <c r="F96" s="80">
+      <c r="F96" s="78">
         <f t="shared" si="7"/>
         <v>9400</v>
       </c>
-      <c r="G96" s="80">
+      <c r="G96" s="78">
         <f t="shared" si="6"/>
         <v>8057.1428571428569</v>
       </c>
-      <c r="H96" s="94">
+      <c r="H96" s="82">
         <f>+B96*0.4</f>
         <v>5371.4285714285725</v>
       </c>
-      <c r="I96" s="79"/>
+      <c r="I96" s="69"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B97" s="80">
+      <c r="B97" s="78">
         <f t="shared" ref="B97:B98" si="8">+E97/0.7</f>
         <v>19714.285714285714</v>
       </c>
-      <c r="C97" s="79">
+      <c r="C97" s="69">
         <v>13800</v>
       </c>
-      <c r="D97" s="79">
+      <c r="D97" s="69">
         <v>13800</v>
       </c>
-      <c r="E97" s="79">
+      <c r="E97" s="69">
         <v>13800</v>
       </c>
-      <c r="F97" s="80">
+      <c r="F97" s="78">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G97" s="80">
+      <c r="G97" s="78">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H97" s="94">
+      <c r="H97" s="82">
         <f t="shared" ref="H97:H98" si="9">+B97*0.4</f>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I97" s="79"/>
+      <c r="I97" s="69"/>
     </row>
     <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B98" s="80">
+      <c r="B98" s="78">
         <f t="shared" si="8"/>
         <v>19714.285714285714</v>
       </c>
-      <c r="C98" s="79">
+      <c r="C98" s="69">
         <v>13800</v>
       </c>
-      <c r="D98" s="79">
+      <c r="D98" s="69">
         <v>13800</v>
       </c>
-      <c r="E98" s="79">
+      <c r="E98" s="69">
         <v>13800</v>
       </c>
-      <c r="F98" s="80">
+      <c r="F98" s="78">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G98" s="80">
+      <c r="G98" s="78">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H98" s="94">
+      <c r="H98" s="82">
         <f t="shared" si="9"/>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I98" s="79"/>
+      <c r="I98" s="69"/>
     </row>
     <row r="99" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B99" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C99" s="75" t="s">
+      <c r="B99" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="C99" s="122"/>
+      <c r="D99" s="122"/>
+      <c r="E99" s="123"/>
+      <c r="F99" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G99" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="H99" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I99" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D99" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E99" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F99" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="G99" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="H99" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I99" s="78" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="50" t="s">
+      <c r="A100" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B100" s="80">
+      <c r="B100" s="78">
         <v>55600</v>
       </c>
-      <c r="C100" s="79">
+      <c r="C100" s="69">
         <v>38700</v>
       </c>
-      <c r="D100" s="79">
+      <c r="D100" s="69">
         <v>38700</v>
       </c>
-      <c r="E100" s="79">
+      <c r="E100" s="69">
         <v>38700</v>
       </c>
-      <c r="F100" s="80">
+      <c r="F100" s="78">
         <f>+B100*0.7</f>
         <v>38920</v>
       </c>
-      <c r="G100" s="80">
+      <c r="G100" s="78">
         <f>+B100*0.6</f>
         <v>33360</v>
       </c>
-      <c r="H100" s="79">
+      <c r="H100" s="69">
         <v>26800</v>
       </c>
-      <c r="I100" s="79">
+      <c r="I100" s="69">
         <v>26800</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="51" t="s">
+      <c r="A101" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="B101" s="80">
+      <c r="B101" s="78">
         <v>13900</v>
       </c>
-      <c r="C101" s="79">
+      <c r="C101" s="69">
         <v>13900</v>
       </c>
-      <c r="D101" s="79">
+      <c r="D101" s="69">
         <v>13900</v>
       </c>
-      <c r="E101" s="79">
+      <c r="E101" s="69">
         <v>13900</v>
       </c>
-      <c r="F101" s="80">
+      <c r="F101" s="78">
         <f>+B101*0.7</f>
         <v>9730</v>
       </c>
-      <c r="G101" s="80">
+      <c r="G101" s="78">
         <f>+B101*0.6</f>
         <v>8340</v>
       </c>
-      <c r="H101" s="96">
+      <c r="H101" s="84">
         <v>13900</v>
       </c>
-      <c r="I101" s="79">
+      <c r="I101" s="69">
         <v>13600</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="52" t="s">
+      <c r="A102" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="B102" s="97"/>
-      <c r="C102" s="97"/>
-      <c r="D102" s="97"/>
-      <c r="E102" s="97"/>
-      <c r="F102" s="97"/>
-      <c r="G102" s="97"/>
-      <c r="H102" s="97"/>
-      <c r="I102" s="97"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="85"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
     </row>
     <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="56" t="s">
+      <c r="A103" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="B103" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C103" s="75" t="s">
+      <c r="B103" s="121" t="s">
+        <v>155</v>
+      </c>
+      <c r="C103" s="122"/>
+      <c r="D103" s="122"/>
+      <c r="E103" s="123"/>
+      <c r="F103" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G103" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H103" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I103" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D103" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E103" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F103" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G103" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H103" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I103" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B104" s="79">
+      <c r="B104" s="69">
         <v>88886</v>
       </c>
-      <c r="C104" s="79">
+      <c r="C104" s="69">
         <v>44443</v>
       </c>
-      <c r="D104" s="79">
+      <c r="D104" s="69">
         <v>44443</v>
       </c>
-      <c r="E104" s="79">
+      <c r="E104" s="69">
         <v>44443</v>
       </c>
-      <c r="F104" s="80">
+      <c r="F104" s="78">
         <f>+B104*0.7</f>
         <v>62220.2</v>
       </c>
-      <c r="G104" s="80">
+      <c r="G104" s="78">
         <f>+B104*0.6</f>
         <v>53331.6</v>
       </c>
-      <c r="H104" s="79">
+      <c r="H104" s="69">
         <v>24647</v>
       </c>
-      <c r="I104" s="79">
+      <c r="I104" s="69">
         <v>24647</v>
       </c>
     </row>
@@ -7534,30 +7592,30 @@
       <c r="A105" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B105" s="79">
+      <c r="B105" s="69">
         <v>103703</v>
       </c>
-      <c r="C105" s="79">
+      <c r="C105" s="69">
         <v>51852</v>
       </c>
-      <c r="D105" s="79">
+      <c r="D105" s="69">
         <v>51852</v>
       </c>
-      <c r="E105" s="79">
+      <c r="E105" s="69">
         <v>51852</v>
       </c>
-      <c r="F105" s="80">
+      <c r="F105" s="78">
         <f t="shared" ref="F105:F129" si="10">+B105*0.7</f>
         <v>72592.099999999991</v>
       </c>
-      <c r="G105" s="80">
+      <c r="G105" s="78">
         <f t="shared" ref="G105:G129" si="11">+B105*0.6</f>
         <v>62221.799999999996</v>
       </c>
-      <c r="H105" s="79">
+      <c r="H105" s="69">
         <v>28755</v>
       </c>
-      <c r="I105" s="79">
+      <c r="I105" s="69">
         <v>28755</v>
       </c>
     </row>
@@ -7565,30 +7623,30 @@
       <c r="A106" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B106" s="79">
+      <c r="B106" s="69">
         <v>174729</v>
       </c>
-      <c r="C106" s="79">
+      <c r="C106" s="69">
         <v>87365</v>
       </c>
-      <c r="D106" s="79">
+      <c r="D106" s="69">
         <v>87365</v>
       </c>
-      <c r="E106" s="79">
+      <c r="E106" s="69">
         <v>87365</v>
       </c>
-      <c r="F106" s="80">
+      <c r="F106" s="78">
         <f t="shared" si="10"/>
         <v>122310.29999999999</v>
       </c>
-      <c r="G106" s="80">
+      <c r="G106" s="78">
         <f t="shared" si="11"/>
         <v>104837.4</v>
       </c>
-      <c r="H106" s="79">
+      <c r="H106" s="69">
         <v>48449</v>
       </c>
-      <c r="I106" s="79">
+      <c r="I106" s="69">
         <v>48449</v>
       </c>
     </row>
@@ -7596,30 +7654,30 @@
       <c r="A107" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="79">
+      <c r="B107" s="69">
         <v>22223</v>
       </c>
-      <c r="C107" s="79">
+      <c r="C107" s="69">
         <v>11112</v>
       </c>
-      <c r="D107" s="79">
+      <c r="D107" s="69">
         <v>11112</v>
       </c>
-      <c r="E107" s="79">
+      <c r="E107" s="69">
         <v>11112</v>
       </c>
-      <c r="F107" s="80">
+      <c r="F107" s="78">
         <f t="shared" si="10"/>
         <v>15556.099999999999</v>
       </c>
-      <c r="G107" s="80">
+      <c r="G107" s="78">
         <f t="shared" si="11"/>
         <v>13333.8</v>
       </c>
-      <c r="H107" s="79">
+      <c r="H107" s="69">
         <v>6162</v>
       </c>
-      <c r="I107" s="79">
+      <c r="I107" s="69">
         <v>6162</v>
       </c>
     </row>
@@ -7627,212 +7685,200 @@
       <c r="A108" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B108" s="79">
+      <c r="B108" s="69">
         <v>111110</v>
       </c>
-      <c r="C108" s="79">
+      <c r="C108" s="69">
         <v>55555</v>
       </c>
-      <c r="D108" s="79">
+      <c r="D108" s="69">
         <v>55555</v>
       </c>
-      <c r="E108" s="79">
+      <c r="E108" s="69">
         <v>55555</v>
       </c>
-      <c r="F108" s="80">
+      <c r="F108" s="78">
         <f t="shared" si="10"/>
         <v>77777</v>
       </c>
-      <c r="G108" s="80">
+      <c r="G108" s="78">
         <f t="shared" si="11"/>
         <v>66666</v>
       </c>
-      <c r="H108" s="79">
+      <c r="H108" s="69">
         <v>30809</v>
       </c>
-      <c r="I108" s="79">
+      <c r="I108" s="69">
         <v>30809</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="B109" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C109" s="75" t="s">
+      <c r="A109" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="B109" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C109" s="122"/>
+      <c r="D109" s="122"/>
+      <c r="E109" s="123"/>
+      <c r="F109" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G109" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H109" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I109" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D109" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E109" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F109" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G109" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H109" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I109" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B110" s="79">
+        <v>146</v>
+      </c>
+      <c r="B110" s="69">
         <v>312686</v>
       </c>
-      <c r="C110" s="79">
+      <c r="C110" s="69">
         <v>156343</v>
       </c>
-      <c r="D110" s="79">
+      <c r="D110" s="69">
         <v>156343</v>
       </c>
-      <c r="E110" s="79">
+      <c r="E110" s="69">
         <v>156343</v>
       </c>
-      <c r="F110" s="80">
+      <c r="F110" s="78">
         <f t="shared" si="10"/>
         <v>218880.19999999998</v>
       </c>
-      <c r="G110" s="80">
+      <c r="G110" s="78">
         <f t="shared" si="11"/>
         <v>187611.6</v>
       </c>
-      <c r="H110" s="79">
+      <c r="H110" s="69">
         <v>85421</v>
       </c>
-      <c r="I110" s="79">
+      <c r="I110" s="69">
         <v>85421</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B111" s="79">
+        <v>147</v>
+      </c>
+      <c r="B111" s="69">
         <v>349723</v>
       </c>
-      <c r="C111" s="79">
+      <c r="C111" s="69">
         <v>174861</v>
       </c>
-      <c r="D111" s="79">
+      <c r="D111" s="69">
         <v>174861</v>
       </c>
-      <c r="E111" s="79">
+      <c r="E111" s="69">
         <v>174861</v>
       </c>
-      <c r="F111" s="80">
+      <c r="F111" s="78">
         <f t="shared" si="10"/>
         <v>244806.09999999998</v>
       </c>
-      <c r="G111" s="80">
+      <c r="G111" s="78">
         <f t="shared" si="11"/>
         <v>209833.8</v>
       </c>
-      <c r="H111" s="79">
+      <c r="H111" s="69">
         <v>95539</v>
       </c>
-      <c r="I111" s="79">
+      <c r="I111" s="69">
         <v>95539</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B112" s="79">
+        <v>148</v>
+      </c>
+      <c r="B112" s="69">
         <v>446016</v>
       </c>
-      <c r="C112" s="79">
+      <c r="C112" s="69">
         <v>223008</v>
       </c>
-      <c r="D112" s="79">
+      <c r="D112" s="69">
         <v>223008</v>
       </c>
-      <c r="E112" s="79">
+      <c r="E112" s="69">
         <v>223008</v>
       </c>
-      <c r="F112" s="80">
+      <c r="F112" s="78">
         <f t="shared" si="10"/>
         <v>312211.19999999995</v>
       </c>
-      <c r="G112" s="80">
+      <c r="G112" s="78">
         <f t="shared" si="11"/>
         <v>267609.59999999998</v>
       </c>
-      <c r="H112" s="79">
+      <c r="H112" s="69">
         <v>121845</v>
       </c>
-      <c r="I112" s="79">
+      <c r="I112" s="69">
         <v>121845</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="54" t="s">
+      <c r="A113" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B113" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C113" s="75" t="s">
+      <c r="B113" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C113" s="122"/>
+      <c r="D113" s="122"/>
+      <c r="E113" s="123"/>
+      <c r="F113" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G113" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H113" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I113" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D113" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E113" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F113" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G113" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H113" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I113" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B114" s="79">
+      <c r="B114" s="69">
         <v>128763</v>
       </c>
-      <c r="C114" s="79">
+      <c r="C114" s="69">
         <v>64381</v>
       </c>
-      <c r="D114" s="79">
+      <c r="D114" s="69">
         <v>64381</v>
       </c>
-      <c r="E114" s="79">
+      <c r="E114" s="69">
         <v>64381</v>
       </c>
-      <c r="F114" s="80">
+      <c r="F114" s="78">
         <f t="shared" si="10"/>
         <v>90134.099999999991</v>
       </c>
-      <c r="G114" s="80">
+      <c r="G114" s="78">
         <f t="shared" si="11"/>
         <v>77257.8</v>
       </c>
-      <c r="H114" s="79">
+      <c r="H114" s="69">
         <v>35704</v>
       </c>
-      <c r="I114" s="79">
+      <c r="I114" s="69">
         <v>35704</v>
       </c>
     </row>
@@ -7840,90 +7886,84 @@
       <c r="A115" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B115" s="79">
+      <c r="B115" s="69">
         <v>199762</v>
       </c>
-      <c r="C115" s="79">
+      <c r="C115" s="69">
         <v>99881</v>
       </c>
-      <c r="D115" s="79">
+      <c r="D115" s="69">
         <v>99881</v>
       </c>
-      <c r="E115" s="79">
+      <c r="E115" s="69">
         <v>99881</v>
       </c>
-      <c r="F115" s="80">
+      <c r="F115" s="78">
         <f t="shared" si="10"/>
         <v>139833.4</v>
       </c>
-      <c r="G115" s="80">
+      <c r="G115" s="78">
         <f t="shared" si="11"/>
         <v>119857.2</v>
       </c>
-      <c r="H115" s="79">
+      <c r="H115" s="69">
         <v>55391</v>
       </c>
-      <c r="I115" s="79">
+      <c r="I115" s="69">
         <v>55391</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="54" t="s">
+      <c r="A116" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="B116" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C116" s="75" t="s">
+      <c r="B116" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C116" s="122"/>
+      <c r="D116" s="122"/>
+      <c r="E116" s="123"/>
+      <c r="F116" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G116" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H116" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I116" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D116" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E116" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F116" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G116" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H116" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I116" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B117" s="79">
+      <c r="B117" s="69">
         <v>477701</v>
       </c>
-      <c r="C117" s="79">
+      <c r="C117" s="69">
         <v>238851</v>
       </c>
-      <c r="D117" s="79">
+      <c r="D117" s="69">
         <v>238851</v>
       </c>
-      <c r="E117" s="79">
+      <c r="E117" s="69">
         <v>238851</v>
       </c>
-      <c r="F117" s="80">
+      <c r="F117" s="78">
         <f t="shared" si="10"/>
         <v>334390.69999999995</v>
       </c>
-      <c r="G117" s="80">
+      <c r="G117" s="78">
         <f t="shared" si="11"/>
         <v>286620.59999999998</v>
       </c>
-      <c r="H117" s="79">
+      <c r="H117" s="69">
         <v>132458</v>
       </c>
-      <c r="I117" s="79">
+      <c r="I117" s="69">
         <v>132458</v>
       </c>
     </row>
@@ -7931,30 +7971,30 @@
       <c r="A118" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B118" s="79">
+      <c r="B118" s="69">
         <v>236516</v>
       </c>
-      <c r="C118" s="79">
+      <c r="C118" s="69">
         <v>118258</v>
       </c>
-      <c r="D118" s="79">
+      <c r="D118" s="69">
         <v>118258</v>
       </c>
-      <c r="E118" s="79">
+      <c r="E118" s="69">
         <v>118258</v>
       </c>
-      <c r="F118" s="80">
+      <c r="F118" s="78">
         <f t="shared" si="10"/>
         <v>165561.19999999998</v>
       </c>
-      <c r="G118" s="80">
+      <c r="G118" s="78">
         <f t="shared" si="11"/>
         <v>141909.6</v>
       </c>
-      <c r="H118" s="79">
+      <c r="H118" s="69">
         <v>65582</v>
       </c>
-      <c r="I118" s="79">
+      <c r="I118" s="69">
         <v>65582</v>
       </c>
     </row>
@@ -7962,30 +8002,30 @@
       <c r="A119" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B119" s="79">
+      <c r="B119" s="69">
         <v>274873</v>
       </c>
-      <c r="C119" s="79">
+      <c r="C119" s="69">
         <v>137436</v>
       </c>
-      <c r="D119" s="79">
+      <c r="D119" s="69">
         <v>137436</v>
       </c>
-      <c r="E119" s="79">
+      <c r="E119" s="69">
         <v>137436</v>
       </c>
-      <c r="F119" s="80">
+      <c r="F119" s="78">
         <f t="shared" si="10"/>
         <v>192411.09999999998</v>
       </c>
-      <c r="G119" s="80">
+      <c r="G119" s="78">
         <f t="shared" si="11"/>
         <v>164923.79999999999</v>
       </c>
-      <c r="H119" s="79">
+      <c r="H119" s="69">
         <v>76217</v>
       </c>
-      <c r="I119" s="79">
+      <c r="I119" s="69">
         <v>76217</v>
       </c>
     </row>
@@ -7993,90 +8033,84 @@
       <c r="A120" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B120" s="79">
+      <c r="B120" s="69">
         <v>313203</v>
       </c>
-      <c r="C120" s="79">
+      <c r="C120" s="69">
         <v>156601</v>
       </c>
-      <c r="D120" s="79">
+      <c r="D120" s="69">
         <v>156601</v>
       </c>
-      <c r="E120" s="79">
+      <c r="E120" s="69">
         <v>156601</v>
       </c>
-      <c r="F120" s="80">
+      <c r="F120" s="78">
         <f t="shared" si="10"/>
         <v>219242.09999999998</v>
       </c>
-      <c r="G120" s="80">
+      <c r="G120" s="78">
         <f t="shared" si="11"/>
         <v>187921.8</v>
       </c>
-      <c r="H120" s="79">
+      <c r="H120" s="69">
         <v>86846</v>
       </c>
-      <c r="I120" s="79">
+      <c r="I120" s="69">
         <v>86846</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="54" t="s">
+      <c r="A121" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="B121" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C121" s="75" t="s">
+      <c r="B121" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C121" s="122"/>
+      <c r="D121" s="122"/>
+      <c r="E121" s="123"/>
+      <c r="F121" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G121" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H121" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I121" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D121" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E121" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F121" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G121" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H121" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I121" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B122" s="79">
+      <c r="B122" s="69">
         <v>139695</v>
       </c>
-      <c r="C122" s="79">
+      <c r="C122" s="69">
         <v>69848</v>
       </c>
-      <c r="D122" s="79">
+      <c r="D122" s="69">
         <v>69848</v>
       </c>
-      <c r="E122" s="79">
+      <c r="E122" s="69">
         <v>69848</v>
       </c>
-      <c r="F122" s="80">
+      <c r="F122" s="78">
         <f t="shared" si="10"/>
         <v>97786.5</v>
       </c>
-      <c r="G122" s="80">
+      <c r="G122" s="78">
         <f t="shared" si="11"/>
         <v>83817</v>
       </c>
-      <c r="H122" s="79">
+      <c r="H122" s="69">
         <v>38735</v>
       </c>
-      <c r="I122" s="79">
+      <c r="I122" s="69">
         <v>38735</v>
       </c>
     </row>
@@ -8084,30 +8118,30 @@
       <c r="A123" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B123" s="79">
+      <c r="B123" s="69">
         <v>153373</v>
       </c>
-      <c r="C123" s="79">
+      <c r="C123" s="69">
         <v>76687</v>
       </c>
-      <c r="D123" s="79">
+      <c r="D123" s="69">
         <v>76687</v>
       </c>
-      <c r="E123" s="79">
+      <c r="E123" s="69">
         <v>76687</v>
       </c>
-      <c r="F123" s="80">
+      <c r="F123" s="78">
         <f t="shared" si="10"/>
         <v>107361.09999999999</v>
       </c>
-      <c r="G123" s="80">
+      <c r="G123" s="78">
         <f t="shared" si="11"/>
         <v>92023.8</v>
       </c>
-      <c r="H123" s="79">
+      <c r="H123" s="69">
         <v>42528</v>
       </c>
-      <c r="I123" s="79">
+      <c r="I123" s="69">
         <v>42528</v>
       </c>
     </row>
@@ -8115,30 +8149,30 @@
       <c r="A124" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B124" s="79">
+      <c r="B124" s="69">
         <v>184044</v>
       </c>
-      <c r="C124" s="79">
+      <c r="C124" s="69">
         <v>92022</v>
       </c>
-      <c r="D124" s="79">
+      <c r="D124" s="69">
         <v>92022</v>
       </c>
-      <c r="E124" s="79">
+      <c r="E124" s="69">
         <v>92022</v>
       </c>
-      <c r="F124" s="80">
+      <c r="F124" s="78">
         <f t="shared" si="10"/>
         <v>128830.79999999999</v>
       </c>
-      <c r="G124" s="80">
+      <c r="G124" s="78">
         <f t="shared" si="11"/>
         <v>110426.4</v>
       </c>
-      <c r="H124" s="79">
+      <c r="H124" s="69">
         <v>51032</v>
       </c>
-      <c r="I124" s="79">
+      <c r="I124" s="69">
         <v>51032</v>
       </c>
     </row>
@@ -8146,90 +8180,84 @@
       <c r="A125" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B125" s="79">
+      <c r="B125" s="69">
         <v>49078</v>
       </c>
-      <c r="C125" s="79">
+      <c r="C125" s="69">
         <v>24539</v>
       </c>
-      <c r="D125" s="79">
+      <c r="D125" s="69">
         <v>24539</v>
       </c>
-      <c r="E125" s="79">
+      <c r="E125" s="69">
         <v>24539</v>
       </c>
-      <c r="F125" s="80">
+      <c r="F125" s="78">
         <f t="shared" si="10"/>
         <v>34354.6</v>
       </c>
-      <c r="G125" s="80">
+      <c r="G125" s="78">
         <f t="shared" si="11"/>
         <v>29446.799999999999</v>
       </c>
-      <c r="H125" s="79">
+      <c r="H125" s="69">
         <v>13608</v>
       </c>
-      <c r="I125" s="79">
+      <c r="I125" s="69">
         <v>13608</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="54" t="s">
+      <c r="A126" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="B126" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C126" s="75" t="s">
+      <c r="B126" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C126" s="122"/>
+      <c r="D126" s="122"/>
+      <c r="E126" s="123"/>
+      <c r="F126" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G126" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H126" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I126" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D126" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E126" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F126" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G126" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H126" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I126" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B127" s="79">
+      <c r="B127" s="69">
         <v>661862</v>
       </c>
-      <c r="C127" s="79">
+      <c r="C127" s="69">
         <v>330931</v>
       </c>
-      <c r="D127" s="79">
+      <c r="D127" s="69">
         <v>330931</v>
       </c>
-      <c r="E127" s="79">
+      <c r="E127" s="69">
         <v>330931</v>
       </c>
-      <c r="F127" s="80">
+      <c r="F127" s="78">
         <f t="shared" si="10"/>
         <v>463303.39999999997</v>
       </c>
-      <c r="G127" s="80">
+      <c r="G127" s="78">
         <f t="shared" si="11"/>
         <v>397117.2</v>
       </c>
-      <c r="H127" s="79">
+      <c r="H127" s="69">
         <v>183523</v>
       </c>
-      <c r="I127" s="79">
+      <c r="I127" s="69">
         <v>183523</v>
       </c>
     </row>
@@ -8237,1127 +8265,1097 @@
       <c r="A128" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B128" s="79">
+      <c r="B128" s="69">
         <v>692556</v>
       </c>
-      <c r="C128" s="79">
+      <c r="C128" s="69">
         <v>346278</v>
       </c>
-      <c r="D128" s="79">
+      <c r="D128" s="69">
         <v>346278</v>
       </c>
-      <c r="E128" s="79">
+      <c r="E128" s="69">
         <v>346278</v>
       </c>
-      <c r="F128" s="80">
+      <c r="F128" s="78">
         <f t="shared" si="10"/>
         <v>484789.19999999995</v>
       </c>
-      <c r="G128" s="80">
+      <c r="G128" s="78">
         <f t="shared" si="11"/>
         <v>415533.6</v>
       </c>
-      <c r="H128" s="79">
+      <c r="H128" s="69">
         <v>192034</v>
       </c>
-      <c r="I128" s="79">
+      <c r="I128" s="69">
         <v>192034</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="53" t="s">
+      <c r="A129" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B129" s="79">
+      <c r="B129" s="69">
         <v>90078</v>
       </c>
-      <c r="C129" s="79">
+      <c r="C129" s="69">
         <v>45039</v>
       </c>
-      <c r="D129" s="79">
+      <c r="D129" s="69">
         <v>45039</v>
       </c>
-      <c r="E129" s="79">
+      <c r="E129" s="69">
         <v>45039</v>
       </c>
-      <c r="F129" s="80">
+      <c r="F129" s="78">
         <f t="shared" si="10"/>
         <v>63054.6</v>
       </c>
-      <c r="G129" s="80">
+      <c r="G129" s="78">
         <f t="shared" si="11"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="H129" s="79">
+      <c r="H129" s="69">
         <v>24977</v>
       </c>
-      <c r="I129" s="79">
+      <c r="I129" s="69">
         <v>24977</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A130" s="57" t="s">
-        <v>177</v>
-      </c>
-      <c r="B130" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C130" s="75" t="s">
+      <c r="A130" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="B130" s="121"/>
+      <c r="C130" s="122"/>
+      <c r="D130" s="122"/>
+      <c r="E130" s="123"/>
+      <c r="F130" s="86"/>
+      <c r="G130" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="H130" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="I130" s="74" t="s">
         <v>130</v>
-      </c>
-      <c r="D130" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E130" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="F130" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G130" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H130" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="I130" s="78" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B131" s="79">
+      <c r="B131" s="69">
         <f>+G131/0.6</f>
         <v>157351.66666666669</v>
       </c>
-      <c r="C131" s="79">
+      <c r="C131" s="69">
         <v>94411</v>
       </c>
-      <c r="D131" s="79">
+      <c r="D131" s="69">
         <v>94411</v>
       </c>
-      <c r="E131" s="79">
+      <c r="E131" s="69">
         <v>94411</v>
       </c>
-      <c r="F131" s="79">
+      <c r="F131" s="69">
         <f>+B131*0.7</f>
         <v>110146.16666666667</v>
       </c>
-      <c r="G131" s="82">
+      <c r="G131" s="75">
         <f>+E131</f>
         <v>94411</v>
       </c>
-      <c r="H131" s="79"/>
-      <c r="I131" s="79"/>
+      <c r="H131" s="69"/>
+      <c r="I131" s="69"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B132" s="79">
+      <c r="B132" s="69">
         <f t="shared" ref="B132:B150" si="12">+G132/0.6</f>
         <v>78706.666666666672</v>
       </c>
-      <c r="C132" s="79">
+      <c r="C132" s="69">
         <v>47224</v>
       </c>
-      <c r="D132" s="79">
+      <c r="D132" s="69">
         <v>47224</v>
       </c>
-      <c r="E132" s="79">
+      <c r="E132" s="69">
         <v>47224</v>
       </c>
-      <c r="F132" s="79">
+      <c r="F132" s="69">
         <f t="shared" ref="F132:F151" si="13">+B132*0.7</f>
         <v>55094.666666666664</v>
       </c>
-      <c r="G132" s="82">
+      <c r="G132" s="75">
         <f t="shared" ref="G132:G150" si="14">+E132</f>
         <v>47224</v>
       </c>
-      <c r="H132" s="79"/>
-      <c r="I132" s="79"/>
+      <c r="H132" s="69"/>
+      <c r="I132" s="69"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B133" s="79">
+      <c r="B133" s="69">
         <f t="shared" si="12"/>
         <v>150468.33333333334</v>
       </c>
-      <c r="C133" s="79">
+      <c r="C133" s="69">
         <v>90281</v>
       </c>
-      <c r="D133" s="79">
+      <c r="D133" s="69">
         <v>90281</v>
       </c>
-      <c r="E133" s="79">
+      <c r="E133" s="69">
         <v>90281</v>
       </c>
-      <c r="F133" s="79">
+      <c r="F133" s="69">
         <f t="shared" si="13"/>
         <v>105327.83333333333</v>
       </c>
-      <c r="G133" s="82">
+      <c r="G133" s="75">
         <f t="shared" si="14"/>
         <v>90281</v>
       </c>
-      <c r="H133" s="79"/>
-      <c r="I133" s="79"/>
+      <c r="H133" s="69"/>
+      <c r="I133" s="69"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B134" s="79">
+      <c r="B134" s="69">
         <f t="shared" si="12"/>
         <v>141788.33333333334</v>
       </c>
-      <c r="C134" s="79">
+      <c r="C134" s="69">
         <v>85073</v>
       </c>
-      <c r="D134" s="79">
+      <c r="D134" s="69">
         <v>85073</v>
       </c>
-      <c r="E134" s="79">
+      <c r="E134" s="69">
         <v>85073</v>
       </c>
-      <c r="F134" s="79">
+      <c r="F134" s="69">
         <f t="shared" si="13"/>
         <v>99251.833333333328</v>
       </c>
-      <c r="G134" s="82">
+      <c r="G134" s="75">
         <f t="shared" si="14"/>
         <v>85073</v>
       </c>
-      <c r="H134" s="79"/>
-      <c r="I134" s="79"/>
+      <c r="H134" s="69"/>
+      <c r="I134" s="69"/>
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="79">
+      <c r="B135" s="69">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C135" s="79">
+      <c r="C135" s="69">
         <v>16783</v>
       </c>
-      <c r="D135" s="79">
+      <c r="D135" s="69">
         <v>16783</v>
       </c>
-      <c r="E135" s="79">
+      <c r="E135" s="69">
         <v>16783</v>
       </c>
-      <c r="F135" s="79">
+      <c r="F135" s="69">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G135" s="82">
+      <c r="G135" s="75">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H135" s="79"/>
-      <c r="I135" s="79"/>
+      <c r="H135" s="69"/>
+      <c r="I135" s="69"/>
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B136" s="79">
+      <c r="B136" s="69">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C136" s="79">
+      <c r="C136" s="69">
         <v>16783</v>
       </c>
-      <c r="D136" s="79">
+      <c r="D136" s="69">
         <v>16783</v>
       </c>
-      <c r="E136" s="79">
+      <c r="E136" s="69">
         <v>16783</v>
       </c>
-      <c r="F136" s="79">
+      <c r="F136" s="69">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G136" s="82">
+      <c r="G136" s="75">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H136" s="79"/>
-      <c r="I136" s="79"/>
+      <c r="H136" s="69"/>
+      <c r="I136" s="69"/>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B137" s="79">
+      <c r="B137" s="69">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C137" s="79">
+      <c r="C137" s="69">
         <v>16783</v>
       </c>
-      <c r="D137" s="79">
+      <c r="D137" s="69">
         <v>16783</v>
       </c>
-      <c r="E137" s="79">
+      <c r="E137" s="69">
         <v>16783</v>
       </c>
-      <c r="F137" s="79">
+      <c r="F137" s="69">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G137" s="82">
+      <c r="G137" s="75">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H137" s="79"/>
-      <c r="I137" s="79"/>
+      <c r="H137" s="69"/>
+      <c r="I137" s="69"/>
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B138" s="79">
+      <c r="B138" s="69">
         <f t="shared" si="12"/>
         <v>27198.333333333336</v>
       </c>
-      <c r="C138" s="79">
+      <c r="C138" s="69">
         <v>16319</v>
       </c>
-      <c r="D138" s="79">
+      <c r="D138" s="69">
         <v>16319</v>
       </c>
-      <c r="E138" s="79">
+      <c r="E138" s="69">
         <v>16319</v>
       </c>
-      <c r="F138" s="79">
+      <c r="F138" s="69">
         <f t="shared" si="13"/>
         <v>19038.833333333332</v>
       </c>
-      <c r="G138" s="82">
+      <c r="G138" s="75">
         <f t="shared" si="14"/>
         <v>16319</v>
       </c>
-      <c r="H138" s="79"/>
-      <c r="I138" s="79"/>
+      <c r="H138" s="69"/>
+      <c r="I138" s="69"/>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B139" s="79">
+      <c r="B139" s="69">
         <f t="shared" si="12"/>
         <v>20146.666666666668</v>
       </c>
-      <c r="C139" s="79">
+      <c r="C139" s="69">
         <v>12088</v>
       </c>
-      <c r="D139" s="79">
+      <c r="D139" s="69">
         <v>12088</v>
       </c>
-      <c r="E139" s="79">
+      <c r="E139" s="69">
         <v>12088</v>
       </c>
-      <c r="F139" s="79">
+      <c r="F139" s="69">
         <f t="shared" si="13"/>
         <v>14102.666666666666</v>
       </c>
-      <c r="G139" s="82">
+      <c r="G139" s="75">
         <f t="shared" si="14"/>
         <v>12088</v>
       </c>
-      <c r="H139" s="79"/>
-      <c r="I139" s="79"/>
+      <c r="H139" s="69"/>
+      <c r="I139" s="69"/>
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B140" s="79">
+      <c r="B140" s="69">
         <f t="shared" si="12"/>
         <v>22550</v>
       </c>
-      <c r="C140" s="79">
+      <c r="C140" s="69">
         <v>13530</v>
       </c>
-      <c r="D140" s="79">
+      <c r="D140" s="69">
         <v>13530</v>
       </c>
-      <c r="E140" s="79">
+      <c r="E140" s="69">
         <v>13530</v>
       </c>
-      <c r="F140" s="79">
+      <c r="F140" s="69">
         <f t="shared" si="13"/>
         <v>15784.999999999998</v>
       </c>
-      <c r="G140" s="82">
+      <c r="G140" s="75">
         <f t="shared" si="14"/>
         <v>13530</v>
       </c>
-      <c r="H140" s="79"/>
-      <c r="I140" s="79"/>
+      <c r="H140" s="69"/>
+      <c r="I140" s="69"/>
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B141" s="79">
+      <c r="B141" s="69">
         <f t="shared" si="12"/>
         <v>22550</v>
       </c>
-      <c r="C141" s="79">
+      <c r="C141" s="69">
         <v>13530</v>
       </c>
-      <c r="D141" s="79">
+      <c r="D141" s="69">
         <v>13530</v>
       </c>
-      <c r="E141" s="79">
+      <c r="E141" s="69">
         <v>13530</v>
       </c>
-      <c r="F141" s="79">
+      <c r="F141" s="69">
         <f t="shared" si="13"/>
         <v>15784.999999999998</v>
       </c>
-      <c r="G141" s="82">
+      <c r="G141" s="75">
         <f t="shared" si="14"/>
         <v>13530</v>
       </c>
-      <c r="H141" s="79"/>
-      <c r="I141" s="79"/>
+      <c r="H141" s="69"/>
+      <c r="I141" s="69"/>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B142" s="79">
+      <c r="B142" s="69">
         <f t="shared" si="12"/>
         <v>33800</v>
       </c>
-      <c r="C142" s="79">
+      <c r="C142" s="69">
         <v>20280</v>
       </c>
-      <c r="D142" s="79">
+      <c r="D142" s="69">
         <v>20280</v>
       </c>
-      <c r="E142" s="79">
+      <c r="E142" s="69">
         <v>20280</v>
       </c>
-      <c r="F142" s="79">
+      <c r="F142" s="69">
         <f t="shared" si="13"/>
         <v>23660</v>
       </c>
-      <c r="G142" s="82">
+      <c r="G142" s="75">
         <f t="shared" si="14"/>
         <v>20280</v>
       </c>
-      <c r="H142" s="79"/>
-      <c r="I142" s="79"/>
+      <c r="H142" s="69"/>
+      <c r="I142" s="69"/>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B143" s="79">
+      <c r="B143" s="69">
         <f t="shared" si="12"/>
         <v>28428.333333333336</v>
       </c>
-      <c r="C143" s="79">
+      <c r="C143" s="69">
         <v>17057</v>
       </c>
-      <c r="D143" s="79">
+      <c r="D143" s="69">
         <v>17057</v>
       </c>
-      <c r="E143" s="79">
+      <c r="E143" s="69">
         <v>17057</v>
       </c>
-      <c r="F143" s="79">
+      <c r="F143" s="69">
         <f t="shared" si="13"/>
         <v>19899.833333333332</v>
       </c>
-      <c r="G143" s="82">
+      <c r="G143" s="75">
         <f t="shared" si="14"/>
         <v>17057</v>
       </c>
-      <c r="H143" s="79"/>
-      <c r="I143" s="79"/>
+      <c r="H143" s="69"/>
+      <c r="I143" s="69"/>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B144" s="79">
+      <c r="B144" s="69">
         <f t="shared" si="12"/>
         <v>26893.333333333336</v>
       </c>
-      <c r="C144" s="79">
+      <c r="C144" s="69">
         <v>16136</v>
       </c>
-      <c r="D144" s="79">
+      <c r="D144" s="69">
         <v>16136</v>
       </c>
-      <c r="E144" s="79">
+      <c r="E144" s="69">
         <v>16136</v>
       </c>
-      <c r="F144" s="79">
+      <c r="F144" s="69">
         <f t="shared" si="13"/>
         <v>18825.333333333332</v>
       </c>
-      <c r="G144" s="82">
+      <c r="G144" s="75">
         <f t="shared" si="14"/>
         <v>16136</v>
       </c>
-      <c r="H144" s="79"/>
-      <c r="I144" s="79"/>
+      <c r="H144" s="69"/>
+      <c r="I144" s="69"/>
     </row>
     <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B145" s="79">
+      <c r="B145" s="69">
         <f t="shared" si="12"/>
         <v>26893.333333333336</v>
       </c>
-      <c r="C145" s="79">
+      <c r="C145" s="69">
         <v>16136</v>
       </c>
-      <c r="D145" s="79">
+      <c r="D145" s="69">
         <v>16136</v>
       </c>
-      <c r="E145" s="79">
+      <c r="E145" s="69">
         <v>16136</v>
       </c>
-      <c r="F145" s="79">
+      <c r="F145" s="69">
         <f t="shared" si="13"/>
         <v>18825.333333333332</v>
       </c>
-      <c r="G145" s="82">
+      <c r="G145" s="75">
         <f t="shared" si="14"/>
         <v>16136</v>
       </c>
-      <c r="H145" s="79"/>
-      <c r="I145" s="79"/>
+      <c r="H145" s="69"/>
+      <c r="I145" s="69"/>
     </row>
     <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B146" s="79">
+      <c r="B146" s="69">
         <f t="shared" si="12"/>
         <v>27198.333333333336</v>
       </c>
-      <c r="C146" s="79">
+      <c r="C146" s="69">
         <v>16319</v>
       </c>
-      <c r="D146" s="79">
+      <c r="D146" s="69">
         <v>16319</v>
       </c>
-      <c r="E146" s="79">
+      <c r="E146" s="69">
         <v>16319</v>
       </c>
-      <c r="F146" s="79">
+      <c r="F146" s="69">
         <f t="shared" si="13"/>
         <v>19038.833333333332</v>
       </c>
-      <c r="G146" s="82">
+      <c r="G146" s="75">
         <f t="shared" si="14"/>
         <v>16319</v>
       </c>
-      <c r="H146" s="79"/>
-      <c r="I146" s="79"/>
+      <c r="H146" s="69"/>
+      <c r="I146" s="69"/>
     </row>
     <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B147" s="79">
+      <c r="B147" s="69">
         <f t="shared" si="12"/>
         <v>32386.666666666668</v>
       </c>
-      <c r="C147" s="79">
+      <c r="C147" s="69">
         <v>19432</v>
       </c>
-      <c r="D147" s="79">
+      <c r="D147" s="69">
         <v>19432</v>
       </c>
-      <c r="E147" s="79">
+      <c r="E147" s="69">
         <v>19432</v>
       </c>
-      <c r="F147" s="79">
+      <c r="F147" s="69">
         <f t="shared" si="13"/>
         <v>22670.666666666668</v>
       </c>
-      <c r="G147" s="82">
+      <c r="G147" s="75">
         <f t="shared" si="14"/>
         <v>19432</v>
       </c>
-      <c r="H147" s="79"/>
-      <c r="I147" s="79"/>
+      <c r="H147" s="69"/>
+      <c r="I147" s="69"/>
     </row>
     <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B148" s="79">
+      <c r="B148" s="69">
         <f t="shared" si="12"/>
         <v>23586.666666666668</v>
       </c>
-      <c r="C148" s="79">
+      <c r="C148" s="69">
         <v>14152</v>
       </c>
-      <c r="D148" s="79">
+      <c r="D148" s="69">
         <v>14152</v>
       </c>
-      <c r="E148" s="79">
+      <c r="E148" s="69">
         <v>14152</v>
       </c>
-      <c r="F148" s="79">
+      <c r="F148" s="69">
         <f t="shared" si="13"/>
         <v>16510.666666666668</v>
       </c>
-      <c r="G148" s="82">
+      <c r="G148" s="75">
         <f t="shared" si="14"/>
         <v>14152</v>
       </c>
-      <c r="H148" s="79"/>
-      <c r="I148" s="79"/>
+      <c r="H148" s="69"/>
+      <c r="I148" s="69"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B149" s="79">
+      <c r="B149" s="69">
         <f t="shared" si="12"/>
         <v>57160</v>
       </c>
-      <c r="C149" s="79">
+      <c r="C149" s="69">
         <v>34296</v>
       </c>
-      <c r="D149" s="79">
+      <c r="D149" s="69">
         <v>34296</v>
       </c>
-      <c r="E149" s="79">
+      <c r="E149" s="69">
         <v>34296</v>
       </c>
-      <c r="F149" s="79">
+      <c r="F149" s="69">
         <f t="shared" si="13"/>
         <v>40012</v>
       </c>
-      <c r="G149" s="82">
+      <c r="G149" s="75">
         <f t="shared" si="14"/>
         <v>34296</v>
       </c>
-      <c r="H149" s="79"/>
-      <c r="I149" s="79"/>
+      <c r="H149" s="69"/>
+      <c r="I149" s="69"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B150" s="79">
+      <c r="B150" s="69">
         <f t="shared" si="12"/>
         <v>61121.666666666672</v>
       </c>
-      <c r="C150" s="79">
+      <c r="C150" s="69">
         <v>36673</v>
       </c>
-      <c r="D150" s="79">
+      <c r="D150" s="69">
         <v>36673</v>
       </c>
-      <c r="E150" s="79">
+      <c r="E150" s="69">
         <v>36673</v>
       </c>
-      <c r="F150" s="79">
+      <c r="F150" s="69">
         <f t="shared" si="13"/>
         <v>42785.166666666664</v>
       </c>
-      <c r="G150" s="82">
+      <c r="G150" s="75">
         <f t="shared" si="14"/>
         <v>36673</v>
       </c>
-      <c r="H150" s="79"/>
-      <c r="I150" s="79"/>
+      <c r="H150" s="69"/>
+      <c r="I150" s="69"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="11" t="s">
+      <c r="A151" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B151" s="79">
+      <c r="B151" s="117">
         <v>70000</v>
       </c>
-      <c r="C151" s="79">
+      <c r="C151" s="117">
         <v>40000</v>
       </c>
-      <c r="D151" s="79">
+      <c r="D151" s="117">
         <v>40000</v>
       </c>
-      <c r="E151" s="79">
+      <c r="E151" s="117">
         <v>40000</v>
       </c>
-      <c r="F151" s="79">
+      <c r="F151" s="117">
         <f t="shared" si="13"/>
         <v>49000</v>
       </c>
-      <c r="G151" s="82">
+      <c r="G151" s="104">
         <f>+B151*0.6</f>
         <v>42000</v>
       </c>
-      <c r="H151" s="79">
+      <c r="H151" s="117">
         <v>20000</v>
       </c>
-      <c r="I151" s="79">
+      <c r="I151" s="117">
         <v>20000</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="60" t="s">
+    <row r="152" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B152" s="99"/>
-      <c r="C152" s="99"/>
-      <c r="D152" s="99"/>
-      <c r="E152" s="99"/>
-      <c r="F152" s="99"/>
-      <c r="G152" s="99"/>
-      <c r="H152" s="99"/>
-      <c r="I152" s="99"/>
-    </row>
-    <row r="153" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="58" t="s">
+      <c r="B152" s="119"/>
+      <c r="C152" s="119"/>
+      <c r="D152" s="119"/>
+      <c r="E152" s="119"/>
+      <c r="F152" s="119"/>
+      <c r="G152" s="119"/>
+      <c r="H152" s="119"/>
+      <c r="I152" s="120"/>
+    </row>
+    <row r="153" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B153" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C153" s="100" t="s">
+      <c r="B153" s="128"/>
+      <c r="C153" s="102"/>
+      <c r="D153" s="102"/>
+      <c r="E153" s="102"/>
+      <c r="F153" s="102"/>
+      <c r="G153" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="H153" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="I153" s="103" t="s">
         <v>130</v>
       </c>
-      <c r="D153" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="E153" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="F153" s="100" t="s">
-        <v>98</v>
-      </c>
-      <c r="G153" s="100" t="s">
-        <v>99</v>
-      </c>
-      <c r="H153" s="100" t="s">
-        <v>100</v>
-      </c>
-      <c r="I153" s="100" t="s">
-        <v>133</v>
-      </c>
-      <c r="K153" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="L153" s="82">
+      <c r="K153" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="L153" s="70">
         <v>12000</v>
       </c>
     </row>
     <row r="154" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="B154" s="100"/>
-      <c r="C154" s="100"/>
-      <c r="D154" s="100"/>
-      <c r="E154" s="100"/>
-      <c r="F154" s="100"/>
-      <c r="G154" s="100">
+      <c r="A154" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="B154" s="89"/>
+      <c r="C154" s="89"/>
+      <c r="D154" s="89"/>
+      <c r="E154" s="89"/>
+      <c r="F154" s="89"/>
+      <c r="G154" s="89">
         <f>+$L$153</f>
         <v>12000</v>
       </c>
-      <c r="H154" s="100">
+      <c r="H154" s="89">
         <f t="shared" ref="H154:I154" si="15">+$L$153</f>
         <v>12000</v>
       </c>
-      <c r="I154" s="100">
+      <c r="I154" s="110">
         <f t="shared" si="15"/>
         <v>12000</v>
       </c>
     </row>
     <row r="155" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="B155" s="100"/>
-      <c r="C155" s="100"/>
-      <c r="D155" s="100"/>
-      <c r="E155" s="100"/>
-      <c r="F155" s="100"/>
-      <c r="G155" s="101">
+      <c r="A155" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155" s="87"/>
+      <c r="C155" s="87"/>
+      <c r="D155" s="87"/>
+      <c r="E155" s="87"/>
+      <c r="F155" s="87"/>
+      <c r="G155" s="88">
         <v>25000</v>
       </c>
-      <c r="H155" s="100">
+      <c r="H155" s="87">
         <f>+G155</f>
         <v>25000</v>
       </c>
-      <c r="I155" s="100">
+      <c r="I155" s="105">
         <f>+G155</f>
         <v>25000</v>
       </c>
-      <c r="K155" s="67" t="s">
-        <v>141</v>
-      </c>
-      <c r="L155" s="82">
+      <c r="K155" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="L155" s="70">
         <v>22000</v>
       </c>
     </row>
     <row r="156" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="B156" s="100"/>
-      <c r="C156" s="100"/>
-      <c r="D156" s="100"/>
-      <c r="E156" s="100"/>
-      <c r="F156" s="100"/>
-      <c r="G156" s="100">
+        <v>168</v>
+      </c>
+      <c r="B156" s="87"/>
+      <c r="C156" s="87"/>
+      <c r="D156" s="87"/>
+      <c r="E156" s="87"/>
+      <c r="F156" s="87"/>
+      <c r="G156" s="87">
         <f>+$L$155</f>
         <v>22000</v>
       </c>
-      <c r="H156" s="100">
+      <c r="H156" s="87">
         <f t="shared" ref="H156:I167" si="16">+$L$155</f>
         <v>22000</v>
       </c>
-      <c r="I156" s="100">
+      <c r="I156" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="157" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="B157" s="100"/>
-      <c r="C157" s="100"/>
-      <c r="D157" s="100"/>
-      <c r="E157" s="100"/>
-      <c r="F157" s="100"/>
-      <c r="G157" s="100">
+        <v>197</v>
+      </c>
+      <c r="B157" s="87"/>
+      <c r="C157" s="87"/>
+      <c r="D157" s="87"/>
+      <c r="E157" s="87"/>
+      <c r="F157" s="87"/>
+      <c r="G157" s="87">
         <f t="shared" ref="G157:G167" si="17">+$L$155</f>
         <v>22000</v>
       </c>
-      <c r="H157" s="100">
+      <c r="H157" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I157" s="100">
+      <c r="I157" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="158" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="B158" s="100"/>
-      <c r="C158" s="100"/>
-      <c r="D158" s="100"/>
-      <c r="E158" s="100"/>
-      <c r="F158" s="100"/>
-      <c r="G158" s="100">
+        <v>198</v>
+      </c>
+      <c r="B158" s="87"/>
+      <c r="C158" s="87"/>
+      <c r="D158" s="87"/>
+      <c r="E158" s="87"/>
+      <c r="F158" s="87"/>
+      <c r="G158" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H158" s="100">
+      <c r="H158" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I158" s="100">
+      <c r="I158" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="159" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="B159" s="100"/>
-      <c r="C159" s="100"/>
-      <c r="D159" s="100"/>
-      <c r="E159" s="100"/>
-      <c r="F159" s="100"/>
-      <c r="G159" s="100">
+        <v>180</v>
+      </c>
+      <c r="B159" s="87"/>
+      <c r="C159" s="87"/>
+      <c r="D159" s="87"/>
+      <c r="E159" s="87"/>
+      <c r="F159" s="87"/>
+      <c r="G159" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H159" s="100">
+      <c r="H159" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I159" s="100">
+      <c r="I159" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="160" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="B160" s="100"/>
-      <c r="C160" s="100"/>
-      <c r="D160" s="100"/>
-      <c r="E160" s="100"/>
-      <c r="F160" s="100"/>
-      <c r="G160" s="100">
+        <v>199</v>
+      </c>
+      <c r="B160" s="87"/>
+      <c r="C160" s="87"/>
+      <c r="D160" s="87"/>
+      <c r="E160" s="87"/>
+      <c r="F160" s="87"/>
+      <c r="G160" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H160" s="100">
+      <c r="H160" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I160" s="100">
+      <c r="I160" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="161" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="B161" s="100"/>
-      <c r="C161" s="100"/>
-      <c r="D161" s="100"/>
-      <c r="E161" s="100"/>
-      <c r="F161" s="100"/>
-      <c r="G161" s="100">
+        <v>200</v>
+      </c>
+      <c r="B161" s="87"/>
+      <c r="C161" s="87"/>
+      <c r="D161" s="87"/>
+      <c r="E161" s="87"/>
+      <c r="F161" s="87"/>
+      <c r="G161" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H161" s="100">
+      <c r="H161" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I161" s="100">
+      <c r="I161" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="162" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="B162" s="100"/>
-      <c r="C162" s="100"/>
-      <c r="D162" s="100"/>
-      <c r="E162" s="100"/>
-      <c r="F162" s="100"/>
-      <c r="G162" s="100">
+        <v>201</v>
+      </c>
+      <c r="B162" s="87"/>
+      <c r="C162" s="87"/>
+      <c r="D162" s="87"/>
+      <c r="E162" s="87"/>
+      <c r="F162" s="87"/>
+      <c r="G162" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H162" s="100">
+      <c r="H162" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I162" s="100">
+      <c r="I162" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="163" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="B163" s="100"/>
-      <c r="C163" s="100"/>
-      <c r="D163" s="100"/>
-      <c r="E163" s="100"/>
-      <c r="F163" s="100"/>
-      <c r="G163" s="100">
+        <v>202</v>
+      </c>
+      <c r="B163" s="87"/>
+      <c r="C163" s="87"/>
+      <c r="D163" s="87"/>
+      <c r="E163" s="87"/>
+      <c r="F163" s="87"/>
+      <c r="G163" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H163" s="100">
+      <c r="H163" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I163" s="100">
+      <c r="I163" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="164" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="B164" s="100"/>
-      <c r="C164" s="100"/>
-      <c r="D164" s="100"/>
-      <c r="E164" s="100"/>
-      <c r="F164" s="100"/>
-      <c r="G164" s="100">
+        <v>170</v>
+      </c>
+      <c r="B164" s="87"/>
+      <c r="C164" s="87"/>
+      <c r="D164" s="87"/>
+      <c r="E164" s="87"/>
+      <c r="F164" s="87"/>
+      <c r="G164" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H164" s="100">
+      <c r="H164" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I164" s="100">
+      <c r="I164" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="165" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B165" s="100"/>
-      <c r="C165" s="100"/>
-      <c r="D165" s="100"/>
-      <c r="E165" s="100"/>
-      <c r="F165" s="100"/>
-      <c r="G165" s="100">
+        <v>203</v>
+      </c>
+      <c r="B165" s="87"/>
+      <c r="C165" s="87"/>
+      <c r="D165" s="87"/>
+      <c r="E165" s="87"/>
+      <c r="F165" s="87"/>
+      <c r="G165" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H165" s="100">
+      <c r="H165" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I165" s="100">
+      <c r="I165" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="166" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="B166" s="100"/>
-      <c r="C166" s="100"/>
-      <c r="D166" s="100"/>
-      <c r="E166" s="100"/>
-      <c r="F166" s="100"/>
-      <c r="G166" s="100">
+        <v>192</v>
+      </c>
+      <c r="B166" s="87"/>
+      <c r="C166" s="87"/>
+      <c r="D166" s="87"/>
+      <c r="E166" s="87"/>
+      <c r="F166" s="87"/>
+      <c r="G166" s="87">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H166" s="100">
+      <c r="H166" s="87">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I166" s="100">
+      <c r="I166" s="105">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="167" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="B167" s="100"/>
-      <c r="C167" s="100"/>
-      <c r="D167" s="100"/>
-      <c r="E167" s="100"/>
-      <c r="F167" s="100"/>
-      <c r="G167" s="100">
+      <c r="A167" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B167" s="107"/>
+      <c r="C167" s="107"/>
+      <c r="D167" s="107"/>
+      <c r="E167" s="107"/>
+      <c r="F167" s="107"/>
+      <c r="G167" s="107">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H167" s="100">
+      <c r="H167" s="107">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I167" s="100">
+      <c r="I167" s="108">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
     </row>
     <row r="168" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B168" s="100"/>
-      <c r="C168" s="100"/>
-      <c r="D168" s="100"/>
-      <c r="E168" s="100"/>
-      <c r="F168" s="100"/>
-      <c r="G168" s="101">
+        <v>137</v>
+      </c>
+      <c r="B168" s="89"/>
+      <c r="C168" s="89"/>
+      <c r="D168" s="89"/>
+      <c r="E168" s="89"/>
+      <c r="F168" s="89"/>
+      <c r="G168" s="109">
         <v>32000</v>
       </c>
-      <c r="H168" s="101">
+      <c r="H168" s="109">
         <f t="shared" ref="H168:H169" si="18">+H167</f>
         <v>22000</v>
       </c>
-      <c r="I168" s="100"/>
+      <c r="I168" s="89"/>
     </row>
     <row r="169" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B169" s="100"/>
-      <c r="C169" s="100"/>
-      <c r="D169" s="100"/>
-      <c r="E169" s="100"/>
-      <c r="F169" s="100"/>
-      <c r="G169" s="101">
+      <c r="A169" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B169" s="95"/>
+      <c r="C169" s="95"/>
+      <c r="D169" s="95"/>
+      <c r="E169" s="95"/>
+      <c r="F169" s="95"/>
+      <c r="G169" s="94">
         <v>32000</v>
       </c>
-      <c r="H169" s="101">
+      <c r="H169" s="94">
         <f t="shared" si="18"/>
         <v>22000</v>
       </c>
-      <c r="I169" s="100"/>
+      <c r="I169" s="95"/>
     </row>
     <row r="170" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="59" t="s">
-        <v>179</v>
-      </c>
-      <c r="B170" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C170" s="102" t="s">
+      <c r="A170" s="93" t="s">
+        <v>171</v>
+      </c>
+      <c r="B170" s="128"/>
+      <c r="C170" s="129"/>
+      <c r="D170" s="129"/>
+      <c r="E170" s="102"/>
+      <c r="F170" s="102"/>
+      <c r="G170" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="H170" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="I170" s="103" t="s">
         <v>130</v>
-      </c>
-      <c r="D170" s="102" t="s">
-        <v>131</v>
-      </c>
-      <c r="E170" s="103" t="s">
-        <v>136</v>
-      </c>
-      <c r="F170" s="104" t="s">
-        <v>98</v>
-      </c>
-      <c r="G170" s="104" t="s">
-        <v>99</v>
-      </c>
-      <c r="H170" s="105" t="s">
-        <v>100</v>
-      </c>
-      <c r="I170" s="105" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B171" s="84"/>
-      <c r="C171" s="84"/>
-      <c r="D171" s="84"/>
-      <c r="E171" s="84"/>
-      <c r="F171" s="84"/>
-      <c r="G171" s="82">
+      <c r="B171" s="100"/>
+      <c r="C171" s="100"/>
+      <c r="D171" s="100"/>
+      <c r="E171" s="100"/>
+      <c r="F171" s="100"/>
+      <c r="G171" s="99">
         <v>24000</v>
       </c>
-      <c r="H171" s="84">
+      <c r="H171" s="100">
         <f>+G171</f>
         <v>24000</v>
       </c>
-      <c r="I171" s="84">
+      <c r="I171" s="101">
         <f>+G171</f>
         <v>24000</v>
       </c>
@@ -9366,519 +9364,519 @@
       <c r="A172" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B172" s="84"/>
-      <c r="C172" s="84"/>
-      <c r="D172" s="84"/>
-      <c r="E172" s="84"/>
-      <c r="F172" s="84"/>
-      <c r="G172" s="84"/>
-      <c r="H172" s="84">
-        <f t="shared" ref="H172:I215" si="19">+G172</f>
+      <c r="B172" s="76"/>
+      <c r="C172" s="76"/>
+      <c r="D172" s="76"/>
+      <c r="E172" s="76"/>
+      <c r="F172" s="76"/>
+      <c r="G172" s="76"/>
+      <c r="H172" s="76">
+        <f t="shared" ref="H172:I214" si="19">+G172</f>
         <v>0</v>
       </c>
-      <c r="I172" s="84">
+      <c r="I172" s="96">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="71" t="s">
-        <v>168</v>
-      </c>
-      <c r="B173" s="106"/>
-      <c r="C173" s="106"/>
-      <c r="D173" s="106"/>
-      <c r="E173" s="106"/>
-      <c r="F173" s="106"/>
-      <c r="G173" s="107">
+      <c r="A173" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B173" s="130"/>
+      <c r="C173" s="130"/>
+      <c r="D173" s="130"/>
+      <c r="E173" s="130"/>
+      <c r="F173" s="130"/>
+      <c r="G173" s="90">
         <f>$L$173</f>
         <v>16640</v>
       </c>
-      <c r="H173" s="107">
+      <c r="H173" s="90">
         <f t="shared" ref="H173:I173" si="20">$L$173</f>
         <v>16640</v>
       </c>
-      <c r="I173" s="107">
+      <c r="I173" s="97">
         <f t="shared" si="20"/>
         <v>16640</v>
       </c>
-      <c r="K173" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="L173" s="82">
+      <c r="K173" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="L173" s="70">
         <v>16640</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="B174" s="106"/>
-      <c r="C174" s="106"/>
-      <c r="D174" s="106"/>
-      <c r="E174" s="106"/>
-      <c r="F174" s="106"/>
-      <c r="G174" s="107">
+      <c r="A174" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="B174" s="130"/>
+      <c r="C174" s="130"/>
+      <c r="D174" s="130"/>
+      <c r="E174" s="130"/>
+      <c r="F174" s="130"/>
+      <c r="G174" s="90">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H174" s="107">
+      <c r="H174" s="90">
         <f t="shared" ref="H174:I174" si="21">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I174" s="107">
+      <c r="I174" s="97">
         <f t="shared" si="21"/>
         <v>9600</v>
       </c>
-      <c r="K174" s="67" t="s">
-        <v>167</v>
-      </c>
-      <c r="L174" s="82">
+      <c r="K174" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="L174" s="70">
         <v>9600</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B175" s="108"/>
-      <c r="C175" s="108"/>
-      <c r="D175" s="108"/>
-      <c r="E175" s="108"/>
-      <c r="F175" s="108"/>
-      <c r="G175" s="108">
+        <v>172</v>
+      </c>
+      <c r="B175" s="91"/>
+      <c r="C175" s="91"/>
+      <c r="D175" s="91"/>
+      <c r="E175" s="91"/>
+      <c r="F175" s="91"/>
+      <c r="G175" s="91">
         <f t="shared" ref="G175:I175" si="22">$L$173</f>
         <v>16640</v>
       </c>
-      <c r="H175" s="108">
+      <c r="H175" s="91">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I175" s="108">
+      <c r="I175" s="98">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="L175" s="73"/>
+      <c r="L175" s="68"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B176" s="108"/>
-      <c r="C176" s="108"/>
-      <c r="D176" s="108"/>
-      <c r="E176" s="108"/>
-      <c r="F176" s="108"/>
-      <c r="G176" s="108">
+        <v>159</v>
+      </c>
+      <c r="B176" s="91"/>
+      <c r="C176" s="91"/>
+      <c r="D176" s="91"/>
+      <c r="E176" s="91"/>
+      <c r="F176" s="91"/>
+      <c r="G176" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H176" s="108">
+      <c r="H176" s="91">
         <f t="shared" ref="H176:I176" si="23">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I176" s="108">
+      <c r="I176" s="98">
         <f t="shared" si="23"/>
         <v>9600</v>
       </c>
-      <c r="K176" s="67" t="s">
-        <v>141</v>
-      </c>
-      <c r="L176" s="82">
+      <c r="K176" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="L176" s="70">
         <v>32000</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B177" s="108"/>
-      <c r="C177" s="108"/>
-      <c r="D177" s="108"/>
-      <c r="E177" s="108"/>
-      <c r="F177" s="108"/>
-      <c r="G177" s="108">
+        <v>173</v>
+      </c>
+      <c r="B177" s="91"/>
+      <c r="C177" s="91"/>
+      <c r="D177" s="91"/>
+      <c r="E177" s="91"/>
+      <c r="F177" s="91"/>
+      <c r="G177" s="91">
         <f>$L$173</f>
         <v>16640</v>
       </c>
-      <c r="H177" s="108">
+      <c r="H177" s="91">
         <f t="shared" ref="H177:I177" si="24">$L$173</f>
         <v>16640</v>
       </c>
-      <c r="I177" s="108">
+      <c r="I177" s="98">
         <f t="shared" si="24"/>
         <v>16640</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B178" s="108"/>
-      <c r="C178" s="108"/>
-      <c r="D178" s="108"/>
-      <c r="E178" s="108"/>
-      <c r="F178" s="108"/>
-      <c r="G178" s="108">
+        <v>159</v>
+      </c>
+      <c r="B178" s="91"/>
+      <c r="C178" s="91"/>
+      <c r="D178" s="91"/>
+      <c r="E178" s="91"/>
+      <c r="F178" s="91"/>
+      <c r="G178" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H178" s="108">
+      <c r="H178" s="91">
         <f t="shared" ref="H178:I178" si="25">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I178" s="108">
+      <c r="I178" s="98">
         <f t="shared" si="25"/>
         <v>9600</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B179" s="108"/>
-      <c r="C179" s="108"/>
-      <c r="D179" s="108"/>
-      <c r="E179" s="108"/>
-      <c r="F179" s="108"/>
-      <c r="G179" s="108">
+        <v>174</v>
+      </c>
+      <c r="B179" s="91"/>
+      <c r="C179" s="91"/>
+      <c r="D179" s="91"/>
+      <c r="E179" s="91"/>
+      <c r="F179" s="91"/>
+      <c r="G179" s="91">
         <f t="shared" ref="G179:I187" si="26">$L$173</f>
         <v>16640</v>
       </c>
-      <c r="H179" s="108">
+      <c r="H179" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="I179" s="108">
+      <c r="I179" s="98">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B180" s="108"/>
-      <c r="C180" s="108"/>
-      <c r="D180" s="108"/>
-      <c r="E180" s="108"/>
-      <c r="F180" s="108"/>
-      <c r="G180" s="108">
+        <v>159</v>
+      </c>
+      <c r="B180" s="91"/>
+      <c r="C180" s="91"/>
+      <c r="D180" s="91"/>
+      <c r="E180" s="91"/>
+      <c r="F180" s="91"/>
+      <c r="G180" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H180" s="108">
+      <c r="H180" s="91">
         <f t="shared" ref="H180:I180" si="27">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I180" s="108">
+      <c r="I180" s="98">
         <f t="shared" si="27"/>
         <v>9600</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B181" s="108"/>
-      <c r="C181" s="108"/>
-      <c r="D181" s="108"/>
-      <c r="E181" s="108"/>
-      <c r="F181" s="108"/>
-      <c r="G181" s="108">
+        <v>175</v>
+      </c>
+      <c r="B181" s="91"/>
+      <c r="C181" s="91"/>
+      <c r="D181" s="91"/>
+      <c r="E181" s="91"/>
+      <c r="F181" s="91"/>
+      <c r="G181" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="H181" s="108">
+      <c r="H181" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="I181" s="108">
+      <c r="I181" s="98">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B182" s="108"/>
-      <c r="C182" s="108"/>
-      <c r="D182" s="108"/>
-      <c r="E182" s="108"/>
-      <c r="F182" s="108"/>
-      <c r="G182" s="108">
+        <v>159</v>
+      </c>
+      <c r="B182" s="91"/>
+      <c r="C182" s="91"/>
+      <c r="D182" s="91"/>
+      <c r="E182" s="91"/>
+      <c r="F182" s="91"/>
+      <c r="G182" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H182" s="108">
+      <c r="H182" s="91">
         <f t="shared" ref="H182:I182" si="28">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I182" s="108">
+      <c r="I182" s="98">
         <f t="shared" si="28"/>
         <v>9600</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B183" s="108"/>
-      <c r="C183" s="108"/>
-      <c r="D183" s="108"/>
-      <c r="E183" s="108"/>
-      <c r="F183" s="108"/>
-      <c r="G183" s="108">
+        <v>176</v>
+      </c>
+      <c r="B183" s="91"/>
+      <c r="C183" s="91"/>
+      <c r="D183" s="91"/>
+      <c r="E183" s="91"/>
+      <c r="F183" s="91"/>
+      <c r="G183" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="H183" s="108">
+      <c r="H183" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="I183" s="108">
+      <c r="I183" s="98">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B184" s="108"/>
-      <c r="C184" s="108"/>
-      <c r="D184" s="108"/>
-      <c r="E184" s="108"/>
-      <c r="F184" s="108"/>
-      <c r="G184" s="108">
+        <v>159</v>
+      </c>
+      <c r="B184" s="91"/>
+      <c r="C184" s="91"/>
+      <c r="D184" s="91"/>
+      <c r="E184" s="91"/>
+      <c r="F184" s="91"/>
+      <c r="G184" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H184" s="108">
+      <c r="H184" s="91">
         <f t="shared" ref="H184:I184" si="29">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I184" s="108">
+      <c r="I184" s="98">
         <f t="shared" si="29"/>
         <v>9600</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B185" s="108"/>
-      <c r="C185" s="108"/>
-      <c r="D185" s="108"/>
-      <c r="E185" s="108"/>
-      <c r="F185" s="108"/>
-      <c r="G185" s="108">
+        <v>177</v>
+      </c>
+      <c r="B185" s="91"/>
+      <c r="C185" s="91"/>
+      <c r="D185" s="91"/>
+      <c r="E185" s="91"/>
+      <c r="F185" s="91"/>
+      <c r="G185" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="H185" s="108">
+      <c r="H185" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="I185" s="108">
+      <c r="I185" s="98">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B186" s="108"/>
-      <c r="C186" s="108"/>
-      <c r="D186" s="108"/>
-      <c r="E186" s="108"/>
-      <c r="F186" s="108"/>
-      <c r="G186" s="108">
+        <v>159</v>
+      </c>
+      <c r="B186" s="91"/>
+      <c r="C186" s="91"/>
+      <c r="D186" s="91"/>
+      <c r="E186" s="91"/>
+      <c r="F186" s="91"/>
+      <c r="G186" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H186" s="108">
+      <c r="H186" s="91">
         <f t="shared" ref="H186:I186" si="30">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I186" s="108">
+      <c r="I186" s="98">
         <f t="shared" si="30"/>
         <v>9600</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B187" s="108"/>
-      <c r="C187" s="108"/>
-      <c r="D187" s="108"/>
-      <c r="E187" s="108"/>
-      <c r="F187" s="108"/>
-      <c r="G187" s="108">
+        <v>178</v>
+      </c>
+      <c r="B187" s="91"/>
+      <c r="C187" s="91"/>
+      <c r="D187" s="91"/>
+      <c r="E187" s="91"/>
+      <c r="F187" s="91"/>
+      <c r="G187" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="H187" s="108">
+      <c r="H187" s="91">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
-      <c r="I187" s="108">
+      <c r="I187" s="98">
         <f t="shared" si="26"/>
         <v>16640</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B188" s="108"/>
-      <c r="C188" s="108"/>
-      <c r="D188" s="108"/>
-      <c r="E188" s="108"/>
-      <c r="F188" s="108"/>
-      <c r="G188" s="108">
+        <v>159</v>
+      </c>
+      <c r="B188" s="91"/>
+      <c r="C188" s="91"/>
+      <c r="D188" s="91"/>
+      <c r="E188" s="91"/>
+      <c r="F188" s="91"/>
+      <c r="G188" s="91">
         <f>$L$174</f>
         <v>9600</v>
       </c>
-      <c r="H188" s="108">
+      <c r="H188" s="91">
         <f t="shared" ref="H188:I188" si="31">$L$174</f>
         <v>9600</v>
       </c>
-      <c r="I188" s="108">
+      <c r="I188" s="98">
         <f t="shared" si="31"/>
         <v>9600</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="B189" s="108"/>
-      <c r="C189" s="108"/>
-      <c r="D189" s="108"/>
-      <c r="E189" s="108"/>
-      <c r="F189" s="108"/>
-      <c r="G189" s="109">
+      <c r="A189" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B189" s="91"/>
+      <c r="C189" s="91"/>
+      <c r="D189" s="91"/>
+      <c r="E189" s="91"/>
+      <c r="F189" s="91"/>
+      <c r="G189" s="92">
         <v>36000</v>
       </c>
-      <c r="H189" s="108">
+      <c r="H189" s="91">
         <f t="shared" si="19"/>
         <v>36000</v>
       </c>
-      <c r="I189" s="108">
+      <c r="I189" s="98">
         <f>+G189</f>
         <v>36000</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B190" s="108"/>
-      <c r="C190" s="108"/>
-      <c r="D190" s="108"/>
-      <c r="E190" s="108"/>
-      <c r="F190" s="108"/>
-      <c r="G190" s="108">
+        <v>179</v>
+      </c>
+      <c r="B190" s="91"/>
+      <c r="C190" s="91"/>
+      <c r="D190" s="91"/>
+      <c r="E190" s="91"/>
+      <c r="F190" s="91"/>
+      <c r="G190" s="91">
         <f>$L$176</f>
         <v>32000</v>
       </c>
-      <c r="H190" s="108">
+      <c r="H190" s="91">
         <f t="shared" ref="H190:I190" si="32">$L$176</f>
         <v>32000</v>
       </c>
-      <c r="I190" s="108">
+      <c r="I190" s="98">
         <f t="shared" si="32"/>
         <v>32000</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="B191" s="108"/>
-      <c r="C191" s="108"/>
-      <c r="D191" s="108"/>
-      <c r="E191" s="108"/>
-      <c r="F191" s="108"/>
-      <c r="G191" s="108">
+        <v>180</v>
+      </c>
+      <c r="B191" s="91"/>
+      <c r="C191" s="91"/>
+      <c r="D191" s="91"/>
+      <c r="E191" s="91"/>
+      <c r="F191" s="91"/>
+      <c r="G191" s="91">
         <f t="shared" ref="G191:I208" si="33">$L$176</f>
         <v>32000</v>
       </c>
-      <c r="H191" s="108">
+      <c r="H191" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I191" s="108">
+      <c r="I191" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B192" s="108"/>
-      <c r="C192" s="108"/>
-      <c r="D192" s="108"/>
-      <c r="E192" s="108"/>
-      <c r="F192" s="108"/>
-      <c r="G192" s="108">
+        <v>181</v>
+      </c>
+      <c r="B192" s="91"/>
+      <c r="C192" s="91"/>
+      <c r="D192" s="91"/>
+      <c r="E192" s="91"/>
+      <c r="F192" s="91"/>
+      <c r="G192" s="91">
         <f>$L$176</f>
         <v>32000</v>
       </c>
-      <c r="H192" s="108">
+      <c r="H192" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I192" s="108">
+      <c r="I192" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B193" s="108"/>
-      <c r="C193" s="108"/>
-      <c r="D193" s="108"/>
-      <c r="E193" s="108"/>
-      <c r="F193" s="108"/>
-      <c r="G193" s="108">
+        <v>182</v>
+      </c>
+      <c r="B193" s="91"/>
+      <c r="C193" s="91"/>
+      <c r="D193" s="91"/>
+      <c r="E193" s="91"/>
+      <c r="F193" s="91"/>
+      <c r="G193" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H193" s="108">
+      <c r="H193" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I193" s="108">
+      <c r="I193" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B194" s="108"/>
-      <c r="C194" s="108"/>
-      <c r="D194" s="108"/>
-      <c r="E194" s="108"/>
-      <c r="F194" s="108"/>
-      <c r="G194" s="108">
+        <v>183</v>
+      </c>
+      <c r="B194" s="91"/>
+      <c r="C194" s="91"/>
+      <c r="D194" s="91"/>
+      <c r="E194" s="91"/>
+      <c r="F194" s="91"/>
+      <c r="G194" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H194" s="108">
+      <c r="H194" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I194" s="108">
+      <c r="I194" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
@@ -9887,20 +9885,20 @@
       <c r="A195" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B195" s="108"/>
-      <c r="C195" s="108"/>
-      <c r="D195" s="108"/>
-      <c r="E195" s="108"/>
-      <c r="F195" s="108"/>
-      <c r="G195" s="108">
+      <c r="B195" s="91"/>
+      <c r="C195" s="91"/>
+      <c r="D195" s="91"/>
+      <c r="E195" s="91"/>
+      <c r="F195" s="91"/>
+      <c r="G195" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H195" s="108">
+      <c r="H195" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I195" s="108">
+      <c r="I195" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
@@ -9909,174 +9907,174 @@
       <c r="A196" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B196" s="108"/>
-      <c r="C196" s="108"/>
-      <c r="D196" s="108"/>
-      <c r="E196" s="108"/>
-      <c r="F196" s="108"/>
-      <c r="G196" s="108">
+      <c r="B196" s="91"/>
+      <c r="C196" s="91"/>
+      <c r="D196" s="91"/>
+      <c r="E196" s="91"/>
+      <c r="F196" s="91"/>
+      <c r="G196" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H196" s="108">
+      <c r="H196" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I196" s="108">
+      <c r="I196" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B197" s="108"/>
-      <c r="C197" s="108"/>
-      <c r="D197" s="108"/>
-      <c r="E197" s="108"/>
-      <c r="F197" s="108"/>
-      <c r="G197" s="108">
+        <v>184</v>
+      </c>
+      <c r="B197" s="91"/>
+      <c r="C197" s="91"/>
+      <c r="D197" s="91"/>
+      <c r="E197" s="91"/>
+      <c r="F197" s="91"/>
+      <c r="G197" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H197" s="108">
+      <c r="H197" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I197" s="108">
+      <c r="I197" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B198" s="108"/>
-      <c r="C198" s="108"/>
-      <c r="D198" s="108"/>
-      <c r="E198" s="108"/>
-      <c r="F198" s="108"/>
-      <c r="G198" s="108">
+        <v>185</v>
+      </c>
+      <c r="B198" s="91"/>
+      <c r="C198" s="91"/>
+      <c r="D198" s="91"/>
+      <c r="E198" s="91"/>
+      <c r="F198" s="91"/>
+      <c r="G198" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H198" s="108">
+      <c r="H198" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I198" s="108">
+      <c r="I198" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="B199" s="108"/>
-      <c r="C199" s="108"/>
-      <c r="D199" s="108"/>
-      <c r="E199" s="108"/>
-      <c r="F199" s="108"/>
-      <c r="G199" s="108">
+        <v>186</v>
+      </c>
+      <c r="B199" s="91"/>
+      <c r="C199" s="91"/>
+      <c r="D199" s="91"/>
+      <c r="E199" s="91"/>
+      <c r="F199" s="91"/>
+      <c r="G199" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H199" s="108">
+      <c r="H199" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I199" s="108">
+      <c r="I199" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="B200" s="108"/>
-      <c r="C200" s="108"/>
-      <c r="D200" s="108"/>
-      <c r="E200" s="108"/>
-      <c r="F200" s="108"/>
-      <c r="G200" s="108">
+        <v>187</v>
+      </c>
+      <c r="B200" s="91"/>
+      <c r="C200" s="91"/>
+      <c r="D200" s="91"/>
+      <c r="E200" s="91"/>
+      <c r="F200" s="91"/>
+      <c r="G200" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H200" s="108">
+      <c r="H200" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I200" s="108">
+      <c r="I200" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="B201" s="108"/>
-      <c r="C201" s="108"/>
-      <c r="D201" s="108"/>
-      <c r="E201" s="108"/>
-      <c r="F201" s="108"/>
-      <c r="G201" s="108">
+        <v>188</v>
+      </c>
+      <c r="B201" s="91"/>
+      <c r="C201" s="91"/>
+      <c r="D201" s="91"/>
+      <c r="E201" s="91"/>
+      <c r="F201" s="91"/>
+      <c r="G201" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H201" s="108">
+      <c r="H201" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I201" s="108">
+      <c r="I201" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="B202" s="108"/>
-      <c r="C202" s="108"/>
-      <c r="D202" s="108"/>
-      <c r="E202" s="108"/>
-      <c r="F202" s="108"/>
-      <c r="G202" s="108">
+        <v>189</v>
+      </c>
+      <c r="B202" s="91"/>
+      <c r="C202" s="91"/>
+      <c r="D202" s="91"/>
+      <c r="E202" s="91"/>
+      <c r="F202" s="91"/>
+      <c r="G202" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H202" s="108">
+      <c r="H202" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I202" s="108">
+      <c r="I202" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="B203" s="108"/>
-      <c r="C203" s="108"/>
-      <c r="D203" s="108"/>
-      <c r="E203" s="108"/>
-      <c r="F203" s="108"/>
-      <c r="G203" s="108">
+        <v>190</v>
+      </c>
+      <c r="B203" s="91"/>
+      <c r="C203" s="91"/>
+      <c r="D203" s="91"/>
+      <c r="E203" s="91"/>
+      <c r="F203" s="91"/>
+      <c r="G203" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H203" s="108">
+      <c r="H203" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I203" s="108">
+      <c r="I203" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
@@ -10085,783 +10083,790 @@
       <c r="A204" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B204" s="108"/>
-      <c r="C204" s="108"/>
-      <c r="D204" s="108"/>
-      <c r="E204" s="108"/>
-      <c r="F204" s="108"/>
-      <c r="G204" s="108">
+      <c r="B204" s="91"/>
+      <c r="C204" s="91"/>
+      <c r="D204" s="91"/>
+      <c r="E204" s="91"/>
+      <c r="F204" s="91"/>
+      <c r="G204" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H204" s="108">
+      <c r="H204" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I204" s="108">
+      <c r="I204" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="B205" s="108"/>
-      <c r="C205" s="108"/>
-      <c r="D205" s="108"/>
-      <c r="E205" s="108"/>
-      <c r="F205" s="108"/>
-      <c r="G205" s="108">
+        <v>191</v>
+      </c>
+      <c r="B205" s="91"/>
+      <c r="C205" s="91"/>
+      <c r="D205" s="91"/>
+      <c r="E205" s="91"/>
+      <c r="F205" s="91"/>
+      <c r="G205" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H205" s="108">
+      <c r="H205" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I205" s="108">
+      <c r="I205" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="B206" s="108"/>
-      <c r="C206" s="108"/>
-      <c r="D206" s="108"/>
-      <c r="E206" s="108"/>
-      <c r="F206" s="108"/>
-      <c r="G206" s="109">
+      <c r="A206" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="B206" s="91"/>
+      <c r="C206" s="91"/>
+      <c r="D206" s="91"/>
+      <c r="E206" s="91"/>
+      <c r="F206" s="91"/>
+      <c r="G206" s="92">
         <v>35000</v>
       </c>
-      <c r="H206" s="108">
+      <c r="H206" s="91">
         <f>+G206</f>
         <v>35000</v>
       </c>
-      <c r="I206" s="108">
+      <c r="I206" s="98">
         <f>+G206</f>
         <v>35000</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="B207" s="108"/>
-      <c r="C207" s="108"/>
-      <c r="D207" s="108"/>
-      <c r="E207" s="108"/>
-      <c r="F207" s="108"/>
-      <c r="G207" s="108">
+        <v>193</v>
+      </c>
+      <c r="B207" s="91"/>
+      <c r="C207" s="91"/>
+      <c r="D207" s="91"/>
+      <c r="E207" s="91"/>
+      <c r="F207" s="91"/>
+      <c r="G207" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H207" s="108">
+      <c r="H207" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I207" s="108">
+      <c r="I207" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="B208" s="108"/>
-      <c r="C208" s="108"/>
-      <c r="D208" s="108"/>
-      <c r="E208" s="108"/>
-      <c r="F208" s="108"/>
-      <c r="G208" s="108">
+        <v>194</v>
+      </c>
+      <c r="B208" s="91"/>
+      <c r="C208" s="91"/>
+      <c r="D208" s="91"/>
+      <c r="E208" s="91"/>
+      <c r="F208" s="91"/>
+      <c r="G208" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="H208" s="108">
+      <c r="H208" s="91">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
-      <c r="I208" s="108">
+      <c r="I208" s="98">
         <f t="shared" si="33"/>
         <v>32000</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="B209" s="108"/>
-      <c r="C209" s="108"/>
-      <c r="D209" s="108"/>
-      <c r="E209" s="108"/>
-      <c r="F209" s="108"/>
-      <c r="G209" s="108">
+        <v>195</v>
+      </c>
+      <c r="B209" s="91"/>
+      <c r="C209" s="91"/>
+      <c r="D209" s="91"/>
+      <c r="E209" s="91"/>
+      <c r="F209" s="91"/>
+      <c r="G209" s="91">
         <f t="shared" ref="G209:I210" si="34">$L$176</f>
         <v>32000</v>
       </c>
-      <c r="H209" s="108">
+      <c r="H209" s="91">
         <f t="shared" si="34"/>
         <v>32000</v>
       </c>
-      <c r="I209" s="108">
+      <c r="I209" s="98">
         <f t="shared" si="34"/>
         <v>32000</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B210" s="108"/>
-      <c r="C210" s="108"/>
-      <c r="D210" s="108"/>
-      <c r="E210" s="108"/>
-      <c r="F210" s="108"/>
-      <c r="G210" s="108">
+        <v>196</v>
+      </c>
+      <c r="B210" s="91"/>
+      <c r="C210" s="91"/>
+      <c r="D210" s="91"/>
+      <c r="E210" s="91"/>
+      <c r="F210" s="91"/>
+      <c r="G210" s="91">
         <f t="shared" si="34"/>
         <v>32000</v>
       </c>
-      <c r="H210" s="108">
+      <c r="H210" s="91">
         <f t="shared" si="34"/>
         <v>32000</v>
       </c>
-      <c r="I210" s="108">
+      <c r="I210" s="98">
         <f t="shared" si="34"/>
         <v>32000</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B211" s="108"/>
-      <c r="C211" s="108"/>
-      <c r="D211" s="108"/>
-      <c r="E211" s="108"/>
-      <c r="F211" s="108"/>
-      <c r="G211" s="108">
+        <v>161</v>
+      </c>
+      <c r="B211" s="91"/>
+      <c r="C211" s="91"/>
+      <c r="D211" s="91"/>
+      <c r="E211" s="91"/>
+      <c r="F211" s="91"/>
+      <c r="G211" s="91">
         <v>78000</v>
       </c>
-      <c r="H211" s="108">
+      <c r="H211" s="91">
         <f t="shared" si="19"/>
         <v>78000</v>
       </c>
-      <c r="I211" s="108">
+      <c r="I211" s="98">
         <f t="shared" si="19"/>
         <v>78000</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B212" s="108"/>
-      <c r="C212" s="108"/>
-      <c r="D212" s="108"/>
-      <c r="E212" s="108"/>
-      <c r="F212" s="108"/>
-      <c r="G212" s="108">
+        <v>163</v>
+      </c>
+      <c r="B212" s="91"/>
+      <c r="C212" s="91"/>
+      <c r="D212" s="91"/>
+      <c r="E212" s="91"/>
+      <c r="F212" s="91"/>
+      <c r="G212" s="91">
         <v>60000</v>
       </c>
-      <c r="H212" s="108">
+      <c r="H212" s="91">
         <f t="shared" si="19"/>
         <v>60000</v>
       </c>
-      <c r="I212" s="108">
+      <c r="I212" s="98">
         <f t="shared" si="19"/>
         <v>60000</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="70" t="s">
-        <v>172</v>
-      </c>
-      <c r="B213" s="108"/>
-      <c r="C213" s="108"/>
-      <c r="D213" s="108"/>
-      <c r="E213" s="108"/>
-      <c r="F213" s="108"/>
-      <c r="G213" s="109">
+      <c r="A213" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B213" s="91"/>
+      <c r="C213" s="91"/>
+      <c r="D213" s="91"/>
+      <c r="E213" s="91"/>
+      <c r="F213" s="91"/>
+      <c r="G213" s="92">
         <v>100000</v>
       </c>
-      <c r="H213" s="108">
+      <c r="H213" s="91">
         <f t="shared" si="19"/>
         <v>100000</v>
       </c>
-      <c r="I213" s="108">
+      <c r="I213" s="98">
         <f t="shared" si="19"/>
         <v>100000</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A214" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="B214" s="108"/>
-      <c r="C214" s="108"/>
-      <c r="D214" s="108"/>
-      <c r="E214" s="108"/>
-      <c r="F214" s="108"/>
-      <c r="G214" s="109">
+      <c r="A214" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="B214" s="91"/>
+      <c r="C214" s="91"/>
+      <c r="D214" s="91"/>
+      <c r="E214" s="91"/>
+      <c r="F214" s="91"/>
+      <c r="G214" s="92">
         <v>75000</v>
       </c>
-      <c r="H214" s="108">
+      <c r="H214" s="91">
         <f t="shared" si="19"/>
         <v>75000</v>
       </c>
-      <c r="I214" s="108">
+      <c r="I214" s="98">
         <f t="shared" si="19"/>
         <v>75000</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B215" s="108"/>
-      <c r="C215" s="108"/>
-      <c r="D215" s="108"/>
-      <c r="E215" s="108"/>
-      <c r="F215" s="108"/>
-      <c r="G215" s="108">
+        <v>204</v>
+      </c>
+      <c r="B215" s="91"/>
+      <c r="C215" s="91"/>
+      <c r="D215" s="91"/>
+      <c r="E215" s="91"/>
+      <c r="F215" s="91"/>
+      <c r="G215" s="91">
         <f>+$L$215</f>
         <v>106880</v>
       </c>
-      <c r="H215" s="108">
+      <c r="H215" s="91">
         <f t="shared" ref="H215:I230" si="35">+$L$215</f>
         <v>106880</v>
       </c>
-      <c r="I215" s="108">
+      <c r="I215" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="K215" s="67" t="s">
-        <v>229</v>
-      </c>
-      <c r="L215" s="82">
+      <c r="K215" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="L215" s="70">
         <v>106880</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B216" s="108"/>
-      <c r="C216" s="108"/>
-      <c r="D216" s="108"/>
-      <c r="E216" s="108"/>
-      <c r="F216" s="108"/>
-      <c r="G216" s="108">
+        <v>205</v>
+      </c>
+      <c r="B216" s="91"/>
+      <c r="C216" s="91"/>
+      <c r="D216" s="91"/>
+      <c r="E216" s="91"/>
+      <c r="F216" s="91"/>
+      <c r="G216" s="91">
         <f t="shared" ref="G216:I231" si="36">+$L$215</f>
         <v>106880</v>
       </c>
-      <c r="H216" s="108">
+      <c r="H216" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I216" s="108">
+      <c r="I216" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B217" s="108"/>
-      <c r="C217" s="108"/>
-      <c r="D217" s="108"/>
-      <c r="E217" s="108"/>
-      <c r="F217" s="108"/>
-      <c r="G217" s="108">
+        <v>206</v>
+      </c>
+      <c r="B217" s="91"/>
+      <c r="C217" s="91"/>
+      <c r="D217" s="91"/>
+      <c r="E217" s="91"/>
+      <c r="F217" s="91"/>
+      <c r="G217" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H217" s="108">
+      <c r="H217" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I217" s="108">
+      <c r="I217" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B218" s="108"/>
-      <c r="C218" s="108"/>
-      <c r="D218" s="108"/>
-      <c r="E218" s="108"/>
-      <c r="F218" s="108"/>
-      <c r="G218" s="108">
+        <v>207</v>
+      </c>
+      <c r="B218" s="91"/>
+      <c r="C218" s="91"/>
+      <c r="D218" s="91"/>
+      <c r="E218" s="91"/>
+      <c r="F218" s="91"/>
+      <c r="G218" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H218" s="108">
+      <c r="H218" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I218" s="108">
+      <c r="I218" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B219" s="108"/>
-      <c r="C219" s="108"/>
-      <c r="D219" s="108"/>
-      <c r="E219" s="108"/>
-      <c r="F219" s="108"/>
-      <c r="G219" s="108">
+        <v>208</v>
+      </c>
+      <c r="B219" s="91"/>
+      <c r="C219" s="91"/>
+      <c r="D219" s="91"/>
+      <c r="E219" s="91"/>
+      <c r="F219" s="91"/>
+      <c r="G219" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H219" s="108">
+      <c r="H219" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I219" s="108">
+      <c r="I219" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B220" s="108"/>
-      <c r="C220" s="108"/>
-      <c r="D220" s="108"/>
-      <c r="E220" s="108"/>
-      <c r="F220" s="108"/>
-      <c r="G220" s="108">
+        <v>220</v>
+      </c>
+      <c r="B220" s="91"/>
+      <c r="C220" s="91"/>
+      <c r="D220" s="91"/>
+      <c r="E220" s="91"/>
+      <c r="F220" s="91"/>
+      <c r="G220" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H220" s="108">
+      <c r="H220" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I220" s="108">
+      <c r="I220" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B221" s="108"/>
-      <c r="C221" s="108"/>
-      <c r="D221" s="108"/>
-      <c r="E221" s="108"/>
-      <c r="F221" s="108"/>
-      <c r="G221" s="108">
+        <v>209</v>
+      </c>
+      <c r="B221" s="91"/>
+      <c r="C221" s="91"/>
+      <c r="D221" s="91"/>
+      <c r="E221" s="91"/>
+      <c r="F221" s="91"/>
+      <c r="G221" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H221" s="108">
+      <c r="H221" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I221" s="108">
+      <c r="I221" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B222" s="108"/>
-      <c r="C222" s="108"/>
-      <c r="D222" s="108"/>
-      <c r="E222" s="108"/>
-      <c r="F222" s="108"/>
-      <c r="G222" s="108">
+        <v>210</v>
+      </c>
+      <c r="B222" s="91"/>
+      <c r="C222" s="91"/>
+      <c r="D222" s="91"/>
+      <c r="E222" s="91"/>
+      <c r="F222" s="91"/>
+      <c r="G222" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H222" s="108">
+      <c r="H222" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I222" s="108">
+      <c r="I222" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B223" s="108"/>
-      <c r="C223" s="108"/>
-      <c r="D223" s="108"/>
-      <c r="E223" s="108"/>
-      <c r="F223" s="108"/>
-      <c r="G223" s="108">
+        <v>211</v>
+      </c>
+      <c r="B223" s="91"/>
+      <c r="C223" s="91"/>
+      <c r="D223" s="91"/>
+      <c r="E223" s="91"/>
+      <c r="F223" s="91"/>
+      <c r="G223" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H223" s="108">
+      <c r="H223" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I223" s="108">
+      <c r="I223" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="B224" s="108"/>
-      <c r="C224" s="108"/>
-      <c r="D224" s="108"/>
-      <c r="E224" s="108"/>
-      <c r="F224" s="108"/>
-      <c r="G224" s="108">
+        <v>212</v>
+      </c>
+      <c r="B224" s="91"/>
+      <c r="C224" s="91"/>
+      <c r="D224" s="91"/>
+      <c r="E224" s="91"/>
+      <c r="F224" s="91"/>
+      <c r="G224" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H224" s="108">
+      <c r="H224" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I224" s="108">
+      <c r="I224" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B225" s="108"/>
-      <c r="C225" s="108"/>
-      <c r="D225" s="108"/>
-      <c r="E225" s="108"/>
-      <c r="F225" s="108"/>
-      <c r="G225" s="108">
+        <v>213</v>
+      </c>
+      <c r="B225" s="91"/>
+      <c r="C225" s="91"/>
+      <c r="D225" s="91"/>
+      <c r="E225" s="91"/>
+      <c r="F225" s="91"/>
+      <c r="G225" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H225" s="108">
+      <c r="H225" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I225" s="108">
+      <c r="I225" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B226" s="108"/>
-      <c r="C226" s="108"/>
-      <c r="D226" s="108"/>
-      <c r="E226" s="108"/>
-      <c r="F226" s="108"/>
-      <c r="G226" s="108">
+        <v>214</v>
+      </c>
+      <c r="B226" s="91"/>
+      <c r="C226" s="91"/>
+      <c r="D226" s="91"/>
+      <c r="E226" s="91"/>
+      <c r="F226" s="91"/>
+      <c r="G226" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H226" s="108">
+      <c r="H226" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I226" s="108">
+      <c r="I226" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="B227" s="108"/>
-      <c r="C227" s="108"/>
-      <c r="D227" s="108"/>
-      <c r="E227" s="108"/>
-      <c r="F227" s="108"/>
-      <c r="G227" s="108">
+        <v>215</v>
+      </c>
+      <c r="B227" s="91"/>
+      <c r="C227" s="91"/>
+      <c r="D227" s="91"/>
+      <c r="E227" s="91"/>
+      <c r="F227" s="91"/>
+      <c r="G227" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H227" s="108">
+      <c r="H227" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I227" s="108">
+      <c r="I227" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B228" s="108"/>
-      <c r="C228" s="108"/>
-      <c r="D228" s="108"/>
-      <c r="E228" s="108"/>
-      <c r="F228" s="108"/>
-      <c r="G228" s="108">
+        <v>216</v>
+      </c>
+      <c r="B228" s="91"/>
+      <c r="C228" s="91"/>
+      <c r="D228" s="91"/>
+      <c r="E228" s="91"/>
+      <c r="F228" s="91"/>
+      <c r="G228" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H228" s="108">
+      <c r="H228" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I228" s="108">
+      <c r="I228" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="B229" s="108"/>
-      <c r="C229" s="108"/>
-      <c r="D229" s="108"/>
-      <c r="E229" s="108"/>
-      <c r="F229" s="108"/>
-      <c r="G229" s="108">
+        <v>217</v>
+      </c>
+      <c r="B229" s="91"/>
+      <c r="C229" s="91"/>
+      <c r="D229" s="91"/>
+      <c r="E229" s="91"/>
+      <c r="F229" s="91"/>
+      <c r="G229" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H229" s="108">
+      <c r="H229" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I229" s="108">
+      <c r="I229" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B230" s="108"/>
-      <c r="C230" s="108"/>
-      <c r="D230" s="108"/>
-      <c r="E230" s="108"/>
-      <c r="F230" s="108"/>
-      <c r="G230" s="108">
+        <v>218</v>
+      </c>
+      <c r="B230" s="91"/>
+      <c r="C230" s="91"/>
+      <c r="D230" s="91"/>
+      <c r="E230" s="91"/>
+      <c r="F230" s="91"/>
+      <c r="G230" s="91">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H230" s="108">
+      <c r="H230" s="91">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
-      <c r="I230" s="108">
+      <c r="I230" s="98">
         <f t="shared" si="35"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="B231" s="108"/>
-      <c r="C231" s="108"/>
-      <c r="D231" s="108"/>
-      <c r="E231" s="108"/>
-      <c r="F231" s="108"/>
-      <c r="G231" s="108">
+    <row r="231" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="111" t="s">
+        <v>219</v>
+      </c>
+      <c r="B231" s="112"/>
+      <c r="C231" s="112"/>
+      <c r="D231" s="112"/>
+      <c r="E231" s="112"/>
+      <c r="F231" s="112"/>
+      <c r="G231" s="112">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="H231" s="108">
+      <c r="H231" s="112">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
-      <c r="I231" s="108">
+      <c r="I231" s="113">
         <f t="shared" si="36"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="35"/>
-      <c r="B232" s="108"/>
-      <c r="C232" s="108"/>
-      <c r="D232" s="108"/>
-      <c r="E232" s="108"/>
-      <c r="F232" s="108"/>
-      <c r="G232" s="108"/>
-      <c r="H232" s="108"/>
-      <c r="I232" s="108"/>
-    </row>
-    <row r="233" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="59" t="s">
+    <row r="232" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="B233" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C233" s="110" t="s">
+      <c r="B232" s="128"/>
+      <c r="C232" s="129"/>
+      <c r="D232" s="129"/>
+      <c r="E232" s="102"/>
+      <c r="F232" s="102"/>
+      <c r="G232" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="H232" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="I232" s="103" t="s">
         <v>130</v>
       </c>
-      <c r="D233" s="110" t="s">
-        <v>131</v>
-      </c>
-      <c r="E233" s="111" t="s">
-        <v>136</v>
-      </c>
-      <c r="F233" s="100" t="s">
+    </row>
+    <row r="233" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B233" s="115"/>
+      <c r="C233" s="115"/>
+      <c r="D233" s="115"/>
+      <c r="E233" s="115"/>
+      <c r="F233" s="115"/>
+      <c r="G233" s="114">
+        <v>40000</v>
+      </c>
+      <c r="H233" s="115">
+        <f>+G233</f>
+        <v>40000</v>
+      </c>
+      <c r="I233" s="116">
+        <f>+G233</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="B234" s="128"/>
+      <c r="C234" s="102"/>
+      <c r="D234" s="102"/>
+      <c r="E234" s="102"/>
+      <c r="F234" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="G233" s="100" t="s">
+      <c r="G234" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="H233" s="112" t="s">
+      <c r="H234" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="I233" s="112" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B234" s="84"/>
-      <c r="C234" s="84"/>
-      <c r="D234" s="84"/>
-      <c r="E234" s="84"/>
-      <c r="F234" s="84"/>
-      <c r="G234" s="82">
-        <v>40000</v>
-      </c>
-      <c r="H234" s="84"/>
-      <c r="I234" s="84"/>
+      <c r="I234" s="103" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="B235" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C235" s="100" t="s">
-        <v>130</v>
-      </c>
-      <c r="D235" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="E235" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="F235" s="100" t="s">
-        <v>98</v>
-      </c>
-      <c r="G235" s="100" t="s">
-        <v>99</v>
-      </c>
-      <c r="H235" s="100" t="s">
-        <v>100</v>
-      </c>
-      <c r="I235" s="100" t="s">
-        <v>133</v>
+      <c r="A235" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B235" s="89"/>
+      <c r="C235" s="89"/>
+      <c r="D235" s="89"/>
+      <c r="E235" s="89"/>
+      <c r="F235" s="109">
+        <v>15000</v>
+      </c>
+      <c r="G235" s="109">
+        <v>15000</v>
+      </c>
+      <c r="H235" s="89">
+        <f>+$G$235</f>
+        <v>15000</v>
+      </c>
+      <c r="I235" s="110">
+        <f>+$G$235</f>
+        <v>15000</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="B236" s="100"/>
-      <c r="C236" s="100"/>
-      <c r="D236" s="100"/>
-      <c r="E236" s="100"/>
-      <c r="F236" s="101">
+      <c r="A236" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B236" s="87"/>
+      <c r="C236" s="87"/>
+      <c r="D236" s="87"/>
+      <c r="E236" s="87"/>
+      <c r="F236" s="88">
+        <v>18000</v>
+      </c>
+      <c r="G236" s="88">
         <v>15000</v>
       </c>
-      <c r="G236" s="101">
+      <c r="H236" s="87">
+        <f>+G236</f>
         <v>15000</v>
       </c>
-      <c r="H236" s="100"/>
-      <c r="I236" s="100"/>
+      <c r="I236" s="105">
+        <f>+G236</f>
+        <v>15000</v>
+      </c>
     </row>
     <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A237" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B237" s="100"/>
-      <c r="C237" s="100"/>
-      <c r="D237" s="100"/>
-      <c r="E237" s="100"/>
-      <c r="F237" s="101">
+      <c r="A237" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B237" s="87"/>
+      <c r="C237" s="87"/>
+      <c r="D237" s="87"/>
+      <c r="E237" s="87"/>
+      <c r="F237" s="88">
         <v>18000</v>
       </c>
-      <c r="G237" s="101">
+      <c r="G237" s="88">
         <v>15000</v>
       </c>
-      <c r="H237" s="100"/>
-      <c r="I237" s="100"/>
+      <c r="H237" s="87">
+        <f>+G237</f>
+        <v>15000</v>
+      </c>
+      <c r="I237" s="105">
+        <f>+G237</f>
+        <v>15000</v>
+      </c>
     </row>
     <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B238" s="100"/>
-      <c r="C238" s="100"/>
-      <c r="D238" s="100"/>
-      <c r="E238" s="100"/>
-      <c r="F238" s="101">
-        <v>18000</v>
-      </c>
-      <c r="G238" s="101">
-        <v>15000</v>
-      </c>
-      <c r="H238" s="100"/>
-      <c r="I238" s="100"/>
-    </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A239" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="B239" s="100"/>
-      <c r="C239" s="100"/>
-      <c r="D239" s="100"/>
-      <c r="E239" s="100"/>
-      <c r="F239" s="100"/>
-      <c r="G239" s="101">
+        <v>222</v>
+      </c>
+      <c r="B238" s="87"/>
+      <c r="C238" s="87"/>
+      <c r="D238" s="87"/>
+      <c r="E238" s="87"/>
+      <c r="F238" s="87"/>
+      <c r="G238" s="88">
         <v>20000</v>
       </c>
-      <c r="H239" s="100"/>
-      <c r="I239" s="100"/>
-    </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A240" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="B240" s="100"/>
-      <c r="C240" s="100"/>
-      <c r="D240" s="100"/>
-      <c r="E240" s="100"/>
-      <c r="F240" s="100"/>
-      <c r="G240" s="101">
+      <c r="H238" s="87">
+        <f>+G238</f>
         <v>20000</v>
       </c>
-      <c r="H240" s="100"/>
-      <c r="I240" s="100"/>
+      <c r="I238" s="105">
+        <f>+G238</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B239" s="107"/>
+      <c r="C239" s="107"/>
+      <c r="D239" s="107"/>
+      <c r="E239" s="107"/>
+      <c r="F239" s="107"/>
+      <c r="G239" s="106">
+        <v>20000</v>
+      </c>
+      <c r="H239" s="107">
+        <f>+G239</f>
+        <v>20000</v>
+      </c>
+      <c r="I239" s="108">
+        <f>+G239</f>
+        <v>20000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2577,7 +2577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A234" authorId="0" shapeId="0">
+    <comment ref="A231" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="226">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3145,9 +3145,6 @@
     <t>RX CONVENCIONAL (POR C/CODIGO)</t>
   </si>
   <si>
-    <t>ECOGRAFIAS (POR C/CODIGO)</t>
-  </si>
-  <si>
     <t>Ecografias Dra. Capponi</t>
   </si>
   <si>
@@ -3232,27 +3229,6 @@
     <t>ECOGRAFIA DE PENE</t>
   </si>
   <si>
-    <t>ECOGRAFIA DE PARTES BLANDAS</t>
-  </si>
-  <si>
-    <t>ECOGRAFIA TIROIDEA</t>
-  </si>
-  <si>
-    <t>ECOGRAFIA ABDOMINAL</t>
-  </si>
-  <si>
-    <t>ECOGRAFIA RENAL UNI O BILATERAL</t>
-  </si>
-  <si>
-    <t>ECOGRAFIA HEPATO-BILIO-PANCREATICA</t>
-  </si>
-  <si>
-    <t>ECOGRAFIA VESICAL O VESICOPROSTATICA</t>
-  </si>
-  <si>
-    <t>ECOGRAFIA GINECOLOGICA</t>
-  </si>
-  <si>
     <t>TAC OTROS ORGANOS Y REGIONES</t>
   </si>
   <si>
@@ -3311,6 +3287,36 @@
   </si>
   <si>
     <t>NEXO TERAPIA</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA DE PARTES BLANDAS (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TIROIDEA (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA MAMARIA UNI O BILATERAL (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA ABDOMINAL (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA RENAL UNI O BILATERAL (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA HEPATO-BILIO-PANCREATICA (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA VESICAL O VESICOPROSTATICA (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA GINECOLOGICA (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TRANSVAGINAL (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA TESTICULAR (POR C/CODIGO)</t>
   </si>
 </sst>
 </file>
@@ -3322,7 +3328,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3441,12 +3447,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -3454,7 +3454,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3548,12 +3548,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4076,7 +4070,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4206,15 +4200,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4269,9 +4259,6 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4288,9 +4275,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4354,10 +4338,10 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4387,9 +4371,6 @@
     <xf numFmtId="165" fontId="9" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="0" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4410,6 +4391,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4698,46 +4682,46 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.85546875" style="72" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="72" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.5703125" style="72" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5703125" style="72" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.85546875" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5703125" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5703125" style="70" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="73" t="s">
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="73" t="s">
+      <c r="G2" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="H2" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -4745,24 +4729,24 @@
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69">
+      <c r="B3" s="68"/>
+      <c r="C3" s="68">
         <v>5550</v>
       </c>
-      <c r="D3" s="69">
+      <c r="D3" s="68">
         <v>5550</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="68">
         <v>5550</v>
       </c>
-      <c r="F3" s="78">
+      <c r="F3" s="76">
         <v>5550</v>
       </c>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69">
+      <c r="G3" s="68"/>
+      <c r="H3" s="68">
         <v>4550</v>
       </c>
-      <c r="I3" s="69">
+      <c r="I3" s="68">
         <v>5550</v>
       </c>
     </row>
@@ -4770,20 +4754,20 @@
       <c r="A4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69">
+      <c r="B4" s="68"/>
+      <c r="C4" s="68">
         <v>8500</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="68">
         <v>8500</v>
       </c>
-      <c r="E4" s="69">
+      <c r="E4" s="68">
         <v>8500</v>
       </c>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69">
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68">
         <f>+I3*2</f>
         <v>11100</v>
       </c>
@@ -4792,24 +4776,24 @@
       <c r="A5" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68">
         <v>20000</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="68">
         <v>20000</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="68">
         <v>30000</v>
       </c>
-      <c r="F5" s="69">
+      <c r="F5" s="68">
         <v>15000</v>
       </c>
-      <c r="G5" s="69">
+      <c r="G5" s="68">
         <v>30000</v>
       </c>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69" t="s">
+      <c r="H5" s="68"/>
+      <c r="I5" s="68" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4817,48 +4801,48 @@
       <c r="A6" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68">
         <v>14000</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="68">
         <v>14000</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="68">
         <v>20000</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="73">
         <f>+F5/2</f>
         <v>7500</v>
       </c>
-      <c r="G6" s="75">
+      <c r="G6" s="73">
         <f>+G5/2</f>
         <v>15000</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="121"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="73" t="s">
+      <c r="B7" s="117"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J7" s="121" t="s">
+      <c r="J7" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K7" s="57"/>
@@ -4867,14 +4851,14 @@
       <c r="A8" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="11">
         <v>4800</v>
       </c>
@@ -4886,21 +4870,21 @@
       <c r="A9" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="69">
+      <c r="B9" s="68">
         <v>10000</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69">
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68">
         <v>4200</v>
       </c>
-      <c r="F9" s="69"/>
-      <c r="G9" s="75">
+      <c r="F9" s="68"/>
+      <c r="G9" s="73">
         <f>+B9*0.6</f>
         <v>6000</v>
       </c>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
     </row>
@@ -4908,20 +4892,20 @@
       <c r="A10" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="69">
+      <c r="B10" s="68">
         <v>30000</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69">
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68">
         <v>10000</v>
       </c>
-      <c r="F10" s="69"/>
-      <c r="G10" s="75">
+      <c r="F10" s="68"/>
+      <c r="G10" s="73">
         <v>15000</v>
       </c>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
     </row>
@@ -4929,20 +4913,20 @@
       <c r="A11" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="69">
+      <c r="B11" s="68">
         <v>25000</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69">
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68">
         <v>8000</v>
       </c>
-      <c r="F11" s="69"/>
-      <c r="G11" s="75">
+      <c r="F11" s="68"/>
+      <c r="G11" s="73">
         <v>12000</v>
       </c>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
@@ -4950,18 +4934,18 @@
       <c r="A12" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69">
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68">
         <v>17000</v>
       </c>
-      <c r="F12" s="69"/>
-      <c r="G12" s="76">
+      <c r="F12" s="68"/>
+      <c r="G12" s="74">
         <v>18000</v>
       </c>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
@@ -4969,18 +4953,18 @@
       <c r="A13" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69">
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68">
         <v>18400</v>
       </c>
-      <c r="F13" s="69"/>
-      <c r="G13" s="76">
+      <c r="F13" s="68"/>
+      <c r="G13" s="74">
         <v>20000</v>
       </c>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
@@ -4988,23 +4972,23 @@
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="121"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="73" t="s">
+      <c r="B14" s="117"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H14" s="74" t="s">
+      <c r="H14" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I14" s="74" t="s">
+      <c r="I14" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J14" s="121" t="s">
+      <c r="J14" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K14" s="60"/>
@@ -5013,28 +4997,28 @@
       <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="69">
+      <c r="B15" s="68">
         <v>88500</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69">
+      <c r="C15" s="68"/>
+      <c r="D15" s="68">
         <v>44800</v>
       </c>
-      <c r="E15" s="69">
+      <c r="E15" s="68">
         <v>44800</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="73">
         <f>+B15*0.7</f>
         <v>61949.999999999993</v>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="73">
         <f>+B15*0.6</f>
         <v>53100</v>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="68">
         <v>14750</v>
       </c>
-      <c r="I15" s="69">
+      <c r="I15" s="68">
         <v>0</v>
       </c>
       <c r="J15" s="11">
@@ -5048,28 +5032,28 @@
       <c r="A16" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="69">
+      <c r="B16" s="68">
         <v>177000</v>
       </c>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69">
+      <c r="C16" s="68"/>
+      <c r="D16" s="68">
         <v>88500</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="68">
         <v>88500</v>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="73">
         <f>+B16*0.7</f>
         <v>123899.99999999999</v>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="73">
         <f>+B16*0.6</f>
         <v>106200</v>
       </c>
-      <c r="H16" s="69">
+      <c r="H16" s="68">
         <v>29500</v>
       </c>
-      <c r="I16" s="69">
+      <c r="I16" s="68">
         <v>0</v>
       </c>
       <c r="J16" s="11">
@@ -5083,16 +5067,16 @@
       <c r="A17" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69">
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68">
         <v>16000</v>
       </c>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
@@ -5100,20 +5084,20 @@
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="121"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="123"/>
-      <c r="F18" s="73" t="s">
+      <c r="B18" s="117"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="73" t="s">
+      <c r="G18" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="74" t="s">
+      <c r="H18" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I18" s="74" t="s">
+      <c r="I18" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5121,45 +5105,45 @@
       <c r="A19" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="69">
+      <c r="B19" s="68">
         <v>20000</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69">
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68">
         <v>8000</v>
       </c>
-      <c r="F19" s="77">
+      <c r="F19" s="75">
         <v>0</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="73">
         <f>+B19*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="121"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="123"/>
-      <c r="F20" s="73" t="s">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="74" t="s">
+      <c r="H20" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="74" t="s">
+      <c r="I20" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J20" s="121" t="s">
+      <c r="J20" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K20" s="57"/>
@@ -5168,26 +5152,26 @@
       <c r="A21" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="69">
+      <c r="B21" s="68">
         <v>35000</v>
       </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69">
+      <c r="C21" s="68"/>
+      <c r="D21" s="68">
         <v>20000</v>
       </c>
-      <c r="E21" s="69">
+      <c r="E21" s="68">
         <v>20000</v>
       </c>
-      <c r="F21" s="77">
+      <c r="F21" s="75">
         <v>0</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="73">
         <v>20000</v>
       </c>
-      <c r="H21" s="69">
+      <c r="H21" s="68">
         <v>7000</v>
       </c>
-      <c r="I21" s="69">
+      <c r="I21" s="68">
         <v>0</v>
       </c>
       <c r="J21" s="11">
@@ -5201,23 +5185,23 @@
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="121"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="73" t="s">
+      <c r="B22" s="117"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="73" t="s">
+      <c r="G22" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H22" s="74" t="s">
+      <c r="H22" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I22" s="74" t="s">
+      <c r="I22" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J22" s="121" t="s">
+      <c r="J22" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K22" s="57"/>
@@ -5226,26 +5210,26 @@
       <c r="A23" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="69">
+      <c r="B23" s="68">
         <v>30000</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69">
+      <c r="C23" s="68"/>
+      <c r="D23" s="68">
         <v>8200</v>
       </c>
-      <c r="E23" s="69">
+      <c r="E23" s="68">
         <v>10400</v>
       </c>
-      <c r="F23" s="77">
+      <c r="F23" s="75">
         <v>18000</v>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="73">
         <v>15000</v>
       </c>
-      <c r="H23" s="69">
+      <c r="H23" s="68">
         <v>4200</v>
       </c>
-      <c r="I23" s="69">
+      <c r="I23" s="68">
         <v>0</v>
       </c>
       <c r="J23" s="11">
@@ -5259,23 +5243,23 @@
       <c r="A24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="123"/>
-      <c r="F24" s="73" t="s">
+      <c r="B24" s="117"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G24" s="73" t="s">
+      <c r="G24" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H24" s="74" t="s">
+      <c r="H24" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I24" s="74" t="s">
+      <c r="I24" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J24" s="121" t="s">
+      <c r="J24" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K24" s="57"/>
@@ -5284,30 +5268,30 @@
       <c r="A25" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="69">
+      <c r="B25" s="68">
         <v>20000</v>
       </c>
-      <c r="C25" s="69">
+      <c r="C25" s="68">
         <v>12600</v>
       </c>
-      <c r="D25" s="69">
+      <c r="D25" s="68">
         <v>8200</v>
       </c>
-      <c r="E25" s="69">
+      <c r="E25" s="68">
         <v>12600</v>
       </c>
-      <c r="F25" s="77">
+      <c r="F25" s="75">
         <f>+B25*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G25" s="75">
+      <c r="G25" s="73">
         <f>+B25*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H25" s="69">
+      <c r="H25" s="68">
         <v>5400</v>
       </c>
-      <c r="I25" s="69">
+      <c r="I25" s="68">
         <v>0</v>
       </c>
       <c r="J25" s="11">
@@ -5321,23 +5305,23 @@
       <c r="A26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="73" t="s">
+      <c r="B26" s="117"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="73" t="s">
+      <c r="G26" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H26" s="74" t="s">
+      <c r="H26" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I26" s="74" t="s">
+      <c r="I26" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J26" s="121" t="s">
+      <c r="J26" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K26" s="57"/>
@@ -5346,30 +5330,30 @@
       <c r="A27" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="69">
+      <c r="B27" s="68">
         <v>228334</v>
       </c>
-      <c r="C27" s="69">
+      <c r="C27" s="68">
         <v>149000</v>
       </c>
-      <c r="D27" s="69">
+      <c r="D27" s="68">
         <v>137000</v>
       </c>
-      <c r="E27" s="69">
+      <c r="E27" s="68">
         <v>149000</v>
       </c>
-      <c r="F27" s="77">
+      <c r="F27" s="75">
         <f>+B27*0.7</f>
         <v>159833.79999999999</v>
       </c>
-      <c r="G27" s="75">
+      <c r="G27" s="73">
         <f>+B27*0.6</f>
         <v>137000.4</v>
       </c>
-      <c r="H27" s="69">
+      <c r="H27" s="68">
         <v>74000</v>
       </c>
-      <c r="I27" s="69">
+      <c r="I27" s="68">
         <v>74000</v>
       </c>
       <c r="J27" s="11">
@@ -5383,23 +5367,23 @@
       <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="121"/>
-      <c r="C28" s="122"/>
-      <c r="D28" s="122"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="73" t="s">
+      <c r="B28" s="117"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G28" s="73" t="s">
+      <c r="G28" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H28" s="74" t="s">
+      <c r="H28" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I28" s="74" t="s">
+      <c r="I28" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J28" s="121" t="s">
+      <c r="J28" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K28" s="57"/>
@@ -5408,30 +5392,30 @@
       <c r="A29" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="69">
+      <c r="B29" s="68">
         <v>72000</v>
       </c>
-      <c r="C29" s="69">
+      <c r="C29" s="68">
         <v>36700</v>
       </c>
-      <c r="D29" s="69">
+      <c r="D29" s="68">
         <v>31000</v>
       </c>
-      <c r="E29" s="69">
+      <c r="E29" s="68">
         <v>36700</v>
       </c>
-      <c r="F29" s="77">
+      <c r="F29" s="75">
         <f>+B29*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G29" s="75">
+      <c r="G29" s="73">
         <f>+B29*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H29" s="69">
+      <c r="H29" s="68">
         <v>16800</v>
       </c>
-      <c r="I29" s="69">
+      <c r="I29" s="68">
         <v>16800</v>
       </c>
       <c r="J29" s="11">
@@ -5445,23 +5429,23 @@
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="121"/>
-      <c r="C30" s="122"/>
-      <c r="D30" s="122"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="73" t="s">
+      <c r="B30" s="117"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H30" s="74" t="s">
+      <c r="H30" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I30" s="74" t="s">
+      <c r="I30" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J30" s="121" t="s">
+      <c r="J30" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K30" s="57"/>
@@ -5470,30 +5454,30 @@
       <c r="A31" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="69">
+      <c r="B31" s="68">
         <v>33000</v>
       </c>
-      <c r="C31" s="69">
+      <c r="C31" s="68">
         <v>16600</v>
       </c>
-      <c r="D31" s="69">
+      <c r="D31" s="68">
         <v>16600</v>
       </c>
-      <c r="E31" s="69">
+      <c r="E31" s="68">
         <v>16600</v>
       </c>
-      <c r="F31" s="77">
+      <c r="F31" s="75">
         <f>+B31*0.7</f>
         <v>23100</v>
       </c>
-      <c r="G31" s="75">
+      <c r="G31" s="73">
         <f>+B31*0.6</f>
         <v>19800</v>
       </c>
-      <c r="H31" s="69">
+      <c r="H31" s="68">
         <v>10800</v>
       </c>
-      <c r="I31" s="69">
+      <c r="I31" s="68">
         <v>10800</v>
       </c>
       <c r="J31" s="11">
@@ -5507,23 +5491,23 @@
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="121"/>
-      <c r="C32" s="122"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="123"/>
-      <c r="F32" s="73" t="s">
+      <c r="B32" s="117"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G32" s="73" t="s">
+      <c r="G32" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H32" s="74" t="s">
+      <c r="H32" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="74" t="s">
+      <c r="I32" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J32" s="121" t="s">
+      <c r="J32" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K32" s="57"/>
@@ -5532,30 +5516,30 @@
       <c r="A33" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="69">
+      <c r="B33" s="68">
         <v>24600</v>
       </c>
-      <c r="C33" s="69">
+      <c r="C33" s="68">
         <v>12500</v>
       </c>
-      <c r="D33" s="69">
+      <c r="D33" s="68">
         <v>12500</v>
       </c>
-      <c r="E33" s="69">
+      <c r="E33" s="68">
         <v>12500</v>
       </c>
-      <c r="F33" s="77">
+      <c r="F33" s="75">
         <f>+B33*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G33" s="75">
+      <c r="G33" s="73">
         <f>+B33*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H33" s="69">
+      <c r="H33" s="68">
         <v>6300</v>
       </c>
-      <c r="I33" s="69">
+      <c r="I33" s="68">
         <v>6300</v>
       </c>
       <c r="J33" s="11">
@@ -5569,23 +5553,23 @@
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="121"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="123"/>
-      <c r="F34" s="73" t="s">
+      <c r="B34" s="117"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H34" s="74" t="s">
+      <c r="H34" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I34" s="74" t="s">
+      <c r="I34" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J34" s="121" t="s">
+      <c r="J34" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K34" s="57"/>
@@ -5594,30 +5578,30 @@
       <c r="A35" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="69">
+      <c r="B35" s="68">
         <v>24600</v>
       </c>
-      <c r="C35" s="69">
+      <c r="C35" s="68">
         <v>12500</v>
       </c>
-      <c r="D35" s="69">
+      <c r="D35" s="68">
         <v>12500</v>
       </c>
-      <c r="E35" s="69">
+      <c r="E35" s="68">
         <v>12500</v>
       </c>
-      <c r="F35" s="77">
+      <c r="F35" s="75">
         <f>+B35*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G35" s="75">
+      <c r="G35" s="73">
         <f>+B35*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H35" s="69">
+      <c r="H35" s="68">
         <v>6300</v>
       </c>
-      <c r="I35" s="69">
+      <c r="I35" s="68">
         <v>6300</v>
       </c>
       <c r="J35" s="11">
@@ -5631,23 +5615,23 @@
       <c r="A36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="121"/>
-      <c r="C36" s="122"/>
-      <c r="D36" s="122"/>
-      <c r="E36" s="123"/>
-      <c r="F36" s="73" t="s">
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="74" t="s">
+      <c r="H36" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I36" s="74" t="s">
+      <c r="I36" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="121" t="s">
+      <c r="J36" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K36" s="57"/>
@@ -5656,30 +5640,30 @@
       <c r="A37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="69">
+      <c r="B37" s="68">
         <v>24600</v>
       </c>
-      <c r="C37" s="69">
+      <c r="C37" s="68">
         <v>12500</v>
       </c>
-      <c r="D37" s="69">
+      <c r="D37" s="68">
         <v>12500</v>
       </c>
-      <c r="E37" s="69">
+      <c r="E37" s="68">
         <v>12500</v>
       </c>
-      <c r="F37" s="77">
+      <c r="F37" s="75">
         <f>+B37*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G37" s="75">
+      <c r="G37" s="73">
         <f>+B37*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H37" s="69">
+      <c r="H37" s="68">
         <v>6300</v>
       </c>
-      <c r="I37" s="69">
+      <c r="I37" s="68">
         <v>6300</v>
       </c>
       <c r="J37" s="11">
@@ -5693,23 +5677,23 @@
       <c r="A38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="121"/>
-      <c r="C38" s="122"/>
-      <c r="D38" s="122"/>
-      <c r="E38" s="123"/>
-      <c r="F38" s="73" t="s">
+      <c r="B38" s="117"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G38" s="73" t="s">
+      <c r="G38" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H38" s="74" t="s">
+      <c r="H38" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I38" s="74" t="s">
+      <c r="I38" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J38" s="121" t="s">
+      <c r="J38" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K38" s="57"/>
@@ -5718,30 +5702,30 @@
       <c r="A39" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="69">
+      <c r="B39" s="68">
         <v>24600</v>
       </c>
-      <c r="C39" s="69">
+      <c r="C39" s="68">
         <v>12500</v>
       </c>
-      <c r="D39" s="69">
+      <c r="D39" s="68">
         <v>12500</v>
       </c>
-      <c r="E39" s="69">
+      <c r="E39" s="68">
         <v>12500</v>
       </c>
-      <c r="F39" s="77">
+      <c r="F39" s="75">
         <f>+B39*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G39" s="75">
+      <c r="G39" s="73">
         <f>+B39*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H39" s="69">
+      <c r="H39" s="68">
         <v>6300</v>
       </c>
-      <c r="I39" s="69">
+      <c r="I39" s="68">
         <v>6300</v>
       </c>
       <c r="J39" s="11">
@@ -5755,23 +5739,23 @@
       <c r="A40" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="121"/>
-      <c r="C40" s="122"/>
-      <c r="D40" s="122"/>
-      <c r="E40" s="123"/>
-      <c r="F40" s="73" t="s">
+      <c r="B40" s="117"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="73" t="s">
+      <c r="G40" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H40" s="74" t="s">
+      <c r="H40" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I40" s="74" t="s">
+      <c r="I40" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J40" s="121" t="s">
+      <c r="J40" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K40" s="57"/>
@@ -5780,30 +5764,30 @@
       <c r="A41" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="69">
+      <c r="B41" s="68">
         <v>72000</v>
       </c>
-      <c r="C41" s="69">
+      <c r="C41" s="68">
         <v>36700</v>
       </c>
-      <c r="D41" s="69">
+      <c r="D41" s="68">
         <v>31000</v>
       </c>
-      <c r="E41" s="69">
+      <c r="E41" s="68">
         <v>36700</v>
       </c>
-      <c r="F41" s="77">
+      <c r="F41" s="75">
         <f>+B41*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G41" s="75">
+      <c r="G41" s="73">
         <f>+B41*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H41" s="69">
+      <c r="H41" s="68">
         <v>16800</v>
       </c>
-      <c r="I41" s="69">
+      <c r="I41" s="68">
         <v>16800</v>
       </c>
       <c r="J41" s="11">
@@ -5817,23 +5801,23 @@
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="121"/>
-      <c r="C42" s="122"/>
-      <c r="D42" s="122"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="73" t="s">
+      <c r="B42" s="117"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G42" s="73" t="s">
+      <c r="G42" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H42" s="74" t="s">
+      <c r="H42" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="74" t="s">
+      <c r="I42" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="J42" s="121" t="s">
+      <c r="J42" s="117" t="s">
         <v>157</v>
       </c>
       <c r="K42" s="57"/>
@@ -5842,30 +5826,30 @@
       <c r="A43" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="B43" s="69">
+      <c r="B43" s="68">
         <v>12000</v>
       </c>
-      <c r="C43" s="69">
+      <c r="C43" s="68">
         <v>4200</v>
       </c>
-      <c r="D43" s="69">
+      <c r="D43" s="68">
         <v>0</v>
       </c>
-      <c r="E43" s="69">
+      <c r="E43" s="68">
         <v>4200</v>
       </c>
-      <c r="F43" s="77">
+      <c r="F43" s="75">
         <f>+B43*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G43" s="77">
+      <c r="G43" s="75">
         <f>+B43*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H43" s="69">
+      <c r="H43" s="68">
         <v>0</v>
       </c>
-      <c r="I43" s="69">
+      <c r="I43" s="68">
         <v>0</v>
       </c>
       <c r="J43" s="11">
@@ -5879,30 +5863,30 @@
       <c r="A44" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B44" s="69">
+      <c r="B44" s="68">
         <v>12000</v>
       </c>
-      <c r="C44" s="69">
+      <c r="C44" s="68">
         <v>4200</v>
       </c>
-      <c r="D44" s="69">
+      <c r="D44" s="68">
         <v>0</v>
       </c>
-      <c r="E44" s="69">
+      <c r="E44" s="68">
         <v>4200</v>
       </c>
-      <c r="F44" s="77">
+      <c r="F44" s="75">
         <f t="shared" ref="F44:F46" si="0">+B44*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G44" s="77">
+      <c r="G44" s="75">
         <f t="shared" ref="G44:G46" si="1">+B44*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H44" s="69">
+      <c r="H44" s="68">
         <v>0</v>
       </c>
-      <c r="I44" s="69">
+      <c r="I44" s="68">
         <v>0</v>
       </c>
       <c r="J44" s="11">
@@ -5916,30 +5900,30 @@
       <c r="A45" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B45" s="69">
+      <c r="B45" s="68">
         <v>12000</v>
       </c>
-      <c r="C45" s="69">
+      <c r="C45" s="68">
         <v>4200</v>
       </c>
-      <c r="D45" s="69">
+      <c r="D45" s="68">
         <v>0</v>
       </c>
-      <c r="E45" s="69">
+      <c r="E45" s="68">
         <v>4200</v>
       </c>
-      <c r="F45" s="77">
+      <c r="F45" s="75">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G45" s="77">
+      <c r="G45" s="75">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H45" s="69">
+      <c r="H45" s="68">
         <v>0</v>
       </c>
-      <c r="I45" s="69">
+      <c r="I45" s="68">
         <v>0</v>
       </c>
       <c r="J45" s="11">
@@ -5953,30 +5937,30 @@
       <c r="A46" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="69">
+      <c r="B46" s="68">
         <v>12000</v>
       </c>
-      <c r="C46" s="69">
+      <c r="C46" s="68">
         <v>4200</v>
       </c>
-      <c r="D46" s="69">
+      <c r="D46" s="68">
         <v>0</v>
       </c>
-      <c r="E46" s="69">
+      <c r="E46" s="68">
         <v>4200</v>
       </c>
-      <c r="F46" s="77">
+      <c r="F46" s="75">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G46" s="77">
+      <c r="G46" s="75">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H46" s="69">
+      <c r="H46" s="68">
         <v>0</v>
       </c>
-      <c r="I46" s="69">
+      <c r="I46" s="68">
         <v>0</v>
       </c>
       <c r="J46" s="11">
@@ -5990,20 +5974,20 @@
       <c r="A47" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="121"/>
-      <c r="C47" s="122"/>
-      <c r="D47" s="122"/>
-      <c r="E47" s="123"/>
-      <c r="F47" s="73" t="s">
+      <c r="B47" s="117"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G47" s="73" t="s">
+      <c r="G47" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H47" s="74" t="s">
+      <c r="H47" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I47" s="74" t="s">
+      <c r="I47" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6011,30 +5995,30 @@
       <c r="A48" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="76">
+      <c r="B48" s="74">
         <v>20000</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="74">
         <v>9500</v>
       </c>
-      <c r="D48" s="76">
+      <c r="D48" s="74">
         <v>9500</v>
       </c>
-      <c r="E48" s="76">
+      <c r="E48" s="74">
         <v>9500</v>
       </c>
-      <c r="F48" s="77">
+      <c r="F48" s="75">
         <f>+B48*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G48" s="77">
+      <c r="G48" s="75">
         <f>+B48*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H48" s="69">
+      <c r="H48" s="68">
         <v>4100</v>
       </c>
-      <c r="I48" s="69">
+      <c r="I48" s="68">
         <v>4100</v>
       </c>
       <c r="J48" s="64"/>
@@ -6043,30 +6027,30 @@
       <c r="A49" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="76">
+      <c r="B49" s="74">
         <v>15000</v>
       </c>
-      <c r="C49" s="76">
+      <c r="C49" s="74">
         <v>5900</v>
       </c>
-      <c r="D49" s="76">
+      <c r="D49" s="74">
         <v>5900</v>
       </c>
-      <c r="E49" s="76">
+      <c r="E49" s="74">
         <v>5900</v>
       </c>
-      <c r="F49" s="77">
+      <c r="F49" s="75">
         <f t="shared" ref="F49:F54" si="2">+B49*0.7</f>
         <v>10500</v>
       </c>
-      <c r="G49" s="77">
+      <c r="G49" s="75">
         <f t="shared" ref="G49:G54" si="3">+B49*0.6</f>
         <v>9000</v>
       </c>
-      <c r="H49" s="69">
+      <c r="H49" s="68">
         <v>4900</v>
       </c>
-      <c r="I49" s="69">
+      <c r="I49" s="68">
         <v>4900</v>
       </c>
       <c r="J49" s="64"/>
@@ -6075,30 +6059,30 @@
       <c r="A50" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="76">
+      <c r="B50" s="74">
         <v>15000</v>
       </c>
-      <c r="C50" s="76">
+      <c r="C50" s="74">
         <v>5800</v>
       </c>
-      <c r="D50" s="76">
+      <c r="D50" s="74">
         <v>5800</v>
       </c>
-      <c r="E50" s="76">
+      <c r="E50" s="74">
         <v>5800</v>
       </c>
-      <c r="F50" s="77">
+      <c r="F50" s="75">
         <f t="shared" si="2"/>
         <v>10500</v>
       </c>
-      <c r="G50" s="77">
+      <c r="G50" s="75">
         <f t="shared" si="3"/>
         <v>9000</v>
       </c>
-      <c r="H50" s="69">
+      <c r="H50" s="68">
         <v>3400</v>
       </c>
-      <c r="I50" s="69">
+      <c r="I50" s="68">
         <v>3400</v>
       </c>
     </row>
@@ -6106,30 +6090,30 @@
       <c r="A51" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="76">
+      <c r="B51" s="74">
         <v>20000</v>
       </c>
-      <c r="C51" s="76">
+      <c r="C51" s="74">
         <v>5800</v>
       </c>
-      <c r="D51" s="76">
+      <c r="D51" s="74">
         <v>5800</v>
       </c>
-      <c r="E51" s="76">
+      <c r="E51" s="74">
         <v>5800</v>
       </c>
-      <c r="F51" s="77">
+      <c r="F51" s="75">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G51" s="77">
+      <c r="G51" s="75">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H51" s="69">
+      <c r="H51" s="68">
         <v>3400</v>
       </c>
-      <c r="I51" s="69">
+      <c r="I51" s="68">
         <v>3400</v>
       </c>
     </row>
@@ -6137,30 +6121,30 @@
       <c r="A52" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="76">
+      <c r="B52" s="74">
         <v>20000</v>
       </c>
-      <c r="C52" s="76">
+      <c r="C52" s="74">
         <v>9500</v>
       </c>
-      <c r="D52" s="76">
+      <c r="D52" s="74">
         <v>9500</v>
       </c>
-      <c r="E52" s="76">
+      <c r="E52" s="74">
         <v>9500</v>
       </c>
-      <c r="F52" s="77">
+      <c r="F52" s="75">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G52" s="77">
+      <c r="G52" s="75">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H52" s="69">
+      <c r="H52" s="68">
         <v>3400</v>
       </c>
-      <c r="I52" s="69">
+      <c r="I52" s="68">
         <v>3400</v>
       </c>
     </row>
@@ -6168,30 +6152,30 @@
       <c r="A53" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="76">
+      <c r="B53" s="74">
         <v>20000</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="74">
         <v>9500</v>
       </c>
-      <c r="D53" s="76">
+      <c r="D53" s="74">
         <v>9500</v>
       </c>
-      <c r="E53" s="76">
+      <c r="E53" s="74">
         <v>9500</v>
       </c>
-      <c r="F53" s="77">
+      <c r="F53" s="75">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G53" s="77">
+      <c r="G53" s="75">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H53" s="69">
+      <c r="H53" s="68">
         <v>3400</v>
       </c>
-      <c r="I53" s="69">
+      <c r="I53" s="68">
         <v>3400</v>
       </c>
     </row>
@@ -6199,30 +6183,30 @@
       <c r="A54" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="76">
+      <c r="B54" s="74">
         <v>20000</v>
       </c>
-      <c r="C54" s="76">
+      <c r="C54" s="74">
         <v>13800</v>
       </c>
-      <c r="D54" s="76">
+      <c r="D54" s="74">
         <v>13800</v>
       </c>
-      <c r="E54" s="76">
+      <c r="E54" s="74">
         <v>13800</v>
       </c>
-      <c r="F54" s="77">
+      <c r="F54" s="75">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G54" s="77">
+      <c r="G54" s="75">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H54" s="69">
+      <c r="H54" s="68">
         <v>5700</v>
       </c>
-      <c r="I54" s="69">
+      <c r="I54" s="68">
         <v>5700</v>
       </c>
     </row>
@@ -6230,20 +6214,20 @@
       <c r="A55" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="121"/>
-      <c r="C55" s="122"/>
-      <c r="D55" s="122"/>
-      <c r="E55" s="123"/>
-      <c r="F55" s="73" t="s">
+      <c r="B55" s="117"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="119"/>
+      <c r="F55" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G55" s="73" t="s">
+      <c r="G55" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H55" s="74" t="s">
+      <c r="H55" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I55" s="74" t="s">
+      <c r="I55" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6251,28 +6235,28 @@
       <c r="A56" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="76">
+      <c r="B56" s="74">
         <v>15000</v>
       </c>
-      <c r="C56" s="69">
+      <c r="C56" s="68">
         <v>7800</v>
       </c>
-      <c r="D56" s="69">
+      <c r="D56" s="68">
         <v>7800</v>
       </c>
-      <c r="E56" s="69">
+      <c r="E56" s="68">
         <v>7800</v>
       </c>
-      <c r="F56" s="78">
+      <c r="F56" s="76">
         <v>9000</v>
       </c>
-      <c r="G56" s="78">
+      <c r="G56" s="76">
         <v>7500</v>
       </c>
-      <c r="H56" s="69">
+      <c r="H56" s="68">
         <v>2700</v>
       </c>
-      <c r="I56" s="69">
+      <c r="I56" s="68">
         <v>0</v>
       </c>
     </row>
@@ -6280,20 +6264,20 @@
       <c r="A57" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="121"/>
-      <c r="C57" s="122"/>
-      <c r="D57" s="122"/>
-      <c r="E57" s="123"/>
-      <c r="F57" s="73" t="s">
+      <c r="B57" s="117"/>
+      <c r="C57" s="118"/>
+      <c r="D57" s="118"/>
+      <c r="E57" s="119"/>
+      <c r="F57" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G57" s="73" t="s">
+      <c r="G57" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H57" s="74" t="s">
+      <c r="H57" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I57" s="74" t="s">
+      <c r="I57" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6301,30 +6285,30 @@
       <c r="A58" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="69">
+      <c r="B58" s="68">
         <v>12000</v>
       </c>
-      <c r="C58" s="69">
+      <c r="C58" s="68">
         <v>6400</v>
       </c>
-      <c r="D58" s="69">
+      <c r="D58" s="68">
         <v>6400</v>
       </c>
-      <c r="E58" s="69">
+      <c r="E58" s="68">
         <v>6400</v>
       </c>
-      <c r="F58" s="78">
+      <c r="F58" s="76">
         <f>+B58*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G58" s="78">
+      <c r="G58" s="76">
         <f>+B58*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H58" s="69">
+      <c r="H58" s="68">
         <v>3900</v>
       </c>
-      <c r="I58" s="69">
+      <c r="I58" s="68">
         <v>2700</v>
       </c>
     </row>
@@ -6332,20 +6316,20 @@
       <c r="A59" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="121"/>
-      <c r="C59" s="122"/>
-      <c r="D59" s="122"/>
-      <c r="E59" s="123"/>
-      <c r="F59" s="73" t="s">
+      <c r="B59" s="117"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="118"/>
+      <c r="E59" s="119"/>
+      <c r="F59" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G59" s="73" t="s">
+      <c r="G59" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H59" s="74" t="s">
+      <c r="H59" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I59" s="74" t="s">
+      <c r="I59" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6353,30 +6337,30 @@
       <c r="A60" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="69">
+      <c r="B60" s="68">
         <v>20000</v>
       </c>
-      <c r="C60" s="124">
+      <c r="C60" s="120">
         <v>10200</v>
       </c>
-      <c r="D60" s="124">
+      <c r="D60" s="120">
         <v>10200</v>
       </c>
-      <c r="E60" s="124">
+      <c r="E60" s="120">
         <v>10200</v>
       </c>
-      <c r="F60" s="78">
+      <c r="F60" s="76">
         <f>+B60*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G60" s="78">
+      <c r="G60" s="76">
         <f>+B60*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H60" s="69">
+      <c r="H60" s="68">
         <v>5500</v>
       </c>
-      <c r="I60" s="69">
+      <c r="I60" s="68">
         <v>5500</v>
       </c>
     </row>
@@ -6384,30 +6368,30 @@
       <c r="A61" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="69">
+      <c r="B61" s="68">
         <v>30000</v>
       </c>
-      <c r="C61" s="124">
+      <c r="C61" s="120">
         <v>15900</v>
       </c>
-      <c r="D61" s="124">
+      <c r="D61" s="120">
         <v>15900</v>
       </c>
-      <c r="E61" s="124">
+      <c r="E61" s="120">
         <v>15900</v>
       </c>
-      <c r="F61" s="78">
+      <c r="F61" s="76">
         <f t="shared" ref="F61:F64" si="4">+B61*0.7</f>
         <v>21000</v>
       </c>
-      <c r="G61" s="78">
+      <c r="G61" s="76">
         <f t="shared" ref="G61:G64" si="5">+B61*0.6</f>
         <v>18000</v>
       </c>
-      <c r="H61" s="69">
+      <c r="H61" s="68">
         <v>8400</v>
       </c>
-      <c r="I61" s="69">
+      <c r="I61" s="68">
         <v>8400</v>
       </c>
     </row>
@@ -6415,30 +6399,30 @@
       <c r="A62" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="69">
+      <c r="B62" s="68">
         <v>20000</v>
       </c>
-      <c r="C62" s="124">
+      <c r="C62" s="120">
         <v>10000</v>
       </c>
-      <c r="D62" s="124">
+      <c r="D62" s="120">
         <v>10000</v>
       </c>
-      <c r="E62" s="124">
+      <c r="E62" s="120">
         <v>10000</v>
       </c>
-      <c r="F62" s="78">
+      <c r="F62" s="76">
         <f t="shared" si="4"/>
         <v>14000</v>
       </c>
-      <c r="G62" s="78">
+      <c r="G62" s="76">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H62" s="69">
+      <c r="H62" s="68">
         <v>5000</v>
       </c>
-      <c r="I62" s="69">
+      <c r="I62" s="68">
         <v>5000</v>
       </c>
     </row>
@@ -6446,30 +6430,30 @@
       <c r="A63" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="76">
+      <c r="B63" s="74">
         <v>30000</v>
       </c>
-      <c r="C63" s="124">
+      <c r="C63" s="120">
         <v>10000</v>
       </c>
-      <c r="D63" s="124">
+      <c r="D63" s="120">
         <v>10000</v>
       </c>
-      <c r="E63" s="124">
+      <c r="E63" s="120">
         <v>10000</v>
       </c>
-      <c r="F63" s="78">
+      <c r="F63" s="76">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G63" s="78">
+      <c r="G63" s="76">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H63" s="69">
+      <c r="H63" s="68">
         <v>5200</v>
       </c>
-      <c r="I63" s="69">
+      <c r="I63" s="68">
         <v>5200</v>
       </c>
     </row>
@@ -6477,30 +6461,30 @@
       <c r="A64" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="76">
+      <c r="B64" s="74">
         <v>30000</v>
       </c>
-      <c r="C64" s="124">
+      <c r="C64" s="120">
         <v>12300</v>
       </c>
-      <c r="D64" s="124">
+      <c r="D64" s="120">
         <v>12300</v>
       </c>
-      <c r="E64" s="124">
+      <c r="E64" s="120">
         <v>12300</v>
       </c>
-      <c r="F64" s="78">
+      <c r="F64" s="76">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G64" s="78">
+      <c r="G64" s="76">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H64" s="69">
+      <c r="H64" s="68">
         <v>7900</v>
       </c>
-      <c r="I64" s="69">
+      <c r="I64" s="68">
         <v>7900</v>
       </c>
     </row>
@@ -6508,35 +6492,35 @@
       <c r="A65" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="79"/>
-      <c r="C65" s="79"/>
-      <c r="D65" s="79"/>
-      <c r="E65" s="79"/>
-      <c r="F65" s="79"/>
-      <c r="G65" s="79"/>
-      <c r="H65" s="79"/>
-      <c r="I65" s="79"/>
+      <c r="B65" s="77"/>
+      <c r="C65" s="77"/>
+      <c r="D65" s="77"/>
+      <c r="E65" s="77"/>
+      <c r="F65" s="77"/>
+      <c r="G65" s="77"/>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
     </row>
     <row r="66" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="121" t="s">
+      <c r="B66" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="122"/>
-      <c r="D66" s="122"/>
-      <c r="E66" s="123"/>
-      <c r="F66" s="73" t="s">
+      <c r="C66" s="118"/>
+      <c r="D66" s="118"/>
+      <c r="E66" s="119"/>
+      <c r="F66" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G66" s="73" t="s">
+      <c r="G66" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H66" s="74" t="s">
+      <c r="H66" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I66" s="74" t="s">
+      <c r="I66" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6544,30 +6528,30 @@
       <c r="A67" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B67" s="78">
+      <c r="B67" s="76">
         <v>111000</v>
       </c>
-      <c r="C67" s="69">
+      <c r="C67" s="68">
         <v>83700</v>
       </c>
-      <c r="D67" s="69">
+      <c r="D67" s="68">
         <v>83700</v>
       </c>
-      <c r="E67" s="69">
+      <c r="E67" s="68">
         <v>83700</v>
       </c>
-      <c r="F67" s="78">
+      <c r="F67" s="76">
         <f>+B67*0.7</f>
         <v>77700</v>
       </c>
-      <c r="G67" s="78">
+      <c r="G67" s="76">
         <f>+B67*0.6</f>
         <v>66600</v>
       </c>
-      <c r="H67" s="69">
+      <c r="H67" s="68">
         <v>46700</v>
       </c>
-      <c r="I67" s="69">
+      <c r="I67" s="68">
         <v>46700</v>
       </c>
     </row>
@@ -6575,30 +6559,30 @@
       <c r="A68" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="B68" s="125">
+      <c r="B68" s="121">
         <v>51000</v>
       </c>
-      <c r="C68" s="126">
+      <c r="C68" s="122">
         <v>51000</v>
       </c>
-      <c r="D68" s="126">
+      <c r="D68" s="122">
         <v>51000</v>
       </c>
-      <c r="E68" s="127">
+      <c r="E68" s="123">
         <v>51000</v>
       </c>
-      <c r="F68" s="78">
+      <c r="F68" s="76">
         <f>+B68*0.7</f>
         <v>35700</v>
       </c>
-      <c r="G68" s="78">
+      <c r="G68" s="76">
         <f>+B68*0.6</f>
         <v>30600</v>
       </c>
-      <c r="H68" s="80">
+      <c r="H68" s="78">
         <v>21300</v>
       </c>
-      <c r="I68" s="69">
+      <c r="I68" s="68">
         <v>21300</v>
       </c>
     </row>
@@ -6606,22 +6590,22 @@
       <c r="A69" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B69" s="121" t="s">
+      <c r="B69" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="122"/>
-      <c r="D69" s="122"/>
-      <c r="E69" s="123"/>
-      <c r="F69" s="73" t="s">
+      <c r="C69" s="118"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="119"/>
+      <c r="F69" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G69" s="73" t="s">
+      <c r="G69" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H69" s="74" t="s">
+      <c r="H69" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I69" s="81" t="s">
+      <c r="I69" s="79" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6629,30 +6613,30 @@
       <c r="A70" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B70" s="78">
+      <c r="B70" s="76">
         <v>241000</v>
       </c>
-      <c r="C70" s="69">
+      <c r="C70" s="68">
         <v>165000</v>
       </c>
-      <c r="D70" s="69">
+      <c r="D70" s="68">
         <v>165000</v>
       </c>
-      <c r="E70" s="69">
+      <c r="E70" s="68">
         <v>165000</v>
       </c>
-      <c r="F70" s="78">
+      <c r="F70" s="76">
         <f>+B70*0.7</f>
         <v>168700</v>
       </c>
-      <c r="G70" s="78">
+      <c r="G70" s="76">
         <f>+B70*0.6</f>
         <v>144600</v>
       </c>
-      <c r="H70" s="69">
+      <c r="H70" s="68">
         <v>76000</v>
       </c>
-      <c r="I70" s="69">
+      <c r="I70" s="68">
         <v>76000</v>
       </c>
     </row>
@@ -6660,30 +6644,30 @@
       <c r="A71" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="B71" s="125">
+      <c r="B71" s="121">
         <v>68000</v>
       </c>
-      <c r="C71" s="126">
+      <c r="C71" s="122">
         <v>68000</v>
       </c>
-      <c r="D71" s="126">
+      <c r="D71" s="122">
         <v>68000</v>
       </c>
-      <c r="E71" s="127">
+      <c r="E71" s="123">
         <v>68000</v>
       </c>
-      <c r="F71" s="78">
+      <c r="F71" s="76">
         <f>+B71*0.7</f>
         <v>47600</v>
       </c>
-      <c r="G71" s="78">
+      <c r="G71" s="76">
         <f t="shared" ref="G71:G98" si="6">+B71*0.6</f>
         <v>40800</v>
       </c>
-      <c r="H71" s="80">
+      <c r="H71" s="78">
         <v>48000</v>
       </c>
-      <c r="I71" s="80">
+      <c r="I71" s="78">
         <v>48000</v>
       </c>
     </row>
@@ -6691,22 +6675,22 @@
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="121" t="s">
+      <c r="B72" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C72" s="122"/>
-      <c r="D72" s="122"/>
-      <c r="E72" s="123"/>
-      <c r="F72" s="73" t="s">
+      <c r="C72" s="118"/>
+      <c r="D72" s="118"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G72" s="73" t="s">
+      <c r="G72" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H72" s="74" t="s">
+      <c r="H72" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I72" s="74" t="s">
+      <c r="I72" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6714,30 +6698,30 @@
       <c r="A73" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B73" s="78">
+      <c r="B73" s="76">
         <v>551000</v>
       </c>
-      <c r="C73" s="69">
+      <c r="C73" s="68">
         <v>418000</v>
       </c>
-      <c r="D73" s="69">
+      <c r="D73" s="68">
         <v>418000</v>
       </c>
-      <c r="E73" s="69">
+      <c r="E73" s="68">
         <v>418000</v>
       </c>
-      <c r="F73" s="78">
+      <c r="F73" s="76">
         <f t="shared" ref="F73:F98" si="7">+B73*0.7</f>
         <v>385700</v>
       </c>
-      <c r="G73" s="78">
+      <c r="G73" s="76">
         <f t="shared" si="6"/>
         <v>330600</v>
       </c>
-      <c r="H73" s="69">
+      <c r="H73" s="68">
         <v>209000</v>
       </c>
-      <c r="I73" s="69">
+      <c r="I73" s="68">
         <v>209000</v>
       </c>
     </row>
@@ -6745,30 +6729,30 @@
       <c r="A74" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="125">
+      <c r="B74" s="121">
         <v>132000</v>
       </c>
-      <c r="C74" s="126">
+      <c r="C74" s="122">
         <v>132000</v>
       </c>
-      <c r="D74" s="126">
+      <c r="D74" s="122">
         <v>132000</v>
       </c>
-      <c r="E74" s="127">
+      <c r="E74" s="123">
         <v>132000</v>
       </c>
-      <c r="F74" s="78">
+      <c r="F74" s="76">
         <f t="shared" si="7"/>
         <v>92400</v>
       </c>
-      <c r="G74" s="78">
+      <c r="G74" s="76">
         <f t="shared" si="6"/>
         <v>79200</v>
       </c>
-      <c r="H74" s="80">
+      <c r="H74" s="78">
         <v>75000</v>
       </c>
-      <c r="I74" s="80">
+      <c r="I74" s="78">
         <v>75000</v>
       </c>
     </row>
@@ -6776,22 +6760,22 @@
       <c r="A75" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="121" t="s">
+      <c r="B75" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C75" s="122"/>
-      <c r="D75" s="122"/>
-      <c r="E75" s="123"/>
-      <c r="F75" s="73" t="s">
+      <c r="C75" s="118"/>
+      <c r="D75" s="118"/>
+      <c r="E75" s="119"/>
+      <c r="F75" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G75" s="73" t="s">
+      <c r="G75" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H75" s="74" t="s">
+      <c r="H75" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I75" s="74" t="s">
+      <c r="I75" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6799,30 +6783,30 @@
       <c r="A76" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="78">
+      <c r="B76" s="76">
         <v>962000</v>
       </c>
-      <c r="C76" s="69">
+      <c r="C76" s="68">
         <v>706000</v>
       </c>
-      <c r="D76" s="69">
+      <c r="D76" s="68">
         <v>706000</v>
       </c>
-      <c r="E76" s="69">
+      <c r="E76" s="68">
         <v>706000</v>
       </c>
-      <c r="F76" s="78">
+      <c r="F76" s="76">
         <f t="shared" si="7"/>
         <v>673400</v>
       </c>
-      <c r="G76" s="78">
+      <c r="G76" s="76">
         <f t="shared" si="6"/>
         <v>577200</v>
       </c>
-      <c r="H76" s="69">
+      <c r="H76" s="68">
         <v>464000</v>
       </c>
-      <c r="I76" s="69">
+      <c r="I76" s="68">
         <v>464000</v>
       </c>
     </row>
@@ -6830,30 +6814,30 @@
       <c r="A77" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B77" s="125">
+      <c r="B77" s="121">
         <v>203000</v>
       </c>
-      <c r="C77" s="126">
+      <c r="C77" s="122">
         <v>203000</v>
       </c>
-      <c r="D77" s="126">
+      <c r="D77" s="122">
         <v>203000</v>
       </c>
-      <c r="E77" s="127">
+      <c r="E77" s="123">
         <v>203000</v>
       </c>
-      <c r="F77" s="78">
+      <c r="F77" s="76">
         <f t="shared" si="7"/>
         <v>142100</v>
       </c>
-      <c r="G77" s="78">
+      <c r="G77" s="76">
         <f t="shared" si="6"/>
         <v>121800</v>
       </c>
-      <c r="H77" s="80">
+      <c r="H77" s="78">
         <v>139000</v>
       </c>
-      <c r="I77" s="80">
+      <c r="I77" s="78">
         <v>139000</v>
       </c>
     </row>
@@ -6861,20 +6845,20 @@
       <c r="A78" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B78" s="121"/>
-      <c r="C78" s="122"/>
-      <c r="D78" s="122"/>
-      <c r="E78" s="123"/>
-      <c r="F78" s="73" t="s">
+      <c r="B78" s="117"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="118"/>
+      <c r="E78" s="119"/>
+      <c r="F78" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G78" s="73" t="s">
+      <c r="G78" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H78" s="74" t="s">
+      <c r="H78" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I78" s="74" t="s">
+      <c r="I78" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6882,30 +6866,30 @@
       <c r="A79" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="75">
+      <c r="B79" s="73">
         <v>176000</v>
       </c>
-      <c r="C79" s="69">
+      <c r="C79" s="68">
         <v>176000</v>
       </c>
-      <c r="D79" s="69">
+      <c r="D79" s="68">
         <v>176000</v>
       </c>
-      <c r="E79" s="69">
+      <c r="E79" s="68">
         <v>176000</v>
       </c>
-      <c r="F79" s="78">
+      <c r="F79" s="76">
         <f t="shared" si="7"/>
         <v>123199.99999999999</v>
       </c>
-      <c r="G79" s="78">
+      <c r="G79" s="76">
         <f t="shared" si="6"/>
         <v>105600</v>
       </c>
-      <c r="H79" s="69">
+      <c r="H79" s="68">
         <v>176000</v>
       </c>
-      <c r="I79" s="69">
+      <c r="I79" s="68">
         <v>176000</v>
       </c>
     </row>
@@ -6913,30 +6897,30 @@
       <c r="A80" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="75">
+      <c r="B80" s="73">
         <v>233000</v>
       </c>
-      <c r="C80" s="69">
+      <c r="C80" s="68">
         <v>233000</v>
       </c>
-      <c r="D80" s="69">
+      <c r="D80" s="68">
         <v>233000</v>
       </c>
-      <c r="E80" s="69">
+      <c r="E80" s="68">
         <v>233000</v>
       </c>
-      <c r="F80" s="78">
+      <c r="F80" s="76">
         <f t="shared" si="7"/>
         <v>163100</v>
       </c>
-      <c r="G80" s="78">
+      <c r="G80" s="76">
         <f t="shared" si="6"/>
         <v>139800</v>
       </c>
-      <c r="H80" s="69">
+      <c r="H80" s="68">
         <v>233000</v>
       </c>
-      <c r="I80" s="69">
+      <c r="I80" s="68">
         <v>233000</v>
       </c>
     </row>
@@ -6944,30 +6928,30 @@
       <c r="A81" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B81" s="75">
+      <c r="B81" s="73">
         <v>41000</v>
       </c>
-      <c r="C81" s="69">
+      <c r="C81" s="68">
         <v>41000</v>
       </c>
-      <c r="D81" s="69">
+      <c r="D81" s="68">
         <v>41000</v>
       </c>
-      <c r="E81" s="69">
+      <c r="E81" s="68">
         <v>41000</v>
       </c>
-      <c r="F81" s="78">
+      <c r="F81" s="76">
         <f t="shared" si="7"/>
         <v>28699.999999999996</v>
       </c>
-      <c r="G81" s="78">
+      <c r="G81" s="76">
         <f t="shared" si="6"/>
         <v>24600</v>
       </c>
-      <c r="H81" s="69">
+      <c r="H81" s="68">
         <v>41000</v>
       </c>
-      <c r="I81" s="69">
+      <c r="I81" s="68">
         <v>41000</v>
       </c>
     </row>
@@ -6975,30 +6959,30 @@
       <c r="A82" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B82" s="75">
+      <c r="B82" s="73">
         <v>7700</v>
       </c>
-      <c r="C82" s="69">
+      <c r="C82" s="68">
         <v>7700</v>
       </c>
-      <c r="D82" s="69">
+      <c r="D82" s="68">
         <v>7700</v>
       </c>
-      <c r="E82" s="69">
+      <c r="E82" s="68">
         <v>7700</v>
       </c>
-      <c r="F82" s="78">
+      <c r="F82" s="76">
         <f t="shared" si="7"/>
         <v>5390</v>
       </c>
-      <c r="G82" s="78">
+      <c r="G82" s="76">
         <f t="shared" si="6"/>
         <v>4620</v>
       </c>
-      <c r="H82" s="69">
+      <c r="H82" s="68">
         <v>7700</v>
       </c>
-      <c r="I82" s="69">
+      <c r="I82" s="68">
         <v>7700</v>
       </c>
     </row>
@@ -7006,20 +6990,20 @@
       <c r="A83" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B83" s="121"/>
-      <c r="C83" s="122"/>
-      <c r="D83" s="122"/>
-      <c r="E83" s="123"/>
-      <c r="F83" s="73" t="s">
+      <c r="B83" s="117"/>
+      <c r="C83" s="118"/>
+      <c r="D83" s="118"/>
+      <c r="E83" s="119"/>
+      <c r="F83" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G83" s="73" t="s">
+      <c r="G83" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H83" s="74" t="s">
+      <c r="H83" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I83" s="74" t="s">
+      <c r="I83" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7027,37 +7011,37 @@
       <c r="A84" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="B84" s="83">
+      <c r="B84" s="81">
         <v>64600</v>
       </c>
-      <c r="C84" s="83"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="83"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="83"/>
-      <c r="I84" s="83"/>
+      <c r="C84" s="81"/>
+      <c r="D84" s="81"/>
+      <c r="E84" s="81"/>
+      <c r="F84" s="80"/>
+      <c r="G84" s="80"/>
+      <c r="H84" s="81"/>
+      <c r="I84" s="81"/>
     </row>
     <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="B85" s="121" t="s">
+      <c r="B85" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C85" s="122"/>
-      <c r="D85" s="122"/>
-      <c r="E85" s="123"/>
-      <c r="F85" s="73" t="s">
+      <c r="C85" s="118"/>
+      <c r="D85" s="118"/>
+      <c r="E85" s="119"/>
+      <c r="F85" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G85" s="73" t="s">
+      <c r="G85" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H85" s="74" t="s">
+      <c r="H85" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I85" s="74" t="s">
+      <c r="I85" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7065,30 +7049,30 @@
       <c r="A86" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="B86" s="78">
+      <c r="B86" s="76">
         <v>97000</v>
       </c>
-      <c r="C86" s="69">
+      <c r="C86" s="68">
         <v>57000</v>
       </c>
-      <c r="D86" s="69">
+      <c r="D86" s="68">
         <v>57000</v>
       </c>
-      <c r="E86" s="69">
+      <c r="E86" s="68">
         <v>57000</v>
       </c>
-      <c r="F86" s="78">
+      <c r="F86" s="76">
         <f t="shared" si="7"/>
         <v>67900</v>
       </c>
-      <c r="G86" s="78">
+      <c r="G86" s="76">
         <f>+B86*0.6</f>
         <v>58200</v>
       </c>
-      <c r="H86" s="69">
+      <c r="H86" s="68">
         <v>23500</v>
       </c>
-      <c r="I86" s="69">
+      <c r="I86" s="68">
         <v>23500</v>
       </c>
     </row>
@@ -7096,30 +7080,30 @@
       <c r="A87" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B87" s="78">
+      <c r="B87" s="76">
         <v>282000</v>
       </c>
-      <c r="C87" s="69">
+      <c r="C87" s="68">
         <v>168000</v>
       </c>
-      <c r="D87" s="69">
+      <c r="D87" s="68">
         <v>168000</v>
       </c>
-      <c r="E87" s="69">
+      <c r="E87" s="68">
         <v>168000</v>
       </c>
-      <c r="F87" s="78">
+      <c r="F87" s="76">
         <f t="shared" si="7"/>
         <v>197400</v>
       </c>
-      <c r="G87" s="78">
+      <c r="G87" s="76">
         <f>+B87*0.6</f>
         <v>169200</v>
       </c>
-      <c r="H87" s="69">
+      <c r="H87" s="68">
         <v>72000</v>
       </c>
-      <c r="I87" s="69">
+      <c r="I87" s="68">
         <v>72000</v>
       </c>
     </row>
@@ -7127,30 +7111,30 @@
       <c r="A88" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="B88" s="78">
+      <c r="B88" s="76">
         <v>256000</v>
       </c>
-      <c r="C88" s="69">
+      <c r="C88" s="68">
         <v>140000</v>
       </c>
-      <c r="D88" s="69">
+      <c r="D88" s="68">
         <v>140000</v>
       </c>
-      <c r="E88" s="69">
+      <c r="E88" s="68">
         <v>140000</v>
       </c>
-      <c r="F88" s="78">
+      <c r="F88" s="76">
         <f t="shared" si="7"/>
         <v>179200</v>
       </c>
-      <c r="G88" s="78">
+      <c r="G88" s="76">
         <f t="shared" si="6"/>
         <v>153600</v>
       </c>
-      <c r="H88" s="69">
+      <c r="H88" s="68">
         <v>62000</v>
       </c>
-      <c r="I88" s="69">
+      <c r="I88" s="68">
         <v>62000</v>
       </c>
     </row>
@@ -7158,61 +7142,61 @@
       <c r="A89" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="B89" s="78">
+      <c r="B89" s="76">
         <v>508000</v>
       </c>
-      <c r="C89" s="69">
+      <c r="C89" s="68">
         <v>287000</v>
       </c>
-      <c r="D89" s="69">
+      <c r="D89" s="68">
         <v>287000</v>
       </c>
-      <c r="E89" s="69">
+      <c r="E89" s="68">
         <v>287000</v>
       </c>
-      <c r="F89" s="78">
+      <c r="F89" s="76">
         <f t="shared" si="7"/>
         <v>355600</v>
       </c>
-      <c r="G89" s="78">
+      <c r="G89" s="76">
         <f t="shared" si="6"/>
         <v>304800</v>
       </c>
-      <c r="H89" s="69">
+      <c r="H89" s="68">
         <v>124000</v>
       </c>
-      <c r="I89" s="69">
+      <c r="I89" s="68">
         <v>1240000</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="131" t="s">
+      <c r="A90" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="B90" s="132">
+      <c r="B90" s="127">
         <v>8200</v>
       </c>
-      <c r="C90" s="117">
+      <c r="C90" s="113">
         <v>6200</v>
       </c>
-      <c r="D90" s="117">
+      <c r="D90" s="113">
         <v>6200</v>
       </c>
-      <c r="E90" s="117">
+      <c r="E90" s="113">
         <v>6200</v>
       </c>
-      <c r="F90" s="132">
+      <c r="F90" s="127">
         <f t="shared" si="7"/>
         <v>5740</v>
       </c>
-      <c r="G90" s="132">
+      <c r="G90" s="127">
         <f t="shared" si="6"/>
         <v>4920</v>
       </c>
-      <c r="H90" s="117">
+      <c r="H90" s="113">
         <v>2500</v>
       </c>
-      <c r="I90" s="117">
+      <c r="I90" s="113">
         <v>2500</v>
       </c>
     </row>
@@ -7220,22 +7204,22 @@
       <c r="A91" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="121" t="s">
+      <c r="B91" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C91" s="135"/>
-      <c r="D91" s="135"/>
-      <c r="E91" s="136"/>
-      <c r="F91" s="137" t="s">
+      <c r="C91" s="130"/>
+      <c r="D91" s="130"/>
+      <c r="E91" s="131"/>
+      <c r="F91" s="132" t="s">
         <v>98</v>
       </c>
-      <c r="G91" s="137" t="s">
+      <c r="G91" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="H91" s="138" t="s">
+      <c r="H91" s="133" t="s">
         <v>100</v>
       </c>
-      <c r="I91" s="138" t="s">
+      <c r="I91" s="133" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7243,49 +7227,49 @@
       <c r="A92" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B92" s="133"/>
-      <c r="C92" s="133"/>
-      <c r="D92" s="133"/>
-      <c r="E92" s="133"/>
-      <c r="F92" s="134">
+      <c r="B92" s="128"/>
+      <c r="C92" s="128"/>
+      <c r="D92" s="128"/>
+      <c r="E92" s="128"/>
+      <c r="F92" s="129">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G92" s="134">
+      <c r="G92" s="129">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H92" s="133"/>
-      <c r="I92" s="133"/>
+      <c r="H92" s="128"/>
+      <c r="I92" s="128"/>
     </row>
     <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B93" s="78">
+      <c r="B93" s="76">
         <v>104000</v>
       </c>
-      <c r="C93" s="69">
+      <c r="C93" s="68">
         <v>94000</v>
       </c>
-      <c r="D93" s="69">
+      <c r="D93" s="68">
         <v>94000</v>
       </c>
-      <c r="E93" s="69">
+      <c r="E93" s="68">
         <v>94000</v>
       </c>
-      <c r="F93" s="78">
+      <c r="F93" s="76">
         <f t="shared" si="7"/>
         <v>72800</v>
       </c>
-      <c r="G93" s="78">
+      <c r="G93" s="76">
         <f t="shared" si="6"/>
         <v>62400</v>
       </c>
-      <c r="H93" s="69">
+      <c r="H93" s="68">
         <v>41600</v>
       </c>
-      <c r="I93" s="69">
+      <c r="I93" s="68">
         <v>41600</v>
       </c>
     </row>
@@ -7293,30 +7277,30 @@
       <c r="A94" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B94" s="78">
+      <c r="B94" s="76">
         <v>144750</v>
       </c>
-      <c r="C94" s="69">
+      <c r="C94" s="68">
         <v>106000</v>
       </c>
-      <c r="D94" s="69">
+      <c r="D94" s="68">
         <v>106000</v>
       </c>
-      <c r="E94" s="69">
+      <c r="E94" s="68">
         <v>106000</v>
       </c>
-      <c r="F94" s="78">
+      <c r="F94" s="76">
         <f t="shared" si="7"/>
         <v>101325</v>
       </c>
-      <c r="G94" s="78">
+      <c r="G94" s="76">
         <f t="shared" si="6"/>
         <v>86850</v>
       </c>
-      <c r="H94" s="69">
+      <c r="H94" s="68">
         <v>57900</v>
       </c>
-      <c r="I94" s="69">
+      <c r="I94" s="68">
         <v>57900</v>
       </c>
     </row>
@@ -7324,22 +7308,22 @@
       <c r="A95" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B95" s="121" t="s">
+      <c r="B95" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C95" s="122"/>
-      <c r="D95" s="122"/>
-      <c r="E95" s="123"/>
-      <c r="F95" s="73" t="s">
+      <c r="C95" s="118"/>
+      <c r="D95" s="118"/>
+      <c r="E95" s="119"/>
+      <c r="F95" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G95" s="73" t="s">
+      <c r="G95" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H95" s="74" t="s">
+      <c r="H95" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I95" s="74" t="s">
+      <c r="I95" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7347,115 +7331,115 @@
       <c r="A96" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B96" s="78">
+      <c r="B96" s="76">
         <f>+E96/0.7</f>
         <v>13428.571428571429</v>
       </c>
-      <c r="C96" s="69">
+      <c r="C96" s="68">
         <v>9400</v>
       </c>
-      <c r="D96" s="69">
+      <c r="D96" s="68">
         <v>9400</v>
       </c>
-      <c r="E96" s="69">
+      <c r="E96" s="68">
         <v>9400</v>
       </c>
-      <c r="F96" s="78">
+      <c r="F96" s="76">
         <f t="shared" si="7"/>
         <v>9400</v>
       </c>
-      <c r="G96" s="78">
+      <c r="G96" s="76">
         <f t="shared" si="6"/>
         <v>8057.1428571428569</v>
       </c>
-      <c r="H96" s="82">
+      <c r="H96" s="80">
         <f>+B96*0.4</f>
         <v>5371.4285714285725</v>
       </c>
-      <c r="I96" s="69"/>
+      <c r="I96" s="68"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B97" s="78">
+      <c r="B97" s="76">
         <f t="shared" ref="B97:B98" si="8">+E97/0.7</f>
         <v>19714.285714285714</v>
       </c>
-      <c r="C97" s="69">
+      <c r="C97" s="68">
         <v>13800</v>
       </c>
-      <c r="D97" s="69">
+      <c r="D97" s="68">
         <v>13800</v>
       </c>
-      <c r="E97" s="69">
+      <c r="E97" s="68">
         <v>13800</v>
       </c>
-      <c r="F97" s="78">
+      <c r="F97" s="76">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G97" s="78">
+      <c r="G97" s="76">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H97" s="82">
+      <c r="H97" s="80">
         <f t="shared" ref="H97:H98" si="9">+B97*0.4</f>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I97" s="69"/>
+      <c r="I97" s="68"/>
     </row>
     <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B98" s="78">
+      <c r="B98" s="76">
         <f t="shared" si="8"/>
         <v>19714.285714285714</v>
       </c>
-      <c r="C98" s="69">
+      <c r="C98" s="68">
         <v>13800</v>
       </c>
-      <c r="D98" s="69">
+      <c r="D98" s="68">
         <v>13800</v>
       </c>
-      <c r="E98" s="69">
+      <c r="E98" s="68">
         <v>13800</v>
       </c>
-      <c r="F98" s="78">
+      <c r="F98" s="76">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G98" s="78">
+      <c r="G98" s="76">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H98" s="82">
+      <c r="H98" s="80">
         <f t="shared" si="9"/>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I98" s="69"/>
+      <c r="I98" s="68"/>
     </row>
     <row r="99" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B99" s="121" t="s">
+      <c r="B99" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C99" s="122"/>
-      <c r="D99" s="122"/>
-      <c r="E99" s="123"/>
-      <c r="F99" s="73" t="s">
+      <c r="C99" s="118"/>
+      <c r="D99" s="118"/>
+      <c r="E99" s="119"/>
+      <c r="F99" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="G99" s="73" t="s">
+      <c r="G99" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="H99" s="74" t="s">
+      <c r="H99" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I99" s="74" t="s">
+      <c r="I99" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7463,30 +7447,30 @@
       <c r="A100" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B100" s="78">
+      <c r="B100" s="76">
         <v>55600</v>
       </c>
-      <c r="C100" s="69">
+      <c r="C100" s="68">
         <v>38700</v>
       </c>
-      <c r="D100" s="69">
+      <c r="D100" s="68">
         <v>38700</v>
       </c>
-      <c r="E100" s="69">
+      <c r="E100" s="68">
         <v>38700</v>
       </c>
-      <c r="F100" s="78">
+      <c r="F100" s="76">
         <f>+B100*0.7</f>
         <v>38920</v>
       </c>
-      <c r="G100" s="78">
+      <c r="G100" s="76">
         <f>+B100*0.6</f>
         <v>33360</v>
       </c>
-      <c r="H100" s="69">
+      <c r="H100" s="68">
         <v>26800</v>
       </c>
-      <c r="I100" s="69">
+      <c r="I100" s="68">
         <v>26800</v>
       </c>
     </row>
@@ -7494,30 +7478,30 @@
       <c r="A101" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="B101" s="78">
+      <c r="B101" s="76">
         <v>13900</v>
       </c>
-      <c r="C101" s="69">
+      <c r="C101" s="68">
         <v>13900</v>
       </c>
-      <c r="D101" s="69">
+      <c r="D101" s="68">
         <v>13900</v>
       </c>
-      <c r="E101" s="69">
+      <c r="E101" s="68">
         <v>13900</v>
       </c>
-      <c r="F101" s="78">
+      <c r="F101" s="76">
         <f>+B101*0.7</f>
         <v>9730</v>
       </c>
-      <c r="G101" s="78">
+      <c r="G101" s="76">
         <f>+B101*0.6</f>
         <v>8340</v>
       </c>
-      <c r="H101" s="84">
+      <c r="H101" s="82">
         <v>13900</v>
       </c>
-      <c r="I101" s="69">
+      <c r="I101" s="68">
         <v>13600</v>
       </c>
     </row>
@@ -7525,35 +7509,35 @@
       <c r="A102" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="B102" s="85"/>
-      <c r="C102" s="85"/>
-      <c r="D102" s="85"/>
-      <c r="E102" s="85"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="85"/>
-      <c r="H102" s="85"/>
-      <c r="I102" s="85"/>
+      <c r="B102" s="83"/>
+      <c r="C102" s="83"/>
+      <c r="D102" s="83"/>
+      <c r="E102" s="83"/>
+      <c r="F102" s="83"/>
+      <c r="G102" s="83"/>
+      <c r="H102" s="83"/>
+      <c r="I102" s="83"/>
     </row>
     <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="B103" s="121" t="s">
+      <c r="B103" s="117" t="s">
         <v>155</v>
       </c>
-      <c r="C103" s="122"/>
-      <c r="D103" s="122"/>
-      <c r="E103" s="123"/>
-      <c r="F103" s="86" t="s">
+      <c r="C103" s="118"/>
+      <c r="D103" s="118"/>
+      <c r="E103" s="119"/>
+      <c r="F103" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="G103" s="86" t="s">
+      <c r="G103" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H103" s="74" t="s">
+      <c r="H103" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I103" s="74" t="s">
+      <c r="I103" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7561,30 +7545,30 @@
       <c r="A104" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B104" s="69">
+      <c r="B104" s="68">
         <v>88886</v>
       </c>
-      <c r="C104" s="69">
+      <c r="C104" s="68">
         <v>44443</v>
       </c>
-      <c r="D104" s="69">
+      <c r="D104" s="68">
         <v>44443</v>
       </c>
-      <c r="E104" s="69">
+      <c r="E104" s="68">
         <v>44443</v>
       </c>
-      <c r="F104" s="78">
+      <c r="F104" s="76">
         <f>+B104*0.7</f>
         <v>62220.2</v>
       </c>
-      <c r="G104" s="78">
+      <c r="G104" s="76">
         <f>+B104*0.6</f>
         <v>53331.6</v>
       </c>
-      <c r="H104" s="69">
+      <c r="H104" s="68">
         <v>24647</v>
       </c>
-      <c r="I104" s="69">
+      <c r="I104" s="68">
         <v>24647</v>
       </c>
     </row>
@@ -7592,30 +7576,30 @@
       <c r="A105" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B105" s="69">
+      <c r="B105" s="68">
         <v>103703</v>
       </c>
-      <c r="C105" s="69">
+      <c r="C105" s="68">
         <v>51852</v>
       </c>
-      <c r="D105" s="69">
+      <c r="D105" s="68">
         <v>51852</v>
       </c>
-      <c r="E105" s="69">
+      <c r="E105" s="68">
         <v>51852</v>
       </c>
-      <c r="F105" s="78">
+      <c r="F105" s="76">
         <f t="shared" ref="F105:F129" si="10">+B105*0.7</f>
         <v>72592.099999999991</v>
       </c>
-      <c r="G105" s="78">
+      <c r="G105" s="76">
         <f t="shared" ref="G105:G129" si="11">+B105*0.6</f>
         <v>62221.799999999996</v>
       </c>
-      <c r="H105" s="69">
+      <c r="H105" s="68">
         <v>28755</v>
       </c>
-      <c r="I105" s="69">
+      <c r="I105" s="68">
         <v>28755</v>
       </c>
     </row>
@@ -7623,30 +7607,30 @@
       <c r="A106" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B106" s="69">
+      <c r="B106" s="68">
         <v>174729</v>
       </c>
-      <c r="C106" s="69">
+      <c r="C106" s="68">
         <v>87365</v>
       </c>
-      <c r="D106" s="69">
+      <c r="D106" s="68">
         <v>87365</v>
       </c>
-      <c r="E106" s="69">
+      <c r="E106" s="68">
         <v>87365</v>
       </c>
-      <c r="F106" s="78">
+      <c r="F106" s="76">
         <f t="shared" si="10"/>
         <v>122310.29999999999</v>
       </c>
-      <c r="G106" s="78">
+      <c r="G106" s="76">
         <f t="shared" si="11"/>
         <v>104837.4</v>
       </c>
-      <c r="H106" s="69">
+      <c r="H106" s="68">
         <v>48449</v>
       </c>
-      <c r="I106" s="69">
+      <c r="I106" s="68">
         <v>48449</v>
       </c>
     </row>
@@ -7654,30 +7638,30 @@
       <c r="A107" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="69">
+      <c r="B107" s="68">
         <v>22223</v>
       </c>
-      <c r="C107" s="69">
+      <c r="C107" s="68">
         <v>11112</v>
       </c>
-      <c r="D107" s="69">
+      <c r="D107" s="68">
         <v>11112</v>
       </c>
-      <c r="E107" s="69">
+      <c r="E107" s="68">
         <v>11112</v>
       </c>
-      <c r="F107" s="78">
+      <c r="F107" s="76">
         <f t="shared" si="10"/>
         <v>15556.099999999999</v>
       </c>
-      <c r="G107" s="78">
+      <c r="G107" s="76">
         <f t="shared" si="11"/>
         <v>13333.8</v>
       </c>
-      <c r="H107" s="69">
+      <c r="H107" s="68">
         <v>6162</v>
       </c>
-      <c r="I107" s="69">
+      <c r="I107" s="68">
         <v>6162</v>
       </c>
     </row>
@@ -7685,30 +7669,30 @@
       <c r="A108" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B108" s="69">
+      <c r="B108" s="68">
         <v>111110</v>
       </c>
-      <c r="C108" s="69">
+      <c r="C108" s="68">
         <v>55555</v>
       </c>
-      <c r="D108" s="69">
+      <c r="D108" s="68">
         <v>55555</v>
       </c>
-      <c r="E108" s="69">
+      <c r="E108" s="68">
         <v>55555</v>
       </c>
-      <c r="F108" s="78">
+      <c r="F108" s="76">
         <f t="shared" si="10"/>
         <v>77777</v>
       </c>
-      <c r="G108" s="78">
+      <c r="G108" s="76">
         <f t="shared" si="11"/>
         <v>66666</v>
       </c>
-      <c r="H108" s="69">
+      <c r="H108" s="68">
         <v>30809</v>
       </c>
-      <c r="I108" s="69">
+      <c r="I108" s="68">
         <v>30809</v>
       </c>
     </row>
@@ -7716,22 +7700,22 @@
       <c r="A109" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="B109" s="121" t="s">
+      <c r="B109" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="C109" s="122"/>
-      <c r="D109" s="122"/>
-      <c r="E109" s="123"/>
-      <c r="F109" s="86" t="s">
+      <c r="C109" s="118"/>
+      <c r="D109" s="118"/>
+      <c r="E109" s="119"/>
+      <c r="F109" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="G109" s="86" t="s">
+      <c r="G109" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H109" s="74" t="s">
+      <c r="H109" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I109" s="74" t="s">
+      <c r="I109" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7739,30 +7723,30 @@
       <c r="A110" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="B110" s="69">
+      <c r="B110" s="68">
         <v>312686</v>
       </c>
-      <c r="C110" s="69">
+      <c r="C110" s="68">
         <v>156343</v>
       </c>
-      <c r="D110" s="69">
+      <c r="D110" s="68">
         <v>156343</v>
       </c>
-      <c r="E110" s="69">
+      <c r="E110" s="68">
         <v>156343</v>
       </c>
-      <c r="F110" s="78">
+      <c r="F110" s="76">
         <f t="shared" si="10"/>
         <v>218880.19999999998</v>
       </c>
-      <c r="G110" s="78">
+      <c r="G110" s="76">
         <f t="shared" si="11"/>
         <v>187611.6</v>
       </c>
-      <c r="H110" s="69">
+      <c r="H110" s="68">
         <v>85421</v>
       </c>
-      <c r="I110" s="69">
+      <c r="I110" s="68">
         <v>85421</v>
       </c>
     </row>
@@ -7770,30 +7754,30 @@
       <c r="A111" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B111" s="69">
+      <c r="B111" s="68">
         <v>349723</v>
       </c>
-      <c r="C111" s="69">
+      <c r="C111" s="68">
         <v>174861</v>
       </c>
-      <c r="D111" s="69">
+      <c r="D111" s="68">
         <v>174861</v>
       </c>
-      <c r="E111" s="69">
+      <c r="E111" s="68">
         <v>174861</v>
       </c>
-      <c r="F111" s="78">
+      <c r="F111" s="76">
         <f t="shared" si="10"/>
         <v>244806.09999999998</v>
       </c>
-      <c r="G111" s="78">
+      <c r="G111" s="76">
         <f t="shared" si="11"/>
         <v>209833.8</v>
       </c>
-      <c r="H111" s="69">
+      <c r="H111" s="68">
         <v>95539</v>
       </c>
-      <c r="I111" s="69">
+      <c r="I111" s="68">
         <v>95539</v>
       </c>
     </row>
@@ -7801,30 +7785,30 @@
       <c r="A112" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B112" s="69">
+      <c r="B112" s="68">
         <v>446016</v>
       </c>
-      <c r="C112" s="69">
+      <c r="C112" s="68">
         <v>223008</v>
       </c>
-      <c r="D112" s="69">
+      <c r="D112" s="68">
         <v>223008</v>
       </c>
-      <c r="E112" s="69">
+      <c r="E112" s="68">
         <v>223008</v>
       </c>
-      <c r="F112" s="78">
+      <c r="F112" s="76">
         <f t="shared" si="10"/>
         <v>312211.19999999995</v>
       </c>
-      <c r="G112" s="78">
+      <c r="G112" s="76">
         <f t="shared" si="11"/>
         <v>267609.59999999998</v>
       </c>
-      <c r="H112" s="69">
+      <c r="H112" s="68">
         <v>121845</v>
       </c>
-      <c r="I112" s="69">
+      <c r="I112" s="68">
         <v>121845</v>
       </c>
     </row>
@@ -7832,22 +7816,22 @@
       <c r="A113" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B113" s="121" t="s">
+      <c r="B113" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="C113" s="122"/>
-      <c r="D113" s="122"/>
-      <c r="E113" s="123"/>
-      <c r="F113" s="86" t="s">
+      <c r="C113" s="118"/>
+      <c r="D113" s="118"/>
+      <c r="E113" s="119"/>
+      <c r="F113" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="G113" s="86" t="s">
+      <c r="G113" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H113" s="74" t="s">
+      <c r="H113" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I113" s="74" t="s">
+      <c r="I113" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7855,30 +7839,30 @@
       <c r="A114" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B114" s="69">
+      <c r="B114" s="68">
         <v>128763</v>
       </c>
-      <c r="C114" s="69">
+      <c r="C114" s="68">
         <v>64381</v>
       </c>
-      <c r="D114" s="69">
+      <c r="D114" s="68">
         <v>64381</v>
       </c>
-      <c r="E114" s="69">
+      <c r="E114" s="68">
         <v>64381</v>
       </c>
-      <c r="F114" s="78">
+      <c r="F114" s="76">
         <f t="shared" si="10"/>
         <v>90134.099999999991</v>
       </c>
-      <c r="G114" s="78">
+      <c r="G114" s="76">
         <f t="shared" si="11"/>
         <v>77257.8</v>
       </c>
-      <c r="H114" s="69">
+      <c r="H114" s="68">
         <v>35704</v>
       </c>
-      <c r="I114" s="69">
+      <c r="I114" s="68">
         <v>35704</v>
       </c>
     </row>
@@ -7886,30 +7870,30 @@
       <c r="A115" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B115" s="69">
+      <c r="B115" s="68">
         <v>199762</v>
       </c>
-      <c r="C115" s="69">
+      <c r="C115" s="68">
         <v>99881</v>
       </c>
-      <c r="D115" s="69">
+      <c r="D115" s="68">
         <v>99881</v>
       </c>
-      <c r="E115" s="69">
+      <c r="E115" s="68">
         <v>99881</v>
       </c>
-      <c r="F115" s="78">
+      <c r="F115" s="76">
         <f t="shared" si="10"/>
         <v>139833.4</v>
       </c>
-      <c r="G115" s="78">
+      <c r="G115" s="76">
         <f t="shared" si="11"/>
         <v>119857.2</v>
       </c>
-      <c r="H115" s="69">
+      <c r="H115" s="68">
         <v>55391</v>
       </c>
-      <c r="I115" s="69">
+      <c r="I115" s="68">
         <v>55391</v>
       </c>
     </row>
@@ -7917,22 +7901,22 @@
       <c r="A116" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="B116" s="121" t="s">
+      <c r="B116" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="C116" s="122"/>
-      <c r="D116" s="122"/>
-      <c r="E116" s="123"/>
-      <c r="F116" s="86" t="s">
+      <c r="C116" s="118"/>
+      <c r="D116" s="118"/>
+      <c r="E116" s="119"/>
+      <c r="F116" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="G116" s="86" t="s">
+      <c r="G116" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H116" s="74" t="s">
+      <c r="H116" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I116" s="74" t="s">
+      <c r="I116" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7940,30 +7924,30 @@
       <c r="A117" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B117" s="69">
+      <c r="B117" s="68">
         <v>477701</v>
       </c>
-      <c r="C117" s="69">
+      <c r="C117" s="68">
         <v>238851</v>
       </c>
-      <c r="D117" s="69">
+      <c r="D117" s="68">
         <v>238851</v>
       </c>
-      <c r="E117" s="69">
+      <c r="E117" s="68">
         <v>238851</v>
       </c>
-      <c r="F117" s="78">
+      <c r="F117" s="76">
         <f t="shared" si="10"/>
         <v>334390.69999999995</v>
       </c>
-      <c r="G117" s="78">
+      <c r="G117" s="76">
         <f t="shared" si="11"/>
         <v>286620.59999999998</v>
       </c>
-      <c r="H117" s="69">
+      <c r="H117" s="68">
         <v>132458</v>
       </c>
-      <c r="I117" s="69">
+      <c r="I117" s="68">
         <v>132458</v>
       </c>
     </row>
@@ -7971,30 +7955,30 @@
       <c r="A118" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B118" s="69">
+      <c r="B118" s="68">
         <v>236516</v>
       </c>
-      <c r="C118" s="69">
+      <c r="C118" s="68">
         <v>118258</v>
       </c>
-      <c r="D118" s="69">
+      <c r="D118" s="68">
         <v>118258</v>
       </c>
-      <c r="E118" s="69">
+      <c r="E118" s="68">
         <v>118258</v>
       </c>
-      <c r="F118" s="78">
+      <c r="F118" s="76">
         <f t="shared" si="10"/>
         <v>165561.19999999998</v>
       </c>
-      <c r="G118" s="78">
+      <c r="G118" s="76">
         <f t="shared" si="11"/>
         <v>141909.6</v>
       </c>
-      <c r="H118" s="69">
+      <c r="H118" s="68">
         <v>65582</v>
       </c>
-      <c r="I118" s="69">
+      <c r="I118" s="68">
         <v>65582</v>
       </c>
     </row>
@@ -8002,30 +7986,30 @@
       <c r="A119" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B119" s="69">
+      <c r="B119" s="68">
         <v>274873</v>
       </c>
-      <c r="C119" s="69">
+      <c r="C119" s="68">
         <v>137436</v>
       </c>
-      <c r="D119" s="69">
+      <c r="D119" s="68">
         <v>137436</v>
       </c>
-      <c r="E119" s="69">
+      <c r="E119" s="68">
         <v>137436</v>
       </c>
-      <c r="F119" s="78">
+      <c r="F119" s="76">
         <f t="shared" si="10"/>
         <v>192411.09999999998</v>
       </c>
-      <c r="G119" s="78">
+      <c r="G119" s="76">
         <f t="shared" si="11"/>
         <v>164923.79999999999</v>
       </c>
-      <c r="H119" s="69">
+      <c r="H119" s="68">
         <v>76217</v>
       </c>
-      <c r="I119" s="69">
+      <c r="I119" s="68">
         <v>76217</v>
       </c>
     </row>
@@ -8033,30 +8017,30 @@
       <c r="A120" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B120" s="69">
+      <c r="B120" s="68">
         <v>313203</v>
       </c>
-      <c r="C120" s="69">
+      <c r="C120" s="68">
         <v>156601</v>
       </c>
-      <c r="D120" s="69">
+      <c r="D120" s="68">
         <v>156601</v>
       </c>
-      <c r="E120" s="69">
+      <c r="E120" s="68">
         <v>156601</v>
       </c>
-      <c r="F120" s="78">
+      <c r="F120" s="76">
         <f t="shared" si="10"/>
         <v>219242.09999999998</v>
       </c>
-      <c r="G120" s="78">
+      <c r="G120" s="76">
         <f t="shared" si="11"/>
         <v>187921.8</v>
       </c>
-      <c r="H120" s="69">
+      <c r="H120" s="68">
         <v>86846</v>
       </c>
-      <c r="I120" s="69">
+      <c r="I120" s="68">
         <v>86846</v>
       </c>
     </row>
@@ -8064,22 +8048,22 @@
       <c r="A121" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="B121" s="121" t="s">
+      <c r="B121" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="C121" s="122"/>
-      <c r="D121" s="122"/>
-      <c r="E121" s="123"/>
-      <c r="F121" s="86" t="s">
+      <c r="C121" s="118"/>
+      <c r="D121" s="118"/>
+      <c r="E121" s="119"/>
+      <c r="F121" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="G121" s="86" t="s">
+      <c r="G121" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H121" s="74" t="s">
+      <c r="H121" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I121" s="74" t="s">
+      <c r="I121" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -8087,30 +8071,30 @@
       <c r="A122" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B122" s="69">
+      <c r="B122" s="68">
         <v>139695</v>
       </c>
-      <c r="C122" s="69">
+      <c r="C122" s="68">
         <v>69848</v>
       </c>
-      <c r="D122" s="69">
+      <c r="D122" s="68">
         <v>69848</v>
       </c>
-      <c r="E122" s="69">
+      <c r="E122" s="68">
         <v>69848</v>
       </c>
-      <c r="F122" s="78">
+      <c r="F122" s="76">
         <f t="shared" si="10"/>
         <v>97786.5</v>
       </c>
-      <c r="G122" s="78">
+      <c r="G122" s="76">
         <f t="shared" si="11"/>
         <v>83817</v>
       </c>
-      <c r="H122" s="69">
+      <c r="H122" s="68">
         <v>38735</v>
       </c>
-      <c r="I122" s="69">
+      <c r="I122" s="68">
         <v>38735</v>
       </c>
     </row>
@@ -8118,30 +8102,30 @@
       <c r="A123" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B123" s="69">
+      <c r="B123" s="68">
         <v>153373</v>
       </c>
-      <c r="C123" s="69">
+      <c r="C123" s="68">
         <v>76687</v>
       </c>
-      <c r="D123" s="69">
+      <c r="D123" s="68">
         <v>76687</v>
       </c>
-      <c r="E123" s="69">
+      <c r="E123" s="68">
         <v>76687</v>
       </c>
-      <c r="F123" s="78">
+      <c r="F123" s="76">
         <f t="shared" si="10"/>
         <v>107361.09999999999</v>
       </c>
-      <c r="G123" s="78">
+      <c r="G123" s="76">
         <f t="shared" si="11"/>
         <v>92023.8</v>
       </c>
-      <c r="H123" s="69">
+      <c r="H123" s="68">
         <v>42528</v>
       </c>
-      <c r="I123" s="69">
+      <c r="I123" s="68">
         <v>42528</v>
       </c>
     </row>
@@ -8149,30 +8133,30 @@
       <c r="A124" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B124" s="69">
+      <c r="B124" s="68">
         <v>184044</v>
       </c>
-      <c r="C124" s="69">
+      <c r="C124" s="68">
         <v>92022</v>
       </c>
-      <c r="D124" s="69">
+      <c r="D124" s="68">
         <v>92022</v>
       </c>
-      <c r="E124" s="69">
+      <c r="E124" s="68">
         <v>92022</v>
       </c>
-      <c r="F124" s="78">
+      <c r="F124" s="76">
         <f t="shared" si="10"/>
         <v>128830.79999999999</v>
       </c>
-      <c r="G124" s="78">
+      <c r="G124" s="76">
         <f t="shared" si="11"/>
         <v>110426.4</v>
       </c>
-      <c r="H124" s="69">
+      <c r="H124" s="68">
         <v>51032</v>
       </c>
-      <c r="I124" s="69">
+      <c r="I124" s="68">
         <v>51032</v>
       </c>
     </row>
@@ -8180,30 +8164,30 @@
       <c r="A125" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B125" s="69">
+      <c r="B125" s="68">
         <v>49078</v>
       </c>
-      <c r="C125" s="69">
+      <c r="C125" s="68">
         <v>24539</v>
       </c>
-      <c r="D125" s="69">
+      <c r="D125" s="68">
         <v>24539</v>
       </c>
-      <c r="E125" s="69">
+      <c r="E125" s="68">
         <v>24539</v>
       </c>
-      <c r="F125" s="78">
+      <c r="F125" s="76">
         <f t="shared" si="10"/>
         <v>34354.6</v>
       </c>
-      <c r="G125" s="78">
+      <c r="G125" s="76">
         <f t="shared" si="11"/>
         <v>29446.799999999999</v>
       </c>
-      <c r="H125" s="69">
+      <c r="H125" s="68">
         <v>13608</v>
       </c>
-      <c r="I125" s="69">
+      <c r="I125" s="68">
         <v>13608</v>
       </c>
     </row>
@@ -8211,22 +8195,22 @@
       <c r="A126" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="B126" s="121" t="s">
+      <c r="B126" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="C126" s="122"/>
-      <c r="D126" s="122"/>
-      <c r="E126" s="123"/>
-      <c r="F126" s="86" t="s">
+      <c r="C126" s="118"/>
+      <c r="D126" s="118"/>
+      <c r="E126" s="119"/>
+      <c r="F126" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="G126" s="86" t="s">
+      <c r="G126" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H126" s="74" t="s">
+      <c r="H126" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I126" s="74" t="s">
+      <c r="I126" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -8234,30 +8218,30 @@
       <c r="A127" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B127" s="69">
+      <c r="B127" s="68">
         <v>661862</v>
       </c>
-      <c r="C127" s="69">
+      <c r="C127" s="68">
         <v>330931</v>
       </c>
-      <c r="D127" s="69">
+      <c r="D127" s="68">
         <v>330931</v>
       </c>
-      <c r="E127" s="69">
+      <c r="E127" s="68">
         <v>330931</v>
       </c>
-      <c r="F127" s="78">
+      <c r="F127" s="76">
         <f t="shared" si="10"/>
         <v>463303.39999999997</v>
       </c>
-      <c r="G127" s="78">
+      <c r="G127" s="76">
         <f t="shared" si="11"/>
         <v>397117.2</v>
       </c>
-      <c r="H127" s="69">
+      <c r="H127" s="68">
         <v>183523</v>
       </c>
-      <c r="I127" s="69">
+      <c r="I127" s="68">
         <v>183523</v>
       </c>
     </row>
@@ -8265,30 +8249,30 @@
       <c r="A128" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B128" s="69">
+      <c r="B128" s="68">
         <v>692556</v>
       </c>
-      <c r="C128" s="69">
+      <c r="C128" s="68">
         <v>346278</v>
       </c>
-      <c r="D128" s="69">
+      <c r="D128" s="68">
         <v>346278</v>
       </c>
-      <c r="E128" s="69">
+      <c r="E128" s="68">
         <v>346278</v>
       </c>
-      <c r="F128" s="78">
+      <c r="F128" s="76">
         <f t="shared" si="10"/>
         <v>484789.19999999995</v>
       </c>
-      <c r="G128" s="78">
+      <c r="G128" s="76">
         <f t="shared" si="11"/>
         <v>415533.6</v>
       </c>
-      <c r="H128" s="69">
+      <c r="H128" s="68">
         <v>192034</v>
       </c>
-      <c r="I128" s="69">
+      <c r="I128" s="68">
         <v>192034</v>
       </c>
     </row>
@@ -8296,49 +8280,49 @@
       <c r="A129" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B129" s="69">
+      <c r="B129" s="68">
         <v>90078</v>
       </c>
-      <c r="C129" s="69">
+      <c r="C129" s="68">
         <v>45039</v>
       </c>
-      <c r="D129" s="69">
+      <c r="D129" s="68">
         <v>45039</v>
       </c>
-      <c r="E129" s="69">
+      <c r="E129" s="68">
         <v>45039</v>
       </c>
-      <c r="F129" s="78">
+      <c r="F129" s="76">
         <f t="shared" si="10"/>
         <v>63054.6</v>
       </c>
-      <c r="G129" s="78">
+      <c r="G129" s="76">
         <f t="shared" si="11"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="H129" s="69">
+      <c r="H129" s="68">
         <v>24977</v>
       </c>
-      <c r="I129" s="69">
+      <c r="I129" s="68">
         <v>24977</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="B130" s="121"/>
-      <c r="C130" s="122"/>
-      <c r="D130" s="122"/>
-      <c r="E130" s="123"/>
-      <c r="F130" s="86"/>
-      <c r="G130" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B130" s="117"/>
+      <c r="C130" s="118"/>
+      <c r="D130" s="118"/>
+      <c r="E130" s="119"/>
+      <c r="F130" s="84"/>
+      <c r="G130" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="H130" s="74" t="s">
+      <c r="H130" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="I130" s="74" t="s">
+      <c r="I130" s="72" t="s">
         <v>130</v>
       </c>
     </row>
@@ -8346,1516 +8330,1516 @@
       <c r="A131" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B131" s="69">
+      <c r="B131" s="68">
         <f>+G131/0.6</f>
         <v>157351.66666666669</v>
       </c>
-      <c r="C131" s="69">
+      <c r="C131" s="68">
         <v>94411</v>
       </c>
-      <c r="D131" s="69">
+      <c r="D131" s="68">
         <v>94411</v>
       </c>
-      <c r="E131" s="69">
+      <c r="E131" s="68">
         <v>94411</v>
       </c>
-      <c r="F131" s="69">
+      <c r="F131" s="68">
         <f>+B131*0.7</f>
         <v>110146.16666666667</v>
       </c>
-      <c r="G131" s="75">
+      <c r="G131" s="73">
         <f>+E131</f>
         <v>94411</v>
       </c>
-      <c r="H131" s="69"/>
-      <c r="I131" s="69"/>
+      <c r="H131" s="68"/>
+      <c r="I131" s="68"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B132" s="69">
+      <c r="B132" s="68">
         <f t="shared" ref="B132:B150" si="12">+G132/0.6</f>
         <v>78706.666666666672</v>
       </c>
-      <c r="C132" s="69">
+      <c r="C132" s="68">
         <v>47224</v>
       </c>
-      <c r="D132" s="69">
+      <c r="D132" s="68">
         <v>47224</v>
       </c>
-      <c r="E132" s="69">
+      <c r="E132" s="68">
         <v>47224</v>
       </c>
-      <c r="F132" s="69">
+      <c r="F132" s="68">
         <f t="shared" ref="F132:F151" si="13">+B132*0.7</f>
         <v>55094.666666666664</v>
       </c>
-      <c r="G132" s="75">
+      <c r="G132" s="73">
         <f t="shared" ref="G132:G150" si="14">+E132</f>
         <v>47224</v>
       </c>
-      <c r="H132" s="69"/>
-      <c r="I132" s="69"/>
+      <c r="H132" s="68"/>
+      <c r="I132" s="68"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B133" s="69">
+      <c r="B133" s="68">
         <f t="shared" si="12"/>
         <v>150468.33333333334</v>
       </c>
-      <c r="C133" s="69">
+      <c r="C133" s="68">
         <v>90281</v>
       </c>
-      <c r="D133" s="69">
+      <c r="D133" s="68">
         <v>90281</v>
       </c>
-      <c r="E133" s="69">
+      <c r="E133" s="68">
         <v>90281</v>
       </c>
-      <c r="F133" s="69">
+      <c r="F133" s="68">
         <f t="shared" si="13"/>
         <v>105327.83333333333</v>
       </c>
-      <c r="G133" s="75">
+      <c r="G133" s="73">
         <f t="shared" si="14"/>
         <v>90281</v>
       </c>
-      <c r="H133" s="69"/>
-      <c r="I133" s="69"/>
+      <c r="H133" s="68"/>
+      <c r="I133" s="68"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B134" s="69">
+      <c r="B134" s="68">
         <f t="shared" si="12"/>
         <v>141788.33333333334</v>
       </c>
-      <c r="C134" s="69">
+      <c r="C134" s="68">
         <v>85073</v>
       </c>
-      <c r="D134" s="69">
+      <c r="D134" s="68">
         <v>85073</v>
       </c>
-      <c r="E134" s="69">
+      <c r="E134" s="68">
         <v>85073</v>
       </c>
-      <c r="F134" s="69">
+      <c r="F134" s="68">
         <f t="shared" si="13"/>
         <v>99251.833333333328</v>
       </c>
-      <c r="G134" s="75">
+      <c r="G134" s="73">
         <f t="shared" si="14"/>
         <v>85073</v>
       </c>
-      <c r="H134" s="69"/>
-      <c r="I134" s="69"/>
+      <c r="H134" s="68"/>
+      <c r="I134" s="68"/>
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="69">
+      <c r="B135" s="68">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C135" s="69">
+      <c r="C135" s="68">
         <v>16783</v>
       </c>
-      <c r="D135" s="69">
+      <c r="D135" s="68">
         <v>16783</v>
       </c>
-      <c r="E135" s="69">
+      <c r="E135" s="68">
         <v>16783</v>
       </c>
-      <c r="F135" s="69">
+      <c r="F135" s="68">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G135" s="75">
+      <c r="G135" s="73">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H135" s="69"/>
-      <c r="I135" s="69"/>
+      <c r="H135" s="68"/>
+      <c r="I135" s="68"/>
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B136" s="69">
+      <c r="B136" s="68">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C136" s="69">
+      <c r="C136" s="68">
         <v>16783</v>
       </c>
-      <c r="D136" s="69">
+      <c r="D136" s="68">
         <v>16783</v>
       </c>
-      <c r="E136" s="69">
+      <c r="E136" s="68">
         <v>16783</v>
       </c>
-      <c r="F136" s="69">
+      <c r="F136" s="68">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G136" s="75">
+      <c r="G136" s="73">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H136" s="69"/>
-      <c r="I136" s="69"/>
+      <c r="H136" s="68"/>
+      <c r="I136" s="68"/>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B137" s="69">
+      <c r="B137" s="68">
         <f t="shared" si="12"/>
         <v>27971.666666666668</v>
       </c>
-      <c r="C137" s="69">
+      <c r="C137" s="68">
         <v>16783</v>
       </c>
-      <c r="D137" s="69">
+      <c r="D137" s="68">
         <v>16783</v>
       </c>
-      <c r="E137" s="69">
+      <c r="E137" s="68">
         <v>16783</v>
       </c>
-      <c r="F137" s="69">
+      <c r="F137" s="68">
         <f t="shared" si="13"/>
         <v>19580.166666666668</v>
       </c>
-      <c r="G137" s="75">
+      <c r="G137" s="73">
         <f t="shared" si="14"/>
         <v>16783</v>
       </c>
-      <c r="H137" s="69"/>
-      <c r="I137" s="69"/>
+      <c r="H137" s="68"/>
+      <c r="I137" s="68"/>
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B138" s="69">
+      <c r="B138" s="68">
         <f t="shared" si="12"/>
         <v>27198.333333333336</v>
       </c>
-      <c r="C138" s="69">
+      <c r="C138" s="68">
         <v>16319</v>
       </c>
-      <c r="D138" s="69">
+      <c r="D138" s="68">
         <v>16319</v>
       </c>
-      <c r="E138" s="69">
+      <c r="E138" s="68">
         <v>16319</v>
       </c>
-      <c r="F138" s="69">
+      <c r="F138" s="68">
         <f t="shared" si="13"/>
         <v>19038.833333333332</v>
       </c>
-      <c r="G138" s="75">
+      <c r="G138" s="73">
         <f t="shared" si="14"/>
         <v>16319</v>
       </c>
-      <c r="H138" s="69"/>
-      <c r="I138" s="69"/>
+      <c r="H138" s="68"/>
+      <c r="I138" s="68"/>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B139" s="69">
+      <c r="B139" s="68">
         <f t="shared" si="12"/>
         <v>20146.666666666668</v>
       </c>
-      <c r="C139" s="69">
+      <c r="C139" s="68">
         <v>12088</v>
       </c>
-      <c r="D139" s="69">
+      <c r="D139" s="68">
         <v>12088</v>
       </c>
-      <c r="E139" s="69">
+      <c r="E139" s="68">
         <v>12088</v>
       </c>
-      <c r="F139" s="69">
+      <c r="F139" s="68">
         <f t="shared" si="13"/>
         <v>14102.666666666666</v>
       </c>
-      <c r="G139" s="75">
+      <c r="G139" s="73">
         <f t="shared" si="14"/>
         <v>12088</v>
       </c>
-      <c r="H139" s="69"/>
-      <c r="I139" s="69"/>
+      <c r="H139" s="68"/>
+      <c r="I139" s="68"/>
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B140" s="69">
+      <c r="B140" s="68">
         <f t="shared" si="12"/>
         <v>22550</v>
       </c>
-      <c r="C140" s="69">
+      <c r="C140" s="68">
         <v>13530</v>
       </c>
-      <c r="D140" s="69">
+      <c r="D140" s="68">
         <v>13530</v>
       </c>
-      <c r="E140" s="69">
+      <c r="E140" s="68">
         <v>13530</v>
       </c>
-      <c r="F140" s="69">
+      <c r="F140" s="68">
         <f t="shared" si="13"/>
         <v>15784.999999999998</v>
       </c>
-      <c r="G140" s="75">
+      <c r="G140" s="73">
         <f t="shared" si="14"/>
         <v>13530</v>
       </c>
-      <c r="H140" s="69"/>
-      <c r="I140" s="69"/>
+      <c r="H140" s="68"/>
+      <c r="I140" s="68"/>
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B141" s="69">
+      <c r="B141" s="68">
         <f t="shared" si="12"/>
         <v>22550</v>
       </c>
-      <c r="C141" s="69">
+      <c r="C141" s="68">
         <v>13530</v>
       </c>
-      <c r="D141" s="69">
+      <c r="D141" s="68">
         <v>13530</v>
       </c>
-      <c r="E141" s="69">
+      <c r="E141" s="68">
         <v>13530</v>
       </c>
-      <c r="F141" s="69">
+      <c r="F141" s="68">
         <f t="shared" si="13"/>
         <v>15784.999999999998</v>
       </c>
-      <c r="G141" s="75">
+      <c r="G141" s="73">
         <f t="shared" si="14"/>
         <v>13530</v>
       </c>
-      <c r="H141" s="69"/>
-      <c r="I141" s="69"/>
+      <c r="H141" s="68"/>
+      <c r="I141" s="68"/>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B142" s="69">
+      <c r="B142" s="68">
         <f t="shared" si="12"/>
         <v>33800</v>
       </c>
-      <c r="C142" s="69">
+      <c r="C142" s="68">
         <v>20280</v>
       </c>
-      <c r="D142" s="69">
+      <c r="D142" s="68">
         <v>20280</v>
       </c>
-      <c r="E142" s="69">
+      <c r="E142" s="68">
         <v>20280</v>
       </c>
-      <c r="F142" s="69">
+      <c r="F142" s="68">
         <f t="shared" si="13"/>
         <v>23660</v>
       </c>
-      <c r="G142" s="75">
+      <c r="G142" s="73">
         <f t="shared" si="14"/>
         <v>20280</v>
       </c>
-      <c r="H142" s="69"/>
-      <c r="I142" s="69"/>
+      <c r="H142" s="68"/>
+      <c r="I142" s="68"/>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B143" s="69">
+      <c r="B143" s="68">
         <f t="shared" si="12"/>
         <v>28428.333333333336</v>
       </c>
-      <c r="C143" s="69">
+      <c r="C143" s="68">
         <v>17057</v>
       </c>
-      <c r="D143" s="69">
+      <c r="D143" s="68">
         <v>17057</v>
       </c>
-      <c r="E143" s="69">
+      <c r="E143" s="68">
         <v>17057</v>
       </c>
-      <c r="F143" s="69">
+      <c r="F143" s="68">
         <f t="shared" si="13"/>
         <v>19899.833333333332</v>
       </c>
-      <c r="G143" s="75">
+      <c r="G143" s="73">
         <f t="shared" si="14"/>
         <v>17057</v>
       </c>
-      <c r="H143" s="69"/>
-      <c r="I143" s="69"/>
+      <c r="H143" s="68"/>
+      <c r="I143" s="68"/>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B144" s="69">
+      <c r="B144" s="68">
         <f t="shared" si="12"/>
         <v>26893.333333333336</v>
       </c>
-      <c r="C144" s="69">
+      <c r="C144" s="68">
         <v>16136</v>
       </c>
-      <c r="D144" s="69">
+      <c r="D144" s="68">
         <v>16136</v>
       </c>
-      <c r="E144" s="69">
+      <c r="E144" s="68">
         <v>16136</v>
       </c>
-      <c r="F144" s="69">
+      <c r="F144" s="68">
         <f t="shared" si="13"/>
         <v>18825.333333333332</v>
       </c>
-      <c r="G144" s="75">
+      <c r="G144" s="73">
         <f t="shared" si="14"/>
         <v>16136</v>
       </c>
-      <c r="H144" s="69"/>
-      <c r="I144" s="69"/>
+      <c r="H144" s="68"/>
+      <c r="I144" s="68"/>
     </row>
     <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B145" s="69">
+      <c r="B145" s="68">
         <f t="shared" si="12"/>
         <v>26893.333333333336</v>
       </c>
-      <c r="C145" s="69">
+      <c r="C145" s="68">
         <v>16136</v>
       </c>
-      <c r="D145" s="69">
+      <c r="D145" s="68">
         <v>16136</v>
       </c>
-      <c r="E145" s="69">
+      <c r="E145" s="68">
         <v>16136</v>
       </c>
-      <c r="F145" s="69">
+      <c r="F145" s="68">
         <f t="shared" si="13"/>
         <v>18825.333333333332</v>
       </c>
-      <c r="G145" s="75">
+      <c r="G145" s="73">
         <f t="shared" si="14"/>
         <v>16136</v>
       </c>
-      <c r="H145" s="69"/>
-      <c r="I145" s="69"/>
+      <c r="H145" s="68"/>
+      <c r="I145" s="68"/>
     </row>
     <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B146" s="69">
+      <c r="B146" s="68">
         <f t="shared" si="12"/>
         <v>27198.333333333336</v>
       </c>
-      <c r="C146" s="69">
+      <c r="C146" s="68">
         <v>16319</v>
       </c>
-      <c r="D146" s="69">
+      <c r="D146" s="68">
         <v>16319</v>
       </c>
-      <c r="E146" s="69">
+      <c r="E146" s="68">
         <v>16319</v>
       </c>
-      <c r="F146" s="69">
+      <c r="F146" s="68">
         <f t="shared" si="13"/>
         <v>19038.833333333332</v>
       </c>
-      <c r="G146" s="75">
+      <c r="G146" s="73">
         <f t="shared" si="14"/>
         <v>16319</v>
       </c>
-      <c r="H146" s="69"/>
-      <c r="I146" s="69"/>
+      <c r="H146" s="68"/>
+      <c r="I146" s="68"/>
     </row>
     <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B147" s="69">
+      <c r="B147" s="68">
         <f t="shared" si="12"/>
         <v>32386.666666666668</v>
       </c>
-      <c r="C147" s="69">
+      <c r="C147" s="68">
         <v>19432</v>
       </c>
-      <c r="D147" s="69">
+      <c r="D147" s="68">
         <v>19432</v>
       </c>
-      <c r="E147" s="69">
+      <c r="E147" s="68">
         <v>19432</v>
       </c>
-      <c r="F147" s="69">
+      <c r="F147" s="68">
         <f t="shared" si="13"/>
         <v>22670.666666666668</v>
       </c>
-      <c r="G147" s="75">
+      <c r="G147" s="73">
         <f t="shared" si="14"/>
         <v>19432</v>
       </c>
-      <c r="H147" s="69"/>
-      <c r="I147" s="69"/>
+      <c r="H147" s="68"/>
+      <c r="I147" s="68"/>
     </row>
     <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B148" s="69">
+      <c r="B148" s="68">
         <f t="shared" si="12"/>
         <v>23586.666666666668</v>
       </c>
-      <c r="C148" s="69">
+      <c r="C148" s="68">
         <v>14152</v>
       </c>
-      <c r="D148" s="69">
+      <c r="D148" s="68">
         <v>14152</v>
       </c>
-      <c r="E148" s="69">
+      <c r="E148" s="68">
         <v>14152</v>
       </c>
-      <c r="F148" s="69">
+      <c r="F148" s="68">
         <f t="shared" si="13"/>
         <v>16510.666666666668</v>
       </c>
-      <c r="G148" s="75">
+      <c r="G148" s="73">
         <f t="shared" si="14"/>
         <v>14152</v>
       </c>
-      <c r="H148" s="69"/>
-      <c r="I148" s="69"/>
+      <c r="H148" s="68"/>
+      <c r="I148" s="68"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B149" s="69">
+      <c r="B149" s="68">
         <f t="shared" si="12"/>
         <v>57160</v>
       </c>
-      <c r="C149" s="69">
+      <c r="C149" s="68">
         <v>34296</v>
       </c>
-      <c r="D149" s="69">
+      <c r="D149" s="68">
         <v>34296</v>
       </c>
-      <c r="E149" s="69">
+      <c r="E149" s="68">
         <v>34296</v>
       </c>
-      <c r="F149" s="69">
+      <c r="F149" s="68">
         <f t="shared" si="13"/>
         <v>40012</v>
       </c>
-      <c r="G149" s="75">
+      <c r="G149" s="73">
         <f t="shared" si="14"/>
         <v>34296</v>
       </c>
-      <c r="H149" s="69"/>
-      <c r="I149" s="69"/>
+      <c r="H149" s="68"/>
+      <c r="I149" s="68"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B150" s="69">
+      <c r="B150" s="68">
         <f t="shared" si="12"/>
         <v>61121.666666666672</v>
       </c>
-      <c r="C150" s="69">
+      <c r="C150" s="68">
         <v>36673</v>
       </c>
-      <c r="D150" s="69">
+      <c r="D150" s="68">
         <v>36673</v>
       </c>
-      <c r="E150" s="69">
+      <c r="E150" s="68">
         <v>36673</v>
       </c>
-      <c r="F150" s="69">
+      <c r="F150" s="68">
         <f t="shared" si="13"/>
         <v>42785.166666666664</v>
       </c>
-      <c r="G150" s="75">
+      <c r="G150" s="73">
         <f t="shared" si="14"/>
         <v>36673</v>
       </c>
-      <c r="H150" s="69"/>
-      <c r="I150" s="69"/>
+      <c r="H150" s="68"/>
+      <c r="I150" s="68"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B151" s="117">
+      <c r="B151" s="113">
         <v>70000</v>
       </c>
-      <c r="C151" s="117">
+      <c r="C151" s="113">
         <v>40000</v>
       </c>
-      <c r="D151" s="117">
+      <c r="D151" s="113">
         <v>40000</v>
       </c>
-      <c r="E151" s="117">
+      <c r="E151" s="113">
         <v>40000</v>
       </c>
-      <c r="F151" s="117">
+      <c r="F151" s="113">
         <f t="shared" si="13"/>
         <v>49000</v>
       </c>
-      <c r="G151" s="104">
+      <c r="G151" s="100">
         <f>+B151*0.6</f>
         <v>42000</v>
       </c>
-      <c r="H151" s="117">
+      <c r="H151" s="113">
         <v>20000</v>
       </c>
-      <c r="I151" s="117">
+      <c r="I151" s="113">
         <v>20000</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="118" t="s">
+      <c r="A152" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B152" s="119"/>
-      <c r="C152" s="119"/>
-      <c r="D152" s="119"/>
-      <c r="E152" s="119"/>
-      <c r="F152" s="119"/>
-      <c r="G152" s="119"/>
-      <c r="H152" s="119"/>
-      <c r="I152" s="120"/>
+      <c r="B152" s="115"/>
+      <c r="C152" s="115"/>
+      <c r="D152" s="115"/>
+      <c r="E152" s="115"/>
+      <c r="F152" s="115"/>
+      <c r="G152" s="115"/>
+      <c r="H152" s="115"/>
+      <c r="I152" s="116"/>
     </row>
     <row r="153" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="93" t="s">
+      <c r="A153" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="B153" s="128"/>
-      <c r="C153" s="102"/>
-      <c r="D153" s="102"/>
-      <c r="E153" s="102"/>
-      <c r="F153" s="102"/>
-      <c r="G153" s="102" t="s">
+      <c r="B153" s="124"/>
+      <c r="C153" s="98"/>
+      <c r="D153" s="98"/>
+      <c r="E153" s="98"/>
+      <c r="F153" s="98"/>
+      <c r="G153" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="H153" s="102" t="s">
+      <c r="H153" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="I153" s="103" t="s">
+      <c r="I153" s="99" t="s">
         <v>130</v>
       </c>
       <c r="K153" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="L153" s="70">
+      <c r="L153" s="69">
         <v>12000</v>
       </c>
     </row>
     <row r="154" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="34" t="s">
+      <c r="A154" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="B154" s="89"/>
-      <c r="C154" s="89"/>
-      <c r="D154" s="89"/>
-      <c r="E154" s="89"/>
-      <c r="F154" s="89"/>
-      <c r="G154" s="89">
+      <c r="B154" s="87"/>
+      <c r="C154" s="87"/>
+      <c r="D154" s="87"/>
+      <c r="E154" s="87"/>
+      <c r="F154" s="87"/>
+      <c r="G154" s="87">
         <f>+$L$153</f>
         <v>12000</v>
       </c>
-      <c r="H154" s="89">
+      <c r="H154" s="87">
         <f t="shared" ref="H154:I154" si="15">+$L$153</f>
         <v>12000</v>
       </c>
-      <c r="I154" s="110">
+      <c r="I154" s="106">
         <f t="shared" si="15"/>
         <v>12000</v>
       </c>
     </row>
     <row r="155" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="66" t="s">
+      <c r="A155" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="B155" s="87"/>
-      <c r="C155" s="87"/>
-      <c r="D155" s="87"/>
-      <c r="E155" s="87"/>
-      <c r="F155" s="87"/>
-      <c r="G155" s="88">
+      <c r="B155" s="85"/>
+      <c r="C155" s="85"/>
+      <c r="D155" s="85"/>
+      <c r="E155" s="85"/>
+      <c r="F155" s="85"/>
+      <c r="G155" s="86">
         <v>25000</v>
       </c>
-      <c r="H155" s="87">
+      <c r="H155" s="85">
         <f>+G155</f>
         <v>25000</v>
       </c>
-      <c r="I155" s="105">
+      <c r="I155" s="101">
         <f>+G155</f>
         <v>25000</v>
       </c>
       <c r="K155" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="L155" s="70">
+      <c r="L155" s="69">
         <v>22000</v>
       </c>
     </row>
     <row r="156" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B156" s="87"/>
-      <c r="C156" s="87"/>
-      <c r="D156" s="87"/>
-      <c r="E156" s="87"/>
-      <c r="F156" s="87"/>
-      <c r="G156" s="87">
-        <f>+$L$155</f>
+        <v>216</v>
+      </c>
+      <c r="B156" s="85"/>
+      <c r="C156" s="85"/>
+      <c r="D156" s="85"/>
+      <c r="E156" s="85"/>
+      <c r="F156" s="85"/>
+      <c r="G156" s="85">
+        <f t="shared" ref="G156:G166" si="16">+$L$155</f>
         <v>22000</v>
       </c>
-      <c r="H156" s="87">
-        <f t="shared" ref="H156:I167" si="16">+$L$155</f>
+      <c r="H156" s="85">
+        <f t="shared" ref="H156:I166" si="17">+$L$155</f>
         <v>22000</v>
       </c>
-      <c r="I156" s="105">
+      <c r="I156" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A157" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B157" s="85"/>
+      <c r="C157" s="85"/>
+      <c r="D157" s="85"/>
+      <c r="E157" s="85"/>
+      <c r="F157" s="85"/>
+      <c r="G157" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="B157" s="87"/>
-      <c r="C157" s="87"/>
-      <c r="D157" s="87"/>
-      <c r="E157" s="87"/>
-      <c r="F157" s="87"/>
-      <c r="G157" s="87">
-        <f t="shared" ref="G157:G167" si="17">+$L$155</f>
+      <c r="H157" s="85">
+        <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H157" s="87">
+      <c r="I157" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A158" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B158" s="85"/>
+      <c r="C158" s="85"/>
+      <c r="D158" s="85"/>
+      <c r="E158" s="85"/>
+      <c r="F158" s="85"/>
+      <c r="G158" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I157" s="105">
+      <c r="H158" s="85">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="I158" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A159" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="B159" s="85"/>
+      <c r="C159" s="85"/>
+      <c r="D159" s="85"/>
+      <c r="E159" s="85"/>
+      <c r="F159" s="85"/>
+      <c r="G159" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="B158" s="87"/>
-      <c r="C158" s="87"/>
-      <c r="D158" s="87"/>
-      <c r="E158" s="87"/>
-      <c r="F158" s="87"/>
-      <c r="G158" s="87">
+      <c r="H159" s="85">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H158" s="87">
+      <c r="I159" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="B160" s="85"/>
+      <c r="C160" s="85"/>
+      <c r="D160" s="85"/>
+      <c r="E160" s="85"/>
+      <c r="F160" s="85"/>
+      <c r="G160" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I158" s="105">
+      <c r="H160" s="85">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="I160" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B161" s="85"/>
+      <c r="C161" s="85"/>
+      <c r="D161" s="85"/>
+      <c r="E161" s="85"/>
+      <c r="F161" s="85"/>
+      <c r="G161" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="B159" s="87"/>
-      <c r="C159" s="87"/>
-      <c r="D159" s="87"/>
-      <c r="E159" s="87"/>
-      <c r="F159" s="87"/>
-      <c r="G159" s="87">
+      <c r="H161" s="85">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H159" s="87">
+      <c r="I161" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A162" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B162" s="85"/>
+      <c r="C162" s="85"/>
+      <c r="D162" s="85"/>
+      <c r="E162" s="85"/>
+      <c r="F162" s="85"/>
+      <c r="G162" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I159" s="105">
+      <c r="H162" s="85">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="I162" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="85"/>
+      <c r="C163" s="85"/>
+      <c r="D163" s="85"/>
+      <c r="E163" s="85"/>
+      <c r="F163" s="85"/>
+      <c r="G163" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="B160" s="87"/>
-      <c r="C160" s="87"/>
-      <c r="D160" s="87"/>
-      <c r="E160" s="87"/>
-      <c r="F160" s="87"/>
-      <c r="G160" s="87">
+      <c r="H163" s="85">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H160" s="87">
+      <c r="I163" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A164" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B164" s="85"/>
+      <c r="C164" s="85"/>
+      <c r="D164" s="85"/>
+      <c r="E164" s="85"/>
+      <c r="F164" s="85"/>
+      <c r="G164" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I160" s="105">
+      <c r="H164" s="85">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="I164" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A165" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="B165" s="85"/>
+      <c r="C165" s="85"/>
+      <c r="D165" s="85"/>
+      <c r="E165" s="85"/>
+      <c r="F165" s="85"/>
+      <c r="G165" s="85">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="B161" s="87"/>
-      <c r="C161" s="87"/>
-      <c r="D161" s="87"/>
-      <c r="E161" s="87"/>
-      <c r="F161" s="87"/>
-      <c r="G161" s="87">
+      <c r="H165" s="85">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H161" s="87">
+      <c r="I165" s="101">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="B166" s="103"/>
+      <c r="C166" s="103"/>
+      <c r="D166" s="103"/>
+      <c r="E166" s="103"/>
+      <c r="F166" s="103"/>
+      <c r="G166" s="103">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I161" s="105">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="B162" s="87"/>
-      <c r="C162" s="87"/>
-      <c r="D162" s="87"/>
-      <c r="E162" s="87"/>
-      <c r="F162" s="87"/>
-      <c r="G162" s="87">
+      <c r="H166" s="103">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H162" s="87">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="I162" s="105">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="B163" s="87"/>
-      <c r="C163" s="87"/>
-      <c r="D163" s="87"/>
-      <c r="E163" s="87"/>
-      <c r="F163" s="87"/>
-      <c r="G163" s="87">
+      <c r="I166" s="104">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-      <c r="H163" s="87">
-        <f t="shared" si="16"/>
+    </row>
+    <row r="167" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B167" s="87"/>
+      <c r="C167" s="87"/>
+      <c r="D167" s="87"/>
+      <c r="E167" s="87"/>
+      <c r="F167" s="87"/>
+      <c r="G167" s="105">
+        <v>32000</v>
+      </c>
+      <c r="H167" s="105">
+        <f t="shared" ref="H167:H168" si="18">+H166</f>
         <v>22000</v>
       </c>
-      <c r="I163" s="105">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="B164" s="87"/>
-      <c r="C164" s="87"/>
-      <c r="D164" s="87"/>
-      <c r="E164" s="87"/>
-      <c r="F164" s="87"/>
-      <c r="G164" s="87">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="H164" s="87">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="I164" s="105">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="B165" s="87"/>
-      <c r="C165" s="87"/>
-      <c r="D165" s="87"/>
-      <c r="E165" s="87"/>
-      <c r="F165" s="87"/>
-      <c r="G165" s="87">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="H165" s="87">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="I165" s="105">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="B166" s="87"/>
-      <c r="C166" s="87"/>
-      <c r="D166" s="87"/>
-      <c r="E166" s="87"/>
-      <c r="F166" s="87"/>
-      <c r="G166" s="87">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="H166" s="87">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="I166" s="105">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B167" s="107"/>
-      <c r="C167" s="107"/>
-      <c r="D167" s="107"/>
-      <c r="E167" s="107"/>
-      <c r="F167" s="107"/>
-      <c r="G167" s="107">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="H167" s="107">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="I167" s="108">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
+      <c r="I167" s="87"/>
     </row>
     <row r="168" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B168" s="89"/>
-      <c r="C168" s="89"/>
-      <c r="D168" s="89"/>
-      <c r="E168" s="89"/>
-      <c r="F168" s="89"/>
-      <c r="G168" s="109">
+      <c r="A168" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B168" s="92"/>
+      <c r="C168" s="92"/>
+      <c r="D168" s="92"/>
+      <c r="E168" s="92"/>
+      <c r="F168" s="92"/>
+      <c r="G168" s="91">
         <v>32000</v>
       </c>
-      <c r="H168" s="109">
-        <f t="shared" ref="H168:H169" si="18">+H167</f>
-        <v>22000</v>
-      </c>
-      <c r="I168" s="89"/>
-    </row>
-    <row r="169" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B169" s="95"/>
-      <c r="C169" s="95"/>
-      <c r="D169" s="95"/>
-      <c r="E169" s="95"/>
-      <c r="F169" s="95"/>
-      <c r="G169" s="94">
-        <v>32000</v>
-      </c>
-      <c r="H169" s="94">
+      <c r="H168" s="91">
         <f t="shared" si="18"/>
         <v>22000</v>
       </c>
-      <c r="I169" s="95"/>
-    </row>
-    <row r="170" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="93" t="s">
-        <v>171</v>
-      </c>
-      <c r="B170" s="128"/>
-      <c r="C170" s="129"/>
-      <c r="D170" s="129"/>
-      <c r="E170" s="102"/>
-      <c r="F170" s="102"/>
-      <c r="G170" s="102" t="s">
+      <c r="I168" s="92"/>
+    </row>
+    <row r="169" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="B169" s="124"/>
+      <c r="C169" s="125"/>
+      <c r="D169" s="125"/>
+      <c r="E169" s="98"/>
+      <c r="F169" s="98"/>
+      <c r="G169" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="H170" s="103" t="s">
+      <c r="H169" s="99" t="s">
         <v>100</v>
       </c>
-      <c r="I170" s="103" t="s">
+      <c r="I169" s="99" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="8" t="s">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B171" s="100"/>
-      <c r="C171" s="100"/>
-      <c r="D171" s="100"/>
-      <c r="E171" s="100"/>
-      <c r="F171" s="100"/>
-      <c r="G171" s="99">
+      <c r="B170" s="96"/>
+      <c r="C170" s="96"/>
+      <c r="D170" s="96"/>
+      <c r="E170" s="96"/>
+      <c r="F170" s="96"/>
+      <c r="G170" s="95">
         <v>24000</v>
       </c>
-      <c r="H171" s="100">
-        <f>+G171</f>
+      <c r="H170" s="96">
+        <f>+G170</f>
         <v>24000</v>
       </c>
-      <c r="I171" s="101">
-        <f>+G171</f>
+      <c r="I170" s="97">
+        <f>+G170</f>
         <v>24000</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="10" t="s">
+    <row r="171" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B172" s="76"/>
-      <c r="C172" s="76"/>
-      <c r="D172" s="76"/>
-      <c r="E172" s="76"/>
-      <c r="F172" s="76"/>
-      <c r="G172" s="76"/>
-      <c r="H172" s="76">
-        <f t="shared" ref="H172:I214" si="19">+G172</f>
+      <c r="B171" s="74"/>
+      <c r="C171" s="74"/>
+      <c r="D171" s="74"/>
+      <c r="E171" s="74"/>
+      <c r="F171" s="74"/>
+      <c r="G171" s="74"/>
+      <c r="H171" s="74">
+        <f t="shared" ref="H171:I211" si="19">+G171</f>
         <v>0</v>
       </c>
-      <c r="I172" s="96">
+      <c r="I171" s="93">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="B173" s="130"/>
-      <c r="C173" s="130"/>
-      <c r="D173" s="130"/>
-      <c r="E173" s="130"/>
-      <c r="F173" s="130"/>
-      <c r="G173" s="90">
-        <f>$L$173</f>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B172" s="88"/>
+      <c r="C172" s="88"/>
+      <c r="D172" s="88"/>
+      <c r="E172" s="88"/>
+      <c r="F172" s="88"/>
+      <c r="G172" s="88">
+        <f t="shared" ref="G172:I172" si="20">$L$172</f>
         <v>16640</v>
       </c>
-      <c r="H173" s="90">
-        <f t="shared" ref="H173:I173" si="20">$L$173</f>
-        <v>16640</v>
-      </c>
-      <c r="I173" s="97">
+      <c r="H172" s="88">
         <f t="shared" si="20"/>
         <v>16640</v>
       </c>
-      <c r="K173" s="63" t="s">
+      <c r="I172" s="94">
+        <f t="shared" si="20"/>
+        <v>16640</v>
+      </c>
+      <c r="K172" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="L173" s="70">
+      <c r="L172" s="69">
         <v>16640</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="67" t="s">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B174" s="130"/>
-      <c r="C174" s="130"/>
-      <c r="D174" s="130"/>
-      <c r="E174" s="130"/>
-      <c r="F174" s="130"/>
-      <c r="G174" s="90">
-        <f>$L$174</f>
+      <c r="B173" s="88"/>
+      <c r="C173" s="88"/>
+      <c r="D173" s="88"/>
+      <c r="E173" s="88"/>
+      <c r="F173" s="88"/>
+      <c r="G173" s="88">
+        <f>$L$173</f>
         <v>9600</v>
       </c>
-      <c r="H174" s="90">
-        <f t="shared" ref="H174:I174" si="21">$L$174</f>
+      <c r="H173" s="88">
+        <f t="shared" ref="H173:I173" si="21">$L$173</f>
         <v>9600</v>
       </c>
-      <c r="I174" s="97">
+      <c r="I173" s="94">
         <f t="shared" si="21"/>
         <v>9600</v>
       </c>
-      <c r="K174" s="63" t="s">
+      <c r="K173" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="L174" s="70">
+      <c r="L173" s="69">
         <v>9600</v>
       </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B174" s="88"/>
+      <c r="C174" s="88"/>
+      <c r="D174" s="88"/>
+      <c r="E174" s="88"/>
+      <c r="F174" s="88"/>
+      <c r="G174" s="88">
+        <f>$L$172</f>
+        <v>16640</v>
+      </c>
+      <c r="H174" s="88">
+        <f t="shared" ref="H174:I174" si="22">$L$172</f>
+        <v>16640</v>
+      </c>
+      <c r="I174" s="94">
+        <f t="shared" si="22"/>
+        <v>16640</v>
+      </c>
+      <c r="L174" s="67"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B175" s="91"/>
-      <c r="C175" s="91"/>
-      <c r="D175" s="91"/>
-      <c r="E175" s="91"/>
-      <c r="F175" s="91"/>
-      <c r="G175" s="91">
-        <f t="shared" ref="G175:I175" si="22">$L$173</f>
-        <v>16640</v>
-      </c>
-      <c r="H175" s="91">
-        <f t="shared" si="22"/>
-        <v>16640</v>
-      </c>
-      <c r="I175" s="98">
-        <f t="shared" si="22"/>
-        <v>16640</v>
-      </c>
-      <c r="L175" s="68"/>
+        <v>159</v>
+      </c>
+      <c r="B175" s="88"/>
+      <c r="C175" s="88"/>
+      <c r="D175" s="88"/>
+      <c r="E175" s="88"/>
+      <c r="F175" s="88"/>
+      <c r="G175" s="88">
+        <f>$L$173</f>
+        <v>9600</v>
+      </c>
+      <c r="H175" s="88">
+        <f t="shared" ref="H175:I175" si="23">$L$173</f>
+        <v>9600</v>
+      </c>
+      <c r="I175" s="94">
+        <f t="shared" si="23"/>
+        <v>9600</v>
+      </c>
+      <c r="K175" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="L175" s="69">
+        <v>32000</v>
+      </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B176" s="91"/>
-      <c r="C176" s="91"/>
-      <c r="D176" s="91"/>
-      <c r="E176" s="91"/>
-      <c r="F176" s="91"/>
-      <c r="G176" s="91">
-        <f>$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="H176" s="91">
-        <f t="shared" ref="H176:I176" si="23">$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="I176" s="98">
-        <f t="shared" si="23"/>
-        <v>9600</v>
-      </c>
-      <c r="K176" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="L176" s="70">
-        <v>32000</v>
+        <v>173</v>
+      </c>
+      <c r="B176" s="88"/>
+      <c r="C176" s="88"/>
+      <c r="D176" s="88"/>
+      <c r="E176" s="88"/>
+      <c r="F176" s="88"/>
+      <c r="G176" s="88">
+        <f t="shared" ref="G176:I184" si="24">$L$172</f>
+        <v>16640</v>
+      </c>
+      <c r="H176" s="88">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+      <c r="I176" s="94">
+        <f t="shared" si="24"/>
+        <v>16640</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B177" s="91"/>
-      <c r="C177" s="91"/>
-      <c r="D177" s="91"/>
-      <c r="E177" s="91"/>
-      <c r="F177" s="91"/>
-      <c r="G177" s="91">
+        <v>159</v>
+      </c>
+      <c r="B177" s="88"/>
+      <c r="C177" s="88"/>
+      <c r="D177" s="88"/>
+      <c r="E177" s="88"/>
+      <c r="F177" s="88"/>
+      <c r="G177" s="88">
         <f>$L$173</f>
-        <v>16640</v>
-      </c>
-      <c r="H177" s="91">
-        <f t="shared" ref="H177:I177" si="24">$L$173</f>
-        <v>16640</v>
-      </c>
-      <c r="I177" s="98">
+        <v>9600</v>
+      </c>
+      <c r="H177" s="88">
+        <f t="shared" ref="H177:I177" si="25">$L$173</f>
+        <v>9600</v>
+      </c>
+      <c r="I177" s="94">
+        <f t="shared" si="25"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B178" s="88"/>
+      <c r="C178" s="88"/>
+      <c r="D178" s="88"/>
+      <c r="E178" s="88"/>
+      <c r="F178" s="88"/>
+      <c r="G178" s="88">
         <f t="shared" si="24"/>
         <v>16640</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B178" s="91"/>
-      <c r="C178" s="91"/>
-      <c r="D178" s="91"/>
-      <c r="E178" s="91"/>
-      <c r="F178" s="91"/>
-      <c r="G178" s="91">
-        <f>$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="H178" s="91">
-        <f t="shared" ref="H178:I178" si="25">$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="I178" s="98">
-        <f t="shared" si="25"/>
-        <v>9600</v>
+      <c r="H178" s="88">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+      <c r="I178" s="94">
+        <f t="shared" si="24"/>
+        <v>16640</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B179" s="91"/>
-      <c r="C179" s="91"/>
-      <c r="D179" s="91"/>
-      <c r="E179" s="91"/>
-      <c r="F179" s="91"/>
-      <c r="G179" s="91">
-        <f t="shared" ref="G179:I187" si="26">$L$173</f>
-        <v>16640</v>
-      </c>
-      <c r="H179" s="91">
+        <v>159</v>
+      </c>
+      <c r="B179" s="88"/>
+      <c r="C179" s="88"/>
+      <c r="D179" s="88"/>
+      <c r="E179" s="88"/>
+      <c r="F179" s="88"/>
+      <c r="G179" s="88">
+        <f>$L$173</f>
+        <v>9600</v>
+      </c>
+      <c r="H179" s="88">
+        <f t="shared" ref="H179:I179" si="26">$L$173</f>
+        <v>9600</v>
+      </c>
+      <c r="I179" s="94">
         <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="I179" s="98">
-        <f t="shared" si="26"/>
-        <v>16640</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B180" s="88"/>
+      <c r="C180" s="88"/>
+      <c r="D180" s="88"/>
+      <c r="E180" s="88"/>
+      <c r="F180" s="88"/>
+      <c r="G180" s="88">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+      <c r="H180" s="88">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+      <c r="I180" s="94">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B180" s="91"/>
-      <c r="C180" s="91"/>
-      <c r="D180" s="91"/>
-      <c r="E180" s="91"/>
-      <c r="F180" s="91"/>
-      <c r="G180" s="91">
-        <f>$L$174</f>
+      <c r="B181" s="88"/>
+      <c r="C181" s="88"/>
+      <c r="D181" s="88"/>
+      <c r="E181" s="88"/>
+      <c r="F181" s="88"/>
+      <c r="G181" s="88">
+        <f>$L$173</f>
         <v>9600</v>
       </c>
-      <c r="H180" s="91">
-        <f t="shared" ref="H180:I180" si="27">$L$174</f>
+      <c r="H181" s="88">
+        <f t="shared" ref="H181:I181" si="27">$L$173</f>
         <v>9600</v>
       </c>
-      <c r="I180" s="98">
+      <c r="I181" s="94">
         <f t="shared" si="27"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B181" s="91"/>
-      <c r="C181" s="91"/>
-      <c r="D181" s="91"/>
-      <c r="E181" s="91"/>
-      <c r="F181" s="91"/>
-      <c r="G181" s="91">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="H181" s="91">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="I181" s="98">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-    </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B182" s="88"/>
+      <c r="C182" s="88"/>
+      <c r="D182" s="88"/>
+      <c r="E182" s="88"/>
+      <c r="F182" s="88"/>
+      <c r="G182" s="88">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+      <c r="H182" s="88">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+      <c r="I182" s="94">
+        <f t="shared" si="24"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B182" s="91"/>
-      <c r="C182" s="91"/>
-      <c r="D182" s="91"/>
-      <c r="E182" s="91"/>
-      <c r="F182" s="91"/>
-      <c r="G182" s="91">
-        <f>$L$174</f>
+      <c r="B183" s="88"/>
+      <c r="C183" s="88"/>
+      <c r="D183" s="88"/>
+      <c r="E183" s="88"/>
+      <c r="F183" s="88"/>
+      <c r="G183" s="88">
+        <f>$L$173</f>
         <v>9600</v>
       </c>
-      <c r="H182" s="91">
-        <f t="shared" ref="H182:I182" si="28">$L$174</f>
+      <c r="H183" s="88">
+        <f t="shared" ref="H183:I183" si="28">$L$173</f>
         <v>9600</v>
       </c>
-      <c r="I182" s="98">
+      <c r="I183" s="94">
         <f t="shared" si="28"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B183" s="91"/>
-      <c r="C183" s="91"/>
-      <c r="D183" s="91"/>
-      <c r="E183" s="91"/>
-      <c r="F183" s="91"/>
-      <c r="G183" s="91">
-        <f t="shared" si="26"/>
+    <row r="184" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B184" s="88"/>
+      <c r="C184" s="88"/>
+      <c r="D184" s="88"/>
+      <c r="E184" s="88"/>
+      <c r="F184" s="88"/>
+      <c r="G184" s="88">
+        <f t="shared" si="24"/>
         <v>16640</v>
       </c>
-      <c r="H183" s="91">
-        <f t="shared" si="26"/>
+      <c r="H184" s="88">
+        <f t="shared" si="24"/>
         <v>16640</v>
       </c>
-      <c r="I183" s="98">
-        <f t="shared" si="26"/>
+      <c r="I184" s="94">
+        <f t="shared" si="24"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="9" t="s">
+    <row r="185" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B184" s="91"/>
-      <c r="C184" s="91"/>
-      <c r="D184" s="91"/>
-      <c r="E184" s="91"/>
-      <c r="F184" s="91"/>
-      <c r="G184" s="91">
-        <f>$L$174</f>
+      <c r="B185" s="88"/>
+      <c r="C185" s="88"/>
+      <c r="D185" s="88"/>
+      <c r="E185" s="88"/>
+      <c r="F185" s="88"/>
+      <c r="G185" s="88">
+        <f>$L$173</f>
         <v>9600</v>
       </c>
-      <c r="H184" s="91">
-        <f t="shared" ref="H184:I184" si="29">$L$174</f>
+      <c r="H185" s="88">
+        <f t="shared" ref="H185:I185" si="29">$L$173</f>
         <v>9600</v>
       </c>
-      <c r="I184" s="98">
+      <c r="I185" s="94">
         <f t="shared" si="29"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B185" s="91"/>
-      <c r="C185" s="91"/>
-      <c r="D185" s="91"/>
-      <c r="E185" s="91"/>
-      <c r="F185" s="91"/>
-      <c r="G185" s="91">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="H185" s="91">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="I185" s="98">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B186" s="91"/>
-      <c r="C186" s="91"/>
-      <c r="D186" s="91"/>
-      <c r="E186" s="91"/>
-      <c r="F186" s="91"/>
-      <c r="G186" s="91">
-        <f>$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="H186" s="91">
-        <f t="shared" ref="H186:I186" si="30">$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="I186" s="98">
-        <f t="shared" si="30"/>
-        <v>9600</v>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B186" s="88"/>
+      <c r="C186" s="88"/>
+      <c r="D186" s="88"/>
+      <c r="E186" s="88"/>
+      <c r="F186" s="88"/>
+      <c r="G186" s="89">
+        <v>36000</v>
+      </c>
+      <c r="H186" s="88">
+        <f t="shared" si="19"/>
+        <v>36000</v>
+      </c>
+      <c r="I186" s="94">
+        <f>+G186</f>
+        <v>36000</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B187" s="91"/>
-      <c r="C187" s="91"/>
-      <c r="D187" s="91"/>
-      <c r="E187" s="91"/>
-      <c r="F187" s="91"/>
-      <c r="G187" s="91">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="H187" s="91">
-        <f t="shared" si="26"/>
-        <v>16640</v>
-      </c>
-      <c r="I187" s="98">
-        <f t="shared" si="26"/>
-        <v>16640</v>
+      <c r="B187" s="88"/>
+      <c r="C187" s="88"/>
+      <c r="D187" s="88"/>
+      <c r="E187" s="88"/>
+      <c r="F187" s="88"/>
+      <c r="G187" s="88">
+        <f>$L$175</f>
+        <v>32000</v>
+      </c>
+      <c r="H187" s="88">
+        <f t="shared" ref="H187:I187" si="30">$L$175</f>
+        <v>32000</v>
+      </c>
+      <c r="I187" s="94">
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B188" s="91"/>
-      <c r="C188" s="91"/>
-      <c r="D188" s="91"/>
-      <c r="E188" s="91"/>
-      <c r="F188" s="91"/>
-      <c r="G188" s="91">
-        <f>$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="H188" s="91">
-        <f t="shared" ref="H188:I188" si="31">$L$174</f>
-        <v>9600</v>
-      </c>
-      <c r="I188" s="98">
+        <v>179</v>
+      </c>
+      <c r="B188" s="88"/>
+      <c r="C188" s="88"/>
+      <c r="D188" s="88"/>
+      <c r="E188" s="88"/>
+      <c r="F188" s="88"/>
+      <c r="G188" s="88">
+        <f t="shared" ref="G188:I205" si="31">$L$175</f>
+        <v>32000</v>
+      </c>
+      <c r="H188" s="88">
         <f t="shared" si="31"/>
-        <v>9600</v>
+        <v>32000</v>
+      </c>
+      <c r="I188" s="94">
+        <f t="shared" si="31"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="66" t="s">
-        <v>162</v>
-      </c>
-      <c r="B189" s="91"/>
-      <c r="C189" s="91"/>
-      <c r="D189" s="91"/>
-      <c r="E189" s="91"/>
-      <c r="F189" s="91"/>
-      <c r="G189" s="92">
-        <v>36000</v>
-      </c>
-      <c r="H189" s="91">
-        <f t="shared" si="19"/>
-        <v>36000</v>
-      </c>
-      <c r="I189" s="98">
-        <f>+G189</f>
-        <v>36000</v>
+      <c r="A189" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B189" s="88"/>
+      <c r="C189" s="88"/>
+      <c r="D189" s="88"/>
+      <c r="E189" s="88"/>
+      <c r="F189" s="88"/>
+      <c r="G189" s="88">
+        <f>$L$175</f>
+        <v>32000</v>
+      </c>
+      <c r="H189" s="88">
+        <f t="shared" si="31"/>
+        <v>32000</v>
+      </c>
+      <c r="I189" s="94">
+        <f t="shared" si="31"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="B190" s="91"/>
-      <c r="C190" s="91"/>
-      <c r="D190" s="91"/>
-      <c r="E190" s="91"/>
-      <c r="F190" s="91"/>
-      <c r="G190" s="91">
-        <f>$L$176</f>
+        <v>181</v>
+      </c>
+      <c r="B190" s="88"/>
+      <c r="C190" s="88"/>
+      <c r="D190" s="88"/>
+      <c r="E190" s="88"/>
+      <c r="F190" s="88"/>
+      <c r="G190" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H190" s="91">
-        <f t="shared" ref="H190:I190" si="32">$L$176</f>
+      <c r="H190" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I190" s="98">
-        <f t="shared" si="32"/>
+      <c r="I190" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B191" s="91"/>
-      <c r="C191" s="91"/>
-      <c r="D191" s="91"/>
-      <c r="E191" s="91"/>
-      <c r="F191" s="91"/>
-      <c r="G191" s="91">
-        <f t="shared" ref="G191:I208" si="33">$L$176</f>
+        <v>182</v>
+      </c>
+      <c r="B191" s="88"/>
+      <c r="C191" s="88"/>
+      <c r="D191" s="88"/>
+      <c r="E191" s="88"/>
+      <c r="F191" s="88"/>
+      <c r="G191" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H191" s="91">
-        <f t="shared" si="33"/>
+      <c r="H191" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I191" s="98">
-        <f t="shared" si="33"/>
+      <c r="I191" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B192" s="91"/>
-      <c r="C192" s="91"/>
-      <c r="D192" s="91"/>
-      <c r="E192" s="91"/>
-      <c r="F192" s="91"/>
-      <c r="G192" s="91">
-        <f>$L$176</f>
+        <v>56</v>
+      </c>
+      <c r="B192" s="88"/>
+      <c r="C192" s="88"/>
+      <c r="D192" s="88"/>
+      <c r="E192" s="88"/>
+      <c r="F192" s="88"/>
+      <c r="G192" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H192" s="91">
-        <f t="shared" si="33"/>
+      <c r="H192" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I192" s="98">
-        <f t="shared" si="33"/>
+      <c r="I192" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B193" s="91"/>
-      <c r="C193" s="91"/>
-      <c r="D193" s="91"/>
-      <c r="E193" s="91"/>
-      <c r="F193" s="91"/>
-      <c r="G193" s="91">
-        <f t="shared" si="33"/>
+        <v>57</v>
+      </c>
+      <c r="B193" s="88"/>
+      <c r="C193" s="88"/>
+      <c r="D193" s="88"/>
+      <c r="E193" s="88"/>
+      <c r="F193" s="88"/>
+      <c r="G193" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H193" s="91">
-        <f t="shared" si="33"/>
+      <c r="H193" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I193" s="98">
-        <f t="shared" si="33"/>
+      <c r="I193" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
@@ -9863,1008 +9847,942 @@
       <c r="A194" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B194" s="91"/>
-      <c r="C194" s="91"/>
-      <c r="D194" s="91"/>
-      <c r="E194" s="91"/>
-      <c r="F194" s="91"/>
-      <c r="G194" s="91">
-        <f t="shared" si="33"/>
+      <c r="B194" s="88"/>
+      <c r="C194" s="88"/>
+      <c r="D194" s="88"/>
+      <c r="E194" s="88"/>
+      <c r="F194" s="88"/>
+      <c r="G194" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H194" s="91">
-        <f t="shared" si="33"/>
+      <c r="H194" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I194" s="98">
-        <f t="shared" si="33"/>
+      <c r="I194" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B195" s="91"/>
-      <c r="C195" s="91"/>
-      <c r="D195" s="91"/>
-      <c r="E195" s="91"/>
-      <c r="F195" s="91"/>
-      <c r="G195" s="91">
-        <f t="shared" si="33"/>
+        <v>184</v>
+      </c>
+      <c r="B195" s="88"/>
+      <c r="C195" s="88"/>
+      <c r="D195" s="88"/>
+      <c r="E195" s="88"/>
+      <c r="F195" s="88"/>
+      <c r="G195" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H195" s="91">
-        <f t="shared" si="33"/>
+      <c r="H195" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I195" s="98">
-        <f t="shared" si="33"/>
+      <c r="I195" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B196" s="91"/>
-      <c r="C196" s="91"/>
-      <c r="D196" s="91"/>
-      <c r="E196" s="91"/>
-      <c r="F196" s="91"/>
-      <c r="G196" s="91">
-        <f t="shared" si="33"/>
+      <c r="A196" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B196" s="88"/>
+      <c r="C196" s="88"/>
+      <c r="D196" s="88"/>
+      <c r="E196" s="88"/>
+      <c r="F196" s="88"/>
+      <c r="G196" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H196" s="91">
-        <f t="shared" si="33"/>
+      <c r="H196" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I196" s="98">
-        <f t="shared" si="33"/>
+      <c r="I196" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B197" s="91"/>
-      <c r="C197" s="91"/>
-      <c r="D197" s="91"/>
-      <c r="E197" s="91"/>
-      <c r="F197" s="91"/>
-      <c r="G197" s="91">
-        <f t="shared" si="33"/>
+      <c r="A197" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="B197" s="88"/>
+      <c r="C197" s="88"/>
+      <c r="D197" s="88"/>
+      <c r="E197" s="88"/>
+      <c r="F197" s="88"/>
+      <c r="G197" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H197" s="91">
-        <f t="shared" si="33"/>
+      <c r="H197" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I197" s="98">
-        <f t="shared" si="33"/>
+      <c r="I197" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B198" s="91"/>
-      <c r="C198" s="91"/>
-      <c r="D198" s="91"/>
-      <c r="E198" s="91"/>
-      <c r="F198" s="91"/>
-      <c r="G198" s="91">
-        <f t="shared" si="33"/>
+      <c r="A198" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="B198" s="88"/>
+      <c r="C198" s="88"/>
+      <c r="D198" s="88"/>
+      <c r="E198" s="88"/>
+      <c r="F198" s="88"/>
+      <c r="G198" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H198" s="91">
-        <f t="shared" si="33"/>
+      <c r="H198" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I198" s="98">
-        <f t="shared" si="33"/>
+      <c r="I198" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="B199" s="91"/>
-      <c r="C199" s="91"/>
-      <c r="D199" s="91"/>
-      <c r="E199" s="91"/>
-      <c r="F199" s="91"/>
-      <c r="G199" s="91">
-        <f t="shared" si="33"/>
+        <v>188</v>
+      </c>
+      <c r="B199" s="88"/>
+      <c r="C199" s="88"/>
+      <c r="D199" s="88"/>
+      <c r="E199" s="88"/>
+      <c r="F199" s="88"/>
+      <c r="G199" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H199" s="91">
-        <f t="shared" si="33"/>
+      <c r="H199" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I199" s="98">
-        <f t="shared" si="33"/>
+      <c r="I199" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="B200" s="91"/>
-      <c r="C200" s="91"/>
-      <c r="D200" s="91"/>
-      <c r="E200" s="91"/>
-      <c r="F200" s="91"/>
-      <c r="G200" s="91">
-        <f t="shared" si="33"/>
+        <v>189</v>
+      </c>
+      <c r="B200" s="88"/>
+      <c r="C200" s="88"/>
+      <c r="D200" s="88"/>
+      <c r="E200" s="88"/>
+      <c r="F200" s="88"/>
+      <c r="G200" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H200" s="91">
-        <f t="shared" si="33"/>
+      <c r="H200" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I200" s="98">
-        <f t="shared" si="33"/>
+      <c r="I200" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="B201" s="91"/>
-      <c r="C201" s="91"/>
-      <c r="D201" s="91"/>
-      <c r="E201" s="91"/>
-      <c r="F201" s="91"/>
-      <c r="G201" s="91">
-        <f t="shared" si="33"/>
+        <v>54</v>
+      </c>
+      <c r="B201" s="88"/>
+      <c r="C201" s="88"/>
+      <c r="D201" s="88"/>
+      <c r="E201" s="88"/>
+      <c r="F201" s="88"/>
+      <c r="G201" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H201" s="91">
-        <f t="shared" si="33"/>
+      <c r="H201" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I201" s="98">
-        <f t="shared" si="33"/>
+      <c r="I201" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="B202" s="91"/>
-      <c r="C202" s="91"/>
-      <c r="D202" s="91"/>
-      <c r="E202" s="91"/>
-      <c r="F202" s="91"/>
-      <c r="G202" s="91">
-        <f t="shared" si="33"/>
+        <v>190</v>
+      </c>
+      <c r="B202" s="88"/>
+      <c r="C202" s="88"/>
+      <c r="D202" s="88"/>
+      <c r="E202" s="88"/>
+      <c r="F202" s="88"/>
+      <c r="G202" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H202" s="91">
-        <f t="shared" si="33"/>
+      <c r="H202" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I202" s="98">
-        <f t="shared" si="33"/>
+      <c r="I202" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="B203" s="91"/>
-      <c r="C203" s="91"/>
-      <c r="D203" s="91"/>
-      <c r="E203" s="91"/>
-      <c r="F203" s="91"/>
-      <c r="G203" s="91">
-        <f t="shared" si="33"/>
-        <v>32000</v>
-      </c>
-      <c r="H203" s="91">
-        <f t="shared" si="33"/>
-        <v>32000</v>
-      </c>
-      <c r="I203" s="98">
-        <f t="shared" si="33"/>
-        <v>32000</v>
+      <c r="A203" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="B203" s="88"/>
+      <c r="C203" s="88"/>
+      <c r="D203" s="88"/>
+      <c r="E203" s="88"/>
+      <c r="F203" s="88"/>
+      <c r="G203" s="89">
+        <v>35000</v>
+      </c>
+      <c r="H203" s="88">
+        <f>+G203</f>
+        <v>35000</v>
+      </c>
+      <c r="I203" s="94">
+        <f>+G203</f>
+        <v>35000</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="B204" s="91"/>
-      <c r="C204" s="91"/>
-      <c r="D204" s="91"/>
-      <c r="E204" s="91"/>
-      <c r="F204" s="91"/>
-      <c r="G204" s="91">
-        <f t="shared" si="33"/>
+        <v>192</v>
+      </c>
+      <c r="B204" s="88"/>
+      <c r="C204" s="88"/>
+      <c r="D204" s="88"/>
+      <c r="E204" s="88"/>
+      <c r="F204" s="88"/>
+      <c r="G204" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H204" s="91">
-        <f t="shared" si="33"/>
+      <c r="H204" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I204" s="98">
-        <f t="shared" si="33"/>
+      <c r="I204" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="B205" s="91"/>
-      <c r="C205" s="91"/>
-      <c r="D205" s="91"/>
-      <c r="E205" s="91"/>
-      <c r="F205" s="91"/>
-      <c r="G205" s="91">
-        <f t="shared" si="33"/>
+        <v>193</v>
+      </c>
+      <c r="B205" s="88"/>
+      <c r="C205" s="88"/>
+      <c r="D205" s="88"/>
+      <c r="E205" s="88"/>
+      <c r="F205" s="88"/>
+      <c r="G205" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="H205" s="91">
-        <f t="shared" si="33"/>
+      <c r="H205" s="88">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
-      <c r="I205" s="98">
-        <f t="shared" si="33"/>
+      <c r="I205" s="94">
+        <f t="shared" si="31"/>
         <v>32000</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="66" t="s">
-        <v>192</v>
-      </c>
-      <c r="B206" s="91"/>
-      <c r="C206" s="91"/>
-      <c r="D206" s="91"/>
-      <c r="E206" s="91"/>
-      <c r="F206" s="91"/>
-      <c r="G206" s="92">
-        <v>35000</v>
-      </c>
-      <c r="H206" s="91">
-        <f>+G206</f>
-        <v>35000</v>
-      </c>
-      <c r="I206" s="98">
-        <f>+G206</f>
-        <v>35000</v>
+      <c r="A206" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="B206" s="88"/>
+      <c r="C206" s="88"/>
+      <c r="D206" s="88"/>
+      <c r="E206" s="88"/>
+      <c r="F206" s="88"/>
+      <c r="G206" s="88">
+        <f t="shared" ref="G206:I207" si="32">$L$175</f>
+        <v>32000</v>
+      </c>
+      <c r="H206" s="88">
+        <f t="shared" si="32"/>
+        <v>32000</v>
+      </c>
+      <c r="I206" s="94">
+        <f t="shared" si="32"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="B207" s="91"/>
-      <c r="C207" s="91"/>
-      <c r="D207" s="91"/>
-      <c r="E207" s="91"/>
-      <c r="F207" s="91"/>
-      <c r="G207" s="91">
-        <f t="shared" si="33"/>
+      <c r="A207" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B207" s="88"/>
+      <c r="C207" s="88"/>
+      <c r="D207" s="88"/>
+      <c r="E207" s="88"/>
+      <c r="F207" s="88"/>
+      <c r="G207" s="88">
+        <f t="shared" si="32"/>
         <v>32000</v>
       </c>
-      <c r="H207" s="91">
-        <f t="shared" si="33"/>
+      <c r="H207" s="88">
+        <f t="shared" si="32"/>
         <v>32000</v>
       </c>
-      <c r="I207" s="98">
-        <f t="shared" si="33"/>
+      <c r="I207" s="94">
+        <f t="shared" si="32"/>
         <v>32000</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="B208" s="91"/>
-      <c r="C208" s="91"/>
-      <c r="D208" s="91"/>
-      <c r="E208" s="91"/>
-      <c r="F208" s="91"/>
-      <c r="G208" s="91">
-        <f t="shared" si="33"/>
-        <v>32000</v>
-      </c>
-      <c r="H208" s="91">
-        <f t="shared" si="33"/>
-        <v>32000</v>
-      </c>
-      <c r="I208" s="98">
-        <f t="shared" si="33"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A209" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="B209" s="91"/>
-      <c r="C209" s="91"/>
-      <c r="D209" s="91"/>
-      <c r="E209" s="91"/>
-      <c r="F209" s="91"/>
-      <c r="G209" s="91">
-        <f t="shared" ref="G209:I210" si="34">$L$176</f>
-        <v>32000</v>
-      </c>
-      <c r="H209" s="91">
-        <f t="shared" si="34"/>
-        <v>32000</v>
-      </c>
-      <c r="I209" s="98">
-        <f t="shared" si="34"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B210" s="91"/>
-      <c r="C210" s="91"/>
-      <c r="D210" s="91"/>
-      <c r="E210" s="91"/>
-      <c r="F210" s="91"/>
-      <c r="G210" s="91">
-        <f t="shared" si="34"/>
-        <v>32000</v>
-      </c>
-      <c r="H210" s="91">
-        <f t="shared" si="34"/>
-        <v>32000</v>
-      </c>
-      <c r="I210" s="98">
-        <f t="shared" si="34"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A211" s="9" t="s">
+      <c r="A208" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B211" s="91"/>
-      <c r="C211" s="91"/>
-      <c r="D211" s="91"/>
-      <c r="E211" s="91"/>
-      <c r="F211" s="91"/>
-      <c r="G211" s="91">
+      <c r="B208" s="88"/>
+      <c r="C208" s="88"/>
+      <c r="D208" s="88"/>
+      <c r="E208" s="88"/>
+      <c r="F208" s="88"/>
+      <c r="G208" s="88">
         <v>78000</v>
       </c>
-      <c r="H211" s="91">
+      <c r="H208" s="88">
         <f t="shared" si="19"/>
         <v>78000</v>
       </c>
-      <c r="I211" s="98">
+      <c r="I208" s="94">
         <f t="shared" si="19"/>
         <v>78000</v>
       </c>
     </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B209" s="88"/>
+      <c r="C209" s="88"/>
+      <c r="D209" s="88"/>
+      <c r="E209" s="88"/>
+      <c r="F209" s="88"/>
+      <c r="G209" s="88">
+        <v>60000</v>
+      </c>
+      <c r="H209" s="88">
+        <f t="shared" si="19"/>
+        <v>60000</v>
+      </c>
+      <c r="I209" s="94">
+        <f t="shared" si="19"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B210" s="88"/>
+      <c r="C210" s="88"/>
+      <c r="D210" s="88"/>
+      <c r="E210" s="88"/>
+      <c r="F210" s="88"/>
+      <c r="G210" s="89">
+        <v>100000</v>
+      </c>
+      <c r="H210" s="88">
+        <f t="shared" si="19"/>
+        <v>100000</v>
+      </c>
+      <c r="I210" s="94">
+        <f t="shared" si="19"/>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="B211" s="88"/>
+      <c r="C211" s="88"/>
+      <c r="D211" s="88"/>
+      <c r="E211" s="88"/>
+      <c r="F211" s="88"/>
+      <c r="G211" s="89">
+        <v>75000</v>
+      </c>
+      <c r="H211" s="88">
+        <f t="shared" si="19"/>
+        <v>75000</v>
+      </c>
+      <c r="I211" s="94">
+        <f t="shared" si="19"/>
+        <v>75000</v>
+      </c>
+    </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B212" s="91"/>
-      <c r="C212" s="91"/>
-      <c r="D212" s="91"/>
-      <c r="E212" s="91"/>
-      <c r="F212" s="91"/>
-      <c r="G212" s="91">
-        <v>60000</v>
-      </c>
-      <c r="H212" s="91">
-        <f t="shared" si="19"/>
-        <v>60000</v>
-      </c>
-      <c r="I212" s="98">
-        <f t="shared" si="19"/>
-        <v>60000</v>
+        <v>196</v>
+      </c>
+      <c r="B212" s="88"/>
+      <c r="C212" s="88"/>
+      <c r="D212" s="88"/>
+      <c r="E212" s="88"/>
+      <c r="F212" s="88"/>
+      <c r="G212" s="88">
+        <f>+$L$214</f>
+        <v>106880</v>
+      </c>
+      <c r="H212" s="88">
+        <f t="shared" ref="H212:I227" si="33">+$L$214</f>
+        <v>106880</v>
+      </c>
+      <c r="I212" s="94">
+        <f t="shared" si="33"/>
+        <v>106880</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="66" t="s">
-        <v>164</v>
-      </c>
-      <c r="B213" s="91"/>
-      <c r="C213" s="91"/>
-      <c r="D213" s="91"/>
-      <c r="E213" s="91"/>
-      <c r="F213" s="91"/>
-      <c r="G213" s="92">
-        <v>100000</v>
-      </c>
-      <c r="H213" s="91">
-        <f t="shared" si="19"/>
-        <v>100000</v>
-      </c>
-      <c r="I213" s="98">
-        <f t="shared" si="19"/>
-        <v>100000</v>
+      <c r="A213" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B213" s="88"/>
+      <c r="C213" s="88"/>
+      <c r="D213" s="88"/>
+      <c r="E213" s="88"/>
+      <c r="F213" s="88"/>
+      <c r="G213" s="88">
+        <f t="shared" ref="G213:I228" si="34">+$L$214</f>
+        <v>106880</v>
+      </c>
+      <c r="H213" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="I213" s="94">
+        <f t="shared" si="33"/>
+        <v>106880</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A214" s="66" t="s">
-        <v>165</v>
-      </c>
-      <c r="B214" s="91"/>
-      <c r="C214" s="91"/>
-      <c r="D214" s="91"/>
-      <c r="E214" s="91"/>
-      <c r="F214" s="91"/>
-      <c r="G214" s="92">
-        <v>75000</v>
-      </c>
-      <c r="H214" s="91">
-        <f t="shared" si="19"/>
-        <v>75000</v>
-      </c>
-      <c r="I214" s="98">
-        <f t="shared" si="19"/>
-        <v>75000</v>
+      <c r="A214" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B214" s="88"/>
+      <c r="C214" s="88"/>
+      <c r="D214" s="88"/>
+      <c r="E214" s="88"/>
+      <c r="F214" s="88"/>
+      <c r="G214" s="88">
+        <f t="shared" si="34"/>
+        <v>106880</v>
+      </c>
+      <c r="H214" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="I214" s="94">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="K214" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="L214" s="69">
+        <v>106880</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B215" s="91"/>
-      <c r="C215" s="91"/>
-      <c r="D215" s="91"/>
-      <c r="E215" s="91"/>
-      <c r="F215" s="91"/>
-      <c r="G215" s="91">
-        <f>+$L$215</f>
+        <v>199</v>
+      </c>
+      <c r="B215" s="88"/>
+      <c r="C215" s="88"/>
+      <c r="D215" s="88"/>
+      <c r="E215" s="88"/>
+      <c r="F215" s="88"/>
+      <c r="G215" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H215" s="91">
-        <f t="shared" ref="H215:I230" si="35">+$L$215</f>
+      <c r="H215" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I215" s="98">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-      <c r="K215" s="63" t="s">
-        <v>221</v>
-      </c>
-      <c r="L215" s="70">
+      <c r="I215" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B216" s="91"/>
-      <c r="C216" s="91"/>
-      <c r="D216" s="91"/>
-      <c r="E216" s="91"/>
-      <c r="F216" s="91"/>
-      <c r="G216" s="91">
-        <f t="shared" ref="G216:I231" si="36">+$L$215</f>
+        <v>200</v>
+      </c>
+      <c r="B216" s="88"/>
+      <c r="C216" s="88"/>
+      <c r="D216" s="88"/>
+      <c r="E216" s="88"/>
+      <c r="F216" s="88"/>
+      <c r="G216" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H216" s="91">
-        <f t="shared" si="35"/>
+      <c r="H216" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I216" s="98">
-        <f t="shared" si="35"/>
+      <c r="I216" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B217" s="91"/>
-      <c r="C217" s="91"/>
-      <c r="D217" s="91"/>
-      <c r="E217" s="91"/>
-      <c r="F217" s="91"/>
-      <c r="G217" s="91">
-        <f t="shared" si="36"/>
+        <v>212</v>
+      </c>
+      <c r="B217" s="88"/>
+      <c r="C217" s="88"/>
+      <c r="D217" s="88"/>
+      <c r="E217" s="88"/>
+      <c r="F217" s="88"/>
+      <c r="G217" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H217" s="91">
-        <f t="shared" si="35"/>
+      <c r="H217" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I217" s="98">
-        <f t="shared" si="35"/>
+      <c r="I217" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B218" s="91"/>
-      <c r="C218" s="91"/>
-      <c r="D218" s="91"/>
-      <c r="E218" s="91"/>
-      <c r="F218" s="91"/>
-      <c r="G218" s="91">
-        <f t="shared" si="36"/>
+        <v>201</v>
+      </c>
+      <c r="B218" s="88"/>
+      <c r="C218" s="88"/>
+      <c r="D218" s="88"/>
+      <c r="E218" s="88"/>
+      <c r="F218" s="88"/>
+      <c r="G218" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H218" s="91">
-        <f t="shared" si="35"/>
+      <c r="H218" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I218" s="98">
-        <f t="shared" si="35"/>
+      <c r="I218" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B219" s="91"/>
-      <c r="C219" s="91"/>
-      <c r="D219" s="91"/>
-      <c r="E219" s="91"/>
-      <c r="F219" s="91"/>
-      <c r="G219" s="91">
-        <f t="shared" si="36"/>
+        <v>202</v>
+      </c>
+      <c r="B219" s="88"/>
+      <c r="C219" s="88"/>
+      <c r="D219" s="88"/>
+      <c r="E219" s="88"/>
+      <c r="F219" s="88"/>
+      <c r="G219" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H219" s="91">
-        <f t="shared" si="35"/>
+      <c r="H219" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I219" s="98">
-        <f t="shared" si="35"/>
+      <c r="I219" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="B220" s="91"/>
-      <c r="C220" s="91"/>
-      <c r="D220" s="91"/>
-      <c r="E220" s="91"/>
-      <c r="F220" s="91"/>
-      <c r="G220" s="91">
-        <f t="shared" si="36"/>
+        <v>203</v>
+      </c>
+      <c r="B220" s="88"/>
+      <c r="C220" s="88"/>
+      <c r="D220" s="88"/>
+      <c r="E220" s="88"/>
+      <c r="F220" s="88"/>
+      <c r="G220" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H220" s="91">
-        <f t="shared" si="35"/>
+      <c r="H220" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I220" s="98">
-        <f t="shared" si="35"/>
+      <c r="I220" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B221" s="91"/>
-      <c r="C221" s="91"/>
-      <c r="D221" s="91"/>
-      <c r="E221" s="91"/>
-      <c r="F221" s="91"/>
-      <c r="G221" s="91">
-        <f t="shared" si="36"/>
+        <v>204</v>
+      </c>
+      <c r="B221" s="88"/>
+      <c r="C221" s="88"/>
+      <c r="D221" s="88"/>
+      <c r="E221" s="88"/>
+      <c r="F221" s="88"/>
+      <c r="G221" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H221" s="91">
-        <f t="shared" si="35"/>
+      <c r="H221" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I221" s="98">
-        <f t="shared" si="35"/>
+      <c r="I221" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B222" s="91"/>
-      <c r="C222" s="91"/>
-      <c r="D222" s="91"/>
-      <c r="E222" s="91"/>
-      <c r="F222" s="91"/>
-      <c r="G222" s="91">
-        <f t="shared" si="36"/>
+        <v>205</v>
+      </c>
+      <c r="B222" s="88"/>
+      <c r="C222" s="88"/>
+      <c r="D222" s="88"/>
+      <c r="E222" s="88"/>
+      <c r="F222" s="88"/>
+      <c r="G222" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H222" s="91">
-        <f t="shared" si="35"/>
+      <c r="H222" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I222" s="98">
-        <f t="shared" si="35"/>
+      <c r="I222" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B223" s="91"/>
-      <c r="C223" s="91"/>
-      <c r="D223" s="91"/>
-      <c r="E223" s="91"/>
-      <c r="F223" s="91"/>
-      <c r="G223" s="91">
-        <f t="shared" si="36"/>
+        <v>206</v>
+      </c>
+      <c r="B223" s="88"/>
+      <c r="C223" s="88"/>
+      <c r="D223" s="88"/>
+      <c r="E223" s="88"/>
+      <c r="F223" s="88"/>
+      <c r="G223" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H223" s="91">
-        <f t="shared" si="35"/>
+      <c r="H223" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I223" s="98">
-        <f t="shared" si="35"/>
+      <c r="I223" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B224" s="91"/>
-      <c r="C224" s="91"/>
-      <c r="D224" s="91"/>
-      <c r="E224" s="91"/>
-      <c r="F224" s="91"/>
-      <c r="G224" s="91">
-        <f t="shared" si="36"/>
+        <v>207</v>
+      </c>
+      <c r="B224" s="88"/>
+      <c r="C224" s="88"/>
+      <c r="D224" s="88"/>
+      <c r="E224" s="88"/>
+      <c r="F224" s="88"/>
+      <c r="G224" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H224" s="91">
-        <f t="shared" si="35"/>
+      <c r="H224" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I224" s="98">
-        <f t="shared" si="35"/>
+      <c r="I224" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B225" s="91"/>
-      <c r="C225" s="91"/>
-      <c r="D225" s="91"/>
-      <c r="E225" s="91"/>
-      <c r="F225" s="91"/>
-      <c r="G225" s="91">
-        <f t="shared" si="36"/>
+        <v>208</v>
+      </c>
+      <c r="B225" s="88"/>
+      <c r="C225" s="88"/>
+      <c r="D225" s="88"/>
+      <c r="E225" s="88"/>
+      <c r="F225" s="88"/>
+      <c r="G225" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H225" s="91">
-        <f t="shared" si="35"/>
+      <c r="H225" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I225" s="98">
-        <f t="shared" si="35"/>
+      <c r="I225" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B226" s="91"/>
-      <c r="C226" s="91"/>
-      <c r="D226" s="91"/>
-      <c r="E226" s="91"/>
-      <c r="F226" s="91"/>
-      <c r="G226" s="91">
-        <f t="shared" si="36"/>
+        <v>209</v>
+      </c>
+      <c r="B226" s="88"/>
+      <c r="C226" s="88"/>
+      <c r="D226" s="88"/>
+      <c r="E226" s="88"/>
+      <c r="F226" s="88"/>
+      <c r="G226" s="88">
+        <f t="shared" si="34"/>
         <v>106880</v>
       </c>
-      <c r="H226" s="91">
-        <f t="shared" si="35"/>
+      <c r="H226" s="88">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I226" s="98">
-        <f t="shared" si="35"/>
+      <c r="I226" s="94">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B227" s="88"/>
+      <c r="C227" s="88"/>
+      <c r="D227" s="88"/>
+      <c r="E227" s="88"/>
+      <c r="F227" s="88"/>
+      <c r="G227" s="88">
+        <f t="shared" si="34"/>
+        <v>106880</v>
+      </c>
+      <c r="H227" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="I227" s="94">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="107" t="s">
+        <v>211</v>
+      </c>
+      <c r="B228" s="108"/>
+      <c r="C228" s="108"/>
+      <c r="D228" s="108"/>
+      <c r="E228" s="108"/>
+      <c r="F228" s="108"/>
+      <c r="G228" s="108">
+        <f t="shared" si="34"/>
+        <v>106880</v>
+      </c>
+      <c r="H228" s="108">
+        <f t="shared" si="34"/>
+        <v>106880</v>
+      </c>
+      <c r="I228" s="109">
+        <f t="shared" si="34"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="B229" s="124"/>
+      <c r="C229" s="125"/>
+      <c r="D229" s="125"/>
+      <c r="E229" s="98"/>
+      <c r="F229" s="98"/>
+      <c r="G229" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H229" s="99" t="s">
+        <v>100</v>
+      </c>
+      <c r="I229" s="99" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B230" s="111"/>
+      <c r="C230" s="111"/>
+      <c r="D230" s="111"/>
+      <c r="E230" s="111"/>
+      <c r="F230" s="111"/>
+      <c r="G230" s="110">
+        <v>40000</v>
+      </c>
+      <c r="H230" s="111">
+        <f>+G230</f>
+        <v>40000</v>
+      </c>
+      <c r="I230" s="112">
+        <f>+G230</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="B227" s="91"/>
-      <c r="C227" s="91"/>
-      <c r="D227" s="91"/>
-      <c r="E227" s="91"/>
-      <c r="F227" s="91"/>
-      <c r="G227" s="91">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-      <c r="H227" s="91">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-      <c r="I227" s="98">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B228" s="91"/>
-      <c r="C228" s="91"/>
-      <c r="D228" s="91"/>
-      <c r="E228" s="91"/>
-      <c r="F228" s="91"/>
-      <c r="G228" s="91">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-      <c r="H228" s="91">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-      <c r="I228" s="98">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B229" s="91"/>
-      <c r="C229" s="91"/>
-      <c r="D229" s="91"/>
-      <c r="E229" s="91"/>
-      <c r="F229" s="91"/>
-      <c r="G229" s="91">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-      <c r="H229" s="91">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-      <c r="I229" s="98">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A230" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B230" s="91"/>
-      <c r="C230" s="91"/>
-      <c r="D230" s="91"/>
-      <c r="E230" s="91"/>
-      <c r="F230" s="91"/>
-      <c r="G230" s="91">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-      <c r="H230" s="91">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-      <c r="I230" s="98">
-        <f t="shared" si="35"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="111" t="s">
-        <v>219</v>
-      </c>
-      <c r="B231" s="112"/>
-      <c r="C231" s="112"/>
-      <c r="D231" s="112"/>
-      <c r="E231" s="112"/>
-      <c r="F231" s="112"/>
-      <c r="G231" s="112">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-      <c r="H231" s="112">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-      <c r="I231" s="113">
-        <f t="shared" si="36"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="93" t="s">
-        <v>6</v>
-      </c>
-      <c r="B232" s="128"/>
-      <c r="C232" s="129"/>
-      <c r="D232" s="129"/>
-      <c r="E232" s="102"/>
-      <c r="F232" s="102"/>
-      <c r="G232" s="102" t="s">
+      <c r="B231" s="124"/>
+      <c r="C231" s="98"/>
+      <c r="D231" s="98"/>
+      <c r="E231" s="98"/>
+      <c r="F231" s="98" t="s">
+        <v>98</v>
+      </c>
+      <c r="G231" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="H232" s="103" t="s">
+      <c r="H231" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="I232" s="103" t="s">
+      <c r="I231" s="99" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B233" s="115"/>
-      <c r="C233" s="115"/>
-      <c r="D233" s="115"/>
-      <c r="E233" s="115"/>
-      <c r="F233" s="115"/>
-      <c r="G233" s="114">
-        <v>40000</v>
-      </c>
-      <c r="H233" s="115">
+    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A232" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B232" s="87"/>
+      <c r="C232" s="87"/>
+      <c r="D232" s="87"/>
+      <c r="E232" s="87"/>
+      <c r="F232" s="105">
+        <v>15000</v>
+      </c>
+      <c r="G232" s="105">
+        <v>15000</v>
+      </c>
+      <c r="H232" s="87">
+        <f>+$G$232</f>
+        <v>15000</v>
+      </c>
+      <c r="I232" s="106">
+        <f>+$G$232</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A233" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B233" s="85"/>
+      <c r="C233" s="85"/>
+      <c r="D233" s="85"/>
+      <c r="E233" s="85"/>
+      <c r="F233" s="86">
+        <v>18000</v>
+      </c>
+      <c r="G233" s="86">
+        <v>15000</v>
+      </c>
+      <c r="H233" s="85">
         <f>+G233</f>
-        <v>40000</v>
-      </c>
-      <c r="I233" s="116">
+        <v>15000</v>
+      </c>
+      <c r="I233" s="101">
         <f>+G233</f>
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="93" t="s">
-        <v>223</v>
-      </c>
-      <c r="B234" s="128"/>
-      <c r="C234" s="102"/>
-      <c r="D234" s="102"/>
-      <c r="E234" s="102"/>
-      <c r="F234" s="102" t="s">
-        <v>98</v>
-      </c>
-      <c r="G234" s="102" t="s">
-        <v>99</v>
-      </c>
-      <c r="H234" s="102" t="s">
-        <v>100</v>
-      </c>
-      <c r="I234" s="103" t="s">
-        <v>130</v>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A234" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B234" s="85"/>
+      <c r="C234" s="85"/>
+      <c r="D234" s="85"/>
+      <c r="E234" s="85"/>
+      <c r="F234" s="86">
+        <v>18000</v>
+      </c>
+      <c r="G234" s="86">
+        <v>15000</v>
+      </c>
+      <c r="H234" s="85">
+        <f>+G234</f>
+        <v>15000</v>
+      </c>
+      <c r="I234" s="101">
+        <f>+G234</f>
+        <v>15000</v>
       </c>
     </row>
     <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B235" s="89"/>
-      <c r="C235" s="89"/>
-      <c r="D235" s="89"/>
-      <c r="E235" s="89"/>
-      <c r="F235" s="109">
-        <v>15000</v>
-      </c>
-      <c r="G235" s="109">
-        <v>15000</v>
-      </c>
-      <c r="H235" s="89">
-        <f>+$G$235</f>
-        <v>15000</v>
-      </c>
-      <c r="I235" s="110">
-        <f>+$G$235</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B236" s="87"/>
-      <c r="C236" s="87"/>
-      <c r="D236" s="87"/>
-      <c r="E236" s="87"/>
-      <c r="F236" s="88">
-        <v>18000</v>
-      </c>
-      <c r="G236" s="88">
-        <v>15000</v>
-      </c>
-      <c r="H236" s="87">
+        <v>214</v>
+      </c>
+      <c r="B235" s="85"/>
+      <c r="C235" s="85"/>
+      <c r="D235" s="85"/>
+      <c r="E235" s="85"/>
+      <c r="F235" s="85"/>
+      <c r="G235" s="86">
+        <v>20000</v>
+      </c>
+      <c r="H235" s="85">
+        <f>+G235</f>
+        <v>20000</v>
+      </c>
+      <c r="I235" s="101">
+        <f>+G235</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B236" s="103"/>
+      <c r="C236" s="103"/>
+      <c r="D236" s="103"/>
+      <c r="E236" s="103"/>
+      <c r="F236" s="103"/>
+      <c r="G236" s="102">
+        <v>20000</v>
+      </c>
+      <c r="H236" s="103">
         <f>+G236</f>
-        <v>15000</v>
-      </c>
-      <c r="I236" s="105">
+        <v>20000</v>
+      </c>
+      <c r="I236" s="104">
         <f>+G236</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A237" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B237" s="87"/>
-      <c r="C237" s="87"/>
-      <c r="D237" s="87"/>
-      <c r="E237" s="87"/>
-      <c r="F237" s="88">
-        <v>18000</v>
-      </c>
-      <c r="G237" s="88">
-        <v>15000</v>
-      </c>
-      <c r="H237" s="87">
-        <f>+G237</f>
-        <v>15000</v>
-      </c>
-      <c r="I237" s="105">
-        <f>+G237</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A238" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="B238" s="87"/>
-      <c r="C238" s="87"/>
-      <c r="D238" s="87"/>
-      <c r="E238" s="87"/>
-      <c r="F238" s="87"/>
-      <c r="G238" s="88">
-        <v>20000</v>
-      </c>
-      <c r="H238" s="87">
-        <f>+G238</f>
-        <v>20000</v>
-      </c>
-      <c r="I238" s="105">
-        <f>+G238</f>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B239" s="107"/>
-      <c r="C239" s="107"/>
-      <c r="D239" s="107"/>
-      <c r="E239" s="107"/>
-      <c r="F239" s="107"/>
-      <c r="G239" s="106">
-        <v>20000</v>
-      </c>
-      <c r="H239" s="107">
-        <f>+G239</f>
-        <v>20000</v>
-      </c>
-      <c r="I239" s="108">
-        <f>+G239</f>
         <v>20000</v>
       </c>
     </row>
@@ -10874,9 +10792,6 @@
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="G174" formula="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2505,7 +2505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B149" authorId="0" shapeId="0">
+    <comment ref="B166" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2529,7 +2529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B150" authorId="0" shapeId="0">
+    <comment ref="B167" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2553,31 +2553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B151" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Administracion:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Valor particular</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A231" authorId="0" shapeId="0">
+    <comment ref="A248" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2582,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="231">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3317,6 +3293,21 @@
   </si>
   <si>
     <t>ECOGRAFIA TESTICULAR (POR C/CODIGO)</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA AMBAS CADERAS</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA MAMARIA Y TRANSVAGINAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA RENOVESICAL</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA GINECOLOGICA con o sin trasductor vaginal</t>
+  </si>
+  <si>
+    <t>ECOGRAFIA VEJIGA O PROSTATA  (VESICOPROSTATICA)</t>
   </si>
 </sst>
 </file>
@@ -3454,7 +3445,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3548,6 +3539,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4070,7 +4067,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4393,6 +4390,18 @@
     <xf numFmtId="165" fontId="9" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4682,7 +4691,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L236"/>
+  <dimension ref="A1:L253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
@@ -4696,13 +4705,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
@@ -8330,26 +8339,13 @@
       <c r="A131" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B131" s="68">
-        <f>+G131/0.6</f>
-        <v>157351.66666666669</v>
-      </c>
-      <c r="C131" s="68">
-        <v>94411</v>
-      </c>
-      <c r="D131" s="68">
-        <v>94411</v>
-      </c>
-      <c r="E131" s="68">
-        <v>94411</v>
-      </c>
-      <c r="F131" s="68">
-        <f>+B131*0.7</f>
-        <v>110146.16666666667</v>
-      </c>
+      <c r="B131" s="68"/>
+      <c r="C131" s="68"/>
+      <c r="D131" s="68"/>
+      <c r="E131" s="68"/>
+      <c r="F131" s="68"/>
       <c r="G131" s="73">
-        <f>+E131</f>
-        <v>94411</v>
+        <v>99890</v>
       </c>
       <c r="H131" s="68"/>
       <c r="I131" s="68"/>
@@ -8358,110 +8354,77 @@
       <c r="A132" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B132" s="68">
-        <f t="shared" ref="B132:B150" si="12">+G132/0.6</f>
-        <v>78706.666666666672</v>
-      </c>
-      <c r="C132" s="68">
-        <v>47224</v>
-      </c>
-      <c r="D132" s="68">
-        <v>47224</v>
-      </c>
-      <c r="E132" s="68">
-        <v>47224</v>
-      </c>
-      <c r="F132" s="68">
-        <f t="shared" ref="F132:F151" si="13">+B132*0.7</f>
-        <v>55094.666666666664</v>
-      </c>
+      <c r="B132" s="68"/>
+      <c r="C132" s="68"/>
+      <c r="D132" s="68"/>
+      <c r="E132" s="68"/>
+      <c r="F132" s="68"/>
       <c r="G132" s="73">
-        <f t="shared" ref="G132:G150" si="14">+E132</f>
-        <v>47224</v>
-      </c>
-      <c r="H132" s="68"/>
-      <c r="I132" s="68"/>
+        <v>49945</v>
+      </c>
+      <c r="H132" s="68">
+        <f>+$G$132</f>
+        <v>49945</v>
+      </c>
+      <c r="I132" s="68">
+        <f>+$G$132</f>
+        <v>49945</v>
+      </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B133" s="68">
-        <f t="shared" si="12"/>
-        <v>150468.33333333334</v>
-      </c>
-      <c r="C133" s="68">
-        <v>90281</v>
-      </c>
-      <c r="D133" s="68">
-        <v>90281</v>
-      </c>
-      <c r="E133" s="68">
-        <v>90281</v>
-      </c>
-      <c r="F133" s="68">
-        <f t="shared" si="13"/>
-        <v>105327.83333333333</v>
-      </c>
+      <c r="B133" s="68"/>
+      <c r="C133" s="68"/>
+      <c r="D133" s="68"/>
+      <c r="E133" s="68"/>
+      <c r="F133" s="68"/>
       <c r="G133" s="73">
-        <f t="shared" si="14"/>
-        <v>90281</v>
-      </c>
-      <c r="H133" s="68"/>
-      <c r="I133" s="68"/>
+        <v>95529</v>
+      </c>
+      <c r="H133" s="68">
+        <f>+$G$133</f>
+        <v>95529</v>
+      </c>
+      <c r="I133" s="68">
+        <f>+$G$133</f>
+        <v>95529</v>
+      </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B134" s="68">
-        <f t="shared" si="12"/>
-        <v>141788.33333333334</v>
-      </c>
-      <c r="C134" s="68">
-        <v>85073</v>
-      </c>
-      <c r="D134" s="68">
-        <v>85073</v>
-      </c>
-      <c r="E134" s="68">
-        <v>85073</v>
-      </c>
-      <c r="F134" s="68">
-        <f t="shared" si="13"/>
-        <v>99251.833333333328</v>
-      </c>
+      <c r="B134" s="68"/>
+      <c r="C134" s="68"/>
+      <c r="D134" s="68"/>
+      <c r="E134" s="68"/>
+      <c r="F134" s="68"/>
       <c r="G134" s="73">
-        <f t="shared" si="14"/>
-        <v>85073</v>
-      </c>
-      <c r="H134" s="68"/>
-      <c r="I134" s="68"/>
+        <v>90026</v>
+      </c>
+      <c r="H134" s="68">
+        <f>+$G$134</f>
+        <v>90026</v>
+      </c>
+      <c r="I134" s="68">
+        <f>+$G$134</f>
+        <v>90026</v>
+      </c>
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="68">
-        <f t="shared" si="12"/>
-        <v>27971.666666666668</v>
-      </c>
-      <c r="C135" s="68">
-        <v>16783</v>
-      </c>
-      <c r="D135" s="68">
-        <v>16783</v>
-      </c>
-      <c r="E135" s="68">
-        <v>16783</v>
-      </c>
-      <c r="F135" s="68">
-        <f t="shared" si="13"/>
-        <v>19580.166666666668</v>
-      </c>
+      <c r="B135" s="68"/>
+      <c r="C135" s="68"/>
+      <c r="D135" s="68"/>
+      <c r="E135" s="68"/>
+      <c r="F135" s="68"/>
       <c r="G135" s="73">
-        <f t="shared" si="14"/>
-        <v>16783</v>
+        <f t="shared" ref="G135:G148" si="12">+E135</f>
+        <v>0</v>
       </c>
       <c r="H135" s="68"/>
       <c r="I135" s="68"/>
@@ -8470,26 +8433,14 @@
       <c r="A136" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B136" s="68">
+      <c r="B136" s="68"/>
+      <c r="C136" s="68"/>
+      <c r="D136" s="68"/>
+      <c r="E136" s="68"/>
+      <c r="F136" s="68"/>
+      <c r="G136" s="73">
         <f t="shared" si="12"/>
-        <v>27971.666666666668</v>
-      </c>
-      <c r="C136" s="68">
-        <v>16783</v>
-      </c>
-      <c r="D136" s="68">
-        <v>16783</v>
-      </c>
-      <c r="E136" s="68">
-        <v>16783</v>
-      </c>
-      <c r="F136" s="68">
-        <f t="shared" si="13"/>
-        <v>19580.166666666668</v>
-      </c>
-      <c r="G136" s="73">
-        <f t="shared" si="14"/>
-        <v>16783</v>
+        <v>0</v>
       </c>
       <c r="H136" s="68"/>
       <c r="I136" s="68"/>
@@ -8498,26 +8449,14 @@
       <c r="A137" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B137" s="68">
+      <c r="B137" s="68"/>
+      <c r="C137" s="68"/>
+      <c r="D137" s="68"/>
+      <c r="E137" s="68"/>
+      <c r="F137" s="68"/>
+      <c r="G137" s="73">
         <f t="shared" si="12"/>
-        <v>27971.666666666668</v>
-      </c>
-      <c r="C137" s="68">
-        <v>16783</v>
-      </c>
-      <c r="D137" s="68">
-        <v>16783</v>
-      </c>
-      <c r="E137" s="68">
-        <v>16783</v>
-      </c>
-      <c r="F137" s="68">
-        <f t="shared" si="13"/>
-        <v>19580.166666666668</v>
-      </c>
-      <c r="G137" s="73">
-        <f t="shared" si="14"/>
-        <v>16783</v>
+        <v>0</v>
       </c>
       <c r="H137" s="68"/>
       <c r="I137" s="68"/>
@@ -8526,26 +8465,14 @@
       <c r="A138" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B138" s="68">
+      <c r="B138" s="68"/>
+      <c r="C138" s="68"/>
+      <c r="D138" s="68"/>
+      <c r="E138" s="68"/>
+      <c r="F138" s="68"/>
+      <c r="G138" s="73">
         <f t="shared" si="12"/>
-        <v>27198.333333333336</v>
-      </c>
-      <c r="C138" s="68">
-        <v>16319</v>
-      </c>
-      <c r="D138" s="68">
-        <v>16319</v>
-      </c>
-      <c r="E138" s="68">
-        <v>16319</v>
-      </c>
-      <c r="F138" s="68">
-        <f t="shared" si="13"/>
-        <v>19038.833333333332</v>
-      </c>
-      <c r="G138" s="73">
-        <f t="shared" si="14"/>
-        <v>16319</v>
+        <v>0</v>
       </c>
       <c r="H138" s="68"/>
       <c r="I138" s="68"/>
@@ -8554,26 +8481,14 @@
       <c r="A139" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B139" s="68">
+      <c r="B139" s="68"/>
+      <c r="C139" s="68"/>
+      <c r="D139" s="68"/>
+      <c r="E139" s="68"/>
+      <c r="F139" s="68"/>
+      <c r="G139" s="73">
         <f t="shared" si="12"/>
-        <v>20146.666666666668</v>
-      </c>
-      <c r="C139" s="68">
-        <v>12088</v>
-      </c>
-      <c r="D139" s="68">
-        <v>12088</v>
-      </c>
-      <c r="E139" s="68">
-        <v>12088</v>
-      </c>
-      <c r="F139" s="68">
-        <f t="shared" si="13"/>
-        <v>14102.666666666666</v>
-      </c>
-      <c r="G139" s="73">
-        <f t="shared" si="14"/>
-        <v>12088</v>
+        <v>0</v>
       </c>
       <c r="H139" s="68"/>
       <c r="I139" s="68"/>
@@ -8582,26 +8497,14 @@
       <c r="A140" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B140" s="68">
+      <c r="B140" s="68"/>
+      <c r="C140" s="68"/>
+      <c r="D140" s="68"/>
+      <c r="E140" s="68"/>
+      <c r="F140" s="68"/>
+      <c r="G140" s="73">
         <f t="shared" si="12"/>
-        <v>22550</v>
-      </c>
-      <c r="C140" s="68">
-        <v>13530</v>
-      </c>
-      <c r="D140" s="68">
-        <v>13530</v>
-      </c>
-      <c r="E140" s="68">
-        <v>13530</v>
-      </c>
-      <c r="F140" s="68">
-        <f t="shared" si="13"/>
-        <v>15784.999999999998</v>
-      </c>
-      <c r="G140" s="73">
-        <f t="shared" si="14"/>
-        <v>13530</v>
+        <v>0</v>
       </c>
       <c r="H140" s="68"/>
       <c r="I140" s="68"/>
@@ -8610,26 +8513,14 @@
       <c r="A141" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B141" s="68">
+      <c r="B141" s="68"/>
+      <c r="C141" s="68"/>
+      <c r="D141" s="68"/>
+      <c r="E141" s="68"/>
+      <c r="F141" s="68"/>
+      <c r="G141" s="73">
         <f t="shared" si="12"/>
-        <v>22550</v>
-      </c>
-      <c r="C141" s="68">
-        <v>13530</v>
-      </c>
-      <c r="D141" s="68">
-        <v>13530</v>
-      </c>
-      <c r="E141" s="68">
-        <v>13530</v>
-      </c>
-      <c r="F141" s="68">
-        <f t="shared" si="13"/>
-        <v>15784.999999999998</v>
-      </c>
-      <c r="G141" s="73">
-        <f t="shared" si="14"/>
-        <v>13530</v>
+        <v>0</v>
       </c>
       <c r="H141" s="68"/>
       <c r="I141" s="68"/>
@@ -8638,26 +8529,14 @@
       <c r="A142" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B142" s="68">
+      <c r="B142" s="68"/>
+      <c r="C142" s="68"/>
+      <c r="D142" s="68"/>
+      <c r="E142" s="68"/>
+      <c r="F142" s="68"/>
+      <c r="G142" s="73">
         <f t="shared" si="12"/>
-        <v>33800</v>
-      </c>
-      <c r="C142" s="68">
-        <v>20280</v>
-      </c>
-      <c r="D142" s="68">
-        <v>20280</v>
-      </c>
-      <c r="E142" s="68">
-        <v>20280</v>
-      </c>
-      <c r="F142" s="68">
-        <f t="shared" si="13"/>
-        <v>23660</v>
-      </c>
-      <c r="G142" s="73">
-        <f t="shared" si="14"/>
-        <v>20280</v>
+        <v>0</v>
       </c>
       <c r="H142" s="68"/>
       <c r="I142" s="68"/>
@@ -8666,26 +8545,14 @@
       <c r="A143" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B143" s="68">
+      <c r="B143" s="68"/>
+      <c r="C143" s="68"/>
+      <c r="D143" s="68"/>
+      <c r="E143" s="68"/>
+      <c r="F143" s="68"/>
+      <c r="G143" s="73">
         <f t="shared" si="12"/>
-        <v>28428.333333333336</v>
-      </c>
-      <c r="C143" s="68">
-        <v>17057</v>
-      </c>
-      <c r="D143" s="68">
-        <v>17057</v>
-      </c>
-      <c r="E143" s="68">
-        <v>17057</v>
-      </c>
-      <c r="F143" s="68">
-        <f t="shared" si="13"/>
-        <v>19899.833333333332</v>
-      </c>
-      <c r="G143" s="73">
-        <f t="shared" si="14"/>
-        <v>17057</v>
+        <v>0</v>
       </c>
       <c r="H143" s="68"/>
       <c r="I143" s="68"/>
@@ -8694,1048 +8561,879 @@
       <c r="A144" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B144" s="68">
+      <c r="B144" s="68"/>
+      <c r="C144" s="68"/>
+      <c r="D144" s="68"/>
+      <c r="E144" s="68"/>
+      <c r="F144" s="68"/>
+      <c r="G144" s="73">
         <f t="shared" si="12"/>
-        <v>26893.333333333336</v>
-      </c>
-      <c r="C144" s="68">
-        <v>16136</v>
-      </c>
-      <c r="D144" s="68">
-        <v>16136</v>
-      </c>
-      <c r="E144" s="68">
-        <v>16136</v>
-      </c>
-      <c r="F144" s="68">
-        <f t="shared" si="13"/>
-        <v>18825.333333333332</v>
-      </c>
-      <c r="G144" s="73">
-        <f t="shared" si="14"/>
-        <v>16136</v>
+        <v>0</v>
       </c>
       <c r="H144" s="68"/>
       <c r="I144" s="68"/>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B145" s="68">
+      <c r="B145" s="68"/>
+      <c r="C145" s="68"/>
+      <c r="D145" s="68"/>
+      <c r="E145" s="68"/>
+      <c r="F145" s="68"/>
+      <c r="G145" s="73">
         <f t="shared" si="12"/>
-        <v>26893.333333333336</v>
-      </c>
-      <c r="C145" s="68">
-        <v>16136</v>
-      </c>
-      <c r="D145" s="68">
-        <v>16136</v>
-      </c>
-      <c r="E145" s="68">
-        <v>16136</v>
-      </c>
-      <c r="F145" s="68">
-        <f t="shared" si="13"/>
-        <v>18825.333333333332</v>
-      </c>
-      <c r="G145" s="73">
-        <f t="shared" si="14"/>
-        <v>16136</v>
+        <v>0</v>
       </c>
       <c r="H145" s="68"/>
       <c r="I145" s="68"/>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B146" s="68">
+      <c r="B146" s="68"/>
+      <c r="C146" s="68"/>
+      <c r="D146" s="68"/>
+      <c r="E146" s="68"/>
+      <c r="F146" s="68"/>
+      <c r="G146" s="73">
         <f t="shared" si="12"/>
-        <v>27198.333333333336</v>
-      </c>
-      <c r="C146" s="68">
-        <v>16319</v>
-      </c>
-      <c r="D146" s="68">
-        <v>16319</v>
-      </c>
-      <c r="E146" s="68">
-        <v>16319</v>
-      </c>
-      <c r="F146" s="68">
-        <f t="shared" si="13"/>
-        <v>19038.833333333332</v>
-      </c>
-      <c r="G146" s="73">
-        <f t="shared" si="14"/>
-        <v>16319</v>
+        <v>0</v>
       </c>
       <c r="H146" s="68"/>
       <c r="I146" s="68"/>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B147" s="68">
+      <c r="B147" s="68"/>
+      <c r="C147" s="68"/>
+      <c r="D147" s="68"/>
+      <c r="E147" s="68"/>
+      <c r="F147" s="68"/>
+      <c r="G147" s="73">
         <f t="shared" si="12"/>
-        <v>32386.666666666668</v>
-      </c>
-      <c r="C147" s="68">
-        <v>19432</v>
-      </c>
-      <c r="D147" s="68">
-        <v>19432</v>
-      </c>
-      <c r="E147" s="68">
-        <v>19432</v>
-      </c>
-      <c r="F147" s="68">
-        <f t="shared" si="13"/>
-        <v>22670.666666666668</v>
-      </c>
-      <c r="G147" s="73">
-        <f t="shared" si="14"/>
-        <v>19432</v>
+        <v>0</v>
       </c>
       <c r="H147" s="68"/>
       <c r="I147" s="68"/>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B148" s="68">
+      <c r="B148" s="68"/>
+      <c r="C148" s="68"/>
+      <c r="D148" s="68"/>
+      <c r="E148" s="68"/>
+      <c r="F148" s="68"/>
+      <c r="G148" s="73">
         <f t="shared" si="12"/>
-        <v>23586.666666666668</v>
-      </c>
-      <c r="C148" s="68">
-        <v>14152</v>
-      </c>
-      <c r="D148" s="68">
-        <v>14152</v>
-      </c>
-      <c r="E148" s="68">
-        <v>14152</v>
-      </c>
-      <c r="F148" s="68">
-        <f t="shared" si="13"/>
-        <v>16510.666666666668</v>
-      </c>
-      <c r="G148" s="73">
-        <f t="shared" si="14"/>
-        <v>14152</v>
+        <v>0</v>
       </c>
       <c r="H148" s="68"/>
       <c r="I148" s="68"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="11" t="s">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="B149" s="113"/>
+      <c r="C149" s="113"/>
+      <c r="D149" s="113"/>
+      <c r="E149" s="113"/>
+      <c r="F149" s="113"/>
+      <c r="G149" s="100">
+        <v>17756</v>
+      </c>
+      <c r="H149" s="135">
+        <f t="shared" ref="G149:I152" si="13">+$G$149</f>
+        <v>17756</v>
+      </c>
+      <c r="I149" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="B150" s="113"/>
+      <c r="C150" s="113"/>
+      <c r="D150" s="113"/>
+      <c r="E150" s="113"/>
+      <c r="F150" s="113"/>
+      <c r="G150" s="135">
+        <f>+$G$149</f>
+        <v>17756</v>
+      </c>
+      <c r="H150" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+      <c r="I150" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B151" s="123"/>
+      <c r="C151" s="123"/>
+      <c r="D151" s="123"/>
+      <c r="E151" s="123"/>
+      <c r="F151" s="123"/>
+      <c r="G151" s="135">
+        <f>+$G$149</f>
+        <v>17756</v>
+      </c>
+      <c r="H151" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+      <c r="I151" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="B152" s="113"/>
+      <c r="C152" s="113"/>
+      <c r="D152" s="113"/>
+      <c r="E152" s="113"/>
+      <c r="F152" s="113"/>
+      <c r="G152" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+      <c r="H152" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+      <c r="I152" s="135">
+        <f t="shared" si="13"/>
+        <v>17756</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B153" s="113"/>
+      <c r="C153" s="113"/>
+      <c r="D153" s="113"/>
+      <c r="E153" s="113"/>
+      <c r="F153" s="113"/>
+      <c r="G153" s="137">
+        <v>35512</v>
+      </c>
+      <c r="H153" s="135">
+        <f>+$G$153</f>
+        <v>35512</v>
+      </c>
+      <c r="I153" s="135">
+        <f>+$G$153</f>
+        <v>35512</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="B154" s="113"/>
+      <c r="C154" s="113"/>
+      <c r="D154" s="113"/>
+      <c r="E154" s="113"/>
+      <c r="F154" s="113"/>
+      <c r="G154" s="100">
+        <v>12772</v>
+      </c>
+      <c r="H154" s="113"/>
+      <c r="I154" s="113"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="B155" s="113"/>
+      <c r="C155" s="113"/>
+      <c r="D155" s="113"/>
+      <c r="E155" s="113"/>
+      <c r="F155" s="113"/>
+      <c r="G155" s="100">
+        <v>14226</v>
+      </c>
+      <c r="H155" s="113">
+        <f>+$G$155</f>
+        <v>14226</v>
+      </c>
+      <c r="I155" s="113">
+        <f>+$G$155</f>
+        <v>14226</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B156" s="113"/>
+      <c r="C156" s="113"/>
+      <c r="D156" s="113"/>
+      <c r="E156" s="113"/>
+      <c r="F156" s="113"/>
+      <c r="G156" s="100">
+        <v>14329</v>
+      </c>
+      <c r="H156" s="113"/>
+      <c r="I156" s="113"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="B157" s="113"/>
+      <c r="C157" s="113"/>
+      <c r="D157" s="113"/>
+      <c r="E157" s="113"/>
+      <c r="F157" s="113"/>
+      <c r="G157" s="100">
+        <v>21390</v>
+      </c>
+      <c r="H157" s="113">
+        <f>+$G$157</f>
+        <v>21390</v>
+      </c>
+      <c r="I157" s="113">
+        <f>+$G$157</f>
+        <v>21390</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="B158" s="113"/>
+      <c r="C158" s="113"/>
+      <c r="D158" s="113"/>
+      <c r="E158" s="113"/>
+      <c r="F158" s="113"/>
+      <c r="G158" s="100">
+        <v>18067</v>
+      </c>
+      <c r="H158" s="113"/>
+      <c r="I158" s="113"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="B159" s="113"/>
+      <c r="C159" s="113"/>
+      <c r="D159" s="113"/>
+      <c r="E159" s="113"/>
+      <c r="F159" s="113"/>
+      <c r="G159" s="100">
+        <v>36134</v>
+      </c>
+      <c r="H159" s="113">
+        <f>+$G$159</f>
+        <v>36134</v>
+      </c>
+      <c r="I159" s="113">
+        <f>+$G$159</f>
+        <v>36134</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B160" s="113"/>
+      <c r="C160" s="113"/>
+      <c r="D160" s="113"/>
+      <c r="E160" s="113"/>
+      <c r="F160" s="113"/>
+      <c r="G160" s="100">
+        <v>17029</v>
+      </c>
+      <c r="H160" s="113"/>
+      <c r="I160" s="113"/>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="B161" s="113"/>
+      <c r="C161" s="113"/>
+      <c r="D161" s="113"/>
+      <c r="E161" s="113"/>
+      <c r="F161" s="113"/>
+      <c r="G161" s="135">
+        <f>+$G$160</f>
+        <v>17029</v>
+      </c>
+      <c r="H161" s="113">
+        <f>+$G$160</f>
+        <v>17029</v>
+      </c>
+      <c r="I161" s="113">
+        <f>+$G$160</f>
+        <v>17029</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B162" s="113"/>
+      <c r="C162" s="113"/>
+      <c r="D162" s="113"/>
+      <c r="E162" s="113"/>
+      <c r="F162" s="113"/>
+      <c r="G162" s="100">
+        <v>17237</v>
+      </c>
+      <c r="H162" s="113"/>
+      <c r="I162" s="113"/>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B163" s="113"/>
+      <c r="C163" s="113"/>
+      <c r="D163" s="113"/>
+      <c r="E163" s="113"/>
+      <c r="F163" s="113"/>
+      <c r="G163" s="100">
+        <v>20560</v>
+      </c>
+      <c r="H163" s="113"/>
+      <c r="I163" s="113"/>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="B164" s="113"/>
+      <c r="C164" s="113"/>
+      <c r="D164" s="113"/>
+      <c r="E164" s="113"/>
+      <c r="F164" s="113"/>
+      <c r="G164" s="100">
+        <v>14952</v>
+      </c>
+      <c r="H164" s="113"/>
+      <c r="I164" s="113"/>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="B165" s="113"/>
+      <c r="C165" s="113"/>
+      <c r="D165" s="113"/>
+      <c r="E165" s="113"/>
+      <c r="F165" s="113"/>
+      <c r="G165" s="100">
+        <f>+$G$164*2</f>
+        <v>29904</v>
+      </c>
+      <c r="H165" s="113">
+        <f>+$G$165</f>
+        <v>29904</v>
+      </c>
+      <c r="I165" s="113">
+        <f>+$G$165</f>
+        <v>29904</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B149" s="68">
-        <f t="shared" si="12"/>
-        <v>57160</v>
-      </c>
-      <c r="C149" s="68">
-        <v>34296</v>
-      </c>
-      <c r="D149" s="68">
-        <v>34296</v>
-      </c>
-      <c r="E149" s="68">
-        <v>34296</v>
-      </c>
-      <c r="F149" s="68">
-        <f t="shared" si="13"/>
-        <v>40012</v>
-      </c>
-      <c r="G149" s="73">
+      <c r="B166" s="68"/>
+      <c r="C166" s="68"/>
+      <c r="D166" s="68"/>
+      <c r="E166" s="68"/>
+      <c r="F166" s="68"/>
+      <c r="G166" s="73">
+        <v>36239</v>
+      </c>
+      <c r="H166" s="68"/>
+      <c r="I166" s="68"/>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B167" s="68"/>
+      <c r="C167" s="68"/>
+      <c r="D167" s="68"/>
+      <c r="E167" s="68"/>
+      <c r="F167" s="68"/>
+      <c r="G167" s="73">
+        <v>38835</v>
+      </c>
+      <c r="H167" s="68"/>
+      <c r="I167" s="68"/>
+    </row>
+    <row r="168" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B168" s="123"/>
+      <c r="C168" s="123"/>
+      <c r="D168" s="123"/>
+      <c r="E168" s="123"/>
+      <c r="F168" s="123"/>
+      <c r="G168" s="134">
+        <v>70000</v>
+      </c>
+      <c r="H168" s="136">
+        <v>25000</v>
+      </c>
+      <c r="I168" s="78">
+        <f>+$H$168</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" s="115"/>
+      <c r="C169" s="115"/>
+      <c r="D169" s="115"/>
+      <c r="E169" s="115"/>
+      <c r="F169" s="115"/>
+      <c r="G169" s="115"/>
+      <c r="H169" s="115"/>
+      <c r="I169" s="116"/>
+    </row>
+    <row r="170" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B170" s="124"/>
+      <c r="C170" s="98"/>
+      <c r="D170" s="98"/>
+      <c r="E170" s="98"/>
+      <c r="F170" s="98"/>
+      <c r="G170" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H170" s="98" t="s">
+        <v>100</v>
+      </c>
+      <c r="I170" s="99" t="s">
+        <v>130</v>
+      </c>
+      <c r="K170" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="L170" s="69">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A171" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B171" s="87"/>
+      <c r="C171" s="87"/>
+      <c r="D171" s="87"/>
+      <c r="E171" s="87"/>
+      <c r="F171" s="87"/>
+      <c r="G171" s="87">
+        <f>+$L$170</f>
+        <v>12000</v>
+      </c>
+      <c r="H171" s="87">
+        <f t="shared" ref="H171:I171" si="14">+$L$170</f>
+        <v>12000</v>
+      </c>
+      <c r="I171" s="106">
         <f t="shared" si="14"/>
-        <v>34296</v>
-      </c>
-      <c r="H149" s="68"/>
-      <c r="I149" s="68"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B150" s="68">
-        <f t="shared" si="12"/>
-        <v>61121.666666666672</v>
-      </c>
-      <c r="C150" s="68">
-        <v>36673</v>
-      </c>
-      <c r="D150" s="68">
-        <v>36673</v>
-      </c>
-      <c r="E150" s="68">
-        <v>36673</v>
-      </c>
-      <c r="F150" s="68">
-        <f t="shared" si="13"/>
-        <v>42785.166666666664</v>
-      </c>
-      <c r="G150" s="73">
-        <f t="shared" si="14"/>
-        <v>36673</v>
-      </c>
-      <c r="H150" s="68"/>
-      <c r="I150" s="68"/>
-    </row>
-    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="B151" s="113">
-        <v>70000</v>
-      </c>
-      <c r="C151" s="113">
-        <v>40000</v>
-      </c>
-      <c r="D151" s="113">
-        <v>40000</v>
-      </c>
-      <c r="E151" s="113">
-        <v>40000</v>
-      </c>
-      <c r="F151" s="113">
-        <f t="shared" si="13"/>
-        <v>49000</v>
-      </c>
-      <c r="G151" s="100">
-        <f>+B151*0.6</f>
-        <v>42000</v>
-      </c>
-      <c r="H151" s="113">
-        <v>20000</v>
-      </c>
-      <c r="I151" s="113">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B152" s="115"/>
-      <c r="C152" s="115"/>
-      <c r="D152" s="115"/>
-      <c r="E152" s="115"/>
-      <c r="F152" s="115"/>
-      <c r="G152" s="115"/>
-      <c r="H152" s="115"/>
-      <c r="I152" s="116"/>
-    </row>
-    <row r="153" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="B153" s="124"/>
-      <c r="C153" s="98"/>
-      <c r="D153" s="98"/>
-      <c r="E153" s="98"/>
-      <c r="F153" s="98"/>
-      <c r="G153" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H153" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="I153" s="99" t="s">
-        <v>130</v>
-      </c>
-      <c r="K153" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="L153" s="69">
         <v>12000</v>
       </c>
     </row>
-    <row r="154" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="B154" s="87"/>
-      <c r="C154" s="87"/>
-      <c r="D154" s="87"/>
-      <c r="E154" s="87"/>
-      <c r="F154" s="87"/>
-      <c r="G154" s="87">
-        <f>+$L$153</f>
-        <v>12000</v>
-      </c>
-      <c r="H154" s="87">
-        <f t="shared" ref="H154:I154" si="15">+$L$153</f>
-        <v>12000</v>
-      </c>
-      <c r="I154" s="106">
+    <row r="172" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A172" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B172" s="85"/>
+      <c r="C172" s="85"/>
+      <c r="D172" s="85"/>
+      <c r="E172" s="85"/>
+      <c r="F172" s="85"/>
+      <c r="G172" s="86">
+        <v>25000</v>
+      </c>
+      <c r="H172" s="85">
+        <f>+G172</f>
+        <v>25000</v>
+      </c>
+      <c r="I172" s="101">
+        <f>+G172</f>
+        <v>25000</v>
+      </c>
+      <c r="K172" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="L172" s="69">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B173" s="85"/>
+      <c r="C173" s="85"/>
+      <c r="D173" s="85"/>
+      <c r="E173" s="85"/>
+      <c r="F173" s="85"/>
+      <c r="G173" s="85">
+        <f t="shared" ref="G173:G183" si="15">+$L$172</f>
+        <v>22000</v>
+      </c>
+      <c r="H173" s="85">
+        <f t="shared" ref="H173:I183" si="16">+$L$172</f>
+        <v>22000</v>
+      </c>
+      <c r="I173" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A174" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B174" s="85"/>
+      <c r="C174" s="85"/>
+      <c r="D174" s="85"/>
+      <c r="E174" s="85"/>
+      <c r="F174" s="85"/>
+      <c r="G174" s="85">
         <f t="shared" si="15"/>
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="B155" s="85"/>
-      <c r="C155" s="85"/>
-      <c r="D155" s="85"/>
-      <c r="E155" s="85"/>
-      <c r="F155" s="85"/>
-      <c r="G155" s="86">
-        <v>25000</v>
-      </c>
-      <c r="H155" s="85">
-        <f>+G155</f>
-        <v>25000</v>
-      </c>
-      <c r="I155" s="101">
-        <f>+G155</f>
-        <v>25000</v>
-      </c>
-      <c r="K155" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="L155" s="69">
         <v>22000</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="B156" s="85"/>
-      <c r="C156" s="85"/>
-      <c r="D156" s="85"/>
-      <c r="E156" s="85"/>
-      <c r="F156" s="85"/>
-      <c r="G156" s="85">
-        <f t="shared" ref="G156:G166" si="16">+$L$155</f>
+      <c r="H174" s="85">
+        <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="H156" s="85">
-        <f t="shared" ref="H156:I166" si="17">+$L$155</f>
+      <c r="I174" s="101">
+        <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I156" s="101">
+    </row>
+    <row r="175" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B175" s="85"/>
+      <c r="C175" s="85"/>
+      <c r="D175" s="85"/>
+      <c r="E175" s="85"/>
+      <c r="F175" s="85"/>
+      <c r="G175" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H175" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I175" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B176" s="85"/>
+      <c r="C176" s="85"/>
+      <c r="D176" s="85"/>
+      <c r="E176" s="85"/>
+      <c r="F176" s="85"/>
+      <c r="G176" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H176" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I176" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B177" s="85"/>
+      <c r="C177" s="85"/>
+      <c r="D177" s="85"/>
+      <c r="E177" s="85"/>
+      <c r="F177" s="85"/>
+      <c r="G177" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H177" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I177" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B178" s="85"/>
+      <c r="C178" s="85"/>
+      <c r="D178" s="85"/>
+      <c r="E178" s="85"/>
+      <c r="F178" s="85"/>
+      <c r="G178" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H178" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I178" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B179" s="85"/>
+      <c r="C179" s="85"/>
+      <c r="D179" s="85"/>
+      <c r="E179" s="85"/>
+      <c r="F179" s="85"/>
+      <c r="G179" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H179" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I179" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B180" s="85"/>
+      <c r="C180" s="85"/>
+      <c r="D180" s="85"/>
+      <c r="E180" s="85"/>
+      <c r="F180" s="85"/>
+      <c r="G180" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H180" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I180" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B181" s="85"/>
+      <c r="C181" s="85"/>
+      <c r="D181" s="85"/>
+      <c r="E181" s="85"/>
+      <c r="F181" s="85"/>
+      <c r="G181" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H181" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I181" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A182" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B182" s="85"/>
+      <c r="C182" s="85"/>
+      <c r="D182" s="85"/>
+      <c r="E182" s="85"/>
+      <c r="F182" s="85"/>
+      <c r="G182" s="85">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H182" s="85">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I182" s="101">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B183" s="103"/>
+      <c r="C183" s="103"/>
+      <c r="D183" s="103"/>
+      <c r="E183" s="103"/>
+      <c r="F183" s="103"/>
+      <c r="G183" s="103">
+        <f t="shared" si="15"/>
+        <v>22000</v>
+      </c>
+      <c r="H183" s="103">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="I183" s="104">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B184" s="87"/>
+      <c r="C184" s="87"/>
+      <c r="D184" s="87"/>
+      <c r="E184" s="87"/>
+      <c r="F184" s="87"/>
+      <c r="G184" s="105">
+        <v>32000</v>
+      </c>
+      <c r="H184" s="105">
+        <f t="shared" ref="H184:H185" si="17">+H183</f>
+        <v>22000</v>
+      </c>
+      <c r="I184" s="87"/>
+    </row>
+    <row r="185" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B185" s="92"/>
+      <c r="C185" s="92"/>
+      <c r="D185" s="92"/>
+      <c r="E185" s="92"/>
+      <c r="F185" s="92"/>
+      <c r="G185" s="91">
+        <v>32000</v>
+      </c>
+      <c r="H185" s="91">
         <f t="shared" si="17"/>
         <v>22000</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="B157" s="85"/>
-      <c r="C157" s="85"/>
-      <c r="D157" s="85"/>
-      <c r="E157" s="85"/>
-      <c r="F157" s="85"/>
-      <c r="G157" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H157" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I157" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="B158" s="85"/>
-      <c r="C158" s="85"/>
-      <c r="D158" s="85"/>
-      <c r="E158" s="85"/>
-      <c r="F158" s="85"/>
-      <c r="G158" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H158" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I158" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="B159" s="85"/>
-      <c r="C159" s="85"/>
-      <c r="D159" s="85"/>
-      <c r="E159" s="85"/>
-      <c r="F159" s="85"/>
-      <c r="G159" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H159" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I159" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="B160" s="85"/>
-      <c r="C160" s="85"/>
-      <c r="D160" s="85"/>
-      <c r="E160" s="85"/>
-      <c r="F160" s="85"/>
-      <c r="G160" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H160" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I160" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="B161" s="85"/>
-      <c r="C161" s="85"/>
-      <c r="D161" s="85"/>
-      <c r="E161" s="85"/>
-      <c r="F161" s="85"/>
-      <c r="G161" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H161" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I161" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="B162" s="85"/>
-      <c r="C162" s="85"/>
-      <c r="D162" s="85"/>
-      <c r="E162" s="85"/>
-      <c r="F162" s="85"/>
-      <c r="G162" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H162" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I162" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B163" s="85"/>
-      <c r="C163" s="85"/>
-      <c r="D163" s="85"/>
-      <c r="E163" s="85"/>
-      <c r="F163" s="85"/>
-      <c r="G163" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H163" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I163" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="B164" s="85"/>
-      <c r="C164" s="85"/>
-      <c r="D164" s="85"/>
-      <c r="E164" s="85"/>
-      <c r="F164" s="85"/>
-      <c r="G164" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H164" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I164" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="B165" s="85"/>
-      <c r="C165" s="85"/>
-      <c r="D165" s="85"/>
-      <c r="E165" s="85"/>
-      <c r="F165" s="85"/>
-      <c r="G165" s="85">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H165" s="85">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I165" s="101">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="B166" s="103"/>
-      <c r="C166" s="103"/>
-      <c r="D166" s="103"/>
-      <c r="E166" s="103"/>
-      <c r="F166" s="103"/>
-      <c r="G166" s="103">
-        <f t="shared" si="16"/>
-        <v>22000</v>
-      </c>
-      <c r="H166" s="103">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I166" s="104">
-        <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B167" s="87"/>
-      <c r="C167" s="87"/>
-      <c r="D167" s="87"/>
-      <c r="E167" s="87"/>
-      <c r="F167" s="87"/>
-      <c r="G167" s="105">
-        <v>32000</v>
-      </c>
-      <c r="H167" s="105">
-        <f t="shared" ref="H167:H168" si="18">+H166</f>
-        <v>22000</v>
-      </c>
-      <c r="I167" s="87"/>
-    </row>
-    <row r="168" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B168" s="92"/>
-      <c r="C168" s="92"/>
-      <c r="D168" s="92"/>
-      <c r="E168" s="92"/>
-      <c r="F168" s="92"/>
-      <c r="G168" s="91">
-        <v>32000</v>
-      </c>
-      <c r="H168" s="91">
+      <c r="I185" s="92"/>
+    </row>
+    <row r="186" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="B186" s="124"/>
+      <c r="C186" s="125"/>
+      <c r="D186" s="125"/>
+      <c r="E186" s="98"/>
+      <c r="F186" s="98"/>
+      <c r="G186" s="98" t="s">
+        <v>99</v>
+      </c>
+      <c r="H186" s="99" t="s">
+        <v>100</v>
+      </c>
+      <c r="I186" s="99" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B187" s="96"/>
+      <c r="C187" s="96"/>
+      <c r="D187" s="96"/>
+      <c r="E187" s="96"/>
+      <c r="F187" s="96"/>
+      <c r="G187" s="95">
+        <v>24000</v>
+      </c>
+      <c r="H187" s="96">
+        <f>+G187</f>
+        <v>24000</v>
+      </c>
+      <c r="I187" s="97">
+        <f>+G187</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B188" s="74"/>
+      <c r="C188" s="74"/>
+      <c r="D188" s="74"/>
+      <c r="E188" s="74"/>
+      <c r="F188" s="74"/>
+      <c r="G188" s="74"/>
+      <c r="H188" s="74">
+        <f t="shared" ref="H188:I228" si="18">+G188</f>
+        <v>0</v>
+      </c>
+      <c r="I188" s="93">
         <f t="shared" si="18"/>
-        <v>22000</v>
-      </c>
-      <c r="I168" s="92"/>
-    </row>
-    <row r="169" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="90" t="s">
-        <v>170</v>
-      </c>
-      <c r="B169" s="124"/>
-      <c r="C169" s="125"/>
-      <c r="D169" s="125"/>
-      <c r="E169" s="98"/>
-      <c r="F169" s="98"/>
-      <c r="G169" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="H169" s="99" t="s">
-        <v>100</v>
-      </c>
-      <c r="I169" s="99" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B170" s="96"/>
-      <c r="C170" s="96"/>
-      <c r="D170" s="96"/>
-      <c r="E170" s="96"/>
-      <c r="F170" s="96"/>
-      <c r="G170" s="95">
-        <v>24000</v>
-      </c>
-      <c r="H170" s="96">
-        <f>+G170</f>
-        <v>24000</v>
-      </c>
-      <c r="I170" s="97">
-        <f>+G170</f>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B171" s="74"/>
-      <c r="C171" s="74"/>
-      <c r="D171" s="74"/>
-      <c r="E171" s="74"/>
-      <c r="F171" s="74"/>
-      <c r="G171" s="74"/>
-      <c r="H171" s="74">
-        <f t="shared" ref="H171:I211" si="19">+G171</f>
         <v>0</v>
       </c>
-      <c r="I171" s="93">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="9" t="s">
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="B172" s="88"/>
-      <c r="C172" s="88"/>
-      <c r="D172" s="88"/>
-      <c r="E172" s="88"/>
-      <c r="F172" s="88"/>
-      <c r="G172" s="88">
-        <f t="shared" ref="G172:I172" si="20">$L$172</f>
-        <v>16640</v>
-      </c>
-      <c r="H172" s="88">
-        <f t="shared" si="20"/>
-        <v>16640</v>
-      </c>
-      <c r="I172" s="94">
-        <f t="shared" si="20"/>
-        <v>16640</v>
-      </c>
-      <c r="K172" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="L172" s="69">
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B173" s="88"/>
-      <c r="C173" s="88"/>
-      <c r="D173" s="88"/>
-      <c r="E173" s="88"/>
-      <c r="F173" s="88"/>
-      <c r="G173" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H173" s="88">
-        <f t="shared" ref="H173:I173" si="21">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I173" s="94">
-        <f t="shared" si="21"/>
-        <v>9600</v>
-      </c>
-      <c r="K173" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="L173" s="69">
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B174" s="88"/>
-      <c r="C174" s="88"/>
-      <c r="D174" s="88"/>
-      <c r="E174" s="88"/>
-      <c r="F174" s="88"/>
-      <c r="G174" s="88">
-        <f>$L$172</f>
-        <v>16640</v>
-      </c>
-      <c r="H174" s="88">
-        <f t="shared" ref="H174:I174" si="22">$L$172</f>
-        <v>16640</v>
-      </c>
-      <c r="I174" s="94">
-        <f t="shared" si="22"/>
-        <v>16640</v>
-      </c>
-      <c r="L174" s="67"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B175" s="88"/>
-      <c r="C175" s="88"/>
-      <c r="D175" s="88"/>
-      <c r="E175" s="88"/>
-      <c r="F175" s="88"/>
-      <c r="G175" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H175" s="88">
-        <f t="shared" ref="H175:I175" si="23">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I175" s="94">
-        <f t="shared" si="23"/>
-        <v>9600</v>
-      </c>
-      <c r="K175" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="L175" s="69">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B176" s="88"/>
-      <c r="C176" s="88"/>
-      <c r="D176" s="88"/>
-      <c r="E176" s="88"/>
-      <c r="F176" s="88"/>
-      <c r="G176" s="88">
-        <f t="shared" ref="G176:I184" si="24">$L$172</f>
-        <v>16640</v>
-      </c>
-      <c r="H176" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="I176" s="94">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B177" s="88"/>
-      <c r="C177" s="88"/>
-      <c r="D177" s="88"/>
-      <c r="E177" s="88"/>
-      <c r="F177" s="88"/>
-      <c r="G177" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H177" s="88">
-        <f t="shared" ref="H177:I177" si="25">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I177" s="94">
-        <f t="shared" si="25"/>
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B178" s="88"/>
-      <c r="C178" s="88"/>
-      <c r="D178" s="88"/>
-      <c r="E178" s="88"/>
-      <c r="F178" s="88"/>
-      <c r="G178" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="H178" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="I178" s="94">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B179" s="88"/>
-      <c r="C179" s="88"/>
-      <c r="D179" s="88"/>
-      <c r="E179" s="88"/>
-      <c r="F179" s="88"/>
-      <c r="G179" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H179" s="88">
-        <f t="shared" ref="H179:I179" si="26">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I179" s="94">
-        <f t="shared" si="26"/>
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B180" s="88"/>
-      <c r="C180" s="88"/>
-      <c r="D180" s="88"/>
-      <c r="E180" s="88"/>
-      <c r="F180" s="88"/>
-      <c r="G180" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="H180" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="I180" s="94">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B181" s="88"/>
-      <c r="C181" s="88"/>
-      <c r="D181" s="88"/>
-      <c r="E181" s="88"/>
-      <c r="F181" s="88"/>
-      <c r="G181" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H181" s="88">
-        <f t="shared" ref="H181:I181" si="27">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I181" s="94">
-        <f t="shared" si="27"/>
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B182" s="88"/>
-      <c r="C182" s="88"/>
-      <c r="D182" s="88"/>
-      <c r="E182" s="88"/>
-      <c r="F182" s="88"/>
-      <c r="G182" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="H182" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="I182" s="94">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B183" s="88"/>
-      <c r="C183" s="88"/>
-      <c r="D183" s="88"/>
-      <c r="E183" s="88"/>
-      <c r="F183" s="88"/>
-      <c r="G183" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H183" s="88">
-        <f t="shared" ref="H183:I183" si="28">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I183" s="94">
-        <f t="shared" si="28"/>
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B184" s="88"/>
-      <c r="C184" s="88"/>
-      <c r="D184" s="88"/>
-      <c r="E184" s="88"/>
-      <c r="F184" s="88"/>
-      <c r="G184" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="H184" s="88">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-      <c r="I184" s="94">
-        <f t="shared" si="24"/>
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B185" s="88"/>
-      <c r="C185" s="88"/>
-      <c r="D185" s="88"/>
-      <c r="E185" s="88"/>
-      <c r="F185" s="88"/>
-      <c r="G185" s="88">
-        <f>$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="H185" s="88">
-        <f t="shared" ref="H185:I185" si="29">$L$173</f>
-        <v>9600</v>
-      </c>
-      <c r="I185" s="94">
-        <f t="shared" si="29"/>
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="66" t="s">
-        <v>162</v>
-      </c>
-      <c r="B186" s="88"/>
-      <c r="C186" s="88"/>
-      <c r="D186" s="88"/>
-      <c r="E186" s="88"/>
-      <c r="F186" s="88"/>
-      <c r="G186" s="89">
-        <v>36000</v>
-      </c>
-      <c r="H186" s="88">
-        <f t="shared" si="19"/>
-        <v>36000</v>
-      </c>
-      <c r="I186" s="94">
-        <f>+G186</f>
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B187" s="88"/>
-      <c r="C187" s="88"/>
-      <c r="D187" s="88"/>
-      <c r="E187" s="88"/>
-      <c r="F187" s="88"/>
-      <c r="G187" s="88">
-        <f>$L$175</f>
-        <v>32000</v>
-      </c>
-      <c r="H187" s="88">
-        <f t="shared" ref="H187:I187" si="30">$L$175</f>
-        <v>32000</v>
-      </c>
-      <c r="I187" s="94">
-        <f t="shared" si="30"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="B188" s="88"/>
-      <c r="C188" s="88"/>
-      <c r="D188" s="88"/>
-      <c r="E188" s="88"/>
-      <c r="F188" s="88"/>
-      <c r="G188" s="88">
-        <f t="shared" ref="G188:I205" si="31">$L$175</f>
-        <v>32000</v>
-      </c>
-      <c r="H188" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-      <c r="I188" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="B189" s="88"/>
       <c r="C189" s="88"/>
@@ -9743,21 +9441,27 @@
       <c r="E189" s="88"/>
       <c r="F189" s="88"/>
       <c r="G189" s="88">
-        <f>$L$175</f>
-        <v>32000</v>
+        <f t="shared" ref="G189:I189" si="19">$L$189</f>
+        <v>16640</v>
       </c>
       <c r="H189" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="19"/>
+        <v>16640</v>
       </c>
       <c r="I189" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>16640</v>
+      </c>
+      <c r="K189" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="L189" s="69">
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="B190" s="88"/>
       <c r="C190" s="88"/>
@@ -9765,21 +9469,27 @@
       <c r="E190" s="88"/>
       <c r="F190" s="88"/>
       <c r="G190" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H190" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H190:I190" si="20">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I190" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>9600</v>
+      </c>
+      <c r="K190" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="L190" s="69">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B191" s="88"/>
       <c r="C191" s="88"/>
@@ -9787,21 +9497,22 @@
       <c r="E191" s="88"/>
       <c r="F191" s="88"/>
       <c r="G191" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$189</f>
+        <v>16640</v>
       </c>
       <c r="H191" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H191:I191" si="21">$L$189</f>
+        <v>16640</v>
       </c>
       <c r="I191" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="21"/>
+        <v>16640</v>
+      </c>
+      <c r="L191" s="67"/>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="B192" s="88"/>
       <c r="C192" s="88"/>
@@ -9809,21 +9520,27 @@
       <c r="E192" s="88"/>
       <c r="F192" s="88"/>
       <c r="G192" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H192" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H192:I192" si="22">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I192" s="94">
-        <f t="shared" si="31"/>
+        <f t="shared" si="22"/>
+        <v>9600</v>
+      </c>
+      <c r="K192" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="L192" s="69">
         <v>32000</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="B193" s="88"/>
       <c r="C193" s="88"/>
@@ -9831,21 +9548,21 @@
       <c r="E193" s="88"/>
       <c r="F193" s="88"/>
       <c r="G193" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="G193:I201" si="23">$L$189</f>
+        <v>16640</v>
       </c>
       <c r="H193" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="I193" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="B194" s="88"/>
       <c r="C194" s="88"/>
@@ -9853,21 +9570,21 @@
       <c r="E194" s="88"/>
       <c r="F194" s="88"/>
       <c r="G194" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H194" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H194:I194" si="24">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I194" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="24"/>
+        <v>9600</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B195" s="88"/>
       <c r="C195" s="88"/>
@@ -9875,21 +9592,21 @@
       <c r="E195" s="88"/>
       <c r="F195" s="88"/>
       <c r="G195" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="H195" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="I195" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="35" t="s">
-        <v>185</v>
+      <c r="A196" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="B196" s="88"/>
       <c r="C196" s="88"/>
@@ -9897,21 +9614,21 @@
       <c r="E196" s="88"/>
       <c r="F196" s="88"/>
       <c r="G196" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H196" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H196:I196" si="25">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I196" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="25"/>
+        <v>9600</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="35" t="s">
-        <v>186</v>
+      <c r="A197" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="B197" s="88"/>
       <c r="C197" s="88"/>
@@ -9919,21 +9636,21 @@
       <c r="E197" s="88"/>
       <c r="F197" s="88"/>
       <c r="G197" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="H197" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="I197" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="35" t="s">
-        <v>187</v>
+      <c r="A198" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="B198" s="88"/>
       <c r="C198" s="88"/>
@@ -9941,21 +9658,21 @@
       <c r="E198" s="88"/>
       <c r="F198" s="88"/>
       <c r="G198" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H198" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H198:I198" si="26">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I198" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="26"/>
+        <v>9600</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="35" t="s">
-        <v>188</v>
+      <c r="A199" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="B199" s="88"/>
       <c r="C199" s="88"/>
@@ -9963,21 +9680,21 @@
       <c r="E199" s="88"/>
       <c r="F199" s="88"/>
       <c r="G199" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="H199" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="I199" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="35" t="s">
-        <v>189</v>
+      <c r="A200" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="B200" s="88"/>
       <c r="C200" s="88"/>
@@ -9985,21 +9702,21 @@
       <c r="E200" s="88"/>
       <c r="F200" s="88"/>
       <c r="G200" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H200" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H200:I200" si="27">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I200" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="35" t="s">
-        <v>54</v>
+        <f t="shared" si="27"/>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B201" s="88"/>
       <c r="C201" s="88"/>
@@ -10007,21 +9724,21 @@
       <c r="E201" s="88"/>
       <c r="F201" s="88"/>
       <c r="G201" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="H201" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
       </c>
       <c r="I201" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="35" t="s">
-        <v>190</v>
+        <f t="shared" si="23"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="B202" s="88"/>
       <c r="C202" s="88"/>
@@ -10029,21 +9746,21 @@
       <c r="E202" s="88"/>
       <c r="F202" s="88"/>
       <c r="G202" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f>$L$190</f>
+        <v>9600</v>
       </c>
       <c r="H202" s="88">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" ref="H202:I202" si="28">$L$190</f>
+        <v>9600</v>
       </c>
       <c r="I202" s="94">
-        <f t="shared" si="31"/>
-        <v>32000</v>
+        <f t="shared" si="28"/>
+        <v>9600</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="66" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="B203" s="88"/>
       <c r="C203" s="88"/>
@@ -10051,20 +9768,20 @@
       <c r="E203" s="88"/>
       <c r="F203" s="88"/>
       <c r="G203" s="89">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="H203" s="88">
-        <f>+G203</f>
-        <v>35000</v>
+        <f t="shared" si="18"/>
+        <v>36000</v>
       </c>
       <c r="I203" s="94">
         <f>+G203</f>
-        <v>35000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="35" t="s">
-        <v>192</v>
+      <c r="A204" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="B204" s="88"/>
       <c r="C204" s="88"/>
@@ -10072,21 +9789,21 @@
       <c r="E204" s="88"/>
       <c r="F204" s="88"/>
       <c r="G204" s="88">
-        <f t="shared" si="31"/>
+        <f>$L$192</f>
         <v>32000</v>
       </c>
       <c r="H204" s="88">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="H204:I204" si="29">$L$192</f>
         <v>32000</v>
       </c>
       <c r="I204" s="94">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="35" t="s">
-        <v>193</v>
+      <c r="A205" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="B205" s="88"/>
       <c r="C205" s="88"/>
@@ -10094,21 +9811,21 @@
       <c r="E205" s="88"/>
       <c r="F205" s="88"/>
       <c r="G205" s="88">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G205:I222" si="30">$L$192</f>
         <v>32000</v>
       </c>
       <c r="H205" s="88">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
       <c r="I205" s="94">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="35" t="s">
-        <v>194</v>
+      <c r="A206" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="B206" s="88"/>
       <c r="C206" s="88"/>
@@ -10116,21 +9833,21 @@
       <c r="E206" s="88"/>
       <c r="F206" s="88"/>
       <c r="G206" s="88">
-        <f t="shared" ref="G206:I207" si="32">$L$175</f>
+        <f>$L$192</f>
         <v>32000</v>
       </c>
       <c r="H206" s="88">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
       <c r="I206" s="94">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B207" s="88"/>
       <c r="C207" s="88"/>
@@ -10138,21 +9855,21 @@
       <c r="E207" s="88"/>
       <c r="F207" s="88"/>
       <c r="G207" s="88">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
       <c r="H207" s="88">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
       <c r="I207" s="94">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>32000</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B208" s="88"/>
       <c r="C208" s="88"/>
@@ -10160,20 +9877,21 @@
       <c r="E208" s="88"/>
       <c r="F208" s="88"/>
       <c r="G208" s="88">
-        <v>78000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H208" s="88">
-        <f t="shared" si="19"/>
-        <v>78000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I208" s="94">
-        <f t="shared" si="19"/>
-        <v>78000</v>
-      </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>163</v>
+        <v>56</v>
       </c>
       <c r="B209" s="88"/>
       <c r="C209" s="88"/>
@@ -10181,62 +9899,65 @@
       <c r="E209" s="88"/>
       <c r="F209" s="88"/>
       <c r="G209" s="88">
-        <v>60000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H209" s="88">
-        <f t="shared" si="19"/>
-        <v>60000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I209" s="94">
-        <f t="shared" si="19"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="66" t="s">
-        <v>164</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="B210" s="88"/>
       <c r="C210" s="88"/>
       <c r="D210" s="88"/>
       <c r="E210" s="88"/>
       <c r="F210" s="88"/>
-      <c r="G210" s="89">
-        <v>100000</v>
+      <c r="G210" s="88">
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H210" s="88">
-        <f t="shared" si="19"/>
-        <v>100000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I210" s="94">
-        <f t="shared" si="19"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A211" s="66" t="s">
-        <v>165</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="B211" s="88"/>
       <c r="C211" s="88"/>
       <c r="D211" s="88"/>
       <c r="E211" s="88"/>
       <c r="F211" s="88"/>
-      <c r="G211" s="89">
-        <v>75000</v>
+      <c r="G211" s="88">
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H211" s="88">
-        <f t="shared" si="19"/>
-        <v>75000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I211" s="94">
-        <f t="shared" si="19"/>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B212" s="88"/>
       <c r="C212" s="88"/>
@@ -10244,21 +9965,21 @@
       <c r="E212" s="88"/>
       <c r="F212" s="88"/>
       <c r="G212" s="88">
-        <f>+$L$214</f>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H212" s="88">
-        <f t="shared" ref="H212:I227" si="33">+$L$214</f>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I212" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="9" t="s">
-        <v>197</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="35" t="s">
+        <v>185</v>
       </c>
       <c r="B213" s="88"/>
       <c r="C213" s="88"/>
@@ -10266,21 +9987,21 @@
       <c r="E213" s="88"/>
       <c r="F213" s="88"/>
       <c r="G213" s="88">
-        <f t="shared" ref="G213:I228" si="34">+$L$214</f>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H213" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I213" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A214" s="9" t="s">
-        <v>198</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="35" t="s">
+        <v>186</v>
       </c>
       <c r="B214" s="88"/>
       <c r="C214" s="88"/>
@@ -10288,27 +10009,21 @@
       <c r="E214" s="88"/>
       <c r="F214" s="88"/>
       <c r="G214" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H214" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I214" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="K214" s="63" t="s">
-        <v>213</v>
-      </c>
-      <c r="L214" s="69">
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A215" s="9" t="s">
-        <v>199</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="35" t="s">
+        <v>187</v>
       </c>
       <c r="B215" s="88"/>
       <c r="C215" s="88"/>
@@ -10316,21 +10031,21 @@
       <c r="E215" s="88"/>
       <c r="F215" s="88"/>
       <c r="G215" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H215" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I215" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A216" s="9" t="s">
-        <v>200</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="35" t="s">
+        <v>188</v>
       </c>
       <c r="B216" s="88"/>
       <c r="C216" s="88"/>
@@ -10338,21 +10053,21 @@
       <c r="E216" s="88"/>
       <c r="F216" s="88"/>
       <c r="G216" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H216" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I216" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A217" s="9" t="s">
-        <v>212</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="35" t="s">
+        <v>189</v>
       </c>
       <c r="B217" s="88"/>
       <c r="C217" s="88"/>
@@ -10360,21 +10075,21 @@
       <c r="E217" s="88"/>
       <c r="F217" s="88"/>
       <c r="G217" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H217" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I217" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A218" s="9" t="s">
-        <v>201</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="B218" s="88"/>
       <c r="C218" s="88"/>
@@ -10382,21 +10097,21 @@
       <c r="E218" s="88"/>
       <c r="F218" s="88"/>
       <c r="G218" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H218" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I218" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A219" s="9" t="s">
-        <v>202</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="35" t="s">
+        <v>190</v>
       </c>
       <c r="B219" s="88"/>
       <c r="C219" s="88"/>
@@ -10404,43 +10119,42 @@
       <c r="E219" s="88"/>
       <c r="F219" s="88"/>
       <c r="G219" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H219" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I219" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A220" s="9" t="s">
-        <v>203</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="66" t="s">
+        <v>191</v>
       </c>
       <c r="B220" s="88"/>
       <c r="C220" s="88"/>
       <c r="D220" s="88"/>
       <c r="E220" s="88"/>
       <c r="F220" s="88"/>
-      <c r="G220" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+      <c r="G220" s="89">
+        <v>35000</v>
       </c>
       <c r="H220" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f>+G220</f>
+        <v>35000</v>
       </c>
       <c r="I220" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A221" s="9" t="s">
-        <v>204</v>
+        <f>+G220</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="35" t="s">
+        <v>192</v>
       </c>
       <c r="B221" s="88"/>
       <c r="C221" s="88"/>
@@ -10448,21 +10162,21 @@
       <c r="E221" s="88"/>
       <c r="F221" s="88"/>
       <c r="G221" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H221" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I221" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A222" s="9" t="s">
-        <v>205</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="35" t="s">
+        <v>193</v>
       </c>
       <c r="B222" s="88"/>
       <c r="C222" s="88"/>
@@ -10470,21 +10184,21 @@
       <c r="E222" s="88"/>
       <c r="F222" s="88"/>
       <c r="G222" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H222" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="I222" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A223" s="9" t="s">
-        <v>206</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="35" t="s">
+        <v>194</v>
       </c>
       <c r="B223" s="88"/>
       <c r="C223" s="88"/>
@@ -10492,21 +10206,21 @@
       <c r="E223" s="88"/>
       <c r="F223" s="88"/>
       <c r="G223" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" ref="G223:I224" si="31">$L$192</f>
+        <v>32000</v>
       </c>
       <c r="H223" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="31"/>
+        <v>32000</v>
       </c>
       <c r="I223" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="31"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B224" s="88"/>
       <c r="C224" s="88"/>
@@ -10514,21 +10228,21 @@
       <c r="E224" s="88"/>
       <c r="F224" s="88"/>
       <c r="G224" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <f t="shared" si="31"/>
+        <v>32000</v>
       </c>
       <c r="H224" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="31"/>
+        <v>32000</v>
       </c>
       <c r="I224" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="31"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="B225" s="88"/>
       <c r="C225" s="88"/>
@@ -10536,21 +10250,20 @@
       <c r="E225" s="88"/>
       <c r="F225" s="88"/>
       <c r="G225" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <v>78000</v>
       </c>
       <c r="H225" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="18"/>
+        <v>78000</v>
       </c>
       <c r="I225" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="B226" s="88"/>
       <c r="C226" s="88"/>
@@ -10558,231 +10271,608 @@
       <c r="E226" s="88"/>
       <c r="F226" s="88"/>
       <c r="G226" s="88">
-        <f t="shared" si="34"/>
-        <v>106880</v>
+        <v>60000</v>
       </c>
       <c r="H226" s="88">
-        <f t="shared" si="33"/>
-        <v>106880</v>
+        <f t="shared" si="18"/>
+        <v>60000</v>
       </c>
       <c r="I226" s="94">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="9" t="s">
-        <v>210</v>
+        <f t="shared" si="18"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" s="66" t="s">
+        <v>164</v>
       </c>
       <c r="B227" s="88"/>
       <c r="C227" s="88"/>
       <c r="D227" s="88"/>
       <c r="E227" s="88"/>
       <c r="F227" s="88"/>
-      <c r="G227" s="88">
-        <f t="shared" si="34"/>
+      <c r="G227" s="89">
+        <v>100000</v>
+      </c>
+      <c r="H227" s="88">
+        <f t="shared" si="18"/>
+        <v>100000</v>
+      </c>
+      <c r="I227" s="94">
+        <f t="shared" si="18"/>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A228" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="B228" s="88"/>
+      <c r="C228" s="88"/>
+      <c r="D228" s="88"/>
+      <c r="E228" s="88"/>
+      <c r="F228" s="88"/>
+      <c r="G228" s="89">
+        <v>75000</v>
+      </c>
+      <c r="H228" s="88">
+        <f t="shared" si="18"/>
+        <v>75000</v>
+      </c>
+      <c r="I228" s="94">
+        <f t="shared" si="18"/>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A229" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B229" s="88"/>
+      <c r="C229" s="88"/>
+      <c r="D229" s="88"/>
+      <c r="E229" s="88"/>
+      <c r="F229" s="88"/>
+      <c r="G229" s="88">
+        <f>+$L$231</f>
         <v>106880</v>
       </c>
-      <c r="H227" s="88">
+      <c r="H229" s="88">
+        <f t="shared" ref="H229:I244" si="32">+$L$231</f>
+        <v>106880</v>
+      </c>
+      <c r="I229" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A230" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B230" s="88"/>
+      <c r="C230" s="88"/>
+      <c r="D230" s="88"/>
+      <c r="E230" s="88"/>
+      <c r="F230" s="88"/>
+      <c r="G230" s="88">
+        <f t="shared" ref="G230:I245" si="33">+$L$231</f>
+        <v>106880</v>
+      </c>
+      <c r="H230" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I230" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A231" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B231" s="88"/>
+      <c r="C231" s="88"/>
+      <c r="D231" s="88"/>
+      <c r="E231" s="88"/>
+      <c r="F231" s="88"/>
+      <c r="G231" s="88">
         <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I227" s="94">
+      <c r="H231" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I231" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="K231" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="L231" s="69">
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A232" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B232" s="88"/>
+      <c r="C232" s="88"/>
+      <c r="D232" s="88"/>
+      <c r="E232" s="88"/>
+      <c r="F232" s="88"/>
+      <c r="G232" s="88">
         <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="107" t="s">
+      <c r="H232" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I232" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A233" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B233" s="88"/>
+      <c r="C233" s="88"/>
+      <c r="D233" s="88"/>
+      <c r="E233" s="88"/>
+      <c r="F233" s="88"/>
+      <c r="G233" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H233" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I233" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A234" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B234" s="88"/>
+      <c r="C234" s="88"/>
+      <c r="D234" s="88"/>
+      <c r="E234" s="88"/>
+      <c r="F234" s="88"/>
+      <c r="G234" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H234" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I234" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A235" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B235" s="88"/>
+      <c r="C235" s="88"/>
+      <c r="D235" s="88"/>
+      <c r="E235" s="88"/>
+      <c r="F235" s="88"/>
+      <c r="G235" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H235" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I235" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B236" s="88"/>
+      <c r="C236" s="88"/>
+      <c r="D236" s="88"/>
+      <c r="E236" s="88"/>
+      <c r="F236" s="88"/>
+      <c r="G236" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H236" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I236" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A237" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B237" s="88"/>
+      <c r="C237" s="88"/>
+      <c r="D237" s="88"/>
+      <c r="E237" s="88"/>
+      <c r="F237" s="88"/>
+      <c r="G237" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H237" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I237" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A238" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B238" s="88"/>
+      <c r="C238" s="88"/>
+      <c r="D238" s="88"/>
+      <c r="E238" s="88"/>
+      <c r="F238" s="88"/>
+      <c r="G238" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H238" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I238" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B239" s="88"/>
+      <c r="C239" s="88"/>
+      <c r="D239" s="88"/>
+      <c r="E239" s="88"/>
+      <c r="F239" s="88"/>
+      <c r="G239" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H239" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I239" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B240" s="88"/>
+      <c r="C240" s="88"/>
+      <c r="D240" s="88"/>
+      <c r="E240" s="88"/>
+      <c r="F240" s="88"/>
+      <c r="G240" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H240" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I240" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B241" s="88"/>
+      <c r="C241" s="88"/>
+      <c r="D241" s="88"/>
+      <c r="E241" s="88"/>
+      <c r="F241" s="88"/>
+      <c r="G241" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H241" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I241" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B242" s="88"/>
+      <c r="C242" s="88"/>
+      <c r="D242" s="88"/>
+      <c r="E242" s="88"/>
+      <c r="F242" s="88"/>
+      <c r="G242" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H242" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I242" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B243" s="88"/>
+      <c r="C243" s="88"/>
+      <c r="D243" s="88"/>
+      <c r="E243" s="88"/>
+      <c r="F243" s="88"/>
+      <c r="G243" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H243" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I243" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B244" s="88"/>
+      <c r="C244" s="88"/>
+      <c r="D244" s="88"/>
+      <c r="E244" s="88"/>
+      <c r="F244" s="88"/>
+      <c r="G244" s="88">
+        <f t="shared" si="33"/>
+        <v>106880</v>
+      </c>
+      <c r="H244" s="88">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I244" s="94">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="107" t="s">
         <v>211</v>
       </c>
-      <c r="B228" s="108"/>
-      <c r="C228" s="108"/>
-      <c r="D228" s="108"/>
-      <c r="E228" s="108"/>
-      <c r="F228" s="108"/>
-      <c r="G228" s="108">
-        <f t="shared" si="34"/>
+      <c r="B245" s="108"/>
+      <c r="C245" s="108"/>
+      <c r="D245" s="108"/>
+      <c r="E245" s="108"/>
+      <c r="F245" s="108"/>
+      <c r="G245" s="108">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="H228" s="108">
-        <f t="shared" si="34"/>
+      <c r="H245" s="108">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
-      <c r="I228" s="109">
-        <f t="shared" si="34"/>
+      <c r="I245" s="109">
+        <f t="shared" si="33"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="90" t="s">
+    <row r="246" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="B229" s="124"/>
-      <c r="C229" s="125"/>
-      <c r="D229" s="125"/>
-      <c r="E229" s="98"/>
-      <c r="F229" s="98"/>
-      <c r="G229" s="98" t="s">
+      <c r="B246" s="124"/>
+      <c r="C246" s="125"/>
+      <c r="D246" s="125"/>
+      <c r="E246" s="98"/>
+      <c r="F246" s="98"/>
+      <c r="G246" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="H229" s="99" t="s">
+      <c r="H246" s="99" t="s">
         <v>100</v>
       </c>
-      <c r="I229" s="99" t="s">
+      <c r="I246" s="99" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="22" t="s">
+    <row r="247" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B230" s="111"/>
-      <c r="C230" s="111"/>
-      <c r="D230" s="111"/>
-      <c r="E230" s="111"/>
-      <c r="F230" s="111"/>
-      <c r="G230" s="110">
+      <c r="B247" s="111"/>
+      <c r="C247" s="111"/>
+      <c r="D247" s="111"/>
+      <c r="E247" s="111"/>
+      <c r="F247" s="111"/>
+      <c r="G247" s="110">
         <v>40000</v>
       </c>
-      <c r="H230" s="111">
-        <f>+G230</f>
+      <c r="H247" s="111">
+        <f>+G247</f>
         <v>40000</v>
       </c>
-      <c r="I230" s="112">
-        <f>+G230</f>
+      <c r="I247" s="112">
+        <f>+G247</f>
         <v>40000</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="90" t="s">
+    <row r="248" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="B231" s="124"/>
-      <c r="C231" s="98"/>
-      <c r="D231" s="98"/>
-      <c r="E231" s="98"/>
-      <c r="F231" s="98" t="s">
+      <c r="B248" s="124"/>
+      <c r="C248" s="98"/>
+      <c r="D248" s="98"/>
+      <c r="E248" s="98"/>
+      <c r="F248" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="G231" s="98" t="s">
+      <c r="G248" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="H231" s="98" t="s">
+      <c r="H248" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="I231" s="99" t="s">
+      <c r="I248" s="99" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A232" s="23" t="s">
+    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A249" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B232" s="87"/>
-      <c r="C232" s="87"/>
-      <c r="D232" s="87"/>
-      <c r="E232" s="87"/>
-      <c r="F232" s="105">
+      <c r="B249" s="87"/>
+      <c r="C249" s="87"/>
+      <c r="D249" s="87"/>
+      <c r="E249" s="87"/>
+      <c r="F249" s="105">
         <v>15000</v>
       </c>
-      <c r="G232" s="105">
+      <c r="G249" s="105">
         <v>15000</v>
       </c>
-      <c r="H232" s="87">
-        <f>+$G$232</f>
+      <c r="H249" s="87">
+        <f>+$G$249</f>
         <v>15000</v>
       </c>
-      <c r="I232" s="106">
-        <f>+$G$232</f>
+      <c r="I249" s="106">
+        <f>+$G$249</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A233" s="23" t="s">
+    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B233" s="85"/>
-      <c r="C233" s="85"/>
-      <c r="D233" s="85"/>
-      <c r="E233" s="85"/>
-      <c r="F233" s="86">
+      <c r="B250" s="85"/>
+      <c r="C250" s="85"/>
+      <c r="D250" s="85"/>
+      <c r="E250" s="85"/>
+      <c r="F250" s="86">
         <v>18000</v>
       </c>
-      <c r="G233" s="86">
+      <c r="G250" s="86">
         <v>15000</v>
       </c>
-      <c r="H233" s="85">
-        <f>+G233</f>
+      <c r="H250" s="85">
+        <f>+G250</f>
         <v>15000</v>
       </c>
-      <c r="I233" s="101">
-        <f>+G233</f>
+      <c r="I250" s="101">
+        <f>+G250</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A234" s="23" t="s">
+    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B234" s="85"/>
-      <c r="C234" s="85"/>
-      <c r="D234" s="85"/>
-      <c r="E234" s="85"/>
-      <c r="F234" s="86">
+      <c r="B251" s="85"/>
+      <c r="C251" s="85"/>
+      <c r="D251" s="85"/>
+      <c r="E251" s="85"/>
+      <c r="F251" s="86">
         <v>18000</v>
       </c>
-      <c r="G234" s="86">
+      <c r="G251" s="86">
         <v>15000</v>
       </c>
-      <c r="H234" s="85">
-        <f>+G234</f>
+      <c r="H251" s="85">
+        <f>+G251</f>
         <v>15000</v>
       </c>
-      <c r="I234" s="101">
-        <f>+G234</f>
+      <c r="I251" s="101">
+        <f>+G251</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="23" t="s">
+    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A252" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="B235" s="85"/>
-      <c r="C235" s="85"/>
-      <c r="D235" s="85"/>
-      <c r="E235" s="85"/>
-      <c r="F235" s="85"/>
-      <c r="G235" s="86">
+      <c r="B252" s="85"/>
+      <c r="C252" s="85"/>
+      <c r="D252" s="85"/>
+      <c r="E252" s="85"/>
+      <c r="F252" s="85"/>
+      <c r="G252" s="86">
         <v>20000</v>
       </c>
-      <c r="H235" s="85">
-        <f>+G235</f>
+      <c r="H252" s="85">
+        <f>+G252</f>
         <v>20000</v>
       </c>
-      <c r="I235" s="101">
-        <f>+G235</f>
+      <c r="I252" s="101">
+        <f>+G252</f>
         <v>20000</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="22" t="s">
+    <row r="253" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="B236" s="103"/>
-      <c r="C236" s="103"/>
-      <c r="D236" s="103"/>
-      <c r="E236" s="103"/>
-      <c r="F236" s="103"/>
-      <c r="G236" s="102">
+      <c r="B253" s="103"/>
+      <c r="C253" s="103"/>
+      <c r="D253" s="103"/>
+      <c r="E253" s="103"/>
+      <c r="F253" s="103"/>
+      <c r="G253" s="102">
         <v>20000</v>
       </c>
-      <c r="H236" s="103">
-        <f>+G236</f>
+      <c r="H253" s="103">
+        <f>+G253</f>
         <v>20000</v>
       </c>
-      <c r="I236" s="104">
-        <f>+G236</f>
+      <c r="I253" s="104">
+        <f>+G253</f>
         <v>20000</v>
       </c>
     </row>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2582,7 +2582,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="233">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -2745,9 +2745,6 @@
     <t>SEPELIO</t>
   </si>
   <si>
-    <t>SEPELIO FAMILIAR</t>
-  </si>
-  <si>
     <t>ECODOPLER FETAL</t>
   </si>
   <si>
@@ -3311,6 +3308,12 @@
   </si>
   <si>
     <t>Cuotas Sepelio</t>
+  </si>
+  <si>
+    <t>incluida</t>
+  </si>
+  <si>
+    <t>SEPELIO FAMILIAR por integrante</t>
   </si>
 </sst>
 </file>
@@ -4482,9 +4485,6 @@
     <xf numFmtId="165" fontId="0" fillId="17" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4549,6 +4549,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4846,38 +4849,38 @@
     <col min="5" max="5" width="10.42578125" style="67" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="11.5703125" style="67" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.5703125" style="67" customWidth="1"/>
-    <col min="10" max="10" width="18" style="156" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="155" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="115"/>
       <c r="D2" s="115"/>
       <c r="E2" s="116"/>
       <c r="F2" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="H2" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I2" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -4897,53 +4900,60 @@
       <c r="F3" s="73">
         <v>5550</v>
       </c>
-      <c r="G3" s="65"/>
+      <c r="G3" s="65" t="s">
+        <v>231</v>
+      </c>
       <c r="H3" s="65">
         <v>4550</v>
       </c>
-      <c r="I3" s="146">
+      <c r="I3" s="145">
         <f>+F3</f>
         <v>5550</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151">
+        <v>232</v>
+      </c>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150">
         <v>8500</v>
       </c>
-      <c r="D4" s="151">
+      <c r="D4" s="150">
         <v>8500</v>
       </c>
-      <c r="E4" s="151">
+      <c r="E4" s="150">
         <v>8500</v>
       </c>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="152">
+      <c r="F4" s="150">
+        <f>+F3</f>
+        <v>5550</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="H4" s="150"/>
+      <c r="I4" s="151">
         <f>+I3*2</f>
         <v>11100</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="154"/>
+        <v>229</v>
+      </c>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="153"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6" s="65"/>
       <c r="C6" s="65">
@@ -4962,63 +4972,63 @@
         <v>30000</v>
       </c>
       <c r="H6" s="65"/>
-      <c r="I6" s="146" t="s">
-        <v>130</v>
+      <c r="I6" s="145" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151">
+        <v>130</v>
+      </c>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150">
         <v>14000</v>
       </c>
-      <c r="D7" s="151">
+      <c r="D7" s="150">
         <v>14000</v>
       </c>
-      <c r="E7" s="151">
+      <c r="E7" s="150">
         <v>20000</v>
       </c>
-      <c r="F7" s="155">
+      <c r="F7" s="154">
         <f>+F6/2</f>
         <v>7500</v>
       </c>
-      <c r="G7" s="155">
+      <c r="G7" s="154">
         <f>+G6/2</f>
         <v>15000</v>
       </c>
-      <c r="H7" s="151"/>
-      <c r="I7" s="152"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="151"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" s="114"/>
       <c r="C8" s="115"/>
       <c r="D8" s="115"/>
       <c r="E8" s="116"/>
       <c r="F8" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="H8" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I8" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K8" s="55"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="65"/>
       <c r="C9" s="65"/>
@@ -5028,7 +5038,7 @@
       <c r="G9" s="65"/>
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
-      <c r="J9" s="157">
+      <c r="J9" s="156">
         <v>4800</v>
       </c>
       <c r="K9" s="11">
@@ -5054,12 +5064,12 @@
       </c>
       <c r="H10" s="65"/>
       <c r="I10" s="65"/>
-      <c r="J10" s="157"/>
+      <c r="J10" s="156"/>
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B11" s="65">
         <v>30000</v>
@@ -5075,7 +5085,7 @@
       </c>
       <c r="H11" s="65"/>
       <c r="I11" s="65"/>
-      <c r="J11" s="157"/>
+      <c r="J11" s="156"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -5096,12 +5106,12 @@
       </c>
       <c r="H12" s="65"/>
       <c r="I12" s="65"/>
-      <c r="J12" s="157"/>
+      <c r="J12" s="156"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B13" s="65"/>
       <c r="C13" s="65"/>
@@ -5115,12 +5125,12 @@
       </c>
       <c r="H13" s="65"/>
       <c r="I13" s="65"/>
-      <c r="J13" s="157"/>
+      <c r="J13" s="156"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
@@ -5134,7 +5144,7 @@
       </c>
       <c r="H14" s="65"/>
       <c r="I14" s="65"/>
-      <c r="J14" s="157"/>
+      <c r="J14" s="156"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5146,19 +5156,19 @@
       <c r="D15" s="115"/>
       <c r="E15" s="116"/>
       <c r="F15" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="H15" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I15" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K15" s="58"/>
     </row>
@@ -5190,7 +5200,7 @@
       <c r="I16" s="65">
         <v>0</v>
       </c>
-      <c r="J16" s="157">
+      <c r="J16" s="156">
         <v>29500</v>
       </c>
       <c r="K16" s="11">
@@ -5225,7 +5235,7 @@
       <c r="I17" s="65">
         <v>0</v>
       </c>
-      <c r="J17" s="157">
+      <c r="J17" s="156">
         <v>59000</v>
       </c>
       <c r="K17" s="11">
@@ -5234,7 +5244,7 @@
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="65"/>
       <c r="C18" s="65"/>
@@ -5246,7 +5256,7 @@
       <c r="G18" s="65"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
-      <c r="J18" s="157"/>
+      <c r="J18" s="156"/>
       <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5258,21 +5268,21 @@
       <c r="D19" s="115"/>
       <c r="E19" s="116"/>
       <c r="F19" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="H19" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I19" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" s="65">
         <v>20000</v>
@@ -5301,25 +5311,25 @@
       <c r="D21" s="115"/>
       <c r="E21" s="116"/>
       <c r="F21" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="H21" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I21" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K21" s="55"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" s="65">
         <v>35000</v>
@@ -5343,7 +5353,7 @@
       <c r="I22" s="65">
         <v>0</v>
       </c>
-      <c r="J22" s="157">
+      <c r="J22" s="156">
         <v>35000</v>
       </c>
       <c r="K22" s="11">
@@ -5359,19 +5369,19 @@
       <c r="D23" s="115"/>
       <c r="E23" s="116"/>
       <c r="F23" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="68" t="s">
+      <c r="H23" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H23" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I23" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K23" s="55"/>
     </row>
@@ -5385,37 +5395,37 @@
       <c r="G24" s="70"/>
       <c r="H24" s="65"/>
       <c r="I24" s="65"/>
-      <c r="J24" s="157"/>
+      <c r="J24" s="156"/>
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="114"/>
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
       <c r="E25" s="116"/>
       <c r="F25" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="H25" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H25" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I25" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J25" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K25" s="55"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="65">
         <v>20000</v>
@@ -5443,7 +5453,7 @@
       <c r="I26" s="65">
         <v>0</v>
       </c>
-      <c r="J26" s="157">
+      <c r="J26" s="156">
         <v>17400</v>
       </c>
       <c r="K26" s="11">
@@ -5452,32 +5462,32 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B27" s="114"/>
       <c r="C27" s="115"/>
       <c r="D27" s="115"/>
       <c r="E27" s="116"/>
       <c r="F27" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G27" s="68" t="s">
+      <c r="H27" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I27" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J27" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K27" s="55"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B28" s="65">
         <v>228334</v>
@@ -5505,7 +5515,7 @@
       <c r="I28" s="65">
         <v>74000</v>
       </c>
-      <c r="J28" s="157">
+      <c r="J28" s="156">
         <v>199000</v>
       </c>
       <c r="K28" s="11">
@@ -5521,25 +5531,25 @@
       <c r="D29" s="115"/>
       <c r="E29" s="116"/>
       <c r="F29" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="H29" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H29" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I29" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K29" s="55"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="65">
         <v>72000</v>
@@ -5567,7 +5577,7 @@
       <c r="I30" s="65">
         <v>16800</v>
       </c>
-      <c r="J30" s="157">
+      <c r="J30" s="156">
         <v>43400</v>
       </c>
       <c r="K30" s="11">
@@ -5583,25 +5593,25 @@
       <c r="D31" s="115"/>
       <c r="E31" s="116"/>
       <c r="F31" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="H31" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I31" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K31" s="55"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" s="65">
         <v>33000</v>
@@ -5629,7 +5639,7 @@
       <c r="I32" s="65">
         <v>10800</v>
       </c>
-      <c r="J32" s="157">
+      <c r="J32" s="156">
         <v>20300</v>
       </c>
       <c r="K32" s="11">
@@ -5645,25 +5655,25 @@
       <c r="D33" s="115"/>
       <c r="E33" s="116"/>
       <c r="F33" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="68" t="s">
+      <c r="H33" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I33" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J33" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K33" s="55"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B34" s="65">
         <v>24600</v>
@@ -5691,7 +5701,7 @@
       <c r="I34" s="65">
         <v>6300</v>
       </c>
-      <c r="J34" s="157">
+      <c r="J34" s="156">
         <v>15200</v>
       </c>
       <c r="K34" s="11">
@@ -5707,25 +5717,25 @@
       <c r="D35" s="115"/>
       <c r="E35" s="116"/>
       <c r="F35" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G35" s="68" t="s">
+      <c r="H35" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H35" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I35" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J35" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K35" s="55"/>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B36" s="65">
         <v>24600</v>
@@ -5753,7 +5763,7 @@
       <c r="I36" s="65">
         <v>6300</v>
       </c>
-      <c r="J36" s="157">
+      <c r="J36" s="156">
         <v>15200</v>
       </c>
       <c r="K36" s="11">
@@ -5769,25 +5779,25 @@
       <c r="D37" s="115"/>
       <c r="E37" s="116"/>
       <c r="F37" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G37" s="68" t="s">
+      <c r="H37" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H37" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I37" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J37" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K37" s="55"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" s="65">
         <v>24600</v>
@@ -5815,7 +5825,7 @@
       <c r="I38" s="65">
         <v>6300</v>
       </c>
-      <c r="J38" s="157">
+      <c r="J38" s="156">
         <v>15200</v>
       </c>
       <c r="K38" s="11">
@@ -5831,25 +5841,25 @@
       <c r="D39" s="115"/>
       <c r="E39" s="116"/>
       <c r="F39" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="68" t="s">
+      <c r="H39" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H39" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I39" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J39" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K39" s="55"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" s="65">
         <v>24600</v>
@@ -5877,7 +5887,7 @@
       <c r="I40" s="65">
         <v>6300</v>
       </c>
-      <c r="J40" s="157">
+      <c r="J40" s="156">
         <v>15200</v>
       </c>
       <c r="K40" s="11">
@@ -5886,32 +5896,32 @@
     </row>
     <row r="41" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B41" s="114"/>
       <c r="C41" s="115"/>
       <c r="D41" s="115"/>
       <c r="E41" s="116"/>
       <c r="F41" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G41" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G41" s="68" t="s">
+      <c r="H41" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H41" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I41" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J41" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K41" s="55"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" s="65">
         <v>72000</v>
@@ -5939,7 +5949,7 @@
       <c r="I42" s="65">
         <v>16800</v>
       </c>
-      <c r="J42" s="157">
+      <c r="J42" s="156">
         <v>43400</v>
       </c>
       <c r="K42" s="11">
@@ -5955,25 +5965,25 @@
       <c r="D43" s="115"/>
       <c r="E43" s="116"/>
       <c r="F43" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G43" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G43" s="68" t="s">
+      <c r="H43" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H43" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I43" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J43" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K43" s="55"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B44" s="65">
         <v>12000</v>
@@ -6001,7 +6011,7 @@
       <c r="I44" s="65">
         <v>0</v>
       </c>
-      <c r="J44" s="157">
+      <c r="J44" s="156">
         <v>5300</v>
       </c>
       <c r="K44" s="11">
@@ -6010,7 +6020,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B45" s="65">
         <v>12000</v>
@@ -6038,7 +6048,7 @@
       <c r="I45" s="65">
         <v>0</v>
       </c>
-      <c r="J45" s="157">
+      <c r="J45" s="156">
         <v>5300</v>
       </c>
       <c r="K45" s="11">
@@ -6047,7 +6057,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B46" s="65">
         <v>12000</v>
@@ -6075,7 +6085,7 @@
       <c r="I46" s="65">
         <v>0</v>
       </c>
-      <c r="J46" s="157">
+      <c r="J46" s="156">
         <v>5300</v>
       </c>
       <c r="K46" s="11">
@@ -6084,7 +6094,7 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B47" s="65">
         <v>12000</v>
@@ -6112,7 +6122,7 @@
       <c r="I47" s="65">
         <v>0</v>
       </c>
-      <c r="J47" s="157">
+      <c r="J47" s="156">
         <v>5300</v>
       </c>
       <c r="K47" s="62">
@@ -6128,21 +6138,21 @@
       <c r="D48" s="115"/>
       <c r="E48" s="116"/>
       <c r="F48" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G48" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="H48" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H48" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I48" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B49" s="71">
         <v>20000</v>
@@ -6170,11 +6180,11 @@
       <c r="I49" s="65">
         <v>4100</v>
       </c>
-      <c r="J49" s="158"/>
+      <c r="J49" s="157"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B50" s="71">
         <v>15000</v>
@@ -6202,11 +6212,11 @@
       <c r="I50" s="65">
         <v>4900</v>
       </c>
-      <c r="J50" s="158"/>
+      <c r="J50" s="157"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B51" s="71">
         <v>15000</v>
@@ -6237,7 +6247,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B52" s="71">
         <v>20000</v>
@@ -6268,7 +6278,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B53" s="71">
         <v>20000</v>
@@ -6299,7 +6309,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B54" s="71">
         <v>20000</v>
@@ -6330,7 +6340,7 @@
     </row>
     <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B55" s="71">
         <v>20000</v>
@@ -6368,21 +6378,21 @@
       <c r="D56" s="115"/>
       <c r="E56" s="116"/>
       <c r="F56" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G56" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="H56" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H56" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I56" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B57" s="71">
         <v>15000</v>
@@ -6411,28 +6421,28 @@
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B58" s="114"/>
       <c r="C58" s="115"/>
       <c r="D58" s="115"/>
       <c r="E58" s="116"/>
       <c r="F58" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G58" s="68" t="s">
+      <c r="H58" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H58" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I58" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B59" s="65">
         <v>12000</v>
@@ -6463,23 +6473,23 @@
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B60" s="114"/>
       <c r="C60" s="115"/>
       <c r="D60" s="115"/>
       <c r="E60" s="116"/>
       <c r="F60" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G60" s="68" t="s">
+      <c r="H60" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H60" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I60" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6655,27 +6665,27 @@
         <v>8</v>
       </c>
       <c r="B67" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C67" s="115"/>
       <c r="D67" s="115"/>
       <c r="E67" s="116"/>
       <c r="F67" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G67" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G67" s="68" t="s">
+      <c r="H67" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H67" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I67" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B68" s="73">
         <v>111000</v>
@@ -6706,7 +6716,7 @@
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B69" s="118">
         <v>51000</v>
@@ -6737,30 +6747,30 @@
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B70" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C70" s="115"/>
       <c r="D70" s="115"/>
       <c r="E70" s="116"/>
       <c r="F70" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G70" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G70" s="68" t="s">
+      <c r="H70" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H70" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I70" s="76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B71" s="73">
         <v>241000</v>
@@ -6791,7 +6801,7 @@
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B72" s="118">
         <v>68000</v>
@@ -6822,30 +6832,30 @@
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C73" s="115"/>
       <c r="D73" s="115"/>
       <c r="E73" s="116"/>
       <c r="F73" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G73" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G73" s="68" t="s">
+      <c r="H73" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H73" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I73" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B74" s="73">
         <v>551000</v>
@@ -6876,7 +6886,7 @@
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B75" s="118">
         <v>132000</v>
@@ -6907,30 +6917,30 @@
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C76" s="115"/>
       <c r="D76" s="115"/>
       <c r="E76" s="116"/>
       <c r="F76" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G76" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G76" s="68" t="s">
+      <c r="H76" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H76" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I76" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B77" s="73">
         <v>962000</v>
@@ -6961,7 +6971,7 @@
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B78" s="118">
         <v>203000</v>
@@ -6999,16 +7009,16 @@
       <c r="D79" s="115"/>
       <c r="E79" s="116"/>
       <c r="F79" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G79" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G79" s="68" t="s">
+      <c r="H79" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H79" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I79" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -7075,7 +7085,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B82" s="70">
         <v>41000</v>
@@ -7137,23 +7147,23 @@
     </row>
     <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B84" s="114"/>
       <c r="C84" s="115"/>
       <c r="D84" s="115"/>
       <c r="E84" s="116"/>
       <c r="F84" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G84" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G84" s="68" t="s">
+      <c r="H84" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H84" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I84" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7176,27 +7186,27 @@
         <v>30</v>
       </c>
       <c r="B86" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C86" s="115"/>
       <c r="D86" s="115"/>
       <c r="E86" s="116"/>
       <c r="F86" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G86" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G86" s="68" t="s">
+      <c r="H86" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H86" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I86" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B87" s="73">
         <v>97000</v>
@@ -7227,7 +7237,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B88" s="73">
         <v>282000</v>
@@ -7258,7 +7268,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B89" s="73">
         <v>256000</v>
@@ -7289,7 +7299,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B90" s="73">
         <v>508000</v>
@@ -7320,7 +7330,7 @@
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B91" s="124">
         <v>8200</v>
@@ -7354,22 +7364,22 @@
         <v>33</v>
       </c>
       <c r="B92" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C92" s="127"/>
       <c r="D92" s="127"/>
       <c r="E92" s="128"/>
       <c r="F92" s="129" t="s">
+        <v>97</v>
+      </c>
+      <c r="G92" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="G92" s="129" t="s">
+      <c r="H92" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="H92" s="130" t="s">
-        <v>100</v>
-      </c>
       <c r="I92" s="130" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -7458,22 +7468,22 @@
         <v>37</v>
       </c>
       <c r="B96" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C96" s="115"/>
       <c r="D96" s="115"/>
       <c r="E96" s="116"/>
       <c r="F96" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G96" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G96" s="68" t="s">
+      <c r="H96" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H96" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I96" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -7574,22 +7584,22 @@
         <v>26</v>
       </c>
       <c r="B100" s="114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C100" s="115"/>
       <c r="D100" s="115"/>
       <c r="E100" s="116"/>
       <c r="F100" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G100" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G100" s="68" t="s">
+      <c r="H100" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H100" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I100" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7656,7 +7666,7 @@
     </row>
     <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B103" s="80"/>
       <c r="C103" s="80"/>
@@ -7669,30 +7679,30 @@
     </row>
     <row r="104" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B104" s="114" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C104" s="115"/>
       <c r="D104" s="115"/>
       <c r="E104" s="116"/>
       <c r="F104" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G104" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="G104" s="81" t="s">
+      <c r="H104" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H104" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I104" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B105" s="65">
         <v>88886</v>
@@ -7723,7 +7733,7 @@
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B106" s="65">
         <v>103703</v>
@@ -7754,7 +7764,7 @@
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B107" s="65">
         <v>174729</v>
@@ -7785,7 +7795,7 @@
     </row>
     <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B108" s="65">
         <v>22223</v>
@@ -7816,7 +7826,7 @@
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B109" s="65">
         <v>111110</v>
@@ -7847,30 +7857,30 @@
     </row>
     <row r="110" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B110" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C110" s="115"/>
       <c r="D110" s="115"/>
       <c r="E110" s="116"/>
       <c r="F110" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G110" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="G110" s="81" t="s">
+      <c r="H110" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H110" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I110" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B111" s="65">
         <v>312686</v>
@@ -7901,7 +7911,7 @@
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B112" s="65">
         <v>349723</v>
@@ -7932,7 +7942,7 @@
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B113" s="65">
         <v>446016</v>
@@ -7963,30 +7973,30 @@
     </row>
     <row r="114" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B114" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C114" s="115"/>
       <c r="D114" s="115"/>
       <c r="E114" s="116"/>
       <c r="F114" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G114" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="G114" s="81" t="s">
+      <c r="H114" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H114" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I114" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B115" s="65">
         <v>128763</v>
@@ -8017,7 +8027,7 @@
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B116" s="65">
         <v>199762</v>
@@ -8048,30 +8058,30 @@
     </row>
     <row r="117" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B117" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C117" s="115"/>
       <c r="D117" s="115"/>
       <c r="E117" s="116"/>
       <c r="F117" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G117" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="G117" s="81" t="s">
+      <c r="H117" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H117" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I117" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B118" s="65">
         <v>477701</v>
@@ -8102,7 +8112,7 @@
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B119" s="65">
         <v>236516</v>
@@ -8133,7 +8143,7 @@
     </row>
     <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B120" s="65">
         <v>274873</v>
@@ -8164,7 +8174,7 @@
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B121" s="65">
         <v>313203</v>
@@ -8195,30 +8205,30 @@
     </row>
     <row r="122" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B122" s="114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C122" s="115"/>
       <c r="D122" s="115"/>
       <c r="E122" s="116"/>
       <c r="F122" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G122" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="G122" s="81" t="s">
+      <c r="H122" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="H122" s="69" t="s">
-        <v>100</v>
-      </c>
       <c r="I122" s="69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B123" s="65">
         <v>139695</v>
@@ -8249,7 +8259,7 @@
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B124" s="65">
         <v>153373</v>
@@ -8280,7 +8290,7 @@
     </row>
     <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B125" s="65">
         <v>184044</v>
@@ -8310,8 +8320,8 @@
       </c>
     </row>
     <row r="126" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="140" t="s">
-        <v>91</v>
+      <c r="A126" s="139" t="s">
+        <v>90</v>
       </c>
       <c r="B126" s="110">
         <v>49078</v>
@@ -8341,42 +8351,42 @@
       </c>
     </row>
     <row r="127" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="142" t="s">
-        <v>95</v>
-      </c>
-      <c r="B127" s="139" t="s">
-        <v>156</v>
+      <c r="A127" s="141" t="s">
+        <v>94</v>
+      </c>
+      <c r="B127" s="138" t="s">
+        <v>155</v>
       </c>
       <c r="C127" s="127"/>
       <c r="D127" s="127"/>
       <c r="E127" s="128"/>
       <c r="F127" s="129" t="s">
+        <v>97</v>
+      </c>
+      <c r="G127" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="G127" s="129" t="s">
+      <c r="H127" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="H127" s="130" t="s">
-        <v>100</v>
-      </c>
       <c r="I127" s="130" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="141" t="s">
-        <v>92</v>
-      </c>
-      <c r="B128" s="137">
+      <c r="A128" s="140" t="s">
+        <v>91</v>
+      </c>
+      <c r="B128" s="136">
         <v>661862</v>
       </c>
-      <c r="C128" s="137">
+      <c r="C128" s="136">
         <v>330931</v>
       </c>
-      <c r="D128" s="137">
+      <c r="D128" s="136">
         <v>330931</v>
       </c>
-      <c r="E128" s="137">
+      <c r="E128" s="136">
         <v>330931</v>
       </c>
       <c r="F128" s="126">
@@ -8387,16 +8397,16 @@
         <f t="shared" si="11"/>
         <v>397117.2</v>
       </c>
-      <c r="H128" s="137">
+      <c r="H128" s="136">
         <v>183523</v>
       </c>
-      <c r="I128" s="137">
+      <c r="I128" s="136">
         <v>183523</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B129" s="65">
         <v>692556</v>
@@ -8426,8 +8436,8 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="136" t="s">
-        <v>94</v>
+      <c r="A130" s="135" t="s">
+        <v>93</v>
       </c>
       <c r="B130" s="110">
         <v>90078</v>
@@ -8457,42 +8467,42 @@
       </c>
     </row>
     <row r="131" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="138" t="s">
-        <v>167</v>
-      </c>
-      <c r="B131" s="139"/>
+      <c r="A131" s="137" t="s">
+        <v>166</v>
+      </c>
+      <c r="B131" s="138"/>
       <c r="C131" s="127"/>
       <c r="D131" s="127"/>
       <c r="E131" s="128"/>
       <c r="F131" s="129"/>
       <c r="G131" s="129" t="s">
+        <v>98</v>
+      </c>
+      <c r="H131" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="H131" s="130" t="s">
-        <v>100</v>
-      </c>
       <c r="I131" s="130" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="143" t="s">
-        <v>48</v>
-      </c>
-      <c r="B132" s="137"/>
-      <c r="C132" s="137"/>
-      <c r="D132" s="137"/>
-      <c r="E132" s="137"/>
-      <c r="F132" s="137"/>
+      <c r="A132" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="B132" s="136"/>
+      <c r="C132" s="136"/>
+      <c r="D132" s="136"/>
+      <c r="E132" s="136"/>
+      <c r="F132" s="136"/>
       <c r="G132" s="92">
         <v>99890</v>
       </c>
-      <c r="H132" s="137"/>
-      <c r="I132" s="144"/>
+      <c r="H132" s="136"/>
+      <c r="I132" s="143"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="145" t="s">
-        <v>49</v>
+      <c r="A133" s="144" t="s">
+        <v>48</v>
       </c>
       <c r="B133" s="65"/>
       <c r="C133" s="65"/>
@@ -8506,14 +8516,14 @@
         <f>+$G$133</f>
         <v>49945</v>
       </c>
-      <c r="I133" s="146">
+      <c r="I133" s="145">
         <f>+$G$133</f>
         <v>49945</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="145" t="s">
-        <v>50</v>
+      <c r="A134" s="144" t="s">
+        <v>49</v>
       </c>
       <c r="B134" s="65"/>
       <c r="C134" s="65"/>
@@ -8527,14 +8537,14 @@
         <f>+$G$134</f>
         <v>95529</v>
       </c>
-      <c r="I134" s="146">
+      <c r="I134" s="145">
         <f>+$G$134</f>
         <v>95529</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="145" t="s">
-        <v>51</v>
+      <c r="A135" s="144" t="s">
+        <v>50</v>
       </c>
       <c r="B135" s="65"/>
       <c r="C135" s="65"/>
@@ -8548,14 +8558,14 @@
         <f>+$G$135</f>
         <v>90026</v>
       </c>
-      <c r="I135" s="146">
+      <c r="I135" s="145">
         <f>+$G$135</f>
         <v>90026</v>
       </c>
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="145" t="s">
-        <v>52</v>
+      <c r="A136" s="144" t="s">
+        <v>51</v>
       </c>
       <c r="B136" s="65"/>
       <c r="C136" s="65"/>
@@ -8567,11 +8577,11 @@
         <v>0</v>
       </c>
       <c r="H136" s="65"/>
-      <c r="I136" s="146"/>
+      <c r="I136" s="145"/>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="145" t="s">
-        <v>67</v>
+      <c r="A137" s="144" t="s">
+        <v>66</v>
       </c>
       <c r="B137" s="65"/>
       <c r="C137" s="65"/>
@@ -8583,11 +8593,11 @@
         <v>0</v>
       </c>
       <c r="H137" s="65"/>
-      <c r="I137" s="146"/>
+      <c r="I137" s="145"/>
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="145" t="s">
-        <v>65</v>
+      <c r="A138" s="144" t="s">
+        <v>64</v>
       </c>
       <c r="B138" s="65"/>
       <c r="C138" s="65"/>
@@ -8599,11 +8609,11 @@
         <v>0</v>
       </c>
       <c r="H138" s="65"/>
-      <c r="I138" s="146"/>
+      <c r="I138" s="145"/>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="145" t="s">
-        <v>53</v>
+      <c r="A139" s="144" t="s">
+        <v>52</v>
       </c>
       <c r="B139" s="65"/>
       <c r="C139" s="65"/>
@@ -8615,11 +8625,11 @@
         <v>0</v>
       </c>
       <c r="H139" s="65"/>
-      <c r="I139" s="146"/>
+      <c r="I139" s="145"/>
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="145" t="s">
-        <v>54</v>
+      <c r="A140" s="144" t="s">
+        <v>53</v>
       </c>
       <c r="B140" s="65"/>
       <c r="C140" s="65"/>
@@ -8631,11 +8641,11 @@
         <v>0</v>
       </c>
       <c r="H140" s="65"/>
-      <c r="I140" s="146"/>
+      <c r="I140" s="145"/>
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="145" t="s">
-        <v>55</v>
+      <c r="A141" s="144" t="s">
+        <v>54</v>
       </c>
       <c r="B141" s="65"/>
       <c r="C141" s="65"/>
@@ -8647,11 +8657,11 @@
         <v>0</v>
       </c>
       <c r="H141" s="65"/>
-      <c r="I141" s="146"/>
+      <c r="I141" s="145"/>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="145" t="s">
-        <v>69</v>
+      <c r="A142" s="144" t="s">
+        <v>68</v>
       </c>
       <c r="B142" s="65"/>
       <c r="C142" s="65"/>
@@ -8663,11 +8673,11 @@
         <v>0</v>
       </c>
       <c r="H142" s="65"/>
-      <c r="I142" s="146"/>
+      <c r="I142" s="145"/>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="145" t="s">
-        <v>56</v>
+      <c r="A143" s="144" t="s">
+        <v>55</v>
       </c>
       <c r="B143" s="65"/>
       <c r="C143" s="65"/>
@@ -8679,11 +8689,11 @@
         <v>0</v>
       </c>
       <c r="H143" s="65"/>
-      <c r="I143" s="146"/>
+      <c r="I143" s="145"/>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="145" t="s">
-        <v>57</v>
+      <c r="A144" s="144" t="s">
+        <v>56</v>
       </c>
       <c r="B144" s="65"/>
       <c r="C144" s="65"/>
@@ -8695,11 +8705,11 @@
         <v>0</v>
       </c>
       <c r="H144" s="65"/>
-      <c r="I144" s="146"/>
+      <c r="I144" s="145"/>
     </row>
     <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="145" t="s">
-        <v>58</v>
+      <c r="A145" s="144" t="s">
+        <v>57</v>
       </c>
       <c r="B145" s="65"/>
       <c r="C145" s="65"/>
@@ -8711,11 +8721,11 @@
         <v>0</v>
       </c>
       <c r="H145" s="65"/>
-      <c r="I145" s="146"/>
+      <c r="I145" s="145"/>
     </row>
     <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="145" t="s">
-        <v>59</v>
+      <c r="A146" s="144" t="s">
+        <v>58</v>
       </c>
       <c r="B146" s="65"/>
       <c r="C146" s="65"/>
@@ -8727,11 +8737,11 @@
         <v>0</v>
       </c>
       <c r="H146" s="65"/>
-      <c r="I146" s="146"/>
+      <c r="I146" s="145"/>
     </row>
     <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="145" t="s">
-        <v>60</v>
+      <c r="A147" s="144" t="s">
+        <v>59</v>
       </c>
       <c r="B147" s="65"/>
       <c r="C147" s="65"/>
@@ -8743,11 +8753,11 @@
         <v>0</v>
       </c>
       <c r="H147" s="65"/>
-      <c r="I147" s="146"/>
+      <c r="I147" s="145"/>
     </row>
     <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="145" t="s">
-        <v>61</v>
+      <c r="A148" s="144" t="s">
+        <v>60</v>
       </c>
       <c r="B148" s="65"/>
       <c r="C148" s="65"/>
@@ -8759,11 +8769,11 @@
         <v>0</v>
       </c>
       <c r="H148" s="65"/>
-      <c r="I148" s="146"/>
+      <c r="I148" s="145"/>
     </row>
     <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="145" t="s">
-        <v>62</v>
+      <c r="A149" s="144" t="s">
+        <v>61</v>
       </c>
       <c r="B149" s="65"/>
       <c r="C149" s="65"/>
@@ -8775,11 +8785,11 @@
         <v>0</v>
       </c>
       <c r="H149" s="65"/>
-      <c r="I149" s="146"/>
+      <c r="I149" s="145"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="147" t="s">
-        <v>228</v>
+      <c r="A150" s="146" t="s">
+        <v>227</v>
       </c>
       <c r="B150" s="110"/>
       <c r="C150" s="110"/>
@@ -8793,14 +8803,14 @@
         <f t="shared" ref="G150:I153" si="13">+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="I150" s="148">
+      <c r="I150" s="147">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="147" t="s">
-        <v>190</v>
+      <c r="A151" s="146" t="s">
+        <v>189</v>
       </c>
       <c r="B151" s="110"/>
       <c r="C151" s="110"/>
@@ -8815,14 +8825,14 @@
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I151" s="148">
+      <c r="I151" s="147">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="147" t="s">
-        <v>65</v>
+      <c r="A152" s="146" t="s">
+        <v>64</v>
       </c>
       <c r="B152" s="120"/>
       <c r="C152" s="120"/>
@@ -8837,14 +8847,14 @@
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I152" s="148">
+      <c r="I152" s="147">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="147" t="s">
-        <v>53</v>
+      <c r="A153" s="146" t="s">
+        <v>52</v>
       </c>
       <c r="B153" s="110"/>
       <c r="C153" s="110"/>
@@ -8859,14 +8869,14 @@
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I153" s="148">
+      <c r="I153" s="147">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="147" t="s">
-        <v>226</v>
+      <c r="A154" s="146" t="s">
+        <v>225</v>
       </c>
       <c r="B154" s="110"/>
       <c r="C154" s="110"/>
@@ -8880,14 +8890,14 @@
         <f>+$G$154</f>
         <v>35512</v>
       </c>
-      <c r="I154" s="148">
+      <c r="I154" s="147">
         <f>+$G$154</f>
         <v>35512</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="147" t="s">
-        <v>54</v>
+      <c r="A155" s="146" t="s">
+        <v>53</v>
       </c>
       <c r="B155" s="110"/>
       <c r="C155" s="110"/>
@@ -8898,11 +8908,11 @@
         <v>12772</v>
       </c>
       <c r="H155" s="110"/>
-      <c r="I155" s="149"/>
+      <c r="I155" s="148"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="147" t="s">
-        <v>55</v>
+      <c r="A156" s="146" t="s">
+        <v>54</v>
       </c>
       <c r="B156" s="110"/>
       <c r="C156" s="110"/>
@@ -8916,14 +8926,14 @@
         <f>+$G$156</f>
         <v>14226</v>
       </c>
-      <c r="I156" s="149">
+      <c r="I156" s="148">
         <f>+$G$156</f>
         <v>14226</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="147" t="s">
-        <v>69</v>
+      <c r="A157" s="146" t="s">
+        <v>68</v>
       </c>
       <c r="B157" s="110"/>
       <c r="C157" s="110"/>
@@ -8934,11 +8944,11 @@
         <v>14329</v>
       </c>
       <c r="H157" s="110"/>
-      <c r="I157" s="149"/>
+      <c r="I157" s="148"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="147" t="s">
-        <v>56</v>
+      <c r="A158" s="146" t="s">
+        <v>55</v>
       </c>
       <c r="B158" s="110"/>
       <c r="C158" s="110"/>
@@ -8952,14 +8962,14 @@
         <f>+$G$158</f>
         <v>21390</v>
       </c>
-      <c r="I158" s="149">
+      <c r="I158" s="148">
         <f>+$G$158</f>
         <v>21390</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="147" t="s">
-        <v>57</v>
+      <c r="A159" s="146" t="s">
+        <v>56</v>
       </c>
       <c r="B159" s="110"/>
       <c r="C159" s="110"/>
@@ -8970,11 +8980,11 @@
         <v>18067</v>
       </c>
       <c r="H159" s="110"/>
-      <c r="I159" s="149"/>
+      <c r="I159" s="148"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="147" t="s">
-        <v>227</v>
+      <c r="A160" s="146" t="s">
+        <v>226</v>
       </c>
       <c r="B160" s="110"/>
       <c r="C160" s="110"/>
@@ -8988,14 +8998,14 @@
         <f>+$G$160</f>
         <v>36134</v>
       </c>
-      <c r="I160" s="149">
+      <c r="I160" s="148">
         <f>+$G$160</f>
         <v>36134</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="147" t="s">
-        <v>193</v>
+      <c r="A161" s="146" t="s">
+        <v>192</v>
       </c>
       <c r="B161" s="110"/>
       <c r="C161" s="110"/>
@@ -9006,11 +9016,11 @@
         <v>17029</v>
       </c>
       <c r="H161" s="110"/>
-      <c r="I161" s="149"/>
+      <c r="I161" s="148"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="147" t="s">
-        <v>229</v>
+      <c r="A162" s="146" t="s">
+        <v>228</v>
       </c>
       <c r="B162" s="110"/>
       <c r="C162" s="110"/>
@@ -9025,14 +9035,14 @@
         <f>+$G$161</f>
         <v>17029</v>
       </c>
-      <c r="I162" s="149">
+      <c r="I162" s="148">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="147" t="s">
-        <v>183</v>
+      <c r="A163" s="146" t="s">
+        <v>182</v>
       </c>
       <c r="B163" s="110"/>
       <c r="C163" s="110"/>
@@ -9043,11 +9053,11 @@
         <v>17237</v>
       </c>
       <c r="H163" s="110"/>
-      <c r="I163" s="149"/>
+      <c r="I163" s="148"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="147" t="s">
-        <v>61</v>
+      <c r="A164" s="146" t="s">
+        <v>60</v>
       </c>
       <c r="B164" s="110"/>
       <c r="C164" s="110"/>
@@ -9058,11 +9068,11 @@
         <v>20560</v>
       </c>
       <c r="H164" s="110"/>
-      <c r="I164" s="149"/>
+      <c r="I164" s="148"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="147" t="s">
-        <v>62</v>
+      <c r="A165" s="146" t="s">
+        <v>61</v>
       </c>
       <c r="B165" s="110"/>
       <c r="C165" s="110"/>
@@ -9073,11 +9083,11 @@
         <v>14952</v>
       </c>
       <c r="H165" s="110"/>
-      <c r="I165" s="149"/>
+      <c r="I165" s="148"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="147" t="s">
-        <v>225</v>
+      <c r="A166" s="146" t="s">
+        <v>224</v>
       </c>
       <c r="B166" s="110"/>
       <c r="C166" s="110"/>
@@ -9092,14 +9102,14 @@
         <f>+$G$166</f>
         <v>29904</v>
       </c>
-      <c r="I166" s="149">
+      <c r="I166" s="148">
         <f>+$G$166</f>
         <v>29904</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="145" t="s">
-        <v>63</v>
+      <c r="A167" s="144" t="s">
+        <v>62</v>
       </c>
       <c r="B167" s="65"/>
       <c r="C167" s="65"/>
@@ -9110,11 +9120,11 @@
         <v>36239</v>
       </c>
       <c r="H167" s="65"/>
-      <c r="I167" s="146"/>
+      <c r="I167" s="145"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="145" t="s">
-        <v>64</v>
+      <c r="A168" s="144" t="s">
+        <v>63</v>
       </c>
       <c r="B168" s="65"/>
       <c r="C168" s="65"/>
@@ -9125,11 +9135,11 @@
         <v>38835</v>
       </c>
       <c r="H168" s="65"/>
-      <c r="I168" s="146"/>
+      <c r="I168" s="145"/>
     </row>
     <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="147" t="s">
-        <v>66</v>
+      <c r="A169" s="146" t="s">
+        <v>65</v>
       </c>
       <c r="B169" s="120"/>
       <c r="C169" s="120"/>
@@ -9142,7 +9152,7 @@
       <c r="H169" s="133">
         <v>25000</v>
       </c>
-      <c r="I169" s="150">
+      <c r="I169" s="149">
         <f>+$H$169</f>
         <v>25000</v>
       </c>
@@ -9170,17 +9180,17 @@
       <c r="E171" s="95"/>
       <c r="F171" s="95"/>
       <c r="G171" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="H171" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="H171" s="95" t="s">
-        <v>100</v>
-      </c>
       <c r="I171" s="96" t="s">
-        <v>129</v>
-      </c>
-      <c r="J171" s="159"/>
+        <v>128</v>
+      </c>
+      <c r="J171" s="158"/>
       <c r="K171" s="61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L171" s="66">
         <v>12000</v>
@@ -9188,7 +9198,7 @@
     </row>
     <row r="172" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B172" s="84"/>
       <c r="C172" s="84"/>
@@ -9207,11 +9217,11 @@
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="J172" s="159"/>
+      <c r="J172" s="158"/>
     </row>
     <row r="173" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B173" s="82"/>
       <c r="C173" s="82"/>
@@ -9229,9 +9239,9 @@
         <f>+G173</f>
         <v>25000</v>
       </c>
-      <c r="J173" s="159"/>
+      <c r="J173" s="158"/>
       <c r="K173" s="61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L173" s="66">
         <v>22000</v>
@@ -9239,7 +9249,7 @@
     </row>
     <row r="174" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B174" s="82"/>
       <c r="C174" s="82"/>
@@ -9258,11 +9268,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J174" s="159"/>
+      <c r="J174" s="158"/>
     </row>
     <row r="175" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B175" s="82"/>
       <c r="C175" s="82"/>
@@ -9281,11 +9291,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J175" s="159"/>
+      <c r="J175" s="158"/>
     </row>
     <row r="176" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B176" s="82"/>
       <c r="C176" s="82"/>
@@ -9304,11 +9314,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J176" s="159"/>
+      <c r="J176" s="158"/>
     </row>
     <row r="177" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B177" s="82"/>
       <c r="C177" s="82"/>
@@ -9327,11 +9337,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J177" s="159"/>
+      <c r="J177" s="158"/>
     </row>
     <row r="178" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B178" s="82"/>
       <c r="C178" s="82"/>
@@ -9350,11 +9360,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J178" s="159"/>
+      <c r="J178" s="158"/>
     </row>
     <row r="179" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B179" s="82"/>
       <c r="C179" s="82"/>
@@ -9373,11 +9383,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J179" s="159"/>
+      <c r="J179" s="158"/>
     </row>
     <row r="180" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B180" s="82"/>
       <c r="C180" s="82"/>
@@ -9396,11 +9406,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J180" s="159"/>
+      <c r="J180" s="158"/>
     </row>
     <row r="181" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B181" s="82"/>
       <c r="C181" s="82"/>
@@ -9419,11 +9429,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J181" s="159"/>
+      <c r="J181" s="158"/>
     </row>
     <row r="182" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B182" s="82"/>
       <c r="C182" s="82"/>
@@ -9442,11 +9452,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J182" s="159"/>
+      <c r="J182" s="158"/>
     </row>
     <row r="183" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B183" s="82"/>
       <c r="C183" s="82"/>
@@ -9465,11 +9475,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J183" s="159"/>
+      <c r="J183" s="158"/>
     </row>
     <row r="184" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B184" s="100"/>
       <c r="C184" s="100"/>
@@ -9488,11 +9498,11 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J184" s="159"/>
+      <c r="J184" s="158"/>
     </row>
     <row r="185" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B185" s="84"/>
       <c r="C185" s="84"/>
@@ -9507,11 +9517,11 @@
         <v>22000</v>
       </c>
       <c r="I185" s="84"/>
-      <c r="J185" s="159"/>
+      <c r="J185" s="158"/>
     </row>
     <row r="186" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B186" s="89"/>
       <c r="C186" s="89"/>
@@ -9526,11 +9536,11 @@
         <v>22000</v>
       </c>
       <c r="I186" s="89"/>
-      <c r="J186" s="159"/>
+      <c r="J186" s="158"/>
     </row>
     <row r="187" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="87" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B187" s="121"/>
       <c r="C187" s="122"/>
@@ -9538,13 +9548,13 @@
       <c r="E187" s="95"/>
       <c r="F187" s="95"/>
       <c r="G187" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="H187" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="H187" s="96" t="s">
-        <v>100</v>
-      </c>
       <c r="I187" s="96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -9570,7 +9580,7 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B189" s="71"/>
       <c r="C189" s="71"/>
@@ -9589,7 +9599,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B190" s="85"/>
       <c r="C190" s="85"/>
@@ -9609,7 +9619,7 @@
         <v>16640</v>
       </c>
       <c r="K190" s="61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L190" s="66">
         <v>16640</v>
@@ -9617,7 +9627,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B191" s="85"/>
       <c r="C191" s="85"/>
@@ -9637,7 +9647,7 @@
         <v>9600</v>
       </c>
       <c r="K191" s="61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L191" s="66">
         <v>9600</v>
@@ -9645,7 +9655,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B192" s="85"/>
       <c r="C192" s="85"/>
@@ -9668,7 +9678,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B193" s="85"/>
       <c r="C193" s="85"/>
@@ -9688,7 +9698,7 @@
         <v>9600</v>
       </c>
       <c r="K193" s="61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L193" s="66">
         <v>32000</v>
@@ -9696,7 +9706,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B194" s="85"/>
       <c r="C194" s="85"/>
@@ -9718,7 +9728,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B195" s="85"/>
       <c r="C195" s="85"/>
@@ -9740,7 +9750,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B196" s="85"/>
       <c r="C196" s="85"/>
@@ -9762,7 +9772,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B197" s="85"/>
       <c r="C197" s="85"/>
@@ -9784,7 +9794,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B198" s="85"/>
       <c r="C198" s="85"/>
@@ -9806,7 +9816,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B199" s="85"/>
       <c r="C199" s="85"/>
@@ -9828,7 +9838,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B200" s="85"/>
       <c r="C200" s="85"/>
@@ -9850,7 +9860,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B201" s="85"/>
       <c r="C201" s="85"/>
@@ -9872,7 +9882,7 @@
     </row>
     <row r="202" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B202" s="85"/>
       <c r="C202" s="85"/>
@@ -9894,7 +9904,7 @@
     </row>
     <row r="203" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B203" s="85"/>
       <c r="C203" s="85"/>
@@ -9916,7 +9926,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B204" s="85"/>
       <c r="C204" s="85"/>
@@ -9937,7 +9947,7 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B205" s="85"/>
       <c r="C205" s="85"/>
@@ -9959,7 +9969,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B206" s="85"/>
       <c r="C206" s="85"/>
@@ -9981,7 +9991,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B207" s="85"/>
       <c r="C207" s="85"/>
@@ -10003,7 +10013,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B208" s="85"/>
       <c r="C208" s="85"/>
@@ -10025,7 +10035,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B209" s="85"/>
       <c r="C209" s="85"/>
@@ -10047,7 +10057,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B210" s="85"/>
       <c r="C210" s="85"/>
@@ -10069,7 +10079,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B211" s="85"/>
       <c r="C211" s="85"/>
@@ -10091,7 +10101,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B212" s="85"/>
       <c r="C212" s="85"/>
@@ -10113,7 +10123,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B213" s="85"/>
       <c r="C213" s="85"/>
@@ -10135,7 +10145,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B214" s="85"/>
       <c r="C214" s="85"/>
@@ -10157,7 +10167,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -10179,7 +10189,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B216" s="85"/>
       <c r="C216" s="85"/>
@@ -10201,7 +10211,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B217" s="85"/>
       <c r="C217" s="85"/>
@@ -10223,7 +10233,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B218" s="85"/>
       <c r="C218" s="85"/>
@@ -10245,7 +10255,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B219" s="85"/>
       <c r="C219" s="85"/>
@@ -10267,7 +10277,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B220" s="85"/>
       <c r="C220" s="85"/>
@@ -10289,7 +10299,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B221" s="85"/>
       <c r="C221" s="85"/>
@@ -10310,7 +10320,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B222" s="85"/>
       <c r="C222" s="85"/>
@@ -10332,7 +10342,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B223" s="85"/>
       <c r="C223" s="85"/>
@@ -10354,7 +10364,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="35" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B224" s="85"/>
       <c r="C224" s="85"/>
@@ -10376,7 +10386,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B225" s="85"/>
       <c r="C225" s="85"/>
@@ -10398,7 +10408,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B226" s="85"/>
       <c r="C226" s="85"/>
@@ -10419,7 +10429,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B227" s="85"/>
       <c r="C227" s="85"/>
@@ -10440,7 +10450,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="63" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B228" s="85"/>
       <c r="C228" s="85"/>
@@ -10461,7 +10471,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B229" s="85"/>
       <c r="C229" s="85"/>
@@ -10482,7 +10492,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B230" s="85"/>
       <c r="C230" s="85"/>
@@ -10504,7 +10514,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B231" s="85"/>
       <c r="C231" s="85"/>
@@ -10526,7 +10536,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B232" s="85"/>
       <c r="C232" s="85"/>
@@ -10546,7 +10556,7 @@
         <v>106880</v>
       </c>
       <c r="K232" s="61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L232" s="66">
         <v>106880</v>
@@ -10554,7 +10564,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B233" s="85"/>
       <c r="C233" s="85"/>
@@ -10576,7 +10586,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B234" s="85"/>
       <c r="C234" s="85"/>
@@ -10598,7 +10608,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B235" s="85"/>
       <c r="C235" s="85"/>
@@ -10620,7 +10630,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B236" s="85"/>
       <c r="C236" s="85"/>
@@ -10642,7 +10652,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B237" s="85"/>
       <c r="C237" s="85"/>
@@ -10664,7 +10674,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B238" s="85"/>
       <c r="C238" s="85"/>
@@ -10686,7 +10696,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B239" s="85"/>
       <c r="C239" s="85"/>
@@ -10708,7 +10718,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B240" s="85"/>
       <c r="C240" s="85"/>
@@ -10730,7 +10740,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B241" s="85"/>
       <c r="C241" s="85"/>
@@ -10752,7 +10762,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B242" s="85"/>
       <c r="C242" s="85"/>
@@ -10774,7 +10784,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B243" s="85"/>
       <c r="C243" s="85"/>
@@ -10796,7 +10806,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B244" s="85"/>
       <c r="C244" s="85"/>
@@ -10818,7 +10828,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B245" s="85"/>
       <c r="C245" s="85"/>
@@ -10840,7 +10850,7 @@
     </row>
     <row r="246" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="104" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B246" s="105"/>
       <c r="C246" s="105"/>
@@ -10870,13 +10880,13 @@
       <c r="E247" s="95"/>
       <c r="F247" s="95"/>
       <c r="G247" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="H247" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="H247" s="96" t="s">
-        <v>100</v>
-      </c>
       <c r="I247" s="96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10902,28 +10912,28 @@
     </row>
     <row r="249" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="87" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B249" s="121"/>
       <c r="C249" s="95"/>
       <c r="D249" s="95"/>
       <c r="E249" s="95"/>
       <c r="F249" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="G249" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="G249" s="95" t="s">
+      <c r="H249" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="H249" s="95" t="s">
-        <v>100</v>
-      </c>
       <c r="I249" s="96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B250" s="84"/>
       <c r="C250" s="84"/>
@@ -10946,7 +10956,7 @@
     </row>
     <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B251" s="82"/>
       <c r="C251" s="82"/>
@@ -10969,7 +10979,7 @@
     </row>
     <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B252" s="82"/>
       <c r="C252" s="82"/>
@@ -10992,7 +11002,7 @@
     </row>
     <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B253" s="82"/>
       <c r="C253" s="82"/>
@@ -11013,7 +11023,7 @@
     </row>
     <row r="254" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B254" s="100"/>
       <c r="C254" s="100"/>
